--- a/static/data/Ratings.xlsx
+++ b/static/data/Ratings.xlsx
@@ -924,10 +924,13 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -939,13 +942,10 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1113,6 +1113,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFE4002C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF26F0CE"/>
         </patternFill>
       </fill>
@@ -1120,7 +1127,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF21976F"/>
+          <bgColor rgb="FFA8A8AB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1141,14 +1148,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
+          <bgColor rgb="FF21976F"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
+          <bgColor rgb="FFDBDFE0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1177,13 +1184,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2718,13 +2718,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:83" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
       <c r="F1" s="17"/>
       <c r="G1" s="17"/>
       <c r="H1" s="17"/>
@@ -2805,11 +2805,11 @@
       <c r="CE1" s="17"/>
     </row>
     <row r="2" spans="1:83" s="14" customFormat="1" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
@@ -2895,150 +2895,150 @@
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
-      <c r="F3" s="39" t="e" vm="1">
+      <c r="F3" s="40" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="43" t="e" vm="2">
+      <c r="G3" s="41"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="38" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="39" t="e" vm="3">
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="40" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="40"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="42" t="e" vm="4">
+      <c r="O3" s="41"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="37" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R3" s="43"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="43"/>
-      <c r="U3" s="44"/>
-      <c r="V3" s="42" t="e" vm="5">
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="37" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
-      <c r="Y3" s="43"/>
-      <c r="Z3" s="44"/>
-      <c r="AA3" s="39" t="e" vm="6">
+      <c r="W3" s="38"/>
+      <c r="X3" s="38"/>
+      <c r="Y3" s="38"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="40" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB3" s="40"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="39" t="e" vm="7">
+      <c r="AB3" s="41"/>
+      <c r="AC3" s="42"/>
+      <c r="AD3" s="40" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE3" s="40"/>
-      <c r="AF3" s="41"/>
-      <c r="AG3" s="39" t="e" vm="8">
+      <c r="AE3" s="41"/>
+      <c r="AF3" s="42"/>
+      <c r="AG3" s="40" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH3" s="40"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="42" t="e" vm="9">
+      <c r="AH3" s="41"/>
+      <c r="AI3" s="42"/>
+      <c r="AJ3" s="37" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK3" s="43"/>
-      <c r="AL3" s="43"/>
-      <c r="AM3" s="43"/>
-      <c r="AN3" s="44"/>
-      <c r="AO3" s="39" t="e" vm="10">
+      <c r="AK3" s="38"/>
+      <c r="AL3" s="38"/>
+      <c r="AM3" s="38"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="40" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP3" s="40"/>
-      <c r="AQ3" s="41"/>
-      <c r="AR3" s="39" t="e" vm="11">
+      <c r="AP3" s="41"/>
+      <c r="AQ3" s="42"/>
+      <c r="AR3" s="40" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS3" s="40"/>
-      <c r="AT3" s="41"/>
-      <c r="AU3" s="42" t="e" vm="12">
+      <c r="AS3" s="41"/>
+      <c r="AT3" s="42"/>
+      <c r="AU3" s="37" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV3" s="43"/>
-      <c r="AW3" s="43"/>
-      <c r="AX3" s="43"/>
-      <c r="AY3" s="44"/>
-      <c r="AZ3" s="39" t="e" vm="13">
+      <c r="AV3" s="38"/>
+      <c r="AW3" s="38"/>
+      <c r="AX3" s="38"/>
+      <c r="AY3" s="39"/>
+      <c r="AZ3" s="40" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA3" s="40"/>
-      <c r="BB3" s="41"/>
-      <c r="BC3" s="39" t="e" vm="7">
+      <c r="BA3" s="41"/>
+      <c r="BB3" s="42"/>
+      <c r="BC3" s="40" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD3" s="40"/>
-      <c r="BE3" s="41"/>
-      <c r="BF3" s="39" t="e" vm="14">
+      <c r="BD3" s="41"/>
+      <c r="BE3" s="42"/>
+      <c r="BF3" s="40" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG3" s="40"/>
-      <c r="BH3" s="41"/>
-      <c r="BI3" s="42" t="e" vm="15">
+      <c r="BG3" s="41"/>
+      <c r="BH3" s="42"/>
+      <c r="BI3" s="37" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ3" s="43"/>
-      <c r="BK3" s="43"/>
-      <c r="BL3" s="43"/>
-      <c r="BM3" s="44"/>
-      <c r="BN3" s="39" t="e" vm="4">
+      <c r="BJ3" s="38"/>
+      <c r="BK3" s="38"/>
+      <c r="BL3" s="38"/>
+      <c r="BM3" s="39"/>
+      <c r="BN3" s="40" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO3" s="40"/>
-      <c r="BP3" s="41"/>
-      <c r="BQ3" s="39" t="e" vm="16">
+      <c r="BO3" s="41"/>
+      <c r="BP3" s="42"/>
+      <c r="BQ3" s="40" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR3" s="40"/>
-      <c r="BS3" s="41"/>
-      <c r="BT3" s="39" t="e" vm="17">
+      <c r="BR3" s="41"/>
+      <c r="BS3" s="42"/>
+      <c r="BT3" s="40" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU3" s="40"/>
-      <c r="BV3" s="41"/>
-      <c r="BW3" s="39" t="e" vm="4">
+      <c r="BU3" s="41"/>
+      <c r="BV3" s="42"/>
+      <c r="BW3" s="40" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX3" s="40"/>
-      <c r="BY3" s="41"/>
-      <c r="BZ3" s="39" t="e" vm="18">
+      <c r="BX3" s="41"/>
+      <c r="BY3" s="42"/>
+      <c r="BZ3" s="40" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA3" s="40"/>
-      <c r="CB3" s="41"/>
-      <c r="CC3" s="39" t="e" vm="19">
+      <c r="CA3" s="41"/>
+      <c r="CB3" s="42"/>
+      <c r="CC3" s="40" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD3" s="40"/>
-      <c r="CE3" s="41"/>
+      <c r="CD3" s="41"/>
+      <c r="CE3" s="42"/>
     </row>
     <row r="4" spans="1:83" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="32" t="s">
@@ -9458,150 +9458,150 @@
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
-      <c r="F29" s="42" t="e" vm="1">
+      <c r="F29" s="37" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G29" s="43"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="43" t="e" vm="2">
+      <c r="G29" s="38"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="38" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J29" s="43"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="43"/>
-      <c r="M29" s="43"/>
-      <c r="N29" s="42" t="e" vm="3">
+      <c r="J29" s="38"/>
+      <c r="K29" s="38"/>
+      <c r="L29" s="38"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="37" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O29" s="43"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="43" t="e" vm="4">
+      <c r="O29" s="38"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="38" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R29" s="43"/>
-      <c r="S29" s="43"/>
-      <c r="T29" s="43"/>
-      <c r="U29" s="44"/>
-      <c r="V29" s="42" t="e" vm="5">
+      <c r="R29" s="38"/>
+      <c r="S29" s="38"/>
+      <c r="T29" s="38"/>
+      <c r="U29" s="39"/>
+      <c r="V29" s="37" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W29" s="43"/>
-      <c r="X29" s="43"/>
-      <c r="Y29" s="43"/>
-      <c r="Z29" s="43"/>
-      <c r="AA29" s="42" t="e" vm="6">
+      <c r="W29" s="38"/>
+      <c r="X29" s="38"/>
+      <c r="Y29" s="38"/>
+      <c r="Z29" s="38"/>
+      <c r="AA29" s="37" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB29" s="43"/>
-      <c r="AC29" s="44"/>
-      <c r="AD29" s="42" t="e" vm="7">
+      <c r="AB29" s="38"/>
+      <c r="AC29" s="39"/>
+      <c r="AD29" s="37" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE29" s="43"/>
-      <c r="AF29" s="44"/>
-      <c r="AG29" s="42" t="e" vm="8">
+      <c r="AE29" s="38"/>
+      <c r="AF29" s="39"/>
+      <c r="AG29" s="37" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH29" s="43"/>
-      <c r="AI29" s="44"/>
-      <c r="AJ29" s="43" t="e" vm="9">
+      <c r="AH29" s="38"/>
+      <c r="AI29" s="39"/>
+      <c r="AJ29" s="38" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK29" s="43"/>
-      <c r="AL29" s="43"/>
-      <c r="AM29" s="43"/>
-      <c r="AN29" s="43"/>
-      <c r="AO29" s="42" t="e" vm="10">
+      <c r="AK29" s="38"/>
+      <c r="AL29" s="38"/>
+      <c r="AM29" s="38"/>
+      <c r="AN29" s="38"/>
+      <c r="AO29" s="37" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP29" s="43"/>
-      <c r="AQ29" s="44"/>
-      <c r="AR29" s="42" t="e" vm="11">
+      <c r="AP29" s="38"/>
+      <c r="AQ29" s="39"/>
+      <c r="AR29" s="37" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS29" s="43"/>
-      <c r="AT29" s="44"/>
-      <c r="AU29" s="43" t="e" vm="12">
+      <c r="AS29" s="38"/>
+      <c r="AT29" s="39"/>
+      <c r="AU29" s="38" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV29" s="43"/>
-      <c r="AW29" s="43"/>
-      <c r="AX29" s="43"/>
-      <c r="AY29" s="43"/>
-      <c r="AZ29" s="42" t="e" vm="13">
+      <c r="AV29" s="38"/>
+      <c r="AW29" s="38"/>
+      <c r="AX29" s="38"/>
+      <c r="AY29" s="38"/>
+      <c r="AZ29" s="37" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA29" s="43"/>
-      <c r="BB29" s="44"/>
-      <c r="BC29" s="42" t="e" vm="7">
+      <c r="BA29" s="38"/>
+      <c r="BB29" s="39"/>
+      <c r="BC29" s="37" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD29" s="43"/>
-      <c r="BE29" s="44"/>
-      <c r="BF29" s="42" t="e" vm="14">
+      <c r="BD29" s="38"/>
+      <c r="BE29" s="39"/>
+      <c r="BF29" s="37" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG29" s="43"/>
-      <c r="BH29" s="44"/>
-      <c r="BI29" s="43" t="e" vm="15">
+      <c r="BG29" s="38"/>
+      <c r="BH29" s="39"/>
+      <c r="BI29" s="38" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ29" s="43"/>
-      <c r="BK29" s="43"/>
-      <c r="BL29" s="43"/>
-      <c r="BM29" s="43"/>
-      <c r="BN29" s="42" t="e" vm="4">
+      <c r="BJ29" s="38"/>
+      <c r="BK29" s="38"/>
+      <c r="BL29" s="38"/>
+      <c r="BM29" s="38"/>
+      <c r="BN29" s="37" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO29" s="43"/>
-      <c r="BP29" s="44"/>
-      <c r="BQ29" s="42" t="e" vm="16">
+      <c r="BO29" s="38"/>
+      <c r="BP29" s="39"/>
+      <c r="BQ29" s="37" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR29" s="43"/>
-      <c r="BS29" s="44"/>
-      <c r="BT29" s="42" t="e" vm="17">
+      <c r="BR29" s="38"/>
+      <c r="BS29" s="39"/>
+      <c r="BT29" s="37" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU29" s="43"/>
-      <c r="BV29" s="44"/>
-      <c r="BW29" s="42" t="e" vm="4">
+      <c r="BU29" s="38"/>
+      <c r="BV29" s="39"/>
+      <c r="BW29" s="37" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX29" s="43"/>
-      <c r="BY29" s="44"/>
-      <c r="BZ29" s="42" t="e" vm="18">
+      <c r="BX29" s="38"/>
+      <c r="BY29" s="39"/>
+      <c r="BZ29" s="37" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA29" s="43"/>
-      <c r="CB29" s="44"/>
-      <c r="CC29" s="42" t="e" vm="19">
+      <c r="CA29" s="38"/>
+      <c r="CB29" s="39"/>
+      <c r="CC29" s="37" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD29" s="43"/>
-      <c r="CE29" s="44"/>
+      <c r="CD29" s="38"/>
+      <c r="CE29" s="39"/>
     </row>
     <row r="30" spans="1:83" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="32" t="s">
@@ -15532,18 +15532,67 @@
     </row>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="BW30:BY30"/>
-    <mergeCell ref="BZ30:CB30"/>
-    <mergeCell ref="CC30:CE30"/>
-    <mergeCell ref="AZ30:BB30"/>
-    <mergeCell ref="BC30:BE30"/>
-    <mergeCell ref="BF30:BH30"/>
-    <mergeCell ref="BI30:BM30"/>
-    <mergeCell ref="BN30:BP30"/>
-    <mergeCell ref="BQ30:BS30"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AG4:AI4"/>
+    <mergeCell ref="AJ4:AN4"/>
+    <mergeCell ref="AO4:AQ4"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="AR29:AT29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:U29"/>
+    <mergeCell ref="V29:Z29"/>
+    <mergeCell ref="V4:Z4"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AN3"/>
+    <mergeCell ref="AO3:AQ3"/>
+    <mergeCell ref="AR3:AT3"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="Q4:U4"/>
+    <mergeCell ref="BW3:BY3"/>
+    <mergeCell ref="BZ3:CB3"/>
+    <mergeCell ref="CC3:CE3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="V3:Z3"/>
+    <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="BT3:BV3"/>
+    <mergeCell ref="AU3:AY3"/>
+    <mergeCell ref="AZ3:BB3"/>
+    <mergeCell ref="BC3:BE3"/>
+    <mergeCell ref="BF3:BH3"/>
+    <mergeCell ref="BI3:BM3"/>
+    <mergeCell ref="BN3:BP3"/>
+    <mergeCell ref="BQ3:BS3"/>
+    <mergeCell ref="CC4:CE4"/>
+    <mergeCell ref="AR4:AT4"/>
+    <mergeCell ref="AU4:AY4"/>
+    <mergeCell ref="AZ4:BB4"/>
+    <mergeCell ref="BC4:BE4"/>
+    <mergeCell ref="BF4:BH4"/>
+    <mergeCell ref="BI4:BM4"/>
+    <mergeCell ref="BN4:BP4"/>
+    <mergeCell ref="BQ4:BS4"/>
+    <mergeCell ref="BT4:BV4"/>
+    <mergeCell ref="BW4:BY4"/>
+    <mergeCell ref="BZ4:CB4"/>
+    <mergeCell ref="BQ29:BS29"/>
+    <mergeCell ref="BT29:BV29"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AN29"/>
+    <mergeCell ref="AO29:AQ29"/>
     <mergeCell ref="BW29:BY29"/>
     <mergeCell ref="BZ29:CB29"/>
     <mergeCell ref="CC29:CE29"/>
@@ -15560,77 +15609,28 @@
     <mergeCell ref="BN29:BP29"/>
     <mergeCell ref="AA29:AC29"/>
     <mergeCell ref="AD29:AF29"/>
+    <mergeCell ref="CC30:CE30"/>
+    <mergeCell ref="AZ30:BB30"/>
+    <mergeCell ref="BC30:BE30"/>
+    <mergeCell ref="BF30:BH30"/>
+    <mergeCell ref="BI30:BM30"/>
+    <mergeCell ref="BN30:BP30"/>
+    <mergeCell ref="BQ30:BS30"/>
+    <mergeCell ref="BT30:BV30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="BW30:BY30"/>
+    <mergeCell ref="BZ30:CB30"/>
     <mergeCell ref="Q30:U30"/>
     <mergeCell ref="V30:Z30"/>
     <mergeCell ref="AA30:AC30"/>
-    <mergeCell ref="BQ29:BS29"/>
-    <mergeCell ref="BT29:BV29"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AN29"/>
-    <mergeCell ref="AO29:AQ29"/>
-    <mergeCell ref="BT30:BV30"/>
     <mergeCell ref="AD30:AF30"/>
     <mergeCell ref="AG30:AI30"/>
     <mergeCell ref="AJ30:AN30"/>
     <mergeCell ref="AO30:AQ30"/>
     <mergeCell ref="AR30:AT30"/>
     <mergeCell ref="AU30:AY30"/>
-    <mergeCell ref="CC4:CE4"/>
-    <mergeCell ref="AR4:AT4"/>
-    <mergeCell ref="AU4:AY4"/>
-    <mergeCell ref="AZ4:BB4"/>
-    <mergeCell ref="BC4:BE4"/>
-    <mergeCell ref="BF4:BH4"/>
-    <mergeCell ref="BI4:BM4"/>
-    <mergeCell ref="BN4:BP4"/>
-    <mergeCell ref="BQ4:BS4"/>
-    <mergeCell ref="BT4:BV4"/>
-    <mergeCell ref="BW4:BY4"/>
-    <mergeCell ref="BZ4:CB4"/>
-    <mergeCell ref="BW3:BY3"/>
-    <mergeCell ref="BZ3:CB3"/>
-    <mergeCell ref="CC3:CE3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="V3:Z3"/>
-    <mergeCell ref="AA3:AC3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="AR29:AT29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:U29"/>
-    <mergeCell ref="V29:Z29"/>
-    <mergeCell ref="V4:Z4"/>
-    <mergeCell ref="BT3:BV3"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AN3"/>
-    <mergeCell ref="AO3:AQ3"/>
-    <mergeCell ref="AR3:AT3"/>
-    <mergeCell ref="AU3:AY3"/>
-    <mergeCell ref="AZ3:BB3"/>
-    <mergeCell ref="BC3:BE3"/>
-    <mergeCell ref="BF3:BH3"/>
-    <mergeCell ref="BI3:BM3"/>
-    <mergeCell ref="BN3:BP3"/>
-    <mergeCell ref="BQ3:BS3"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="Q4:U4"/>
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AG4:AI4"/>
-    <mergeCell ref="AJ4:AN4"/>
-    <mergeCell ref="AO4:AQ4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B27 D6:D27 B32:B53 D32:D53">
     <cfRule type="expression" dxfId="65" priority="329">
@@ -16684,7 +16684,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2 G4 G6 G8 G10 G12 G14 G16 G18 G20 G22">
+  <conditionalFormatting sqref="G4 G2 G6 G8 G10 G12 G14 G16 G18 G20 G22">
     <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="percentile" val="0"/>
@@ -16744,38 +16744,38 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2 O2 H2:H3 J2:J3">
-    <cfRule type="expression" dxfId="32" priority="347">
-      <formula>$J2="Ferrari"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="348">
+    <cfRule type="expression" dxfId="32" priority="348">
       <formula>$J2="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="349">
+    <cfRule type="expression" dxfId="31" priority="349">
       <formula>$J2="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="350">
+    <cfRule type="expression" dxfId="30" priority="350">
       <formula>$J2="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="351">
+    <cfRule type="expression" dxfId="29" priority="351">
       <formula>$J2="Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="344">
+    <cfRule type="expression" dxfId="28" priority="352">
+      <formula>$J2="Haas"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="345">
+      <formula>$J2="Aston Martin"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="342">
+      <formula>$J2="Williams"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="343">
+      <formula>$J2="Audi"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="344">
       <formula>$J2="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="352">
-      <formula>$J2="Haas"</formula>
+    <cfRule type="expression" dxfId="23" priority="346">
+      <formula>$J2="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="342">
-      <formula>$J2="Williams"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="343">
-      <formula>$J2="Audi"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="345">
-      <formula>$J2="Aston Martin"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="346">
-      <formula>$J2="Mercedes"</formula>
+    <cfRule type="expression" dxfId="22" priority="347">
+      <formula>$J2="Ferrari"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3:M12">

--- a/static/data/Ratings.xlsx
+++ b/static/data/Ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Programming\webdev\portfolio\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E75D56B-7EC1-4A49-B7DC-0CE0F3AEC0FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC51BD6-B6D8-45CB-8B07-1C39270728F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="2" xr2:uid="{BD88BCC4-2E11-4C36-830D-A75A044EF5A6}"/>
   </bookViews>
@@ -924,6 +924,12 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -940,12 +946,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2718,13 +2718,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:83" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
       <c r="F1" s="17"/>
       <c r="G1" s="17"/>
       <c r="H1" s="17"/>
@@ -2805,11 +2805,11 @@
       <c r="CE1" s="17"/>
     </row>
     <row r="2" spans="1:83" s="14" customFormat="1" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
@@ -2895,150 +2895,150 @@
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
-      <c r="F3" s="40" t="e" vm="1">
+      <c r="F3" s="42" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G3" s="41"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="38" t="e" vm="2">
+      <c r="G3" s="43"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="40" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="40" t="e" vm="3">
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="42" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="41"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="37" t="e" vm="4">
+      <c r="O3" s="43"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="39" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="37" t="e" vm="5">
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="39" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W3" s="38"/>
-      <c r="X3" s="38"/>
-      <c r="Y3" s="38"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="40" t="e" vm="6">
+      <c r="W3" s="40"/>
+      <c r="X3" s="40"/>
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="41"/>
+      <c r="AA3" s="42" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="42"/>
-      <c r="AD3" s="40" t="e" vm="7">
+      <c r="AB3" s="43"/>
+      <c r="AC3" s="44"/>
+      <c r="AD3" s="42" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="42"/>
-      <c r="AG3" s="40" t="e" vm="8">
+      <c r="AE3" s="43"/>
+      <c r="AF3" s="44"/>
+      <c r="AG3" s="42" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="42"/>
-      <c r="AJ3" s="37" t="e" vm="9">
+      <c r="AH3" s="43"/>
+      <c r="AI3" s="44"/>
+      <c r="AJ3" s="39" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK3" s="38"/>
-      <c r="AL3" s="38"/>
-      <c r="AM3" s="38"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="40" t="e" vm="10">
+      <c r="AK3" s="40"/>
+      <c r="AL3" s="40"/>
+      <c r="AM3" s="40"/>
+      <c r="AN3" s="41"/>
+      <c r="AO3" s="42" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP3" s="41"/>
-      <c r="AQ3" s="42"/>
-      <c r="AR3" s="40" t="e" vm="11">
+      <c r="AP3" s="43"/>
+      <c r="AQ3" s="44"/>
+      <c r="AR3" s="42" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS3" s="41"/>
-      <c r="AT3" s="42"/>
-      <c r="AU3" s="37" t="e" vm="12">
+      <c r="AS3" s="43"/>
+      <c r="AT3" s="44"/>
+      <c r="AU3" s="39" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV3" s="38"/>
-      <c r="AW3" s="38"/>
-      <c r="AX3" s="38"/>
-      <c r="AY3" s="39"/>
-      <c r="AZ3" s="40" t="e" vm="13">
+      <c r="AV3" s="40"/>
+      <c r="AW3" s="40"/>
+      <c r="AX3" s="40"/>
+      <c r="AY3" s="41"/>
+      <c r="AZ3" s="42" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA3" s="41"/>
-      <c r="BB3" s="42"/>
-      <c r="BC3" s="40" t="e" vm="7">
+      <c r="BA3" s="43"/>
+      <c r="BB3" s="44"/>
+      <c r="BC3" s="42" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD3" s="41"/>
-      <c r="BE3" s="42"/>
-      <c r="BF3" s="40" t="e" vm="14">
+      <c r="BD3" s="43"/>
+      <c r="BE3" s="44"/>
+      <c r="BF3" s="42" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG3" s="41"/>
-      <c r="BH3" s="42"/>
-      <c r="BI3" s="37" t="e" vm="15">
+      <c r="BG3" s="43"/>
+      <c r="BH3" s="44"/>
+      <c r="BI3" s="39" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ3" s="38"/>
-      <c r="BK3" s="38"/>
-      <c r="BL3" s="38"/>
-      <c r="BM3" s="39"/>
-      <c r="BN3" s="40" t="e" vm="4">
+      <c r="BJ3" s="40"/>
+      <c r="BK3" s="40"/>
+      <c r="BL3" s="40"/>
+      <c r="BM3" s="41"/>
+      <c r="BN3" s="42" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO3" s="41"/>
-      <c r="BP3" s="42"/>
-      <c r="BQ3" s="40" t="e" vm="16">
+      <c r="BO3" s="43"/>
+      <c r="BP3" s="44"/>
+      <c r="BQ3" s="42" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR3" s="41"/>
-      <c r="BS3" s="42"/>
-      <c r="BT3" s="40" t="e" vm="17">
+      <c r="BR3" s="43"/>
+      <c r="BS3" s="44"/>
+      <c r="BT3" s="42" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU3" s="41"/>
-      <c r="BV3" s="42"/>
-      <c r="BW3" s="40" t="e" vm="4">
+      <c r="BU3" s="43"/>
+      <c r="BV3" s="44"/>
+      <c r="BW3" s="42" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX3" s="41"/>
-      <c r="BY3" s="42"/>
-      <c r="BZ3" s="40" t="e" vm="18">
+      <c r="BX3" s="43"/>
+      <c r="BY3" s="44"/>
+      <c r="BZ3" s="42" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA3" s="41"/>
-      <c r="CB3" s="42"/>
-      <c r="CC3" s="40" t="e" vm="19">
+      <c r="CA3" s="43"/>
+      <c r="CB3" s="44"/>
+      <c r="CC3" s="42" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD3" s="41"/>
-      <c r="CE3" s="42"/>
+      <c r="CD3" s="43"/>
+      <c r="CE3" s="44"/>
     </row>
     <row r="4" spans="1:83" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="32" t="s">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="E6" s="2" cm="1">
         <f t="array" ref="E6">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H6,M6,P6,U6,Z6,AC6,AF6,AI6,AN6,AQ6,AT6,AY6,BB6,BE6,BH6,BM6,BP6,BS6,BV6,BY6,CB6,CE6), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="F6" s="21">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="28">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W6" s="23">
         <v>0</v>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="Z6" s="24">
         <f>(AVERAGE(V6:W6)*0.24) + (AVERAGE(X6:Y6)*0.76)</f>
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AA6" s="28">
         <v>0</v>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="E7" s="2" cm="1">
         <f t="array" ref="E7">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H7,M7,P7,U7,Z7,AC7,AF7,AI7,AN7,AQ7,AT7,AY7,BB7,BE7,BH7,BM7,BP7,BS7,BV7,BY7,CB7,CE7), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="F7" s="21">
         <v>0</v>
@@ -3764,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="28">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W7" s="23">
         <v>0</v>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="Z7" s="24">
         <f t="shared" ref="Z7:Z27" si="4">(AVERAGE(V7:W7)*0.24) + (AVERAGE(X7:Y7)*0.76)</f>
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AA7" s="28">
         <v>0</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="E10" s="2" cm="1">
         <f t="array" ref="E10">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H10,M10,P10,U10,Z10,AC10,AF10,AI10,AN10,AQ10,AT10,AY10,BB10,BE10,BH10,BM10,BP10,BS10,BV10,BY10,CB10,CE10), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="F10" s="21">
         <v>0</v>
@@ -4586,7 +4586,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="28">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="W10" s="23">
         <v>0</v>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="Z10" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AA10" s="28">
         <v>0</v>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E11" s="2" cm="1">
         <f t="array" ref="E11">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H11,M11,P11,U11,Z11,AC11,AF11,AI11,AN11,AQ11,AT11,AY11,BB11,BE11,BH11,BM11,BP11,BS11,BV11,BY11,CB11,CE11), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="F11" s="21">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="28">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W11" s="23">
         <v>0</v>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="Z11" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="AA11" s="28">
         <v>0</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="E12" s="2" cm="1">
         <f t="array" ref="E12">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H12,M12,P12,U12,Z12,AC12,AF12,AI12,AN12,AQ12,AT12,AY12,BB12,BE12,BH12,BM12,BP12,BS12,BV12,BY12,CB12,CE12), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="F12" s="21">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="28">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W12" s="23">
         <v>0</v>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="Z12" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="AA12" s="28">
         <v>0</v>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="E13" s="2" cm="1">
         <f t="array" ref="E13">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H13,M13,P13,U13,Z13,AC13,AF13,AI13,AN13,AQ13,AT13,AY13,BB13,BE13,BH13,BM13,BP13,BS13,BV13,BY13,CB13,CE13), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="F13" s="21">
         <v>0</v>
@@ -5408,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="28">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W13" s="23">
         <v>0</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Z13" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="AA13" s="28">
         <v>0</v>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="E14" s="2" cm="1">
         <f t="array" ref="E14">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H14,M14,P14,U14,Z14,AC14,AF14,AI14,AN14,AQ14,AT14,AY14,BB14,BE14,BH14,BM14,BP14,BS14,BV14,BY14,CB14,CE14), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="F14" s="21">
         <v>0</v>
@@ -5682,7 +5682,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W14" s="23">
         <v>0</v>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="Z14" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AA14" s="28">
         <v>0</v>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="E15" s="2" cm="1">
         <f t="array" ref="E15">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H15,M15,P15,U15,Z15,AC15,AF15,AI15,AN15,AQ15,AT15,AY15,BB15,BE15,BH15,BM15,BP15,BS15,BV15,BY15,CB15,CE15), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="F15" s="21">
         <v>0</v>
@@ -5956,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="28">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W15" s="23">
         <v>0</v>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="Z15" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AA15" s="28">
         <v>0</v>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="E16" s="2" cm="1">
         <f t="array" ref="E16">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H16,M16,P16,U16,Z16,AC16,AF16,AI16,AN16,AQ16,AT16,AY16,BB16,BE16,BH16,BM16,BP16,BS16,BV16,BY16,CB16,CE16), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="F16" s="21">
         <v>0</v>
@@ -6230,7 +6230,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="28">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W16" s="23">
         <v>0</v>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="Z16" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AA16" s="28">
         <v>0</v>
@@ -6449,7 +6449,7 @@
       </c>
       <c r="E17" s="2" cm="1">
         <f t="array" ref="E17">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H17,M17,P17,U17,Z17,AC17,AF17,AI17,AN17,AQ17,AT17,AY17,BB17,BE17,BH17,BM17,BP17,BS17,BV17,BY17,CB17,CE17), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="F17" s="21">
         <v>0</v>
@@ -6504,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="28">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W17" s="23">
         <v>0</v>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="Z17" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="AA17" s="28">
         <v>0</v>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="E18" s="2" cm="1">
         <f t="array" ref="E18">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H18,M18,P18,U18,Z18,AC18,AF18,AI18,AN18,AQ18,AT18,AY18,BB18,BE18,BH18,BM18,BP18,BS18,BV18,BY18,CB18,CE18), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="F18" s="21">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="28">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W18" s="23">
         <v>0</v>
@@ -6791,7 +6791,7 @@
       </c>
       <c r="Z18" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AA18" s="28">
         <v>0</v>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="E19" s="2" cm="1">
         <f t="array" ref="E19">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H19,M19,P19,U19,Z19,AC19,AF19,AI19,AN19,AQ19,AT19,AY19,BB19,BE19,BH19,BM19,BP19,BS19,BV19,BY19,CB19,CE19), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="F19" s="21">
         <v>0</v>
@@ -7052,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="28">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W19" s="23">
         <v>0</v>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="Z19" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AA19" s="28">
         <v>0</v>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="E20" s="2" cm="1">
         <f t="array" ref="E20">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H20,M20,P20,U20,Z20,AC20,AF20,AI20,AN20,AQ20,AT20,AY20,BB20,BE20,BH20,BM20,BP20,BS20,BV20,BY20,CB20,CE20), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="F20" s="21">
         <v>0</v>
@@ -7326,7 +7326,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="28">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W20" s="23">
         <v>0</v>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="Z20" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AA20" s="28">
         <v>0</v>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="E21" s="2" cm="1">
         <f t="array" ref="E21">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H21,M21,P21,U21,Z21,AC21,AF21,AI21,AN21,AQ21,AT21,AY21,BB21,BE21,BH21,BM21,BP21,BS21,BV21,BY21,CB21,CE21), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="F21" s="21">
         <v>0</v>
@@ -7600,7 +7600,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="28">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W21" s="23">
         <v>0</v>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="Z21" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AA21" s="28">
         <v>0</v>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="E22" s="2" cm="1">
         <f t="array" ref="E22">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H22,M22,P22,U22,Z22,AC22,AF22,AI22,AN22,AQ22,AT22,AY22,BB22,BE22,BH22,BM22,BP22,BS22,BV22,BY22,CB22,CE22), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="F22" s="21">
         <v>0</v>
@@ -7873,7 +7873,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="28">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W22" s="23">
         <v>0</v>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="Z22" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AA22" s="28">
         <v>0</v>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="E23" s="2" cm="1">
         <f t="array" ref="E23">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H23,M23,P23,U23,Z23,AC23,AF23,AI23,AN23,AQ23,AT23,AY23,BB23,BE23,BH23,BM23,BP23,BS23,BV23,BY23,CB23,CE23), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="F23" s="21">
         <v>0</v>
@@ -8147,7 +8147,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="28">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="W23" s="23">
         <v>0</v>
@@ -8160,7 +8160,7 @@
       </c>
       <c r="Z23" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="AA23" s="28">
         <v>0</v>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="E24" s="2" cm="1">
         <f t="array" ref="E24">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H24,M24,P24,U24,Z24,AC24,AF24,AI24,AN24,AQ24,AT24,AY24,BB24,BE24,BH24,BM24,BP24,BS24,BV24,BY24,CB24,CE24), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="F24" s="21">
         <v>0</v>
@@ -8420,7 +8420,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="28">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W24" s="23">
         <v>0</v>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="Z24" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AA24" s="28">
         <v>0</v>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="E25" s="2" cm="1">
         <f t="array" ref="E25">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H25,M25,P25,U25,Z25,AC25,AF25,AI25,AN25,AQ25,AT25,AY25,BB25,BE25,BH25,BM25,BP25,BS25,BV25,BY25,CB25,CE25), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F25" s="21">
         <v>0</v>
@@ -8694,7 +8694,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="23">
         <v>0</v>
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Z25" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AA25" s="28">
         <v>0</v>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="E26" s="2" cm="1">
         <f t="array" ref="E26">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H26,M26,P26,U26,Z26,AC26,AF26,AI26,AN26,AQ26,AT26,AY26,BB26,BE26,BH26,BM26,BP26,BS26,BV26,BY26,CB26,CE26), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="F26" s="21">
         <v>0</v>
@@ -8968,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="28">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W26" s="23">
         <v>0</v>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="Z26" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="AA26" s="28">
         <v>0</v>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="E27" s="2" cm="1">
         <f t="array" ref="E27">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H27,M27,P27,U27,Z27,AC27,AF27,AI27,AN27,AQ27,AT27,AY27,BB27,BE27,BH27,BM27,BP27,BS27,BV27,BY27,CB27,CE27), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="F27" s="21">
         <v>0</v>
@@ -9242,7 +9242,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="28">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W27" s="23">
         <v>0</v>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="Z27" s="24">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AA27" s="28">
         <v>0</v>
@@ -9458,150 +9458,150 @@
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
-      <c r="F29" s="37" t="e" vm="1">
+      <c r="F29" s="39" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G29" s="38"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="38" t="e" vm="2">
+      <c r="G29" s="40"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="40" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J29" s="38"/>
-      <c r="K29" s="38"/>
-      <c r="L29" s="38"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="37" t="e" vm="3">
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="39" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O29" s="38"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="38" t="e" vm="4">
+      <c r="O29" s="40"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="40" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R29" s="38"/>
-      <c r="S29" s="38"/>
-      <c r="T29" s="38"/>
-      <c r="U29" s="39"/>
-      <c r="V29" s="37" t="e" vm="5">
+      <c r="R29" s="40"/>
+      <c r="S29" s="40"/>
+      <c r="T29" s="40"/>
+      <c r="U29" s="41"/>
+      <c r="V29" s="39" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W29" s="38"/>
-      <c r="X29" s="38"/>
-      <c r="Y29" s="38"/>
-      <c r="Z29" s="38"/>
-      <c r="AA29" s="37" t="e" vm="6">
+      <c r="W29" s="40"/>
+      <c r="X29" s="40"/>
+      <c r="Y29" s="40"/>
+      <c r="Z29" s="40"/>
+      <c r="AA29" s="39" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB29" s="38"/>
-      <c r="AC29" s="39"/>
-      <c r="AD29" s="37" t="e" vm="7">
+      <c r="AB29" s="40"/>
+      <c r="AC29" s="41"/>
+      <c r="AD29" s="39" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE29" s="38"/>
-      <c r="AF29" s="39"/>
-      <c r="AG29" s="37" t="e" vm="8">
+      <c r="AE29" s="40"/>
+      <c r="AF29" s="41"/>
+      <c r="AG29" s="39" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH29" s="38"/>
-      <c r="AI29" s="39"/>
-      <c r="AJ29" s="38" t="e" vm="9">
+      <c r="AH29" s="40"/>
+      <c r="AI29" s="41"/>
+      <c r="AJ29" s="40" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK29" s="38"/>
-      <c r="AL29" s="38"/>
-      <c r="AM29" s="38"/>
-      <c r="AN29" s="38"/>
-      <c r="AO29" s="37" t="e" vm="10">
+      <c r="AK29" s="40"/>
+      <c r="AL29" s="40"/>
+      <c r="AM29" s="40"/>
+      <c r="AN29" s="40"/>
+      <c r="AO29" s="39" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP29" s="38"/>
-      <c r="AQ29" s="39"/>
-      <c r="AR29" s="37" t="e" vm="11">
+      <c r="AP29" s="40"/>
+      <c r="AQ29" s="41"/>
+      <c r="AR29" s="39" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS29" s="38"/>
-      <c r="AT29" s="39"/>
-      <c r="AU29" s="38" t="e" vm="12">
+      <c r="AS29" s="40"/>
+      <c r="AT29" s="41"/>
+      <c r="AU29" s="40" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV29" s="38"/>
-      <c r="AW29" s="38"/>
-      <c r="AX29" s="38"/>
-      <c r="AY29" s="38"/>
-      <c r="AZ29" s="37" t="e" vm="13">
+      <c r="AV29" s="40"/>
+      <c r="AW29" s="40"/>
+      <c r="AX29" s="40"/>
+      <c r="AY29" s="40"/>
+      <c r="AZ29" s="39" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA29" s="38"/>
-      <c r="BB29" s="39"/>
-      <c r="BC29" s="37" t="e" vm="7">
+      <c r="BA29" s="40"/>
+      <c r="BB29" s="41"/>
+      <c r="BC29" s="39" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD29" s="38"/>
-      <c r="BE29" s="39"/>
-      <c r="BF29" s="37" t="e" vm="14">
+      <c r="BD29" s="40"/>
+      <c r="BE29" s="41"/>
+      <c r="BF29" s="39" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG29" s="38"/>
-      <c r="BH29" s="39"/>
-      <c r="BI29" s="38" t="e" vm="15">
+      <c r="BG29" s="40"/>
+      <c r="BH29" s="41"/>
+      <c r="BI29" s="40" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ29" s="38"/>
-      <c r="BK29" s="38"/>
-      <c r="BL29" s="38"/>
-      <c r="BM29" s="38"/>
-      <c r="BN29" s="37" t="e" vm="4">
+      <c r="BJ29" s="40"/>
+      <c r="BK29" s="40"/>
+      <c r="BL29" s="40"/>
+      <c r="BM29" s="40"/>
+      <c r="BN29" s="39" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO29" s="38"/>
-      <c r="BP29" s="39"/>
-      <c r="BQ29" s="37" t="e" vm="16">
+      <c r="BO29" s="40"/>
+      <c r="BP29" s="41"/>
+      <c r="BQ29" s="39" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR29" s="38"/>
-      <c r="BS29" s="39"/>
-      <c r="BT29" s="37" t="e" vm="17">
+      <c r="BR29" s="40"/>
+      <c r="BS29" s="41"/>
+      <c r="BT29" s="39" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU29" s="38"/>
-      <c r="BV29" s="39"/>
-      <c r="BW29" s="37" t="e" vm="4">
+      <c r="BU29" s="40"/>
+      <c r="BV29" s="41"/>
+      <c r="BW29" s="39" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX29" s="38"/>
-      <c r="BY29" s="39"/>
-      <c r="BZ29" s="37" t="e" vm="18">
+      <c r="BX29" s="40"/>
+      <c r="BY29" s="41"/>
+      <c r="BZ29" s="39" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA29" s="38"/>
-      <c r="CB29" s="39"/>
-      <c r="CC29" s="37" t="e" vm="19">
+      <c r="CA29" s="40"/>
+      <c r="CB29" s="41"/>
+      <c r="CC29" s="39" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD29" s="38"/>
-      <c r="CE29" s="39"/>
+      <c r="CD29" s="40"/>
+      <c r="CE29" s="41"/>
     </row>
     <row r="30" spans="1:83" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="32" t="s">
@@ -10500,7 +10500,7 @@
         <v>Mercedes</v>
       </c>
       <c r="E34" s="2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="F34" s="21">
         <v>0</v>
@@ -10551,7 +10551,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="28">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W34" s="23">
         <v>0</v>
@@ -10563,7 +10563,7 @@
         <v>0</v>
       </c>
       <c r="Z34" s="24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AA34" s="28">
         <v>0</v>
@@ -10742,16 +10742,16 @@
         <v>4</v>
       </c>
       <c r="B35" s="1">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="C35" s="12" t="str">
-        <v>Kimi Antonelli</v>
+        <v>Franco Colapinto</v>
       </c>
       <c r="D35" s="1" t="str">
-        <v>Mercedes</v>
+        <v>Alpine</v>
       </c>
       <c r="E35" s="2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="F35" s="21">
         <v>0</v>
@@ -10802,7 +10802,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="28">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W35" s="23">
         <v>0</v>
@@ -10814,7 +10814,7 @@
         <v>0</v>
       </c>
       <c r="Z35" s="24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AA35" s="28">
         <v>0</v>
@@ -10993,16 +10993,16 @@
         <v>5</v>
       </c>
       <c r="B36" s="3">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="C36" s="12" t="str">
-        <v>Charles Leclerc</v>
+        <v>Carlos Sainz</v>
       </c>
       <c r="D36" s="3" t="str">
-        <v>Ferrari</v>
+        <v>Williams</v>
       </c>
       <c r="E36" s="2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="F36" s="21">
         <v>0</v>
@@ -11053,7 +11053,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="28">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W36" s="23">
         <v>0</v>
@@ -11065,7 +11065,7 @@
         <v>0</v>
       </c>
       <c r="Z36" s="24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AA36" s="28">
         <v>0</v>
@@ -11244,16 +11244,16 @@
         <v>6</v>
       </c>
       <c r="B37" s="3">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C37" s="12" t="str">
-        <v>Lewis Hamilton</v>
+        <v>Sergio Perez</v>
       </c>
       <c r="D37" s="3" t="str">
-        <v>Ferrari</v>
+        <v>Cadillac</v>
       </c>
       <c r="E37" s="2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="F37" s="21">
         <v>0</v>
@@ -11304,7 +11304,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="28">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W37" s="23">
         <v>0</v>
@@ -11316,7 +11316,7 @@
         <v>0</v>
       </c>
       <c r="Z37" s="24">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AA37" s="28">
         <v>0</v>
@@ -11495,16 +11495,16 @@
         <v>7</v>
       </c>
       <c r="B38" s="4">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C38" s="12" t="str">
-        <v>Max Verstappen</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="D38" s="4" t="str">
-        <v>Red Bull</v>
+        <v>Ferrari</v>
       </c>
       <c r="E38" s="2">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="F38" s="21">
         <v>0</v>
@@ -11555,7 +11555,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="28">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="W38" s="23">
         <v>0</v>
@@ -11567,7 +11567,7 @@
         <v>0</v>
       </c>
       <c r="Z38" s="24">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AA38" s="28">
         <v>0</v>
@@ -11746,16 +11746,16 @@
         <v>8</v>
       </c>
       <c r="B39" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C39" s="12" t="str">
-        <v>Isack Hadjar</v>
+        <v>Kimi Antonelli</v>
       </c>
       <c r="D39" s="4" t="str">
-        <v>Red Bull</v>
+        <v>Mercedes</v>
       </c>
       <c r="E39" s="2">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="F39" s="21">
         <v>0</v>
@@ -11806,7 +11806,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="28">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W39" s="23">
         <v>0</v>
@@ -11818,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="Z39" s="24">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AA39" s="28">
         <v>0</v>
@@ -11997,16 +11997,16 @@
         <v>9</v>
       </c>
       <c r="B40" s="5">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C40" s="12" t="str">
-        <v>Pierre Gasly</v>
+        <v>Nico Hulkenberg</v>
       </c>
       <c r="D40" s="5" t="str">
-        <v>Alpine</v>
+        <v>Audi</v>
       </c>
       <c r="E40" s="2">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="F40" s="21">
         <v>0</v>
@@ -12057,7 +12057,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="28">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W40" s="23">
         <v>0</v>
@@ -12069,7 +12069,7 @@
         <v>0</v>
       </c>
       <c r="Z40" s="24">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AA40" s="28">
         <v>0</v>
@@ -12248,16 +12248,16 @@
         <v>10</v>
       </c>
       <c r="B41" s="5">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="C41" s="12" t="str">
-        <v>Franco Colapinto</v>
+        <v>Max Verstappen</v>
       </c>
       <c r="D41" s="5" t="str">
-        <v>Alpine</v>
+        <v>Red Bull</v>
       </c>
       <c r="E41" s="2">
-        <v>0</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="F41" s="21">
         <v>0</v>
@@ -12308,7 +12308,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="28">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="W41" s="23">
         <v>0</v>
@@ -12320,7 +12320,7 @@
         <v>0</v>
       </c>
       <c r="Z41" s="24">
-        <v>0</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="AA41" s="28">
         <v>0</v>
@@ -12499,16 +12499,16 @@
         <v>11</v>
       </c>
       <c r="B42" s="6">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C42" s="12" t="str">
-        <v>Liam Lawson</v>
+        <v>Isack Hadjar</v>
       </c>
       <c r="D42" s="6" t="str">
-        <v>Racing Bulls</v>
+        <v>Red Bull</v>
       </c>
       <c r="E42" s="2">
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="F42" s="21">
         <v>0</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="28">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W42" s="23">
         <v>0</v>
@@ -12571,7 +12571,7 @@
         <v>0</v>
       </c>
       <c r="Z42" s="24">
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="AA42" s="28">
         <v>0</v>
@@ -12759,7 +12759,7 @@
         <v>Racing Bulls</v>
       </c>
       <c r="E43" s="2">
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="F43" s="21">
         <v>0</v>
@@ -12810,7 +12810,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="28">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W43" s="23">
         <v>0</v>
@@ -12822,7 +12822,7 @@
         <v>0</v>
       </c>
       <c r="Z43" s="24">
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="AA43" s="28">
         <v>0</v>
@@ -13001,16 +13001,16 @@
         <v>13</v>
       </c>
       <c r="B44" s="7">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C44" s="12" t="str">
-        <v>Esteban Ocon</v>
+        <v>Fernando Alonso</v>
       </c>
       <c r="D44" s="7" t="str">
-        <v>Hass</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E44" s="2">
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="F44" s="21">
         <v>0</v>
@@ -13061,7 +13061,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="28">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W44" s="23">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>0</v>
       </c>
       <c r="Z44" s="24">
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="AA44" s="28">
         <v>0</v>
@@ -13252,16 +13252,16 @@
         <v>14</v>
       </c>
       <c r="B45" s="7">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="C45" s="12" t="str">
-        <v>Oliver Bearman</v>
+        <v>Gabriel Bortoleto</v>
       </c>
       <c r="D45" s="7" t="str">
-        <v>Hass</v>
+        <v>Audi</v>
       </c>
       <c r="E45" s="2">
-        <v>0</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="F45" s="21">
         <v>0</v>
@@ -13312,7 +13312,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="28">
-        <v>0</v>
+        <v>7.45</v>
       </c>
       <c r="W45" s="23">
         <v>0</v>
@@ -13324,7 +13324,7 @@
         <v>0</v>
       </c>
       <c r="Z45" s="24">
-        <v>0</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="AA45" s="28">
         <v>0</v>
@@ -13503,16 +13503,16 @@
         <v>15</v>
       </c>
       <c r="B46" s="8">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C46" s="12" t="str">
-        <v>Carlos Sainz</v>
+        <v>Liam Lawson</v>
       </c>
       <c r="D46" s="8" t="str">
-        <v>Williams</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E46" s="2">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="F46" s="21">
         <v>0</v>
@@ -13563,7 +13563,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="28">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W46" s="23">
         <v>0</v>
@@ -13575,7 +13575,7 @@
         <v>0</v>
       </c>
       <c r="Z46" s="24">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AA46" s="28">
         <v>0</v>
@@ -13754,16 +13754,16 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C47" s="12" t="str">
-        <v>Alexander Albon</v>
+        <v>Esteban Ocon</v>
       </c>
       <c r="D47" s="8" t="str">
-        <v>Williams</v>
+        <v>Hass</v>
       </c>
       <c r="E47" s="2">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="F47" s="21">
         <v>0</v>
@@ -13814,7 +13814,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="28">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W47" s="23">
         <v>0</v>
@@ -13826,7 +13826,7 @@
         <v>0</v>
       </c>
       <c r="Z47" s="24">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AA47" s="28">
         <v>0</v>
@@ -14005,16 +14005,16 @@
         <v>17</v>
       </c>
       <c r="B48" s="9">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C48" s="12" t="str">
-        <v>Nico Hulkenberg</v>
+        <v>Alexander Albon</v>
       </c>
       <c r="D48" s="9" t="str">
-        <v>Audi</v>
+        <v>Williams</v>
       </c>
       <c r="E48" s="2">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="F48" s="21">
         <v>0</v>
@@ -14065,7 +14065,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="28">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W48" s="23">
         <v>0</v>
@@ -14077,7 +14077,7 @@
         <v>0</v>
       </c>
       <c r="Z48" s="24">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AA48" s="28">
         <v>0</v>
@@ -14256,16 +14256,16 @@
         <v>18</v>
       </c>
       <c r="B49" s="9">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="C49" s="12" t="str">
-        <v>Gabriel Bortoleto</v>
+        <v>Oliver Bearman</v>
       </c>
       <c r="D49" s="9" t="str">
-        <v>Audi</v>
+        <v>Hass</v>
       </c>
       <c r="E49" s="2">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="F49" s="21">
         <v>0</v>
@@ -14316,7 +14316,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="28">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W49" s="23">
         <v>0</v>
@@ -14328,7 +14328,7 @@
         <v>0</v>
       </c>
       <c r="Z49" s="24">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AA49" s="28">
         <v>0</v>
@@ -14507,16 +14507,16 @@
         <v>19</v>
       </c>
       <c r="B50" s="10">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C50" s="12" t="str">
-        <v>Sergio Perez</v>
+        <v>Lance Stroll</v>
       </c>
       <c r="D50" s="10" t="str">
-        <v>Cadillac</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E50" s="2">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="F50" s="21">
         <v>0</v>
@@ -14567,7 +14567,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="28">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W50" s="23">
         <v>0</v>
@@ -14579,7 +14579,7 @@
         <v>0</v>
       </c>
       <c r="Z50" s="24">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="AA50" s="28">
         <v>0</v>
@@ -14758,16 +14758,16 @@
         <v>20</v>
       </c>
       <c r="B51" s="10">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="C51" s="12" t="str">
-        <v>Valtteri Bottas</v>
+        <v>Lewis Hamilton</v>
       </c>
       <c r="D51" s="10" t="str">
-        <v>Cadillac</v>
+        <v>Ferrari</v>
       </c>
       <c r="E51" s="2">
-        <v>0</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="F51" s="21">
         <v>0</v>
@@ -14818,7 +14818,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="28">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W51" s="23">
         <v>0</v>
@@ -14830,7 +14830,7 @@
         <v>0</v>
       </c>
       <c r="Z51" s="24">
-        <v>0</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="AA51" s="28">
         <v>0</v>
@@ -15009,16 +15009,16 @@
         <v>21</v>
       </c>
       <c r="B52" s="11">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C52" s="12" t="str">
-        <v>Fernando Alonso</v>
+        <v>Pierre Gasly</v>
       </c>
       <c r="D52" s="11" t="str">
-        <v>Aston Martin</v>
+        <v>Alpine</v>
       </c>
       <c r="E52" s="2">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="F52" s="21">
         <v>0</v>
@@ -15069,7 +15069,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W52" s="23">
         <v>0</v>
@@ -15081,7 +15081,7 @@
         <v>0</v>
       </c>
       <c r="Z52" s="24">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AA52" s="28">
         <v>0</v>
@@ -15260,16 +15260,16 @@
         <v>22</v>
       </c>
       <c r="B53" s="11">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="C53" s="12" t="str">
-        <v>Lance Stroll</v>
+        <v>Valtteri Bottas</v>
       </c>
       <c r="D53" s="11" t="str">
-        <v>Aston Martin</v>
+        <v>Cadillac</v>
       </c>
       <c r="E53" s="2">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F53" s="21">
         <v>0</v>
@@ -15320,7 +15320,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W53" s="23">
         <v>0</v>
@@ -15332,7 +15332,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="24">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AA53" s="28">
         <v>0</v>
@@ -15532,34 +15532,61 @@
     </row>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AG4:AI4"/>
-    <mergeCell ref="AJ4:AN4"/>
-    <mergeCell ref="AO4:AQ4"/>
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="AR29:AT29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:U29"/>
-    <mergeCell ref="V29:Z29"/>
-    <mergeCell ref="V4:Z4"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AN3"/>
-    <mergeCell ref="AO3:AQ3"/>
-    <mergeCell ref="AR3:AT3"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="Q4:U4"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="BW30:BY30"/>
+    <mergeCell ref="BZ30:CB30"/>
+    <mergeCell ref="Q30:U30"/>
+    <mergeCell ref="V30:Z30"/>
+    <mergeCell ref="AA30:AC30"/>
+    <mergeCell ref="AD30:AF30"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AJ30:AN30"/>
+    <mergeCell ref="AO30:AQ30"/>
+    <mergeCell ref="AR30:AT30"/>
+    <mergeCell ref="AU30:AY30"/>
+    <mergeCell ref="CC30:CE30"/>
+    <mergeCell ref="AZ30:BB30"/>
+    <mergeCell ref="BC30:BE30"/>
+    <mergeCell ref="BF30:BH30"/>
+    <mergeCell ref="BI30:BM30"/>
+    <mergeCell ref="BN30:BP30"/>
+    <mergeCell ref="BQ30:BS30"/>
+    <mergeCell ref="BT30:BV30"/>
+    <mergeCell ref="BW29:BY29"/>
+    <mergeCell ref="BZ29:CB29"/>
+    <mergeCell ref="CC29:CE29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="AU29:AY29"/>
+    <mergeCell ref="AZ29:BB29"/>
+    <mergeCell ref="BC29:BE29"/>
+    <mergeCell ref="BF29:BH29"/>
+    <mergeCell ref="BI29:BM29"/>
+    <mergeCell ref="BN29:BP29"/>
+    <mergeCell ref="AA29:AC29"/>
+    <mergeCell ref="AD29:AF29"/>
+    <mergeCell ref="BQ29:BS29"/>
+    <mergeCell ref="BT29:BV29"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AN29"/>
+    <mergeCell ref="AO29:AQ29"/>
+    <mergeCell ref="CC4:CE4"/>
+    <mergeCell ref="AR4:AT4"/>
+    <mergeCell ref="AU4:AY4"/>
+    <mergeCell ref="AZ4:BB4"/>
+    <mergeCell ref="BC4:BE4"/>
+    <mergeCell ref="BF4:BH4"/>
+    <mergeCell ref="BI4:BM4"/>
+    <mergeCell ref="BN4:BP4"/>
+    <mergeCell ref="BQ4:BS4"/>
+    <mergeCell ref="BT4:BV4"/>
+    <mergeCell ref="BW4:BY4"/>
+    <mergeCell ref="BZ4:CB4"/>
     <mergeCell ref="BW3:BY3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="CC3:CE3"/>
@@ -15576,61 +15603,34 @@
     <mergeCell ref="BI3:BM3"/>
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BQ3:BS3"/>
-    <mergeCell ref="CC4:CE4"/>
-    <mergeCell ref="AR4:AT4"/>
-    <mergeCell ref="AU4:AY4"/>
-    <mergeCell ref="AZ4:BB4"/>
-    <mergeCell ref="BC4:BE4"/>
-    <mergeCell ref="BF4:BH4"/>
-    <mergeCell ref="BI4:BM4"/>
-    <mergeCell ref="BN4:BP4"/>
-    <mergeCell ref="BQ4:BS4"/>
-    <mergeCell ref="BT4:BV4"/>
-    <mergeCell ref="BW4:BY4"/>
-    <mergeCell ref="BZ4:CB4"/>
-    <mergeCell ref="BQ29:BS29"/>
-    <mergeCell ref="BT29:BV29"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AN29"/>
-    <mergeCell ref="AO29:AQ29"/>
-    <mergeCell ref="BW29:BY29"/>
-    <mergeCell ref="BZ29:CB29"/>
-    <mergeCell ref="CC29:CE29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="AU29:AY29"/>
-    <mergeCell ref="AZ29:BB29"/>
-    <mergeCell ref="BC29:BE29"/>
-    <mergeCell ref="BF29:BH29"/>
-    <mergeCell ref="BI29:BM29"/>
-    <mergeCell ref="BN29:BP29"/>
-    <mergeCell ref="AA29:AC29"/>
-    <mergeCell ref="AD29:AF29"/>
-    <mergeCell ref="CC30:CE30"/>
-    <mergeCell ref="AZ30:BB30"/>
-    <mergeCell ref="BC30:BE30"/>
-    <mergeCell ref="BF30:BH30"/>
-    <mergeCell ref="BI30:BM30"/>
-    <mergeCell ref="BN30:BP30"/>
-    <mergeCell ref="BQ30:BS30"/>
-    <mergeCell ref="BT30:BV30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="BW30:BY30"/>
-    <mergeCell ref="BZ30:CB30"/>
-    <mergeCell ref="Q30:U30"/>
-    <mergeCell ref="V30:Z30"/>
-    <mergeCell ref="AA30:AC30"/>
-    <mergeCell ref="AD30:AF30"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AJ30:AN30"/>
-    <mergeCell ref="AO30:AQ30"/>
-    <mergeCell ref="AR30:AT30"/>
-    <mergeCell ref="AU30:AY30"/>
+    <mergeCell ref="V4:Z4"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AN3"/>
+    <mergeCell ref="AO3:AQ3"/>
+    <mergeCell ref="AR3:AT3"/>
+    <mergeCell ref="AR29:AT29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:U29"/>
+    <mergeCell ref="V29:Z29"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="Q4:U4"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AG4:AI4"/>
+    <mergeCell ref="AJ4:AN4"/>
+    <mergeCell ref="AO4:AQ4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B27 D6:D27 B32:B53 D32:D53">
     <cfRule type="expression" dxfId="65" priority="329">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="G2" s="45">
         <f>K2-K3</f>
-        <v>0</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="H2" s="18">
         <v>63</v>
@@ -15829,14 +15829,14 @@
       </c>
       <c r="K2" s="2">
         <f>Ratings!E6</f>
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M2" s="18">
         <v>63</v>
       </c>
       <c r="N2" s="29">
         <f>Simplified!G2</f>
-        <v>0</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="O2" s="18">
         <v>12</v>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="K3" s="2">
         <f>Ratings!E7</f>
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="M3" s="1">
         <v>1</v>
@@ -15897,7 +15897,7 @@
         <v>Mercedes</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="G4" s="45">
         <f>K4-K5</f>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="N4" s="29">
         <f>Simplified!G6</f>
-        <v>0</v>
+        <v>0.29400000000000004</v>
       </c>
       <c r="O4" s="3">
         <v>44</v>
@@ -15932,16 +15932,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="C5" s="12" t="str">
-        <v>Kimi Antonelli</v>
+        <v>Franco Colapinto</v>
       </c>
       <c r="D5" s="1" t="str">
-        <v>Mercedes</v>
+        <v>Alpine</v>
       </c>
       <c r="E5" s="2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="G5" s="45"/>
       <c r="H5" s="1">
@@ -15962,7 +15962,7 @@
       </c>
       <c r="N5" s="29">
         <f>Simplified!G8</f>
-        <v>0</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="O5" s="4">
         <v>6</v>
@@ -15973,20 +15973,20 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="C6" s="12" t="str">
-        <v>Charles Leclerc</v>
+        <v>Carlos Sainz</v>
       </c>
       <c r="D6" s="3" t="str">
-        <v>Ferrari</v>
+        <v>Williams</v>
       </c>
       <c r="E6" s="2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="G6" s="45">
         <f>K6-K7</f>
-        <v>0</v>
+        <v>0.29400000000000004</v>
       </c>
       <c r="H6" s="3">
         <v>16</v>
@@ -15999,14 +15999,14 @@
       </c>
       <c r="K6" s="2">
         <f>Ratings!E10</f>
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="M6" s="5">
         <v>10</v>
       </c>
       <c r="N6" s="29">
         <f>Simplified!G10</f>
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="O6" s="5">
         <v>43</v>
@@ -16017,16 +16017,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="C7" s="12" t="str">
-        <v>Lewis Hamilton</v>
+        <v>Sergio Perez</v>
       </c>
       <c r="D7" s="3" t="str">
-        <v>Ferrari</v>
+        <v>Cadillac</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="G7" s="45"/>
       <c r="H7" s="3">
@@ -16040,14 +16040,14 @@
       </c>
       <c r="K7" s="2">
         <f>Ratings!E11</f>
-        <v>0</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="M7" s="6">
         <v>30</v>
       </c>
       <c r="N7" s="29">
         <f>Simplified!G12</f>
-        <v>0</v>
+        <v>-5.9999999999999942E-2</v>
       </c>
       <c r="O7" s="6">
         <v>41</v>
@@ -16058,20 +16058,20 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C8" s="12" t="str">
-        <v>Max Verstappen</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="D8" s="4" t="str">
-        <v>Red Bull</v>
+        <v>Ferrari</v>
       </c>
       <c r="E8" s="2">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="G8" s="45">
         <f>K8-K9</f>
-        <v>0</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="H8" s="4">
         <v>3</v>
@@ -16084,14 +16084,14 @@
       </c>
       <c r="K8" s="2">
         <f>Ratings!E12</f>
-        <v>0</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="M8" s="7">
         <v>31</v>
       </c>
       <c r="N8" s="29">
         <f>Simplified!G14</f>
-        <v>0</v>
+        <v>5.9999999999999942E-2</v>
       </c>
       <c r="O8" s="7">
         <v>87</v>
@@ -16102,16 +16102,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C9" s="12" t="str">
-        <v>Isack Hadjar</v>
+        <v>Kimi Antonelli</v>
       </c>
       <c r="D9" s="4" t="str">
-        <v>Red Bull</v>
+        <v>Mercedes</v>
       </c>
       <c r="E9" s="2">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="G9" s="45"/>
       <c r="H9" s="4">
@@ -16125,14 +16125,14 @@
       </c>
       <c r="K9" s="2">
         <f>Ratings!E13</f>
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="M9" s="8">
         <v>55</v>
       </c>
       <c r="N9" s="29">
         <f>Simplified!G16</f>
-        <v>0</v>
+        <v>0.18000000000000005</v>
       </c>
       <c r="O9" s="8">
         <v>23</v>
@@ -16143,20 +16143,20 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C10" s="12" t="str">
-        <v>Pierre Gasly</v>
+        <v>Nico Hulkenberg</v>
       </c>
       <c r="D10" s="5" t="str">
-        <v>Alpine</v>
+        <v>Audi</v>
       </c>
       <c r="E10" s="2">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="G10" s="45">
         <f>K10-K11</f>
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="H10" s="5">
         <v>10</v>
@@ -16169,14 +16169,14 @@
       </c>
       <c r="K10" s="2">
         <f>Ratings!E14</f>
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="M10" s="9">
         <v>27</v>
       </c>
       <c r="N10" s="29">
         <f>Simplified!G18</f>
-        <v>0</v>
+        <v>6.5999999999999948E-2</v>
       </c>
       <c r="O10" s="9">
         <v>5</v>
@@ -16187,16 +16187,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="5">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="C11" s="12" t="str">
-        <v>Franco Colapinto</v>
+        <v>Max Verstappen</v>
       </c>
       <c r="D11" s="5" t="str">
-        <v>Alpine</v>
+        <v>Red Bull</v>
       </c>
       <c r="E11" s="2">
-        <v>0</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="G11" s="45"/>
       <c r="H11" s="5">
@@ -16210,14 +16210,14 @@
       </c>
       <c r="K11" s="2">
         <f>Ratings!E15</f>
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="M11" s="10">
         <v>11</v>
       </c>
       <c r="N11" s="29">
         <f>Simplified!G20</f>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="O11" s="10">
         <v>77</v>
@@ -16228,20 +16228,20 @@
         <v>11</v>
       </c>
       <c r="B12" s="6">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C12" s="12" t="str">
-        <v>Liam Lawson</v>
+        <v>Isack Hadjar</v>
       </c>
       <c r="D12" s="6" t="str">
-        <v>Racing Bulls</v>
+        <v>Red Bull</v>
       </c>
       <c r="E12" s="2">
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="G12" s="45">
         <f>K12-K13</f>
-        <v>0</v>
+        <v>-5.9999999999999942E-2</v>
       </c>
       <c r="H12" s="6">
         <v>30</v>
@@ -16254,14 +16254,14 @@
       </c>
       <c r="K12" s="2">
         <f>Ratings!E16</f>
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="M12" s="11">
         <v>14</v>
       </c>
       <c r="N12" s="29">
         <f>Simplified!G22</f>
-        <v>0</v>
+        <v>0.17999999999999994</v>
       </c>
       <c r="O12" s="11">
         <v>18</v>
@@ -16281,7 +16281,7 @@
         <v>Racing Bulls</v>
       </c>
       <c r="E13" s="2">
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="G13" s="45"/>
       <c r="H13" s="6">
@@ -16295,7 +16295,7 @@
       </c>
       <c r="K13" s="2">
         <f>Ratings!E17</f>
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
@@ -16303,20 +16303,20 @@
         <v>13</v>
       </c>
       <c r="B14" s="7">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C14" s="12" t="str">
-        <v>Esteban Ocon</v>
+        <v>Fernando Alonso</v>
       </c>
       <c r="D14" s="7" t="str">
-        <v>Hass</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E14" s="2">
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="G14" s="45">
         <f>K14-K15</f>
-        <v>0</v>
+        <v>5.9999999999999942E-2</v>
       </c>
       <c r="H14" s="7">
         <v>31</v>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="K14" s="2">
         <f>Ratings!E18</f>
-        <v>0</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
@@ -16337,16 +16337,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="7">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="C15" s="12" t="str">
-        <v>Oliver Bearman</v>
+        <v>Gabriel Bortoleto</v>
       </c>
       <c r="D15" s="7" t="str">
-        <v>Hass</v>
+        <v>Audi</v>
       </c>
       <c r="E15" s="2">
-        <v>0</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="G15" s="45"/>
       <c r="H15" s="7">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="K15" s="2">
         <f>Ratings!E19</f>
-        <v>0</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
@@ -16368,20 +16368,20 @@
         <v>15</v>
       </c>
       <c r="B16" s="8">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C16" s="12" t="str">
-        <v>Carlos Sainz</v>
+        <v>Liam Lawson</v>
       </c>
       <c r="D16" s="8" t="str">
-        <v>Williams</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E16" s="2">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="G16" s="45">
         <f>K16-K17</f>
-        <v>0</v>
+        <v>0.18000000000000005</v>
       </c>
       <c r="H16" s="8">
         <v>55</v>
@@ -16394,7 +16394,7 @@
       </c>
       <c r="K16" s="2">
         <f>Ratings!E20</f>
-        <v>0</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -16402,16 +16402,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="8">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C17" s="12" t="str">
-        <v>Alexander Albon</v>
+        <v>Esteban Ocon</v>
       </c>
       <c r="D17" s="8" t="str">
-        <v>Williams</v>
+        <v>Hass</v>
       </c>
       <c r="E17" s="2">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="G17" s="45"/>
       <c r="H17" s="8">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="K17" s="2">
         <f>Ratings!E21</f>
-        <v>0</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -16433,20 +16433,20 @@
         <v>17</v>
       </c>
       <c r="B18" s="9">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C18" s="12" t="str">
-        <v>Nico Hulkenberg</v>
+        <v>Alexander Albon</v>
       </c>
       <c r="D18" s="9" t="str">
-        <v>Audi</v>
+        <v>Williams</v>
       </c>
       <c r="E18" s="2">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="G18" s="45">
         <f>K18-K19</f>
-        <v>0</v>
+        <v>6.5999999999999948E-2</v>
       </c>
       <c r="H18" s="9">
         <v>27</v>
@@ -16459,7 +16459,7 @@
       </c>
       <c r="K18" s="2">
         <f>Ratings!E22</f>
-        <v>0</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -16467,16 +16467,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="9">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="C19" s="12" t="str">
-        <v>Gabriel Bortoleto</v>
+        <v>Oliver Bearman</v>
       </c>
       <c r="D19" s="9" t="str">
-        <v>Audi</v>
+        <v>Hass</v>
       </c>
       <c r="E19" s="2">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="G19" s="45"/>
       <c r="H19" s="9">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="K19" s="2">
         <f>Ratings!E23</f>
-        <v>0</v>
+        <v>0.89400000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -16498,20 +16498,20 @@
         <v>19</v>
       </c>
       <c r="B20" s="10">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C20" s="12" t="str">
-        <v>Sergio Perez</v>
+        <v>Lance Stroll</v>
       </c>
       <c r="D20" s="10" t="str">
-        <v>Cadillac</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E20" s="2">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="G20" s="45">
         <f>K20-K21</f>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H20" s="10">
         <v>11</v>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="K20" s="2">
         <f>Ratings!E24</f>
-        <v>0</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -16532,16 +16532,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="10">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="C21" s="12" t="str">
-        <v>Valtteri Bottas</v>
+        <v>Lewis Hamilton</v>
       </c>
       <c r="D21" s="10" t="str">
-        <v>Cadillac</v>
+        <v>Ferrari</v>
       </c>
       <c r="E21" s="2">
-        <v>0</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="G21" s="45"/>
       <c r="H21" s="10">
@@ -16555,7 +16555,7 @@
       </c>
       <c r="K21" s="2">
         <f>Ratings!E25</f>
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -16563,20 +16563,20 @@
         <v>21</v>
       </c>
       <c r="B22" s="11">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C22" s="12" t="str">
-        <v>Fernando Alonso</v>
+        <v>Pierre Gasly</v>
       </c>
       <c r="D22" s="11" t="str">
-        <v>Aston Martin</v>
+        <v>Alpine</v>
       </c>
       <c r="E22" s="2">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="G22" s="45">
         <f>K22-K23</f>
-        <v>0</v>
+        <v>0.17999999999999994</v>
       </c>
       <c r="H22" s="11">
         <v>14</v>
@@ -16589,7 +16589,7 @@
       </c>
       <c r="K22" s="2">
         <f>Ratings!E26</f>
-        <v>0</v>
+        <v>0.89999999999999991</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -16597,16 +16597,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="11">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="C23" s="12" t="str">
-        <v>Lance Stroll</v>
+        <v>Valtteri Bottas</v>
       </c>
       <c r="D23" s="11" t="str">
-        <v>Aston Martin</v>
+        <v>Cadillac</v>
       </c>
       <c r="E23" s="2">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="G23" s="45"/>
       <c r="H23" s="11">
@@ -16620,7 +16620,7 @@
       </c>
       <c r="K23" s="2">
         <f>Ratings!E27</f>
-        <v>0</v>
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -16684,7 +16684,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4 G2 G6 G8 G10 G12 G14 G16 G18 G20 G22">
+  <conditionalFormatting sqref="G2 G4 G6 G8 G10 G12 G14 G16 G18 G20 G22">
     <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="percentile" val="0"/>

--- a/static/data/Ratings.xlsx
+++ b/static/data/Ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Programming\webdev\portfolio\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC51BD6-B6D8-45CB-8B07-1C39270728F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB68969A-3BD9-4485-8BE5-55D3B8DFED46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="2" xr2:uid="{BD88BCC4-2E11-4C36-830D-A75A044EF5A6}"/>
   </bookViews>
@@ -924,12 +924,6 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -946,6 +940,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2718,13 +2718,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:83" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
       <c r="F1" s="17"/>
       <c r="G1" s="17"/>
       <c r="H1" s="17"/>
@@ -2805,11 +2805,11 @@
       <c r="CE1" s="17"/>
     </row>
     <row r="2" spans="1:83" s="14" customFormat="1" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
@@ -2895,150 +2895,150 @@
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
-      <c r="F3" s="42" t="e" vm="1">
+      <c r="F3" s="40" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="40" t="e" vm="2">
+      <c r="G3" s="41"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="38" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="42" t="e" vm="3">
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="40" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="43"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="39" t="e" vm="4">
+      <c r="O3" s="41"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="37" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="41"/>
-      <c r="V3" s="39" t="e" vm="5">
+      <c r="R3" s="38"/>
+      <c r="S3" s="38"/>
+      <c r="T3" s="38"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="37" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W3" s="40"/>
-      <c r="X3" s="40"/>
-      <c r="Y3" s="40"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="42" t="e" vm="6">
+      <c r="W3" s="38"/>
+      <c r="X3" s="38"/>
+      <c r="Y3" s="38"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="40" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB3" s="43"/>
-      <c r="AC3" s="44"/>
-      <c r="AD3" s="42" t="e" vm="7">
+      <c r="AB3" s="41"/>
+      <c r="AC3" s="42"/>
+      <c r="AD3" s="40" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE3" s="43"/>
-      <c r="AF3" s="44"/>
-      <c r="AG3" s="42" t="e" vm="8">
+      <c r="AE3" s="41"/>
+      <c r="AF3" s="42"/>
+      <c r="AG3" s="40" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH3" s="43"/>
-      <c r="AI3" s="44"/>
-      <c r="AJ3" s="39" t="e" vm="9">
+      <c r="AH3" s="41"/>
+      <c r="AI3" s="42"/>
+      <c r="AJ3" s="37" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK3" s="40"/>
-      <c r="AL3" s="40"/>
-      <c r="AM3" s="40"/>
-      <c r="AN3" s="41"/>
-      <c r="AO3" s="42" t="e" vm="10">
+      <c r="AK3" s="38"/>
+      <c r="AL3" s="38"/>
+      <c r="AM3" s="38"/>
+      <c r="AN3" s="39"/>
+      <c r="AO3" s="40" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP3" s="43"/>
-      <c r="AQ3" s="44"/>
-      <c r="AR3" s="42" t="e" vm="11">
+      <c r="AP3" s="41"/>
+      <c r="AQ3" s="42"/>
+      <c r="AR3" s="40" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS3" s="43"/>
-      <c r="AT3" s="44"/>
-      <c r="AU3" s="39" t="e" vm="12">
+      <c r="AS3" s="41"/>
+      <c r="AT3" s="42"/>
+      <c r="AU3" s="37" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV3" s="40"/>
-      <c r="AW3" s="40"/>
-      <c r="AX3" s="40"/>
-      <c r="AY3" s="41"/>
-      <c r="AZ3" s="42" t="e" vm="13">
+      <c r="AV3" s="38"/>
+      <c r="AW3" s="38"/>
+      <c r="AX3" s="38"/>
+      <c r="AY3" s="39"/>
+      <c r="AZ3" s="40" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA3" s="43"/>
-      <c r="BB3" s="44"/>
-      <c r="BC3" s="42" t="e" vm="7">
+      <c r="BA3" s="41"/>
+      <c r="BB3" s="42"/>
+      <c r="BC3" s="40" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD3" s="43"/>
-      <c r="BE3" s="44"/>
-      <c r="BF3" s="42" t="e" vm="14">
+      <c r="BD3" s="41"/>
+      <c r="BE3" s="42"/>
+      <c r="BF3" s="40" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG3" s="43"/>
-      <c r="BH3" s="44"/>
-      <c r="BI3" s="39" t="e" vm="15">
+      <c r="BG3" s="41"/>
+      <c r="BH3" s="42"/>
+      <c r="BI3" s="37" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ3" s="40"/>
-      <c r="BK3" s="40"/>
-      <c r="BL3" s="40"/>
-      <c r="BM3" s="41"/>
-      <c r="BN3" s="42" t="e" vm="4">
+      <c r="BJ3" s="38"/>
+      <c r="BK3" s="38"/>
+      <c r="BL3" s="38"/>
+      <c r="BM3" s="39"/>
+      <c r="BN3" s="40" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO3" s="43"/>
-      <c r="BP3" s="44"/>
-      <c r="BQ3" s="42" t="e" vm="16">
+      <c r="BO3" s="41"/>
+      <c r="BP3" s="42"/>
+      <c r="BQ3" s="40" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR3" s="43"/>
-      <c r="BS3" s="44"/>
-      <c r="BT3" s="42" t="e" vm="17">
+      <c r="BR3" s="41"/>
+      <c r="BS3" s="42"/>
+      <c r="BT3" s="40" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU3" s="43"/>
-      <c r="BV3" s="44"/>
-      <c r="BW3" s="42" t="e" vm="4">
+      <c r="BU3" s="41"/>
+      <c r="BV3" s="42"/>
+      <c r="BW3" s="40" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX3" s="43"/>
-      <c r="BY3" s="44"/>
-      <c r="BZ3" s="42" t="e" vm="18">
+      <c r="BX3" s="41"/>
+      <c r="BY3" s="42"/>
+      <c r="BZ3" s="40" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA3" s="43"/>
-      <c r="CB3" s="44"/>
-      <c r="CC3" s="42" t="e" vm="19">
+      <c r="CA3" s="41"/>
+      <c r="CB3" s="42"/>
+      <c r="CC3" s="40" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD3" s="43"/>
-      <c r="CE3" s="44"/>
+      <c r="CD3" s="41"/>
+      <c r="CE3" s="42"/>
     </row>
     <row r="4" spans="1:83" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="32" t="s">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="E10" s="2" cm="1">
         <f t="array" ref="E10">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H10,M10,P10,U10,Z10,AC10,AF10,AI10,AN10,AQ10,AT10,AY10,BB10,BE10,BH10,BM10,BP10,BS10,BV10,BY10,CB10,CE10), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0.99</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="F10" s="21">
         <v>0</v>
@@ -4586,7 +4586,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="28">
-        <v>8.25</v>
+        <v>5.8</v>
       </c>
       <c r="W10" s="23">
         <v>0</v>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="Z10" s="24">
         <f t="shared" si="4"/>
-        <v>0.99</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="AA10" s="28">
         <v>0</v>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="E11" s="2" cm="1">
         <f t="array" ref="E11">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H11,M11,P11,U11,Z11,AC11,AF11,AI11,AN11,AQ11,AT11,AY11,BB11,BE11,BH11,BM11,BP11,BS11,BV11,BY11,CB11,CE11), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0.69599999999999995</v>
+        <v>0.99</v>
       </c>
       <c r="F11" s="21">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="28">
-        <v>5.8</v>
+        <v>8.25</v>
       </c>
       <c r="W11" s="23">
         <v>0</v>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="Z11" s="24">
         <f t="shared" si="4"/>
-        <v>0.69599999999999995</v>
+        <v>0.99</v>
       </c>
       <c r="AA11" s="28">
         <v>0</v>
@@ -9458,150 +9458,150 @@
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
-      <c r="F29" s="39" t="e" vm="1">
+      <c r="F29" s="37" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G29" s="40"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="40" t="e" vm="2">
+      <c r="G29" s="38"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="38" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="40"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="39" t="e" vm="3">
+      <c r="J29" s="38"/>
+      <c r="K29" s="38"/>
+      <c r="L29" s="38"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="37" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O29" s="40"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="40" t="e" vm="4">
+      <c r="O29" s="38"/>
+      <c r="P29" s="39"/>
+      <c r="Q29" s="38" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R29" s="40"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="40"/>
-      <c r="U29" s="41"/>
-      <c r="V29" s="39" t="e" vm="5">
+      <c r="R29" s="38"/>
+      <c r="S29" s="38"/>
+      <c r="T29" s="38"/>
+      <c r="U29" s="39"/>
+      <c r="V29" s="37" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W29" s="40"/>
-      <c r="X29" s="40"/>
-      <c r="Y29" s="40"/>
-      <c r="Z29" s="40"/>
-      <c r="AA29" s="39" t="e" vm="6">
+      <c r="W29" s="38"/>
+      <c r="X29" s="38"/>
+      <c r="Y29" s="38"/>
+      <c r="Z29" s="38"/>
+      <c r="AA29" s="37" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB29" s="40"/>
-      <c r="AC29" s="41"/>
-      <c r="AD29" s="39" t="e" vm="7">
+      <c r="AB29" s="38"/>
+      <c r="AC29" s="39"/>
+      <c r="AD29" s="37" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE29" s="40"/>
-      <c r="AF29" s="41"/>
-      <c r="AG29" s="39" t="e" vm="8">
+      <c r="AE29" s="38"/>
+      <c r="AF29" s="39"/>
+      <c r="AG29" s="37" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH29" s="40"/>
-      <c r="AI29" s="41"/>
-      <c r="AJ29" s="40" t="e" vm="9">
+      <c r="AH29" s="38"/>
+      <c r="AI29" s="39"/>
+      <c r="AJ29" s="38" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK29" s="40"/>
-      <c r="AL29" s="40"/>
-      <c r="AM29" s="40"/>
-      <c r="AN29" s="40"/>
-      <c r="AO29" s="39" t="e" vm="10">
+      <c r="AK29" s="38"/>
+      <c r="AL29" s="38"/>
+      <c r="AM29" s="38"/>
+      <c r="AN29" s="38"/>
+      <c r="AO29" s="37" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP29" s="40"/>
-      <c r="AQ29" s="41"/>
-      <c r="AR29" s="39" t="e" vm="11">
+      <c r="AP29" s="38"/>
+      <c r="AQ29" s="39"/>
+      <c r="AR29" s="37" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS29" s="40"/>
-      <c r="AT29" s="41"/>
-      <c r="AU29" s="40" t="e" vm="12">
+      <c r="AS29" s="38"/>
+      <c r="AT29" s="39"/>
+      <c r="AU29" s="38" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV29" s="40"/>
-      <c r="AW29" s="40"/>
-      <c r="AX29" s="40"/>
-      <c r="AY29" s="40"/>
-      <c r="AZ29" s="39" t="e" vm="13">
+      <c r="AV29" s="38"/>
+      <c r="AW29" s="38"/>
+      <c r="AX29" s="38"/>
+      <c r="AY29" s="38"/>
+      <c r="AZ29" s="37" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA29" s="40"/>
-      <c r="BB29" s="41"/>
-      <c r="BC29" s="39" t="e" vm="7">
+      <c r="BA29" s="38"/>
+      <c r="BB29" s="39"/>
+      <c r="BC29" s="37" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD29" s="40"/>
-      <c r="BE29" s="41"/>
-      <c r="BF29" s="39" t="e" vm="14">
+      <c r="BD29" s="38"/>
+      <c r="BE29" s="39"/>
+      <c r="BF29" s="37" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG29" s="40"/>
-      <c r="BH29" s="41"/>
-      <c r="BI29" s="40" t="e" vm="15">
+      <c r="BG29" s="38"/>
+      <c r="BH29" s="39"/>
+      <c r="BI29" s="38" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ29" s="40"/>
-      <c r="BK29" s="40"/>
-      <c r="BL29" s="40"/>
-      <c r="BM29" s="40"/>
-      <c r="BN29" s="39" t="e" vm="4">
+      <c r="BJ29" s="38"/>
+      <c r="BK29" s="38"/>
+      <c r="BL29" s="38"/>
+      <c r="BM29" s="38"/>
+      <c r="BN29" s="37" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO29" s="40"/>
-      <c r="BP29" s="41"/>
-      <c r="BQ29" s="39" t="e" vm="16">
+      <c r="BO29" s="38"/>
+      <c r="BP29" s="39"/>
+      <c r="BQ29" s="37" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR29" s="40"/>
-      <c r="BS29" s="41"/>
-      <c r="BT29" s="39" t="e" vm="17">
+      <c r="BR29" s="38"/>
+      <c r="BS29" s="39"/>
+      <c r="BT29" s="37" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU29" s="40"/>
-      <c r="BV29" s="41"/>
-      <c r="BW29" s="39" t="e" vm="4">
+      <c r="BU29" s="38"/>
+      <c r="BV29" s="39"/>
+      <c r="BW29" s="37" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX29" s="40"/>
-      <c r="BY29" s="41"/>
-      <c r="BZ29" s="39" t="e" vm="18">
+      <c r="BX29" s="38"/>
+      <c r="BY29" s="39"/>
+      <c r="BZ29" s="37" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA29" s="40"/>
-      <c r="CB29" s="41"/>
-      <c r="CC29" s="39" t="e" vm="19">
+      <c r="CA29" s="38"/>
+      <c r="CB29" s="39"/>
+      <c r="CC29" s="37" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD29" s="40"/>
-      <c r="CE29" s="41"/>
+      <c r="CD29" s="38"/>
+      <c r="CE29" s="39"/>
     </row>
     <row r="30" spans="1:83" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="32" t="s">
@@ -11495,10 +11495,10 @@
         <v>7</v>
       </c>
       <c r="B38" s="4">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C38" s="12" t="str">
-        <v>Charles Leclerc</v>
+        <v>Lewis Hamilton</v>
       </c>
       <c r="D38" s="4" t="str">
         <v>Ferrari</v>
@@ -14758,10 +14758,10 @@
         <v>20</v>
       </c>
       <c r="B51" s="10">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C51" s="12" t="str">
-        <v>Lewis Hamilton</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="D51" s="10" t="str">
         <v>Ferrari</v>
@@ -15532,28 +15532,67 @@
     </row>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="BW30:BY30"/>
-    <mergeCell ref="BZ30:CB30"/>
-    <mergeCell ref="Q30:U30"/>
-    <mergeCell ref="V30:Z30"/>
-    <mergeCell ref="AA30:AC30"/>
-    <mergeCell ref="AD30:AF30"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AJ30:AN30"/>
-    <mergeCell ref="AO30:AQ30"/>
-    <mergeCell ref="AR30:AT30"/>
-    <mergeCell ref="AU30:AY30"/>
-    <mergeCell ref="CC30:CE30"/>
-    <mergeCell ref="AZ30:BB30"/>
-    <mergeCell ref="BC30:BE30"/>
-    <mergeCell ref="BF30:BH30"/>
-    <mergeCell ref="BI30:BM30"/>
-    <mergeCell ref="BN30:BP30"/>
-    <mergeCell ref="BQ30:BS30"/>
-    <mergeCell ref="BT30:BV30"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="Q4:U4"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:U29"/>
+    <mergeCell ref="V29:Z29"/>
+    <mergeCell ref="V4:Z4"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AN3"/>
+    <mergeCell ref="AO3:AQ3"/>
+    <mergeCell ref="AR3:AT3"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AG4:AI4"/>
+    <mergeCell ref="AJ4:AN4"/>
+    <mergeCell ref="AO4:AQ4"/>
+    <mergeCell ref="BW3:BY3"/>
+    <mergeCell ref="BZ3:CB3"/>
+    <mergeCell ref="CC3:CE3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="V3:Z3"/>
+    <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="BT3:BV3"/>
+    <mergeCell ref="AU3:AY3"/>
+    <mergeCell ref="AZ3:BB3"/>
+    <mergeCell ref="BC3:BE3"/>
+    <mergeCell ref="BF3:BH3"/>
+    <mergeCell ref="BI3:BM3"/>
+    <mergeCell ref="BN3:BP3"/>
+    <mergeCell ref="BQ3:BS3"/>
+    <mergeCell ref="CC4:CE4"/>
+    <mergeCell ref="AR4:AT4"/>
+    <mergeCell ref="AU4:AY4"/>
+    <mergeCell ref="AZ4:BB4"/>
+    <mergeCell ref="BC4:BE4"/>
+    <mergeCell ref="BF4:BH4"/>
+    <mergeCell ref="BI4:BM4"/>
+    <mergeCell ref="BN4:BP4"/>
+    <mergeCell ref="BQ4:BS4"/>
+    <mergeCell ref="BT4:BV4"/>
+    <mergeCell ref="BW4:BY4"/>
+    <mergeCell ref="BZ4:CB4"/>
+    <mergeCell ref="BQ29:BS29"/>
+    <mergeCell ref="BT29:BV29"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AN29"/>
+    <mergeCell ref="AO29:AQ29"/>
+    <mergeCell ref="AR29:AT29"/>
     <mergeCell ref="BW29:BY29"/>
     <mergeCell ref="BZ29:CB29"/>
     <mergeCell ref="CC29:CE29"/>
@@ -15570,67 +15609,28 @@
     <mergeCell ref="BN29:BP29"/>
     <mergeCell ref="AA29:AC29"/>
     <mergeCell ref="AD29:AF29"/>
-    <mergeCell ref="BQ29:BS29"/>
-    <mergeCell ref="BT29:BV29"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AN29"/>
-    <mergeCell ref="AO29:AQ29"/>
-    <mergeCell ref="CC4:CE4"/>
-    <mergeCell ref="AR4:AT4"/>
-    <mergeCell ref="AU4:AY4"/>
-    <mergeCell ref="AZ4:BB4"/>
-    <mergeCell ref="BC4:BE4"/>
-    <mergeCell ref="BF4:BH4"/>
-    <mergeCell ref="BI4:BM4"/>
-    <mergeCell ref="BN4:BP4"/>
-    <mergeCell ref="BQ4:BS4"/>
-    <mergeCell ref="BT4:BV4"/>
-    <mergeCell ref="BW4:BY4"/>
-    <mergeCell ref="BZ4:CB4"/>
-    <mergeCell ref="BW3:BY3"/>
-    <mergeCell ref="BZ3:CB3"/>
-    <mergeCell ref="CC3:CE3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="V3:Z3"/>
-    <mergeCell ref="AA3:AC3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="BT3:BV3"/>
-    <mergeCell ref="AU3:AY3"/>
-    <mergeCell ref="AZ3:BB3"/>
-    <mergeCell ref="BC3:BE3"/>
-    <mergeCell ref="BF3:BH3"/>
-    <mergeCell ref="BI3:BM3"/>
-    <mergeCell ref="BN3:BP3"/>
-    <mergeCell ref="BQ3:BS3"/>
-    <mergeCell ref="V4:Z4"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AN3"/>
-    <mergeCell ref="AO3:AQ3"/>
-    <mergeCell ref="AR3:AT3"/>
-    <mergeCell ref="AR29:AT29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:U29"/>
-    <mergeCell ref="V29:Z29"/>
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="Q4:U4"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AG4:AI4"/>
-    <mergeCell ref="AJ4:AN4"/>
-    <mergeCell ref="AO4:AQ4"/>
+    <mergeCell ref="CC30:CE30"/>
+    <mergeCell ref="AZ30:BB30"/>
+    <mergeCell ref="BC30:BE30"/>
+    <mergeCell ref="BF30:BH30"/>
+    <mergeCell ref="BI30:BM30"/>
+    <mergeCell ref="BN30:BP30"/>
+    <mergeCell ref="BQ30:BS30"/>
+    <mergeCell ref="BT30:BV30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="BW30:BY30"/>
+    <mergeCell ref="BZ30:CB30"/>
+    <mergeCell ref="Q30:U30"/>
+    <mergeCell ref="V30:Z30"/>
+    <mergeCell ref="AA30:AC30"/>
+    <mergeCell ref="AD30:AF30"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AJ30:AN30"/>
+    <mergeCell ref="AO30:AQ30"/>
+    <mergeCell ref="AR30:AT30"/>
+    <mergeCell ref="AU30:AY30"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B27 D6:D27 B32:B53 D32:D53">
     <cfRule type="expression" dxfId="65" priority="329">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="N4" s="29">
         <f>Simplified!G6</f>
-        <v>0.29400000000000004</v>
+        <v>-0.29400000000000004</v>
       </c>
       <c r="O4" s="3">
         <v>44</v>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="G6" s="45">
         <f>K6-K7</f>
-        <v>0.29400000000000004</v>
+        <v>-0.29400000000000004</v>
       </c>
       <c r="H6" s="3">
         <v>16</v>
@@ -15999,7 +15999,7 @@
       </c>
       <c r="K6" s="2">
         <f>Ratings!E10</f>
-        <v>0.99</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="M6" s="5">
         <v>10</v>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="K7" s="2">
         <f>Ratings!E11</f>
-        <v>0.69599999999999995</v>
+        <v>0.99</v>
       </c>
       <c r="M7" s="6">
         <v>30</v>
@@ -16058,10 +16058,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="C8" s="12" t="str">
-        <v>Charles Leclerc</v>
+        <v>Lewis Hamilton</v>
       </c>
       <c r="D8" s="4" t="str">
         <v>Ferrari</v>
@@ -16532,10 +16532,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="10">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C21" s="12" t="str">
-        <v>Lewis Hamilton</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="D21" s="10" t="str">
         <v>Ferrari</v>
@@ -16684,7 +16684,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2 G4 G6 G8 G10 G12 G14 G16 G18 G20 G22">
+  <conditionalFormatting sqref="G4 G2 G6 G8 G10 G12 G14 G16 G18 G20 G22">
     <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="percentile" val="0"/>

--- a/static/data/Ratings.xlsx
+++ b/static/data/Ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Programming\webdev\portfolio\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB68969A-3BD9-4485-8BE5-55D3B8DFED46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DFC0EF-5CD6-4E8E-A821-A92654F377E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="2" xr2:uid="{BD88BCC4-2E11-4C36-830D-A75A044EF5A6}"/>
   </bookViews>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="E8" s="2" cm="1">
         <f t="array" ref="E8">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H8,M8,P8,U8,Z8,AC8,AF8,AI8,AN8,AQ8,AT8,AY8,BB8,BE8,BH8,BM8,BP8,BS8,BV8,BY8,CB8,CE8), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>8.6859999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="F8" s="21">
         <v>0</v>
@@ -4041,17 +4041,17 @@
         <v>8.75</v>
       </c>
       <c r="W8" s="23">
-        <v>9.8000000000000007</v>
+        <v>0</v>
       </c>
       <c r="X8" s="23">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="23">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="24">
         <f t="shared" si="4"/>
-        <v>8.6859999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="AA8" s="28">
         <v>0</v>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="E9" s="2" cm="1">
         <f t="array" ref="E9">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H9,M9,P9,U9,Z9,AC9,AF9,AI9,AN9,AQ9,AT9,AY9,BB9,BE9,BH9,BM9,BP9,BS9,BV9,BY9,CB9,CE9), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>5.827</v>
+        <v>1.02</v>
       </c>
       <c r="F9" s="21">
         <v>0</v>
@@ -4315,17 +4315,17 @@
         <v>8.5</v>
       </c>
       <c r="W9" s="23">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="X9" s="23">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="24">
         <f t="shared" si="4"/>
-        <v>5.827</v>
+        <v>1.02</v>
       </c>
       <c r="AA9" s="28">
         <v>0</v>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="E10" s="2" cm="1">
         <f t="array" ref="E10">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H10,M10,P10,U10,Z10,AC10,AF10,AI10,AN10,AQ10,AT10,AY10,BB10,BE10,BH10,BM10,BP10,BS10,BV10,BY10,CB10,CE10), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0.69599999999999995</v>
+        <v>0.72</v>
       </c>
       <c r="F10" s="21">
         <v>0</v>
@@ -4586,7 +4586,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="28">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="W10" s="23">
         <v>0</v>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="Z10" s="24">
         <f t="shared" si="4"/>
-        <v>0.69599999999999995</v>
+        <v>0.72</v>
       </c>
       <c r="AA10" s="28">
         <v>0</v>
@@ -5627,7 +5627,7 @@
       </c>
       <c r="E14" s="2" cm="1">
         <f t="array" ref="E14">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H14,M14,P14,U14,Z14,AC14,AF14,AI14,AN14,AQ14,AT14,AY14,BB14,BE14,BH14,BM14,BP14,BS14,BV14,BY14,CB14,CE14), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="F14" s="21">
         <v>0</v>
@@ -5682,7 +5682,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="28">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="W14" s="23">
         <v>0</v>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="Z14" s="24">
         <f t="shared" si="4"/>
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="AA14" s="28">
         <v>0</v>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="E15" s="2" cm="1">
         <f t="array" ref="E15">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H15,M15,P15,U15,Z15,AC15,AF15,AI15,AN15,AQ15,AT15,AY15,BB15,BE15,BH15,BM15,BP15,BS15,BV15,BY15,CB15,CE15), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="F15" s="21">
         <v>0</v>
@@ -5956,7 +5956,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="28">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="W15" s="23">
         <v>0</v>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="Z15" s="24">
         <f t="shared" si="4"/>
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AA15" s="28">
         <v>0</v>
@@ -8366,7 +8366,7 @@
       </c>
       <c r="E24" s="2" cm="1">
         <f t="array" ref="E24">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H24,M24,P24,U24,Z24,AC24,AF24,AI24,AN24,AQ24,AT24,AY24,BB24,BE24,BH24,BM24,BP24,BS24,BV24,BY24,CB24,CE24), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="F24" s="21">
         <v>0</v>
@@ -8420,7 +8420,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="28">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W24" s="23">
         <v>0</v>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="Z24" s="24">
         <f t="shared" si="4"/>
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
       <c r="AA24" s="28">
         <v>0</v>
@@ -9187,7 +9187,7 @@
       </c>
       <c r="E27" s="2" cm="1">
         <f t="array" ref="E27">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H27,M27,P27,U27,Z27,AC27,AF27,AI27,AN27,AQ27,AT27,AY27,BB27,BE27,BH27,BM27,BP27,BS27,BV27,BY27,CB27,CE27), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="F27" s="21">
         <v>0</v>
@@ -9242,7 +9242,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W27" s="23">
         <v>0</v>
@@ -9255,7 +9255,7 @@
       </c>
       <c r="Z27" s="24">
         <f t="shared" si="4"/>
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="AA27" s="28">
         <v>0</v>
@@ -9998,7 +9998,7 @@
         <v>McLaren</v>
       </c>
       <c r="E32" s="2">
-        <v>8.6859999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="F32" s="21">
         <v>0</v>
@@ -10052,16 +10052,16 @@
         <v>8.75</v>
       </c>
       <c r="W32" s="23">
-        <v>9.8000000000000007</v>
+        <v>0</v>
       </c>
       <c r="X32" s="23">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="23">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="24">
-        <v>8.6859999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="AA32" s="28">
         <v>0</v>
@@ -10240,16 +10240,16 @@
         <v>2</v>
       </c>
       <c r="B33" s="18">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="C33" s="12" t="str">
-        <v>Oscar Piastri</v>
+        <v>Franco Colapinto</v>
       </c>
       <c r="D33" s="18" t="str">
-        <v>McLaren</v>
+        <v>Alpine</v>
       </c>
       <c r="E33" s="2">
-        <v>5.827</v>
+        <v>1.05</v>
       </c>
       <c r="F33" s="21">
         <v>0</v>
@@ -10300,19 +10300,19 @@
         <v>0</v>
       </c>
       <c r="V33" s="28">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="W33" s="23">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="X33" s="23">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Y33" s="23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="24">
-        <v>5.827</v>
+        <v>1.05</v>
       </c>
       <c r="AA33" s="28">
         <v>0</v>
@@ -10742,13 +10742,13 @@
         <v>4</v>
       </c>
       <c r="B35" s="1">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="C35" s="12" t="str">
-        <v>Franco Colapinto</v>
+        <v>Oscar Piastri</v>
       </c>
       <c r="D35" s="1" t="str">
-        <v>Alpine</v>
+        <v>McLaren</v>
       </c>
       <c r="E35" s="2">
         <v>1.02</v>
@@ -11244,16 +11244,16 @@
         <v>6</v>
       </c>
       <c r="B37" s="3">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="C37" s="12" t="str">
-        <v>Sergio Perez</v>
+        <v>Lewis Hamilton</v>
       </c>
       <c r="D37" s="3" t="str">
-        <v>Cadillac</v>
+        <v>Ferrari</v>
       </c>
       <c r="E37" s="2">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="F37" s="21">
         <v>0</v>
@@ -11304,7 +11304,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="28">
-        <v>8.5</v>
+        <v>8.25</v>
       </c>
       <c r="W37" s="23">
         <v>0</v>
@@ -11316,7 +11316,7 @@
         <v>0</v>
       </c>
       <c r="Z37" s="24">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="AA37" s="28">
         <v>0</v>
@@ -11495,16 +11495,16 @@
         <v>7</v>
       </c>
       <c r="B38" s="4">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C38" s="12" t="str">
-        <v>Lewis Hamilton</v>
+        <v>Kimi Antonelli</v>
       </c>
       <c r="D38" s="4" t="str">
-        <v>Ferrari</v>
+        <v>Mercedes</v>
       </c>
       <c r="E38" s="2">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="F38" s="21">
         <v>0</v>
@@ -11555,7 +11555,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="28">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="W38" s="23">
         <v>0</v>
@@ -11567,7 +11567,7 @@
         <v>0</v>
       </c>
       <c r="Z38" s="24">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="AA38" s="28">
         <v>0</v>
@@ -11746,13 +11746,13 @@
         <v>8</v>
       </c>
       <c r="B39" s="4">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C39" s="12" t="str">
-        <v>Kimi Antonelli</v>
+        <v>Nico Hulkenberg</v>
       </c>
       <c r="D39" s="4" t="str">
-        <v>Mercedes</v>
+        <v>Audi</v>
       </c>
       <c r="E39" s="2">
         <v>0.96</v>
@@ -11997,13 +11997,13 @@
         <v>9</v>
       </c>
       <c r="B40" s="5">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C40" s="12" t="str">
-        <v>Nico Hulkenberg</v>
+        <v>Sergio Perez</v>
       </c>
       <c r="D40" s="5" t="str">
-        <v>Audi</v>
+        <v>Cadillac</v>
       </c>
       <c r="E40" s="2">
         <v>0.96</v>
@@ -14507,13 +14507,13 @@
         <v>19</v>
       </c>
       <c r="B50" s="10">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C50" s="12" t="str">
-        <v>Lance Stroll</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="D50" s="10" t="str">
-        <v>Aston Martin</v>
+        <v>Ferrari</v>
       </c>
       <c r="E50" s="2">
         <v>0.72</v>
@@ -14758,16 +14758,16 @@
         <v>20</v>
       </c>
       <c r="B51" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C51" s="12" t="str">
-        <v>Charles Leclerc</v>
+        <v>Lance Stroll</v>
       </c>
       <c r="D51" s="10" t="str">
-        <v>Ferrari</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E51" s="2">
-        <v>0.69599999999999995</v>
+        <v>0.6</v>
       </c>
       <c r="F51" s="21">
         <v>0</v>
@@ -14818,7 +14818,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="28">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="W51" s="23">
         <v>0</v>
@@ -14830,7 +14830,7 @@
         <v>0</v>
       </c>
       <c r="Z51" s="24">
-        <v>0.69599999999999995</v>
+        <v>0.6</v>
       </c>
       <c r="AA51" s="28">
         <v>0</v>
@@ -15018,7 +15018,7 @@
         <v>Alpine</v>
       </c>
       <c r="E52" s="2">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="F52" s="21">
         <v>0</v>
@@ -15069,7 +15069,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="28">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="W52" s="23">
         <v>0</v>
@@ -15081,7 +15081,7 @@
         <v>0</v>
       </c>
       <c r="Z52" s="24">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="AA52" s="28">
         <v>0</v>
@@ -15812,7 +15812,7 @@
         <v>McLaren</v>
       </c>
       <c r="E2" s="2">
-        <v>8.6859999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="G2" s="45">
         <f>K2-K3</f>
@@ -15847,16 +15847,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="18">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="C3" s="12" t="str">
-        <v>Oscar Piastri</v>
+        <v>Franco Colapinto</v>
       </c>
       <c r="D3" s="18" t="str">
-        <v>McLaren</v>
+        <v>Alpine</v>
       </c>
       <c r="E3" s="2">
-        <v>5.827</v>
+        <v>1.05</v>
       </c>
       <c r="G3" s="45"/>
       <c r="H3" s="18">
@@ -15877,7 +15877,7 @@
       </c>
       <c r="N3" s="29">
         <f>Simplified!G4</f>
-        <v>2.859</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="O3" s="1">
         <v>81</v>
@@ -15901,7 +15901,7 @@
       </c>
       <c r="G4" s="45">
         <f>K4-K5</f>
-        <v>2.859</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -15914,14 +15914,14 @@
       </c>
       <c r="K4" s="2">
         <f>Ratings!E8</f>
-        <v>8.6859999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="M4" s="3">
         <v>16</v>
       </c>
       <c r="N4" s="29">
         <f>Simplified!G6</f>
-        <v>-0.29400000000000004</v>
+        <v>-0.27</v>
       </c>
       <c r="O4" s="3">
         <v>44</v>
@@ -15932,13 +15932,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="C5" s="12" t="str">
-        <v>Franco Colapinto</v>
+        <v>Oscar Piastri</v>
       </c>
       <c r="D5" s="1" t="str">
-        <v>Alpine</v>
+        <v>McLaren</v>
       </c>
       <c r="E5" s="2">
         <v>1.02</v>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="K5" s="2">
         <f>Ratings!E9</f>
-        <v>5.827</v>
+        <v>1.02</v>
       </c>
       <c r="M5" s="4">
         <v>3</v>
@@ -15986,7 +15986,7 @@
       </c>
       <c r="G6" s="45">
         <f>K6-K7</f>
-        <v>-0.29400000000000004</v>
+        <v>-0.27</v>
       </c>
       <c r="H6" s="3">
         <v>16</v>
@@ -15999,14 +15999,14 @@
       </c>
       <c r="K6" s="2">
         <f>Ratings!E10</f>
-        <v>0.69599999999999995</v>
+        <v>0.72</v>
       </c>
       <c r="M6" s="5">
         <v>10</v>
       </c>
       <c r="N6" s="29">
         <f>Simplified!G10</f>
-        <v>-0.54</v>
+        <v>-0.63000000000000012</v>
       </c>
       <c r="O6" s="5">
         <v>43</v>
@@ -16017,16 +16017,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="C7" s="12" t="str">
-        <v>Sergio Perez</v>
+        <v>Lewis Hamilton</v>
       </c>
       <c r="D7" s="3" t="str">
-        <v>Cadillac</v>
+        <v>Ferrari</v>
       </c>
       <c r="E7" s="2">
-        <v>1.02</v>
+        <v>0.99</v>
       </c>
       <c r="G7" s="45"/>
       <c r="H7" s="3">
@@ -16058,16 +16058,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C8" s="12" t="str">
-        <v>Lewis Hamilton</v>
+        <v>Kimi Antonelli</v>
       </c>
       <c r="D8" s="4" t="str">
-        <v>Ferrari</v>
+        <v>Mercedes</v>
       </c>
       <c r="E8" s="2">
-        <v>0.99</v>
+        <v>0.96</v>
       </c>
       <c r="G8" s="45">
         <f>K8-K9</f>
@@ -16102,13 +16102,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C9" s="12" t="str">
-        <v>Kimi Antonelli</v>
+        <v>Nico Hulkenberg</v>
       </c>
       <c r="D9" s="4" t="str">
-        <v>Mercedes</v>
+        <v>Audi</v>
       </c>
       <c r="E9" s="2">
         <v>0.96</v>
@@ -16143,20 +16143,20 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="C10" s="12" t="str">
-        <v>Nico Hulkenberg</v>
+        <v>Sergio Perez</v>
       </c>
       <c r="D10" s="5" t="str">
-        <v>Audi</v>
+        <v>Cadillac</v>
       </c>
       <c r="E10" s="2">
         <v>0.96</v>
       </c>
       <c r="G10" s="45">
         <f>K10-K11</f>
-        <v>-0.54</v>
+        <v>-0.63000000000000012</v>
       </c>
       <c r="H10" s="5">
         <v>10</v>
@@ -16169,7 +16169,7 @@
       </c>
       <c r="K10" s="2">
         <f>Ratings!E14</f>
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="M10" s="9">
         <v>27</v>
@@ -16210,14 +16210,14 @@
       </c>
       <c r="K11" s="2">
         <f>Ratings!E15</f>
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="M11" s="10">
         <v>11</v>
       </c>
       <c r="N11" s="29">
         <f>Simplified!G20</f>
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="O11" s="10">
         <v>77</v>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="N12" s="29">
         <f>Simplified!G22</f>
-        <v>0.17999999999999994</v>
+        <v>0.29999999999999993</v>
       </c>
       <c r="O12" s="11">
         <v>18</v>
@@ -16498,20 +16498,20 @@
         <v>19</v>
       </c>
       <c r="B20" s="10">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" s="12" t="str">
-        <v>Lance Stroll</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="D20" s="10" t="str">
-        <v>Aston Martin</v>
+        <v>Ferrari</v>
       </c>
       <c r="E20" s="2">
         <v>0.72</v>
       </c>
       <c r="G20" s="45">
         <f>K20-K21</f>
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="H20" s="10">
         <v>11</v>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="K20" s="2">
         <f>Ratings!E24</f>
-        <v>1.02</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -16532,16 +16532,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C21" s="12" t="str">
-        <v>Charles Leclerc</v>
+        <v>Lance Stroll</v>
       </c>
       <c r="D21" s="10" t="str">
-        <v>Ferrari</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E21" s="2">
-        <v>0.69599999999999995</v>
+        <v>0.6</v>
       </c>
       <c r="G21" s="45"/>
       <c r="H21" s="10">
@@ -16572,11 +16572,11 @@
         <v>Alpine</v>
       </c>
       <c r="E22" s="2">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="G22" s="45">
         <f>K22-K23</f>
-        <v>0.17999999999999994</v>
+        <v>0.29999999999999993</v>
       </c>
       <c r="H22" s="11">
         <v>14</v>
@@ -16620,7 +16620,7 @@
       </c>
       <c r="K23" s="2">
         <f>Ratings!E27</f>
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/static/data/Ratings.xlsx
+++ b/static/data/Ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Programming\webdev\portfolio\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05DFC0EF-5CD6-4E8E-A821-A92654F377E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6FE96B4-3B4B-4F42-AD69-28AF6C6412A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="2" xr2:uid="{BD88BCC4-2E11-4C36-830D-A75A044EF5A6}"/>
   </bookViews>
@@ -259,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="73">
   <si>
     <t>RANK</t>
   </si>
@@ -475,6 +475,9 @@
   </si>
   <si>
     <t>Dummy</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -906,10 +909,34 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -922,30 +949,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2718,13 +2721,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:83" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
       <c r="F1" s="17"/>
       <c r="G1" s="17"/>
       <c r="H1" s="17"/>
@@ -2805,11 +2808,11 @@
       <c r="CE1" s="17"/>
     </row>
     <row r="2" spans="1:83" s="14" customFormat="1" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
@@ -2895,296 +2898,296 @@
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
-      <c r="F3" s="40" t="e" vm="1">
+      <c r="F3" s="37" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G3" s="41"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="38" t="e" vm="2">
+      <c r="G3" s="38"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="34" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="40" t="e" vm="3">
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="37" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="41"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="37" t="e" vm="4">
+      <c r="O3" s="38"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="33" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="37" t="e" vm="5">
+      <c r="R3" s="34"/>
+      <c r="S3" s="34"/>
+      <c r="T3" s="34"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="33" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W3" s="38"/>
-      <c r="X3" s="38"/>
-      <c r="Y3" s="38"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="40" t="e" vm="6">
+      <c r="W3" s="34"/>
+      <c r="X3" s="34"/>
+      <c r="Y3" s="34"/>
+      <c r="Z3" s="35"/>
+      <c r="AA3" s="37" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="42"/>
-      <c r="AD3" s="40" t="e" vm="7">
+      <c r="AB3" s="38"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="37" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="42"/>
-      <c r="AG3" s="40" t="e" vm="8">
+      <c r="AE3" s="38"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="37" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="42"/>
-      <c r="AJ3" s="37" t="e" vm="9">
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="39"/>
+      <c r="AJ3" s="33" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK3" s="38"/>
-      <c r="AL3" s="38"/>
-      <c r="AM3" s="38"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="40" t="e" vm="10">
+      <c r="AK3" s="34"/>
+      <c r="AL3" s="34"/>
+      <c r="AM3" s="34"/>
+      <c r="AN3" s="35"/>
+      <c r="AO3" s="37" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP3" s="41"/>
-      <c r="AQ3" s="42"/>
-      <c r="AR3" s="40" t="e" vm="11">
+      <c r="AP3" s="38"/>
+      <c r="AQ3" s="39"/>
+      <c r="AR3" s="37" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS3" s="41"/>
-      <c r="AT3" s="42"/>
-      <c r="AU3" s="37" t="e" vm="12">
+      <c r="AS3" s="38"/>
+      <c r="AT3" s="39"/>
+      <c r="AU3" s="33" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV3" s="38"/>
-      <c r="AW3" s="38"/>
-      <c r="AX3" s="38"/>
-      <c r="AY3" s="39"/>
-      <c r="AZ3" s="40" t="e" vm="13">
+      <c r="AV3" s="34"/>
+      <c r="AW3" s="34"/>
+      <c r="AX3" s="34"/>
+      <c r="AY3" s="35"/>
+      <c r="AZ3" s="37" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA3" s="41"/>
-      <c r="BB3" s="42"/>
-      <c r="BC3" s="40" t="e" vm="7">
+      <c r="BA3" s="38"/>
+      <c r="BB3" s="39"/>
+      <c r="BC3" s="37" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD3" s="41"/>
-      <c r="BE3" s="42"/>
-      <c r="BF3" s="40" t="e" vm="14">
+      <c r="BD3" s="38"/>
+      <c r="BE3" s="39"/>
+      <c r="BF3" s="37" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG3" s="41"/>
-      <c r="BH3" s="42"/>
-      <c r="BI3" s="37" t="e" vm="15">
+      <c r="BG3" s="38"/>
+      <c r="BH3" s="39"/>
+      <c r="BI3" s="33" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ3" s="38"/>
-      <c r="BK3" s="38"/>
-      <c r="BL3" s="38"/>
-      <c r="BM3" s="39"/>
-      <c r="BN3" s="40" t="e" vm="4">
+      <c r="BJ3" s="34"/>
+      <c r="BK3" s="34"/>
+      <c r="BL3" s="34"/>
+      <c r="BM3" s="35"/>
+      <c r="BN3" s="37" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO3" s="41"/>
-      <c r="BP3" s="42"/>
-      <c r="BQ3" s="40" t="e" vm="16">
+      <c r="BO3" s="38"/>
+      <c r="BP3" s="39"/>
+      <c r="BQ3" s="37" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR3" s="41"/>
-      <c r="BS3" s="42"/>
-      <c r="BT3" s="40" t="e" vm="17">
+      <c r="BR3" s="38"/>
+      <c r="BS3" s="39"/>
+      <c r="BT3" s="37" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU3" s="41"/>
-      <c r="BV3" s="42"/>
-      <c r="BW3" s="40" t="e" vm="4">
+      <c r="BU3" s="38"/>
+      <c r="BV3" s="39"/>
+      <c r="BW3" s="37" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX3" s="41"/>
-      <c r="BY3" s="42"/>
-      <c r="BZ3" s="40" t="e" vm="18">
+      <c r="BX3" s="38"/>
+      <c r="BY3" s="39"/>
+      <c r="BZ3" s="37" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA3" s="41"/>
-      <c r="CB3" s="42"/>
-      <c r="CC3" s="40" t="e" vm="19">
+      <c r="CA3" s="38"/>
+      <c r="CB3" s="39"/>
+      <c r="CC3" s="37" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD3" s="41"/>
-      <c r="CE3" s="42"/>
+      <c r="CD3" s="38"/>
+      <c r="CE3" s="39"/>
     </row>
     <row r="4" spans="1:83" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="32" t="s">
+      <c r="A4" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="32" t="s">
+      <c r="G4" s="36"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="31" t="s">
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="32"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="34" t="s">
+      <c r="O4" s="36"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="36"/>
-      <c r="V4" s="34" t="s">
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="44"/>
+      <c r="V4" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="31" t="s">
+      <c r="W4" s="43"/>
+      <c r="X4" s="43"/>
+      <c r="Y4" s="43"/>
+      <c r="Z4" s="44"/>
+      <c r="AA4" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="33"/>
-      <c r="AD4" s="31" t="s">
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="41"/>
+      <c r="AD4" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="AE4" s="32"/>
-      <c r="AF4" s="33"/>
-      <c r="AG4" s="31" t="s">
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="41"/>
+      <c r="AG4" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="AH4" s="32"/>
-      <c r="AI4" s="33"/>
-      <c r="AJ4" s="34" t="s">
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="41"/>
+      <c r="AJ4" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="AK4" s="35"/>
-      <c r="AL4" s="35"/>
-      <c r="AM4" s="35"/>
-      <c r="AN4" s="36"/>
-      <c r="AO4" s="31" t="s">
+      <c r="AK4" s="43"/>
+      <c r="AL4" s="43"/>
+      <c r="AM4" s="43"/>
+      <c r="AN4" s="44"/>
+      <c r="AO4" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="AP4" s="32"/>
-      <c r="AQ4" s="33"/>
-      <c r="AR4" s="31" t="s">
+      <c r="AP4" s="36"/>
+      <c r="AQ4" s="41"/>
+      <c r="AR4" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="AS4" s="32"/>
-      <c r="AT4" s="33"/>
-      <c r="AU4" s="34" t="s">
+      <c r="AS4" s="36"/>
+      <c r="AT4" s="41"/>
+      <c r="AU4" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="AV4" s="35"/>
-      <c r="AW4" s="35"/>
-      <c r="AX4" s="35"/>
-      <c r="AY4" s="36"/>
-      <c r="AZ4" s="31" t="s">
+      <c r="AV4" s="43"/>
+      <c r="AW4" s="43"/>
+      <c r="AX4" s="43"/>
+      <c r="AY4" s="44"/>
+      <c r="AZ4" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="BA4" s="32"/>
-      <c r="BB4" s="33"/>
-      <c r="BC4" s="31" t="s">
+      <c r="BA4" s="36"/>
+      <c r="BB4" s="41"/>
+      <c r="BC4" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="BD4" s="32"/>
-      <c r="BE4" s="33"/>
-      <c r="BF4" s="31" t="s">
+      <c r="BD4" s="36"/>
+      <c r="BE4" s="41"/>
+      <c r="BF4" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="BG4" s="32"/>
-      <c r="BH4" s="33"/>
-      <c r="BI4" s="34" t="s">
+      <c r="BG4" s="36"/>
+      <c r="BH4" s="41"/>
+      <c r="BI4" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="BJ4" s="35"/>
-      <c r="BK4" s="35"/>
-      <c r="BL4" s="35"/>
-      <c r="BM4" s="36"/>
-      <c r="BN4" s="31" t="s">
+      <c r="BJ4" s="43"/>
+      <c r="BK4" s="43"/>
+      <c r="BL4" s="43"/>
+      <c r="BM4" s="44"/>
+      <c r="BN4" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="BO4" s="32"/>
-      <c r="BP4" s="33"/>
-      <c r="BQ4" s="31" t="s">
+      <c r="BO4" s="36"/>
+      <c r="BP4" s="41"/>
+      <c r="BQ4" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="BR4" s="32"/>
-      <c r="BS4" s="33"/>
-      <c r="BT4" s="31" t="s">
+      <c r="BR4" s="36"/>
+      <c r="BS4" s="41"/>
+      <c r="BT4" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="BU4" s="32"/>
-      <c r="BV4" s="33"/>
-      <c r="BW4" s="31" t="s">
+      <c r="BU4" s="36"/>
+      <c r="BV4" s="41"/>
+      <c r="BW4" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="BX4" s="32"/>
-      <c r="BY4" s="33"/>
-      <c r="BZ4" s="31" t="s">
+      <c r="BX4" s="36"/>
+      <c r="BY4" s="41"/>
+      <c r="BZ4" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="CA4" s="32"/>
-      <c r="CB4" s="33"/>
-      <c r="CC4" s="31" t="s">
+      <c r="CA4" s="36"/>
+      <c r="CB4" s="41"/>
+      <c r="CC4" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="CD4" s="32"/>
-      <c r="CE4" s="33"/>
+      <c r="CD4" s="36"/>
+      <c r="CE4" s="41"/>
     </row>
     <row r="5" spans="1:83" s="16" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
       <c r="F5" s="22" t="s">
         <v>26</v>
       </c>
@@ -5353,7 +5356,7 @@
       </c>
       <c r="E13" s="2" cm="1">
         <f t="array" ref="E13">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H13,M13,P13,U13,Z13,AC13,AF13,AI13,AN13,AQ13,AT13,AY13,BB13,BE13,BH13,BM13,BP13,BS13,BV13,BY13,CB13,CE13), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0.89999999999999991</v>
+        <v>0.87</v>
       </c>
       <c r="F13" s="21">
         <v>0</v>
@@ -5408,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="28">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="W13" s="23">
         <v>0</v>
@@ -5421,7 +5424,7 @@
       </c>
       <c r="Z13" s="24">
         <f t="shared" si="4"/>
-        <v>0.89999999999999991</v>
+        <v>0.87</v>
       </c>
       <c r="AA13" s="28">
         <v>0</v>
@@ -6175,7 +6178,7 @@
       </c>
       <c r="E16" s="2" cm="1">
         <f t="array" ref="E16">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H16,M16,P16,U16,Z16,AC16,AF16,AI16,AN16,AQ16,AT16,AY16,BB16,BE16,BH16,BM16,BP16,BS16,BV16,BY16,CB16,CE16), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="F16" s="21">
         <v>0</v>
@@ -6229,8 +6232,8 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V16" s="28">
-        <v>7</v>
+      <c r="V16" s="28" t="s">
+        <v>72</v>
       </c>
       <c r="W16" s="23">
         <v>0</v>
@@ -6243,7 +6246,7 @@
       </c>
       <c r="Z16" s="24">
         <f t="shared" si="4"/>
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AA16" s="28">
         <v>0</v>
@@ -6449,7 +6452,7 @@
       </c>
       <c r="E17" s="2" cm="1">
         <f t="array" ref="E17">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H17,M17,P17,U17,Z17,AC17,AF17,AI17,AN17,AQ17,AT17,AY17,BB17,BE17,BH17,BM17,BP17,BS17,BV17,BY17,CB17,CE17), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0.89999999999999991</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="F17" s="21">
         <v>0</v>
@@ -6504,7 +6507,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="28">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="W17" s="23">
         <v>0</v>
@@ -6517,7 +6520,7 @@
       </c>
       <c r="Z17" s="24">
         <f t="shared" si="4"/>
-        <v>0.89999999999999991</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="AA17" s="28">
         <v>0</v>
@@ -6997,7 +7000,7 @@
       </c>
       <c r="E19" s="2" cm="1">
         <f t="array" ref="E19">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H19,M19,P19,U19,Z19,AC19,AF19,AI19,AN19,AQ19,AT19,AY19,BB19,BE19,BH19,BM19,BP19,BS19,BV19,BY19,CB19,CE19), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="F19" s="21">
         <v>0</v>
@@ -7052,7 +7055,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="28">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="W19" s="23">
         <v>0</v>
@@ -7065,7 +7068,7 @@
       </c>
       <c r="Z19" s="24">
         <f t="shared" si="4"/>
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="AA19" s="28">
         <v>0</v>
@@ -7545,7 +7548,7 @@
       </c>
       <c r="E21" s="2" cm="1">
         <f t="array" ref="E21">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H21,M21,P21,U21,Z21,AC21,AF21,AI21,AN21,AQ21,AT21,AY21,BB21,BE21,BH21,BM21,BP21,BS21,BV21,BY21,CB21,CE21), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="F21" s="21">
         <v>0</v>
@@ -7599,8 +7602,8 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V21" s="28">
-        <v>7</v>
+      <c r="V21" s="28" t="s">
+        <v>72</v>
       </c>
       <c r="W21" s="23">
         <v>0</v>
@@ -7613,7 +7616,7 @@
       </c>
       <c r="Z21" s="24">
         <f t="shared" si="4"/>
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="28">
         <v>0</v>
@@ -8092,7 +8095,7 @@
       </c>
       <c r="E23" s="2" cm="1">
         <f t="array" ref="E23">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H23,M23,P23,U23,Z23,AC23,AF23,AI23,AN23,AQ23,AT23,AY23,BB23,BE23,BH23,BM23,BP23,BS23,BV23,BY23,CB23,CE23), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0.89400000000000002</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="F23" s="21">
         <v>0</v>
@@ -8147,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="28">
-        <v>7.45</v>
+        <v>7.5</v>
       </c>
       <c r="W23" s="23">
         <v>0</v>
@@ -8160,7 +8163,7 @@
       </c>
       <c r="Z23" s="24">
         <f t="shared" si="4"/>
-        <v>0.89400000000000002</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="AA23" s="28">
         <v>0</v>
@@ -8366,7 +8369,7 @@
       </c>
       <c r="E24" s="2" cm="1">
         <f t="array" ref="E24">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H24,M24,P24,U24,Z24,AC24,AF24,AI24,AN24,AQ24,AT24,AY24,BB24,BE24,BH24,BM24,BP24,BS24,BV24,BY24,CB24,CE24), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="F24" s="21">
         <v>0</v>
@@ -8420,7 +8423,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="28">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="W24" s="23">
         <v>0</v>
@@ -8433,7 +8436,7 @@
       </c>
       <c r="Z24" s="24">
         <f t="shared" si="4"/>
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="AA24" s="28">
         <v>0</v>
@@ -8639,7 +8642,7 @@
       </c>
       <c r="E25" s="2" cm="1">
         <f t="array" ref="E25">_xlfn.LET(_xlpm.scores, _xlfn.VSTACK(H25,M25,P25,U25,Z25,AC25,AF25,AI25,AN25,AQ25,AT25,AY25,BB25,BE25,BH25,BM25,BP25,BS25,BV25,BY25,CB25,CE25), IFERROR(AVERAGE(_xlfn._xlws.FILTER(_xlpm.scores, _xlpm.scores&gt;0)), 0))</f>
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="F25" s="21">
         <v>0</v>
@@ -8694,7 +8697,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="28">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W25" s="23">
         <v>0</v>
@@ -8707,7 +8710,7 @@
       </c>
       <c r="Z25" s="24">
         <f t="shared" si="4"/>
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="AA25" s="28">
         <v>0</v>
@@ -9458,296 +9461,296 @@
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
-      <c r="F29" s="37" t="e" vm="1">
+      <c r="F29" s="33" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G29" s="38"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="38" t="e" vm="2">
+      <c r="G29" s="34"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="34" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J29" s="38"/>
-      <c r="K29" s="38"/>
-      <c r="L29" s="38"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="37" t="e" vm="3">
+      <c r="J29" s="34"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="34"/>
+      <c r="M29" s="34"/>
+      <c r="N29" s="33" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O29" s="38"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="38" t="e" vm="4">
+      <c r="O29" s="34"/>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="34" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R29" s="38"/>
-      <c r="S29" s="38"/>
-      <c r="T29" s="38"/>
-      <c r="U29" s="39"/>
-      <c r="V29" s="37" t="e" vm="5">
+      <c r="R29" s="34"/>
+      <c r="S29" s="34"/>
+      <c r="T29" s="34"/>
+      <c r="U29" s="35"/>
+      <c r="V29" s="33" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W29" s="38"/>
-      <c r="X29" s="38"/>
-      <c r="Y29" s="38"/>
-      <c r="Z29" s="38"/>
-      <c r="AA29" s="37" t="e" vm="6">
+      <c r="W29" s="34"/>
+      <c r="X29" s="34"/>
+      <c r="Y29" s="34"/>
+      <c r="Z29" s="34"/>
+      <c r="AA29" s="33" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB29" s="38"/>
-      <c r="AC29" s="39"/>
-      <c r="AD29" s="37" t="e" vm="7">
+      <c r="AB29" s="34"/>
+      <c r="AC29" s="35"/>
+      <c r="AD29" s="33" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE29" s="38"/>
-      <c r="AF29" s="39"/>
-      <c r="AG29" s="37" t="e" vm="8">
+      <c r="AE29" s="34"/>
+      <c r="AF29" s="35"/>
+      <c r="AG29" s="33" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH29" s="38"/>
-      <c r="AI29" s="39"/>
-      <c r="AJ29" s="38" t="e" vm="9">
+      <c r="AH29" s="34"/>
+      <c r="AI29" s="35"/>
+      <c r="AJ29" s="34" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK29" s="38"/>
-      <c r="AL29" s="38"/>
-      <c r="AM29" s="38"/>
-      <c r="AN29" s="38"/>
-      <c r="AO29" s="37" t="e" vm="10">
+      <c r="AK29" s="34"/>
+      <c r="AL29" s="34"/>
+      <c r="AM29" s="34"/>
+      <c r="AN29" s="34"/>
+      <c r="AO29" s="33" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP29" s="38"/>
-      <c r="AQ29" s="39"/>
-      <c r="AR29" s="37" t="e" vm="11">
+      <c r="AP29" s="34"/>
+      <c r="AQ29" s="35"/>
+      <c r="AR29" s="33" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS29" s="38"/>
-      <c r="AT29" s="39"/>
-      <c r="AU29" s="38" t="e" vm="12">
+      <c r="AS29" s="34"/>
+      <c r="AT29" s="35"/>
+      <c r="AU29" s="34" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV29" s="38"/>
-      <c r="AW29" s="38"/>
-      <c r="AX29" s="38"/>
-      <c r="AY29" s="38"/>
-      <c r="AZ29" s="37" t="e" vm="13">
+      <c r="AV29" s="34"/>
+      <c r="AW29" s="34"/>
+      <c r="AX29" s="34"/>
+      <c r="AY29" s="34"/>
+      <c r="AZ29" s="33" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA29" s="38"/>
-      <c r="BB29" s="39"/>
-      <c r="BC29" s="37" t="e" vm="7">
+      <c r="BA29" s="34"/>
+      <c r="BB29" s="35"/>
+      <c r="BC29" s="33" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD29" s="38"/>
-      <c r="BE29" s="39"/>
-      <c r="BF29" s="37" t="e" vm="14">
+      <c r="BD29" s="34"/>
+      <c r="BE29" s="35"/>
+      <c r="BF29" s="33" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG29" s="38"/>
-      <c r="BH29" s="39"/>
-      <c r="BI29" s="38" t="e" vm="15">
+      <c r="BG29" s="34"/>
+      <c r="BH29" s="35"/>
+      <c r="BI29" s="34" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ29" s="38"/>
-      <c r="BK29" s="38"/>
-      <c r="BL29" s="38"/>
-      <c r="BM29" s="38"/>
-      <c r="BN29" s="37" t="e" vm="4">
+      <c r="BJ29" s="34"/>
+      <c r="BK29" s="34"/>
+      <c r="BL29" s="34"/>
+      <c r="BM29" s="34"/>
+      <c r="BN29" s="33" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO29" s="38"/>
-      <c r="BP29" s="39"/>
-      <c r="BQ29" s="37" t="e" vm="16">
+      <c r="BO29" s="34"/>
+      <c r="BP29" s="35"/>
+      <c r="BQ29" s="33" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR29" s="38"/>
-      <c r="BS29" s="39"/>
-      <c r="BT29" s="37" t="e" vm="17">
+      <c r="BR29" s="34"/>
+      <c r="BS29" s="35"/>
+      <c r="BT29" s="33" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU29" s="38"/>
-      <c r="BV29" s="39"/>
-      <c r="BW29" s="37" t="e" vm="4">
+      <c r="BU29" s="34"/>
+      <c r="BV29" s="35"/>
+      <c r="BW29" s="33" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX29" s="38"/>
-      <c r="BY29" s="39"/>
-      <c r="BZ29" s="37" t="e" vm="18">
+      <c r="BX29" s="34"/>
+      <c r="BY29" s="35"/>
+      <c r="BZ29" s="33" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA29" s="38"/>
-      <c r="CB29" s="39"/>
-      <c r="CC29" s="37" t="e" vm="19">
+      <c r="CA29" s="34"/>
+      <c r="CB29" s="35"/>
+      <c r="CC29" s="33" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD29" s="38"/>
-      <c r="CE29" s="39"/>
+      <c r="CD29" s="34"/>
+      <c r="CE29" s="35"/>
     </row>
     <row r="30" spans="1:83" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" s="32" t="s">
+      <c r="A30" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="32" t="s">
+      <c r="C30" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="32" t="s">
+      <c r="E30" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="F30" s="31" t="s">
+      <c r="F30" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G30" s="32"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="32" t="s">
+      <c r="G30" s="36"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
-      <c r="N30" s="31" t="s">
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="O30" s="32"/>
-      <c r="P30" s="33"/>
-      <c r="Q30" s="34" t="s">
+      <c r="O30" s="36"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="R30" s="35"/>
-      <c r="S30" s="35"/>
-      <c r="T30" s="35"/>
-      <c r="U30" s="36"/>
-      <c r="V30" s="34" t="s">
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="43"/>
+      <c r="U30" s="44"/>
+      <c r="V30" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="W30" s="35"/>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="35"/>
-      <c r="Z30" s="36"/>
-      <c r="AA30" s="31" t="s">
+      <c r="W30" s="43"/>
+      <c r="X30" s="43"/>
+      <c r="Y30" s="43"/>
+      <c r="Z30" s="44"/>
+      <c r="AA30" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="AB30" s="32"/>
-      <c r="AC30" s="33"/>
-      <c r="AD30" s="31" t="s">
+      <c r="AB30" s="36"/>
+      <c r="AC30" s="41"/>
+      <c r="AD30" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="AE30" s="32"/>
-      <c r="AF30" s="33"/>
-      <c r="AG30" s="31" t="s">
+      <c r="AE30" s="36"/>
+      <c r="AF30" s="41"/>
+      <c r="AG30" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="AH30" s="32"/>
-      <c r="AI30" s="33"/>
-      <c r="AJ30" s="32" t="s">
+      <c r="AH30" s="36"/>
+      <c r="AI30" s="41"/>
+      <c r="AJ30" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="AK30" s="32"/>
-      <c r="AL30" s="32"/>
-      <c r="AM30" s="32"/>
-      <c r="AN30" s="32"/>
-      <c r="AO30" s="31" t="s">
+      <c r="AK30" s="36"/>
+      <c r="AL30" s="36"/>
+      <c r="AM30" s="36"/>
+      <c r="AN30" s="36"/>
+      <c r="AO30" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="AP30" s="32"/>
-      <c r="AQ30" s="33"/>
-      <c r="AR30" s="31" t="s">
+      <c r="AP30" s="36"/>
+      <c r="AQ30" s="41"/>
+      <c r="AR30" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="AS30" s="32"/>
-      <c r="AT30" s="33"/>
-      <c r="AU30" s="34" t="s">
+      <c r="AS30" s="36"/>
+      <c r="AT30" s="41"/>
+      <c r="AU30" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="AV30" s="35"/>
-      <c r="AW30" s="35"/>
-      <c r="AX30" s="35"/>
-      <c r="AY30" s="36"/>
-      <c r="AZ30" s="31" t="s">
+      <c r="AV30" s="43"/>
+      <c r="AW30" s="43"/>
+      <c r="AX30" s="43"/>
+      <c r="AY30" s="44"/>
+      <c r="AZ30" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="BA30" s="32"/>
-      <c r="BB30" s="33"/>
-      <c r="BC30" s="31" t="s">
+      <c r="BA30" s="36"/>
+      <c r="BB30" s="41"/>
+      <c r="BC30" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="BD30" s="32"/>
-      <c r="BE30" s="33"/>
-      <c r="BF30" s="31" t="s">
+      <c r="BD30" s="36"/>
+      <c r="BE30" s="41"/>
+      <c r="BF30" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="BG30" s="32"/>
-      <c r="BH30" s="33"/>
-      <c r="BI30" s="34" t="s">
+      <c r="BG30" s="36"/>
+      <c r="BH30" s="41"/>
+      <c r="BI30" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="BJ30" s="35"/>
-      <c r="BK30" s="35"/>
-      <c r="BL30" s="35"/>
-      <c r="BM30" s="36"/>
-      <c r="BN30" s="31" t="s">
+      <c r="BJ30" s="43"/>
+      <c r="BK30" s="43"/>
+      <c r="BL30" s="43"/>
+      <c r="BM30" s="44"/>
+      <c r="BN30" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="BO30" s="32"/>
-      <c r="BP30" s="33"/>
-      <c r="BQ30" s="31" t="s">
+      <c r="BO30" s="36"/>
+      <c r="BP30" s="41"/>
+      <c r="BQ30" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="BR30" s="32"/>
-      <c r="BS30" s="33"/>
-      <c r="BT30" s="31" t="s">
+      <c r="BR30" s="36"/>
+      <c r="BS30" s="41"/>
+      <c r="BT30" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="BU30" s="32"/>
-      <c r="BV30" s="33"/>
-      <c r="BW30" s="31" t="s">
+      <c r="BU30" s="36"/>
+      <c r="BV30" s="41"/>
+      <c r="BW30" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="BX30" s="32"/>
-      <c r="BY30" s="33"/>
-      <c r="BZ30" s="31" t="s">
+      <c r="BX30" s="36"/>
+      <c r="BY30" s="41"/>
+      <c r="BZ30" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="CA30" s="32"/>
-      <c r="CB30" s="33"/>
-      <c r="CC30" s="31" t="s">
+      <c r="CA30" s="36"/>
+      <c r="CB30" s="41"/>
+      <c r="CC30" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="CD30" s="32"/>
-      <c r="CE30" s="33"/>
+      <c r="CD30" s="36"/>
+      <c r="CE30" s="41"/>
     </row>
     <row r="31" spans="1:83" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="32"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
+      <c r="A31" s="36"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
       <c r="F31" s="22" t="s">
         <v>26</v>
       </c>
@@ -11495,16 +11498,16 @@
         <v>7</v>
       </c>
       <c r="B38" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38" s="12" t="str">
-        <v>Kimi Antonelli</v>
+        <v>Sergio Perez</v>
       </c>
       <c r="D38" s="4" t="str">
-        <v>Mercedes</v>
+        <v>Cadillac</v>
       </c>
       <c r="E38" s="2">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="F38" s="21">
         <v>0</v>
@@ -11555,7 +11558,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="28">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="W38" s="23">
         <v>0</v>
@@ -11567,7 +11570,7 @@
         <v>0</v>
       </c>
       <c r="Z38" s="24">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="AA38" s="28">
         <v>0</v>
@@ -11746,13 +11749,13 @@
         <v>8</v>
       </c>
       <c r="B39" s="4">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C39" s="12" t="str">
-        <v>Nico Hulkenberg</v>
+        <v>Kimi Antonelli</v>
       </c>
       <c r="D39" s="4" t="str">
-        <v>Audi</v>
+        <v>Mercedes</v>
       </c>
       <c r="E39" s="2">
         <v>0.96</v>
@@ -11997,13 +12000,13 @@
         <v>9</v>
       </c>
       <c r="B40" s="5">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C40" s="12" t="str">
-        <v>Sergio Perez</v>
+        <v>Nico Hulkenberg</v>
       </c>
       <c r="D40" s="5" t="str">
-        <v>Cadillac</v>
+        <v>Audi</v>
       </c>
       <c r="E40" s="2">
         <v>0.96</v>
@@ -12499,16 +12502,16 @@
         <v>11</v>
       </c>
       <c r="B42" s="6">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C42" s="12" t="str">
-        <v>Isack Hadjar</v>
+        <v>Arvid Lindblad</v>
       </c>
       <c r="D42" s="6" t="str">
-        <v>Red Bull</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E42" s="2">
-        <v>0.89999999999999991</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="F42" s="21">
         <v>0</v>
@@ -12559,7 +12562,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="28">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="W42" s="23">
         <v>0</v>
@@ -12571,7 +12574,7 @@
         <v>0</v>
       </c>
       <c r="Z42" s="24">
-        <v>0.89999999999999991</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="AA42" s="28">
         <v>0</v>
@@ -12750,13 +12753,13 @@
         <v>12</v>
       </c>
       <c r="B43" s="6">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C43" s="12" t="str">
-        <v>Arvid Lindblad</v>
+        <v>Gabriel Bortoleto</v>
       </c>
       <c r="D43" s="6" t="str">
-        <v>Racing Bulls</v>
+        <v>Audi</v>
       </c>
       <c r="E43" s="2">
         <v>0.89999999999999991</v>
@@ -13252,16 +13255,16 @@
         <v>14</v>
       </c>
       <c r="B45" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C45" s="12" t="str">
-        <v>Gabriel Bortoleto</v>
+        <v>Isack Hadjar</v>
       </c>
       <c r="D45" s="7" t="str">
-        <v>Audi</v>
+        <v>Red Bull</v>
       </c>
       <c r="E45" s="2">
-        <v>0.89400000000000002</v>
+        <v>0.87</v>
       </c>
       <c r="F45" s="21">
         <v>0</v>
@@ -13312,7 +13315,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="28">
-        <v>7.45</v>
+        <v>7.25</v>
       </c>
       <c r="W45" s="23">
         <v>0</v>
@@ -13324,7 +13327,7 @@
         <v>0</v>
       </c>
       <c r="Z45" s="24">
-        <v>0.89400000000000002</v>
+        <v>0.87</v>
       </c>
       <c r="AA45" s="28">
         <v>0</v>
@@ -13503,13 +13506,13 @@
         <v>15</v>
       </c>
       <c r="B46" s="8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C46" s="12" t="str">
-        <v>Liam Lawson</v>
+        <v>Esteban Ocon</v>
       </c>
       <c r="D46" s="8" t="str">
-        <v>Racing Bulls</v>
+        <v>Hass</v>
       </c>
       <c r="E46" s="2">
         <v>0.84</v>
@@ -13754,16 +13757,16 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C47" s="12" t="str">
-        <v>Esteban Ocon</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="D47" s="8" t="str">
-        <v>Hass</v>
+        <v>Ferrari</v>
       </c>
       <c r="E47" s="2">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="F47" s="21">
         <v>0</v>
@@ -13814,7 +13817,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W47" s="23">
         <v>0</v>
@@ -13826,7 +13829,7 @@
         <v>0</v>
       </c>
       <c r="Z47" s="24">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="AA47" s="28">
         <v>0</v>
@@ -14005,16 +14008,16 @@
         <v>17</v>
       </c>
       <c r="B48" s="9">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="C48" s="12" t="str">
-        <v>Alexander Albon</v>
+        <v>Oliver Bearman</v>
       </c>
       <c r="D48" s="9" t="str">
-        <v>Williams</v>
+        <v>Hass</v>
       </c>
       <c r="E48" s="2">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="F48" s="21">
         <v>0</v>
@@ -14065,7 +14068,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W48" s="23">
         <v>0</v>
@@ -14077,7 +14080,7 @@
         <v>0</v>
       </c>
       <c r="Z48" s="24">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="AA48" s="28">
         <v>0</v>
@@ -14256,16 +14259,16 @@
         <v>18</v>
       </c>
       <c r="B49" s="9">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="C49" s="12" t="str">
-        <v>Oliver Bearman</v>
+        <v>Lance Stroll</v>
       </c>
       <c r="D49" s="9" t="str">
-        <v>Hass</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E49" s="2">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="F49" s="21">
         <v>0</v>
@@ -14316,7 +14319,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="28">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="W49" s="23">
         <v>0</v>
@@ -14328,7 +14331,7 @@
         <v>0</v>
       </c>
       <c r="Z49" s="24">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="AA49" s="28">
         <v>0</v>
@@ -14507,16 +14510,16 @@
         <v>19</v>
       </c>
       <c r="B50" s="10">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C50" s="12" t="str">
-        <v>Charles Leclerc</v>
+        <v>Pierre Gasly</v>
       </c>
       <c r="D50" s="10" t="str">
-        <v>Ferrari</v>
+        <v>Alpine</v>
       </c>
       <c r="E50" s="2">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
       <c r="F50" s="21">
         <v>0</v>
@@ -14567,7 +14570,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="28">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="W50" s="23">
         <v>0</v>
@@ -14579,7 +14582,7 @@
         <v>0</v>
       </c>
       <c r="Z50" s="24">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
       <c r="AA50" s="28">
         <v>0</v>
@@ -14758,16 +14761,16 @@
         <v>20</v>
       </c>
       <c r="B51" s="10">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="C51" s="12" t="str">
-        <v>Lance Stroll</v>
+        <v>Valtteri Bottas</v>
       </c>
       <c r="D51" s="10" t="str">
-        <v>Aston Martin</v>
+        <v>Cadillac</v>
       </c>
       <c r="E51" s="2">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="F51" s="21">
         <v>0</v>
@@ -14818,7 +14821,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="28">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="W51" s="23">
         <v>0</v>
@@ -14830,7 +14833,7 @@
         <v>0</v>
       </c>
       <c r="Z51" s="24">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="AA51" s="28">
         <v>0</v>
@@ -15009,16 +15012,16 @@
         <v>21</v>
       </c>
       <c r="B52" s="11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C52" s="12" t="str">
-        <v>Pierre Gasly</v>
+        <v>Liam Lawson</v>
       </c>
       <c r="D52" s="11" t="str">
-        <v>Alpine</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E52" s="2">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="F52" s="21">
         <v>0</v>
@@ -15068,8 +15071,8 @@
       <c r="U52" s="24">
         <v>0</v>
       </c>
-      <c r="V52" s="28">
-        <v>3.5</v>
+      <c r="V52" s="28" t="str">
+        <v>-</v>
       </c>
       <c r="W52" s="23">
         <v>0</v>
@@ -15081,7 +15084,7 @@
         <v>0</v>
       </c>
       <c r="Z52" s="24">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="28">
         <v>0</v>
@@ -15260,16 +15263,16 @@
         <v>22</v>
       </c>
       <c r="B53" s="11">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="C53" s="12" t="str">
-        <v>Valtteri Bottas</v>
+        <v>Alexander Albon</v>
       </c>
       <c r="D53" s="11" t="str">
-        <v>Cadillac</v>
+        <v>Williams</v>
       </c>
       <c r="E53" s="2">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="F53" s="21">
         <v>0</v>
@@ -15319,8 +15322,8 @@
       <c r="U53" s="24">
         <v>0</v>
       </c>
-      <c r="V53" s="28">
-        <v>1</v>
+      <c r="V53" s="28" t="str">
+        <v>-</v>
       </c>
       <c r="W53" s="23">
         <v>0</v>
@@ -15332,7 +15335,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="24">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="AA53" s="28">
         <v>0</v>
@@ -15532,33 +15535,62 @@
     </row>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="Q4:U4"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:U29"/>
-    <mergeCell ref="V29:Z29"/>
-    <mergeCell ref="V4:Z4"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AN3"/>
-    <mergeCell ref="AO3:AQ3"/>
-    <mergeCell ref="AR3:AT3"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AG4:AI4"/>
-    <mergeCell ref="AJ4:AN4"/>
-    <mergeCell ref="AO4:AQ4"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="BW30:BY30"/>
+    <mergeCell ref="BZ30:CB30"/>
+    <mergeCell ref="Q30:U30"/>
+    <mergeCell ref="V30:Z30"/>
+    <mergeCell ref="AA30:AC30"/>
+    <mergeCell ref="AD30:AF30"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AJ30:AN30"/>
+    <mergeCell ref="AO30:AQ30"/>
+    <mergeCell ref="AR30:AT30"/>
+    <mergeCell ref="AU30:AY30"/>
+    <mergeCell ref="CC30:CE30"/>
+    <mergeCell ref="AZ30:BB30"/>
+    <mergeCell ref="BC30:BE30"/>
+    <mergeCell ref="BF30:BH30"/>
+    <mergeCell ref="BI30:BM30"/>
+    <mergeCell ref="BN30:BP30"/>
+    <mergeCell ref="BQ30:BS30"/>
+    <mergeCell ref="BT30:BV30"/>
+    <mergeCell ref="BW29:BY29"/>
+    <mergeCell ref="BZ29:CB29"/>
+    <mergeCell ref="CC29:CE29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="AU29:AY29"/>
+    <mergeCell ref="AZ29:BB29"/>
+    <mergeCell ref="BC29:BE29"/>
+    <mergeCell ref="BF29:BH29"/>
+    <mergeCell ref="BI29:BM29"/>
+    <mergeCell ref="BN29:BP29"/>
+    <mergeCell ref="AA29:AC29"/>
+    <mergeCell ref="AD29:AF29"/>
+    <mergeCell ref="BQ29:BS29"/>
+    <mergeCell ref="BT29:BV29"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AN29"/>
+    <mergeCell ref="AO29:AQ29"/>
+    <mergeCell ref="AR29:AT29"/>
+    <mergeCell ref="CC4:CE4"/>
+    <mergeCell ref="AR4:AT4"/>
+    <mergeCell ref="AU4:AY4"/>
+    <mergeCell ref="AZ4:BB4"/>
+    <mergeCell ref="BC4:BE4"/>
+    <mergeCell ref="BF4:BH4"/>
+    <mergeCell ref="BI4:BM4"/>
+    <mergeCell ref="BN4:BP4"/>
+    <mergeCell ref="BQ4:BS4"/>
+    <mergeCell ref="BT4:BV4"/>
+    <mergeCell ref="BW4:BY4"/>
+    <mergeCell ref="BZ4:CB4"/>
     <mergeCell ref="BW3:BY3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="CC3:CE3"/>
@@ -15575,62 +15607,33 @@
     <mergeCell ref="BI3:BM3"/>
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BQ3:BS3"/>
-    <mergeCell ref="CC4:CE4"/>
-    <mergeCell ref="AR4:AT4"/>
-    <mergeCell ref="AU4:AY4"/>
-    <mergeCell ref="AZ4:BB4"/>
-    <mergeCell ref="BC4:BE4"/>
-    <mergeCell ref="BF4:BH4"/>
-    <mergeCell ref="BI4:BM4"/>
-    <mergeCell ref="BN4:BP4"/>
-    <mergeCell ref="BQ4:BS4"/>
-    <mergeCell ref="BT4:BV4"/>
-    <mergeCell ref="BW4:BY4"/>
-    <mergeCell ref="BZ4:CB4"/>
-    <mergeCell ref="BQ29:BS29"/>
-    <mergeCell ref="BT29:BV29"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AN29"/>
-    <mergeCell ref="AO29:AQ29"/>
-    <mergeCell ref="AR29:AT29"/>
-    <mergeCell ref="BW29:BY29"/>
-    <mergeCell ref="BZ29:CB29"/>
-    <mergeCell ref="CC29:CE29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="AU29:AY29"/>
-    <mergeCell ref="AZ29:BB29"/>
-    <mergeCell ref="BC29:BE29"/>
-    <mergeCell ref="BF29:BH29"/>
-    <mergeCell ref="BI29:BM29"/>
-    <mergeCell ref="BN29:BP29"/>
-    <mergeCell ref="AA29:AC29"/>
-    <mergeCell ref="AD29:AF29"/>
-    <mergeCell ref="CC30:CE30"/>
-    <mergeCell ref="AZ30:BB30"/>
-    <mergeCell ref="BC30:BE30"/>
-    <mergeCell ref="BF30:BH30"/>
-    <mergeCell ref="BI30:BM30"/>
-    <mergeCell ref="BN30:BP30"/>
-    <mergeCell ref="BQ30:BS30"/>
-    <mergeCell ref="BT30:BV30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="BW30:BY30"/>
-    <mergeCell ref="BZ30:CB30"/>
-    <mergeCell ref="Q30:U30"/>
-    <mergeCell ref="V30:Z30"/>
-    <mergeCell ref="AA30:AC30"/>
-    <mergeCell ref="AD30:AF30"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AJ30:AN30"/>
-    <mergeCell ref="AO30:AQ30"/>
-    <mergeCell ref="AR30:AT30"/>
-    <mergeCell ref="AU30:AY30"/>
+    <mergeCell ref="V4:Z4"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AN3"/>
+    <mergeCell ref="AO3:AQ3"/>
+    <mergeCell ref="AR3:AT3"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AG4:AI4"/>
+    <mergeCell ref="AJ4:AN4"/>
+    <mergeCell ref="AO4:AQ4"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:U29"/>
+    <mergeCell ref="V29:Z29"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="Q4:U4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B27 D6:D27 B32:B53 D32:D53">
     <cfRule type="expression" dxfId="65" priority="329">
@@ -15962,7 +15965,7 @@
       </c>
       <c r="N5" s="29">
         <f>Simplified!G8</f>
-        <v>3.0000000000000027E-2</v>
+        <v>5.9999999999999942E-2</v>
       </c>
       <c r="O5" s="4">
         <v>6</v>
@@ -16047,7 +16050,7 @@
       </c>
       <c r="N7" s="29">
         <f>Simplified!G12</f>
-        <v>-5.9999999999999942E-2</v>
+        <v>-0.92999999999999994</v>
       </c>
       <c r="O7" s="6">
         <v>41</v>
@@ -16058,20 +16061,20 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="12" t="str">
-        <v>Kimi Antonelli</v>
+        <v>Sergio Perez</v>
       </c>
       <c r="D8" s="4" t="str">
-        <v>Mercedes</v>
+        <v>Cadillac</v>
       </c>
       <c r="E8" s="2">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="G8" s="45">
         <f>K8-K9</f>
-        <v>3.0000000000000027E-2</v>
+        <v>5.9999999999999942E-2</v>
       </c>
       <c r="H8" s="4">
         <v>3</v>
@@ -16091,7 +16094,7 @@
       </c>
       <c r="N8" s="29">
         <f>Simplified!G14</f>
-        <v>5.9999999999999942E-2</v>
+        <v>0.12</v>
       </c>
       <c r="O8" s="7">
         <v>87</v>
@@ -16102,13 +16105,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C9" s="12" t="str">
-        <v>Nico Hulkenberg</v>
+        <v>Kimi Antonelli</v>
       </c>
       <c r="D9" s="4" t="str">
-        <v>Audi</v>
+        <v>Mercedes</v>
       </c>
       <c r="E9" s="2">
         <v>0.96</v>
@@ -16125,14 +16128,14 @@
       </c>
       <c r="K9" s="2">
         <f>Ratings!E13</f>
-        <v>0.89999999999999991</v>
+        <v>0.87</v>
       </c>
       <c r="M9" s="8">
         <v>55</v>
       </c>
       <c r="N9" s="29">
         <f>Simplified!G16</f>
-        <v>0.18000000000000005</v>
+        <v>1.02</v>
       </c>
       <c r="O9" s="8">
         <v>23</v>
@@ -16143,13 +16146,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C10" s="12" t="str">
-        <v>Sergio Perez</v>
+        <v>Nico Hulkenberg</v>
       </c>
       <c r="D10" s="5" t="str">
-        <v>Cadillac</v>
+        <v>Audi</v>
       </c>
       <c r="E10" s="2">
         <v>0.96</v>
@@ -16176,7 +16179,7 @@
       </c>
       <c r="N10" s="29">
         <f>Simplified!G18</f>
-        <v>6.5999999999999948E-2</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="O10" s="9">
         <v>5</v>
@@ -16217,7 +16220,7 @@
       </c>
       <c r="N11" s="29">
         <f>Simplified!G20</f>
-        <v>0.84</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="O11" s="10">
         <v>77</v>
@@ -16228,20 +16231,20 @@
         <v>11</v>
       </c>
       <c r="B12" s="6">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C12" s="12" t="str">
-        <v>Isack Hadjar</v>
+        <v>Arvid Lindblad</v>
       </c>
       <c r="D12" s="6" t="str">
-        <v>Red Bull</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E12" s="2">
-        <v>0.89999999999999991</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="G12" s="45">
         <f>K12-K13</f>
-        <v>-5.9999999999999942E-2</v>
+        <v>-0.92999999999999994</v>
       </c>
       <c r="H12" s="6">
         <v>30</v>
@@ -16254,7 +16257,7 @@
       </c>
       <c r="K12" s="2">
         <f>Ratings!E16</f>
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="M12" s="11">
         <v>14</v>
@@ -16272,13 +16275,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="6">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C13" s="12" t="str">
-        <v>Arvid Lindblad</v>
+        <v>Gabriel Bortoleto</v>
       </c>
       <c r="D13" s="6" t="str">
-        <v>Racing Bulls</v>
+        <v>Audi</v>
       </c>
       <c r="E13" s="2">
         <v>0.89999999999999991</v>
@@ -16295,7 +16298,7 @@
       </c>
       <c r="K13" s="2">
         <f>Ratings!E17</f>
-        <v>0.89999999999999991</v>
+        <v>0.92999999999999994</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
@@ -16316,7 +16319,7 @@
       </c>
       <c r="G14" s="45">
         <f>K14-K15</f>
-        <v>5.9999999999999942E-2</v>
+        <v>0.12</v>
       </c>
       <c r="H14" s="7">
         <v>31</v>
@@ -16337,16 +16340,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="12" t="str">
-        <v>Gabriel Bortoleto</v>
+        <v>Isack Hadjar</v>
       </c>
       <c r="D15" s="7" t="str">
-        <v>Audi</v>
+        <v>Red Bull</v>
       </c>
       <c r="E15" s="2">
-        <v>0.89400000000000002</v>
+        <v>0.87</v>
       </c>
       <c r="G15" s="45"/>
       <c r="H15" s="7">
@@ -16360,7 +16363,7 @@
       </c>
       <c r="K15" s="2">
         <f>Ratings!E19</f>
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
@@ -16368,20 +16371,20 @@
         <v>15</v>
       </c>
       <c r="B16" s="8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C16" s="12" t="str">
-        <v>Liam Lawson</v>
+        <v>Esteban Ocon</v>
       </c>
       <c r="D16" s="8" t="str">
-        <v>Racing Bulls</v>
+        <v>Hass</v>
       </c>
       <c r="E16" s="2">
         <v>0.84</v>
       </c>
       <c r="G16" s="45">
         <f>K16-K17</f>
-        <v>0.18000000000000005</v>
+        <v>1.02</v>
       </c>
       <c r="H16" s="8">
         <v>55</v>
@@ -16402,16 +16405,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="8">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C17" s="12" t="str">
-        <v>Esteban Ocon</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="D17" s="8" t="str">
-        <v>Hass</v>
+        <v>Ferrari</v>
       </c>
       <c r="E17" s="2">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="G17" s="45"/>
       <c r="H17" s="8">
@@ -16425,7 +16428,7 @@
       </c>
       <c r="K17" s="2">
         <f>Ratings!E21</f>
-        <v>0.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -16433,20 +16436,20 @@
         <v>17</v>
       </c>
       <c r="B18" s="9">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="C18" s="12" t="str">
-        <v>Alexander Albon</v>
+        <v>Oliver Bearman</v>
       </c>
       <c r="D18" s="9" t="str">
-        <v>Williams</v>
+        <v>Hass</v>
       </c>
       <c r="E18" s="2">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="G18" s="45">
         <f>K18-K19</f>
-        <v>6.5999999999999948E-2</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="H18" s="9">
         <v>27</v>
@@ -16467,16 +16470,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="9">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="C19" s="12" t="str">
-        <v>Oliver Bearman</v>
+        <v>Lance Stroll</v>
       </c>
       <c r="D19" s="9" t="str">
-        <v>Hass</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E19" s="2">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="G19" s="45"/>
       <c r="H19" s="9">
@@ -16490,7 +16493,7 @@
       </c>
       <c r="K19" s="2">
         <f>Ratings!E23</f>
-        <v>0.89400000000000002</v>
+        <v>0.89999999999999991</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -16498,20 +16501,20 @@
         <v>19</v>
       </c>
       <c r="B20" s="10">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C20" s="12" t="str">
-        <v>Charles Leclerc</v>
+        <v>Pierre Gasly</v>
       </c>
       <c r="D20" s="10" t="str">
-        <v>Ferrari</v>
+        <v>Alpine</v>
       </c>
       <c r="E20" s="2">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
       <c r="G20" s="45">
         <f>K20-K21</f>
-        <v>0.84</v>
+        <v>0.92999999999999994</v>
       </c>
       <c r="H20" s="10">
         <v>11</v>
@@ -16524,7 +16527,7 @@
       </c>
       <c r="K20" s="2">
         <f>Ratings!E24</f>
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -16532,16 +16535,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="10">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="C21" s="12" t="str">
-        <v>Lance Stroll</v>
+        <v>Valtteri Bottas</v>
       </c>
       <c r="D21" s="10" t="str">
-        <v>Aston Martin</v>
+        <v>Cadillac</v>
       </c>
       <c r="E21" s="2">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="G21" s="45"/>
       <c r="H21" s="10">
@@ -16555,7 +16558,7 @@
       </c>
       <c r="K21" s="2">
         <f>Ratings!E25</f>
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -16563,16 +16566,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C22" s="12" t="str">
-        <v>Pierre Gasly</v>
+        <v>Liam Lawson</v>
       </c>
       <c r="D22" s="11" t="str">
-        <v>Alpine</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E22" s="2">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="G22" s="45">
         <f>K22-K23</f>
@@ -16597,16 +16600,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="11">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="C23" s="12" t="str">
-        <v>Valtteri Bottas</v>
+        <v>Alexander Albon</v>
       </c>
       <c r="D23" s="11" t="str">
-        <v>Cadillac</v>
+        <v>Williams</v>
       </c>
       <c r="E23" s="2">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="G23" s="45"/>
       <c r="H23" s="11">
@@ -16684,7 +16687,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4 G2 G6 G8 G10 G12 G14 G16 G18 G20 G22">
+  <conditionalFormatting sqref="G2 G4 G6 G8 G10 G12 G14 G16 G18 G20 G22">
     <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="percentile" val="0"/>

--- a/static/data/Ratings.xlsx
+++ b/static/data/Ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Programming\webdev\portfolio\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D73CB6-7B40-4AF3-9ED5-CED2D673A13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5723FFCB-36F9-4BDA-B804-36ED04A77BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="2" xr2:uid="{BD88BCC4-2E11-4C36-830D-A75A044EF5A6}"/>
   </bookViews>
@@ -259,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="73">
   <si>
     <t>RANK</t>
   </si>
@@ -910,10 +910,37 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -928,741 +955,14 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="155">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF26F0CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF21976F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF26F0CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF21976F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF26F0CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF21976F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF26F0CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF21976F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF26F0CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF21976F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF26F0CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF21976F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF26F0CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF21976F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="70">
     <dxf>
       <fill>
         <patternFill>
@@ -2045,6 +1345,111 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFD7F00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDBDFE0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF638FFD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF009FE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF366FC3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFD7F00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE4002C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF26F0CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF21976F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA8A8AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFA2B00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF1767D8"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3348,13 +2753,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:83" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
       <c r="F1" s="17"/>
       <c r="G1" s="17"/>
       <c r="H1" s="17"/>
@@ -3435,11 +2840,11 @@
       <c r="CE1" s="17"/>
     </row>
     <row r="2" spans="1:83" s="14" customFormat="1" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="44"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
@@ -3525,296 +2930,296 @@
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
-      <c r="F3" s="40" t="e" vm="1">
+      <c r="F3" s="38" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G3" s="41"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="38" t="e" vm="2">
+      <c r="G3" s="39"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="35" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="40" t="e" vm="3">
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="38" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="41"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="37" t="e" vm="4">
+      <c r="O3" s="39"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="34" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="37" t="e" vm="5">
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="34" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W3" s="38"/>
-      <c r="X3" s="38"/>
-      <c r="Y3" s="38"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="40" t="e" vm="6">
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="35"/>
+      <c r="Z3" s="36"/>
+      <c r="AA3" s="38" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="42"/>
-      <c r="AD3" s="40" t="e" vm="7">
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="40"/>
+      <c r="AD3" s="38" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="42"/>
-      <c r="AG3" s="40" t="e" vm="8">
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="40"/>
+      <c r="AG3" s="38" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="42"/>
-      <c r="AJ3" s="37" t="e" vm="9">
+      <c r="AH3" s="39"/>
+      <c r="AI3" s="40"/>
+      <c r="AJ3" s="34" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK3" s="38"/>
-      <c r="AL3" s="38"/>
-      <c r="AM3" s="38"/>
-      <c r="AN3" s="39"/>
-      <c r="AO3" s="40" t="e" vm="10">
+      <c r="AK3" s="35"/>
+      <c r="AL3" s="35"/>
+      <c r="AM3" s="35"/>
+      <c r="AN3" s="36"/>
+      <c r="AO3" s="38" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP3" s="41"/>
-      <c r="AQ3" s="42"/>
-      <c r="AR3" s="40" t="e" vm="11">
+      <c r="AP3" s="39"/>
+      <c r="AQ3" s="40"/>
+      <c r="AR3" s="38" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS3" s="41"/>
-      <c r="AT3" s="42"/>
-      <c r="AU3" s="37" t="e" vm="12">
+      <c r="AS3" s="39"/>
+      <c r="AT3" s="40"/>
+      <c r="AU3" s="34" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV3" s="38"/>
-      <c r="AW3" s="38"/>
-      <c r="AX3" s="38"/>
-      <c r="AY3" s="39"/>
-      <c r="AZ3" s="40" t="e" vm="13">
+      <c r="AV3" s="35"/>
+      <c r="AW3" s="35"/>
+      <c r="AX3" s="35"/>
+      <c r="AY3" s="36"/>
+      <c r="AZ3" s="38" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA3" s="41"/>
-      <c r="BB3" s="42"/>
-      <c r="BC3" s="40" t="e" vm="7">
+      <c r="BA3" s="39"/>
+      <c r="BB3" s="40"/>
+      <c r="BC3" s="38" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD3" s="41"/>
-      <c r="BE3" s="42"/>
-      <c r="BF3" s="40" t="e" vm="14">
+      <c r="BD3" s="39"/>
+      <c r="BE3" s="40"/>
+      <c r="BF3" s="38" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG3" s="41"/>
-      <c r="BH3" s="42"/>
-      <c r="BI3" s="37" t="e" vm="15">
+      <c r="BG3" s="39"/>
+      <c r="BH3" s="40"/>
+      <c r="BI3" s="34" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ3" s="38"/>
-      <c r="BK3" s="38"/>
-      <c r="BL3" s="38"/>
-      <c r="BM3" s="39"/>
-      <c r="BN3" s="40" t="e" vm="4">
+      <c r="BJ3" s="35"/>
+      <c r="BK3" s="35"/>
+      <c r="BL3" s="35"/>
+      <c r="BM3" s="36"/>
+      <c r="BN3" s="38" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO3" s="41"/>
-      <c r="BP3" s="42"/>
-      <c r="BQ3" s="40" t="e" vm="16">
+      <c r="BO3" s="39"/>
+      <c r="BP3" s="40"/>
+      <c r="BQ3" s="38" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR3" s="41"/>
-      <c r="BS3" s="42"/>
-      <c r="BT3" s="40" t="e" vm="17">
+      <c r="BR3" s="39"/>
+      <c r="BS3" s="40"/>
+      <c r="BT3" s="38" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU3" s="41"/>
-      <c r="BV3" s="42"/>
-      <c r="BW3" s="40" t="e" vm="4">
+      <c r="BU3" s="39"/>
+      <c r="BV3" s="40"/>
+      <c r="BW3" s="38" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX3" s="41"/>
-      <c r="BY3" s="42"/>
-      <c r="BZ3" s="40" t="e" vm="18">
+      <c r="BX3" s="39"/>
+      <c r="BY3" s="40"/>
+      <c r="BZ3" s="38" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA3" s="41"/>
-      <c r="CB3" s="42"/>
-      <c r="CC3" s="40" t="e" vm="19">
+      <c r="CA3" s="39"/>
+      <c r="CB3" s="40"/>
+      <c r="CC3" s="38" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD3" s="41"/>
-      <c r="CE3" s="42"/>
+      <c r="CD3" s="39"/>
+      <c r="CE3" s="40"/>
     </row>
     <row r="4" spans="1:83" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="32" t="s">
+      <c r="G4" s="37"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="31" t="s">
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+      <c r="L4" s="37"/>
+      <c r="M4" s="37"/>
+      <c r="N4" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="32"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="34" t="s">
+      <c r="O4" s="37"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="35"/>
-      <c r="U4" s="36"/>
-      <c r="V4" s="34" t="s">
+      <c r="R4" s="44"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="44"/>
+      <c r="U4" s="45"/>
+      <c r="V4" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="W4" s="35"/>
-      <c r="X4" s="35"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="31" t="s">
+      <c r="W4" s="44"/>
+      <c r="X4" s="44"/>
+      <c r="Y4" s="44"/>
+      <c r="Z4" s="45"/>
+      <c r="AA4" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="33"/>
-      <c r="AD4" s="31" t="s">
+      <c r="AB4" s="37"/>
+      <c r="AC4" s="42"/>
+      <c r="AD4" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="AE4" s="32"/>
-      <c r="AF4" s="33"/>
-      <c r="AG4" s="31" t="s">
+      <c r="AE4" s="37"/>
+      <c r="AF4" s="42"/>
+      <c r="AG4" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="AH4" s="32"/>
-      <c r="AI4" s="33"/>
-      <c r="AJ4" s="34" t="s">
+      <c r="AH4" s="37"/>
+      <c r="AI4" s="42"/>
+      <c r="AJ4" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="AK4" s="35"/>
-      <c r="AL4" s="35"/>
-      <c r="AM4" s="35"/>
-      <c r="AN4" s="36"/>
-      <c r="AO4" s="31" t="s">
+      <c r="AK4" s="44"/>
+      <c r="AL4" s="44"/>
+      <c r="AM4" s="44"/>
+      <c r="AN4" s="45"/>
+      <c r="AO4" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="AP4" s="32"/>
-      <c r="AQ4" s="33"/>
-      <c r="AR4" s="31" t="s">
+      <c r="AP4" s="37"/>
+      <c r="AQ4" s="42"/>
+      <c r="AR4" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="AS4" s="32"/>
-      <c r="AT4" s="33"/>
-      <c r="AU4" s="34" t="s">
+      <c r="AS4" s="37"/>
+      <c r="AT4" s="42"/>
+      <c r="AU4" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="AV4" s="35"/>
-      <c r="AW4" s="35"/>
-      <c r="AX4" s="35"/>
-      <c r="AY4" s="36"/>
-      <c r="AZ4" s="31" t="s">
+      <c r="AV4" s="44"/>
+      <c r="AW4" s="44"/>
+      <c r="AX4" s="44"/>
+      <c r="AY4" s="45"/>
+      <c r="AZ4" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="BA4" s="32"/>
-      <c r="BB4" s="33"/>
-      <c r="BC4" s="31" t="s">
+      <c r="BA4" s="37"/>
+      <c r="BB4" s="42"/>
+      <c r="BC4" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="BD4" s="32"/>
-      <c r="BE4" s="33"/>
-      <c r="BF4" s="31" t="s">
+      <c r="BD4" s="37"/>
+      <c r="BE4" s="42"/>
+      <c r="BF4" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="BG4" s="32"/>
-      <c r="BH4" s="33"/>
-      <c r="BI4" s="34" t="s">
+      <c r="BG4" s="37"/>
+      <c r="BH4" s="42"/>
+      <c r="BI4" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="BJ4" s="35"/>
-      <c r="BK4" s="35"/>
-      <c r="BL4" s="35"/>
-      <c r="BM4" s="36"/>
-      <c r="BN4" s="31" t="s">
+      <c r="BJ4" s="44"/>
+      <c r="BK4" s="44"/>
+      <c r="BL4" s="44"/>
+      <c r="BM4" s="45"/>
+      <c r="BN4" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="BO4" s="32"/>
-      <c r="BP4" s="33"/>
-      <c r="BQ4" s="31" t="s">
+      <c r="BO4" s="37"/>
+      <c r="BP4" s="42"/>
+      <c r="BQ4" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="BR4" s="32"/>
-      <c r="BS4" s="33"/>
-      <c r="BT4" s="31" t="s">
+      <c r="BR4" s="37"/>
+      <c r="BS4" s="42"/>
+      <c r="BT4" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="BU4" s="32"/>
-      <c r="BV4" s="33"/>
-      <c r="BW4" s="31" t="s">
+      <c r="BU4" s="37"/>
+      <c r="BV4" s="42"/>
+      <c r="BW4" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="BX4" s="32"/>
-      <c r="BY4" s="33"/>
-      <c r="BZ4" s="31" t="s">
+      <c r="BX4" s="37"/>
+      <c r="BY4" s="42"/>
+      <c r="BZ4" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="CA4" s="32"/>
-      <c r="CB4" s="33"/>
-      <c r="CC4" s="31" t="s">
+      <c r="CA4" s="37"/>
+      <c r="CB4" s="42"/>
+      <c r="CC4" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="CD4" s="32"/>
-      <c r="CE4" s="33"/>
+      <c r="CD4" s="37"/>
+      <c r="CE4" s="42"/>
     </row>
     <row r="5" spans="1:83" s="16" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
       <c r="F5" s="22" t="s">
         <v>26</v>
       </c>
@@ -4063,9 +3468,9 @@
       <c r="D6" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="46">
+      <c r="E6" s="31">
         <f>IFERROR(AVERAGE(H6,M6,P6,U6,Z6,AC6,AF6,AI6,AN6,AQ6,AT6,AY6,BB6,BE6,BH6,BM6,BP6,BS6,BV6,BY6,CB6,CE6),-1)</f>
-        <v>2.04</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>72</v>
@@ -4122,8 +3527,8 @@
       <c r="V6" s="28">
         <v>8.5</v>
       </c>
-      <c r="W6" s="21" t="s">
-        <v>72</v>
+      <c r="W6" s="21">
+        <v>8.75</v>
       </c>
       <c r="X6" s="21" t="s">
         <v>72</v>
@@ -4133,7 +3538,7 @@
       </c>
       <c r="Z6" s="24">
         <f>IF(AND(V6="-", W6="-", X6="-", Y6="-"), "-", (IFERROR(AVERAGE(V6:W6), 0)*0.24) + (IFERROR(AVERAGE(X6:Y6), 0)*0.76))</f>
-        <v>2.04</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AA6" s="21" t="s">
         <v>72</v>
@@ -4337,9 +3742,9 @@
       <c r="D7" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="31">
         <f t="shared" ref="E7:E27" si="0">IFERROR(AVERAGE(H7,M7,P7,U7,Z7,AC7,AF7,AI7,AN7,AQ7,AT7,AY7,BB7,BE7,BH7,BM7,BP7,BS7,BV7,BY7,CB7,CE7),-1)</f>
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>72</v>
@@ -4396,8 +3801,8 @@
       <c r="V7" s="28">
         <v>8</v>
       </c>
-      <c r="W7" s="21" t="s">
-        <v>72</v>
+      <c r="W7" s="21">
+        <v>5.75</v>
       </c>
       <c r="X7" s="21" t="s">
         <v>72</v>
@@ -4407,7 +3812,7 @@
       </c>
       <c r="Z7" s="24">
         <f t="shared" ref="Z7:Z27" si="5">IF(AND(V7="-", W7="-", X7="-", Y7="-"), "-", (IFERROR(AVERAGE(V7:W7), 0)*0.24) + (IFERROR(AVERAGE(X7:Y7), 0)*0.76))</f>
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AA7" s="21" t="s">
         <v>72</v>
@@ -4611,9 +4016,9 @@
       <c r="D8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="46">
+      <c r="E8" s="31">
         <f t="shared" si="0"/>
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>72</v>
@@ -4670,8 +4075,8 @@
       <c r="V8" s="28">
         <v>8.75</v>
       </c>
-      <c r="W8" s="21" t="s">
-        <v>72</v>
+      <c r="W8" s="21">
+        <v>9.25</v>
       </c>
       <c r="X8" s="21" t="s">
         <v>72</v>
@@ -4681,7 +4086,7 @@
       </c>
       <c r="Z8" s="24">
         <f t="shared" si="5"/>
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AA8" s="21" t="s">
         <v>72</v>
@@ -4885,9 +4290,9 @@
       <c r="D9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="31">
         <f t="shared" si="0"/>
-        <v>2.04</v>
+        <v>1.8299999999999998</v>
       </c>
       <c r="F9" s="21" t="s">
         <v>72</v>
@@ -4944,8 +4349,8 @@
       <c r="V9" s="28">
         <v>8.5</v>
       </c>
-      <c r="W9" s="21" t="s">
-        <v>72</v>
+      <c r="W9" s="21">
+        <v>6.75</v>
       </c>
       <c r="X9" s="21" t="s">
         <v>72</v>
@@ -4955,7 +4360,7 @@
       </c>
       <c r="Z9" s="24">
         <f t="shared" si="5"/>
-        <v>2.04</v>
+        <v>1.8299999999999998</v>
       </c>
       <c r="AA9" s="21" t="s">
         <v>72</v>
@@ -5159,9 +4564,9 @@
       <c r="D10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="31">
         <f t="shared" si="0"/>
-        <v>1.44</v>
+        <v>1.512</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>72</v>
@@ -5218,8 +4623,8 @@
       <c r="V10" s="28">
         <v>6</v>
       </c>
-      <c r="W10" s="21" t="s">
-        <v>72</v>
+      <c r="W10" s="21">
+        <v>6.6</v>
       </c>
       <c r="X10" s="21" t="s">
         <v>72</v>
@@ -5229,7 +4634,7 @@
       </c>
       <c r="Z10" s="24">
         <f t="shared" si="5"/>
-        <v>1.44</v>
+        <v>1.512</v>
       </c>
       <c r="AA10" s="21" t="s">
         <v>72</v>
@@ -5433,9 +4838,9 @@
       <c r="D11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="31">
         <f t="shared" si="0"/>
-        <v>1.98</v>
+        <v>1.8599999999999999</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>72</v>
@@ -5492,8 +4897,8 @@
       <c r="V11" s="28">
         <v>8.25</v>
       </c>
-      <c r="W11" s="21" t="s">
-        <v>72</v>
+      <c r="W11" s="21">
+        <v>7.25</v>
       </c>
       <c r="X11" s="21" t="s">
         <v>72</v>
@@ -5503,7 +4908,7 @@
       </c>
       <c r="Z11" s="24">
         <f t="shared" si="5"/>
-        <v>1.98</v>
+        <v>1.8599999999999999</v>
       </c>
       <c r="AA11" s="21" t="s">
         <v>72</v>
@@ -5707,9 +5112,9 @@
       <c r="D12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="31">
         <f t="shared" si="0"/>
-        <v>1.8599999999999999</v>
+        <v>1.89</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>72</v>
@@ -5766,8 +5171,8 @@
       <c r="V12" s="28">
         <v>7.75</v>
       </c>
-      <c r="W12" s="21" t="s">
-        <v>72</v>
+      <c r="W12" s="21">
+        <v>8</v>
       </c>
       <c r="X12" s="21" t="s">
         <v>72</v>
@@ -5777,7 +5182,7 @@
       </c>
       <c r="Z12" s="24">
         <f t="shared" si="5"/>
-        <v>1.8599999999999999</v>
+        <v>1.89</v>
       </c>
       <c r="AA12" s="21" t="s">
         <v>72</v>
@@ -5981,9 +5386,9 @@
       <c r="D13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="46">
+      <c r="E13" s="31">
         <f t="shared" si="0"/>
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="F13" s="21" t="s">
         <v>72</v>
@@ -6040,8 +5445,8 @@
       <c r="V13" s="28">
         <v>7.25</v>
       </c>
-      <c r="W13" s="21" t="s">
-        <v>72</v>
+      <c r="W13" s="21">
+        <v>7</v>
       </c>
       <c r="X13" s="21" t="s">
         <v>72</v>
@@ -6051,7 +5456,7 @@
       </c>
       <c r="Z13" s="24">
         <f t="shared" si="5"/>
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AA13" s="21" t="s">
         <v>72</v>
@@ -6255,9 +5660,9 @@
       <c r="D14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="31">
         <f t="shared" si="0"/>
-        <v>0.84</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>72</v>
@@ -6314,8 +5719,8 @@
       <c r="V14" s="28">
         <v>3.5</v>
       </c>
-      <c r="W14" s="21" t="s">
-        <v>72</v>
+      <c r="W14" s="21">
+        <v>6</v>
       </c>
       <c r="X14" s="21" t="s">
         <v>72</v>
@@ -6325,7 +5730,7 @@
       </c>
       <c r="Z14" s="24">
         <f t="shared" si="5"/>
-        <v>0.84</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="AA14" s="21" t="s">
         <v>72</v>
@@ -6529,9 +5934,9 @@
       <c r="D15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="46">
+      <c r="E15" s="31">
         <f t="shared" si="0"/>
-        <v>2.1</v>
+        <v>2.1120000000000001</v>
       </c>
       <c r="F15" s="21" t="s">
         <v>72</v>
@@ -6586,10 +5991,10 @@
         <v>-</v>
       </c>
       <c r="V15" s="28">
-        <v>8.75</v>
-      </c>
-      <c r="W15" s="21" t="s">
-        <v>72</v>
+        <v>8.5</v>
+      </c>
+      <c r="W15" s="21">
+        <v>9.1</v>
       </c>
       <c r="X15" s="21" t="s">
         <v>72</v>
@@ -6599,7 +6004,7 @@
       </c>
       <c r="Z15" s="24">
         <f t="shared" si="5"/>
-        <v>2.1</v>
+        <v>2.1120000000000001</v>
       </c>
       <c r="AA15" s="21" t="s">
         <v>72</v>
@@ -6803,9 +6208,9 @@
       <c r="D16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="46">
+      <c r="E16" s="31">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>2.04</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>72</v>
@@ -6862,8 +6267,8 @@
       <c r="V16" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="W16" s="21" t="s">
-        <v>72</v>
+      <c r="W16" s="21">
+        <v>8.5</v>
       </c>
       <c r="X16" s="21" t="s">
         <v>72</v>
@@ -6871,9 +6276,9 @@
       <c r="Y16" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="Z16" s="24" t="str">
+      <c r="Z16" s="24">
         <f t="shared" si="5"/>
-        <v>-</v>
+        <v>2.04</v>
       </c>
       <c r="AA16" s="21" t="s">
         <v>72</v>
@@ -7077,9 +6482,9 @@
       <c r="D17" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="46">
+      <c r="E17" s="31">
         <f t="shared" si="0"/>
-        <v>1.8599999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="F17" s="21" t="s">
         <v>72</v>
@@ -7136,8 +6541,8 @@
       <c r="V17" s="28">
         <v>7.75</v>
       </c>
-      <c r="W17" s="21" t="s">
-        <v>72</v>
+      <c r="W17" s="21">
+        <v>8.5</v>
       </c>
       <c r="X17" s="21" t="s">
         <v>72</v>
@@ -7147,7 +6552,7 @@
       </c>
       <c r="Z17" s="24">
         <f t="shared" si="5"/>
-        <v>1.8599999999999999</v>
+        <v>1.95</v>
       </c>
       <c r="AA17" s="21" t="s">
         <v>72</v>
@@ -7351,9 +6756,9 @@
       <c r="D18" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="46">
+      <c r="E18" s="31">
         <f t="shared" si="0"/>
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>72</v>
@@ -7410,8 +6815,8 @@
       <c r="V18" s="28">
         <v>7</v>
       </c>
-      <c r="W18" s="21" t="s">
-        <v>72</v>
+      <c r="W18" s="21">
+        <v>5</v>
       </c>
       <c r="X18" s="21" t="s">
         <v>72</v>
@@ -7421,7 +6826,7 @@
       </c>
       <c r="Z18" s="24">
         <f t="shared" si="5"/>
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AA18" s="21" t="s">
         <v>72</v>
@@ -7625,9 +7030,9 @@
       <c r="D19" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="46">
+      <c r="E19" s="31">
         <f t="shared" si="0"/>
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>72</v>
@@ -7684,8 +7089,8 @@
       <c r="V19" s="28">
         <v>6</v>
       </c>
-      <c r="W19" s="21" t="s">
-        <v>72</v>
+      <c r="W19" s="21">
+        <v>5.5</v>
       </c>
       <c r="X19" s="21" t="s">
         <v>72</v>
@@ -7695,7 +7100,7 @@
       </c>
       <c r="Z19" s="24">
         <f t="shared" si="5"/>
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AA19" s="21" t="s">
         <v>72</v>
@@ -7899,9 +7304,9 @@
       <c r="D20" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="46">
+      <c r="E20" s="31">
         <f t="shared" si="0"/>
-        <v>2.04</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>72</v>
@@ -7956,10 +7361,10 @@
         <v>-</v>
       </c>
       <c r="V20" s="28">
-        <v>8.5</v>
-      </c>
-      <c r="W20" s="21" t="s">
-        <v>72</v>
+        <v>8.75</v>
+      </c>
+      <c r="W20" s="21">
+        <v>8</v>
       </c>
       <c r="X20" s="21" t="s">
         <v>72</v>
@@ -7969,7 +7374,7 @@
       </c>
       <c r="Z20" s="24">
         <f t="shared" si="5"/>
-        <v>2.04</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="AA20" s="21" t="s">
         <v>72</v>
@@ -8173,9 +7578,9 @@
       <c r="D21" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="46">
+      <c r="E21" s="31">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>1.44</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>72</v>
@@ -8232,8 +7637,8 @@
       <c r="V21" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="W21" s="21" t="s">
-        <v>72</v>
+      <c r="W21" s="21">
+        <v>6</v>
       </c>
       <c r="X21" s="21" t="s">
         <v>72</v>
@@ -8241,9 +7646,9 @@
       <c r="Y21" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="Z21" s="24" t="str">
+      <c r="Z21" s="24">
         <f t="shared" si="5"/>
-        <v>-</v>
+        <v>1.44</v>
       </c>
       <c r="AA21" s="21" t="s">
         <v>72</v>
@@ -8447,9 +7852,9 @@
       <c r="D22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="46">
+      <c r="E22" s="31">
         <f t="shared" si="0"/>
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>72</v>
@@ -8506,8 +7911,8 @@
       <c r="V22" s="28">
         <v>8</v>
       </c>
-      <c r="W22" s="21" t="s">
-        <v>72</v>
+      <c r="W22" s="21">
+        <v>5</v>
       </c>
       <c r="X22" s="21" t="s">
         <v>72</v>
@@ -8517,7 +7922,7 @@
       </c>
       <c r="Z22" s="24">
         <f t="shared" si="5"/>
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="AA22" s="21" t="s">
         <v>72</v>
@@ -8721,9 +8126,9 @@
       <c r="D23" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="46">
+      <c r="E23" s="31">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>1.68</v>
       </c>
       <c r="F23" s="21" t="s">
         <v>72</v>
@@ -8780,8 +8185,8 @@
       <c r="V23" s="28">
         <v>7.5</v>
       </c>
-      <c r="W23" s="21" t="s">
-        <v>72</v>
+      <c r="W23" s="21">
+        <v>6.5</v>
       </c>
       <c r="X23" s="21" t="s">
         <v>72</v>
@@ -8791,7 +8196,7 @@
       </c>
       <c r="Z23" s="24">
         <f t="shared" si="5"/>
-        <v>1.7999999999999998</v>
+        <v>1.68</v>
       </c>
       <c r="AA23" s="21" t="s">
         <v>72</v>
@@ -8995,9 +8400,9 @@
       <c r="D24" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="46">
+      <c r="E24" s="31">
         <f t="shared" si="0"/>
-        <v>1.98</v>
+        <v>2.0279999999999996</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>72</v>
@@ -9052,10 +8457,10 @@
         <v>-</v>
       </c>
       <c r="V24" s="28">
-        <v>8.25</v>
-      </c>
-      <c r="W24" s="21" t="s">
-        <v>72</v>
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="W24" s="21">
+        <v>8.6</v>
       </c>
       <c r="X24" s="21" t="s">
         <v>72</v>
@@ -9065,7 +8470,7 @@
       </c>
       <c r="Z24" s="24">
         <f t="shared" si="5"/>
-        <v>1.98</v>
+        <v>2.0279999999999996</v>
       </c>
       <c r="AA24" s="21" t="s">
         <v>72</v>
@@ -9269,9 +8674,9 @@
       <c r="D25" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="46">
+      <c r="E25" s="31">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.65999999999999992</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>72</v>
@@ -9328,8 +8733,8 @@
       <c r="V25" s="28">
         <v>0.5</v>
       </c>
-      <c r="W25" s="21" t="s">
-        <v>72</v>
+      <c r="W25" s="21">
+        <v>5</v>
       </c>
       <c r="X25" s="21" t="s">
         <v>72</v>
@@ -9339,7 +8744,7 @@
       </c>
       <c r="Z25" s="24">
         <f t="shared" si="5"/>
-        <v>0.12</v>
+        <v>0.65999999999999992</v>
       </c>
       <c r="AA25" s="21" t="s">
         <v>72</v>
@@ -9543,9 +8948,9 @@
       <c r="D26" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="46">
+      <c r="E26" s="31">
         <f t="shared" si="0"/>
-        <v>1.7999999999999998</v>
+        <v>1.74</v>
       </c>
       <c r="F26" s="21" t="s">
         <v>72</v>
@@ -9602,8 +9007,8 @@
       <c r="V26" s="28">
         <v>7.5</v>
       </c>
-      <c r="W26" s="21" t="s">
-        <v>72</v>
+      <c r="W26" s="21">
+        <v>7</v>
       </c>
       <c r="X26" s="21" t="s">
         <v>72</v>
@@ -9613,7 +9018,7 @@
       </c>
       <c r="Z26" s="24">
         <f t="shared" si="5"/>
-        <v>1.7999999999999998</v>
+        <v>1.74</v>
       </c>
       <c r="AA26" s="21" t="s">
         <v>72</v>
@@ -9817,9 +9222,9 @@
       <c r="D27" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="46">
+      <c r="E27" s="31">
         <f t="shared" si="0"/>
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="F27" s="21" t="s">
         <v>72</v>
@@ -9874,10 +9279,10 @@
         <v>-</v>
       </c>
       <c r="V27" s="28">
+        <v>4</v>
+      </c>
+      <c r="W27" s="21">
         <v>5</v>
-      </c>
-      <c r="W27" s="21" t="s">
-        <v>72</v>
       </c>
       <c r="X27" s="21" t="s">
         <v>72</v>
@@ -9887,7 +9292,7 @@
       </c>
       <c r="Z27" s="24">
         <f t="shared" si="5"/>
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AA27" s="21" t="s">
         <v>72</v>
@@ -10243,296 +9648,296 @@
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
-      <c r="F29" s="37" t="e" vm="1">
+      <c r="F29" s="34" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G29" s="38"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="38" t="e" vm="2">
+      <c r="G29" s="35"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="35" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J29" s="38"/>
-      <c r="K29" s="38"/>
-      <c r="L29" s="38"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="37" t="e" vm="3">
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="34" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O29" s="38"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="38" t="e" vm="4">
+      <c r="O29" s="35"/>
+      <c r="P29" s="36"/>
+      <c r="Q29" s="35" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R29" s="38"/>
-      <c r="S29" s="38"/>
-      <c r="T29" s="38"/>
-      <c r="U29" s="39"/>
-      <c r="V29" s="37" t="e" vm="5">
+      <c r="R29" s="35"/>
+      <c r="S29" s="35"/>
+      <c r="T29" s="35"/>
+      <c r="U29" s="36"/>
+      <c r="V29" s="34" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W29" s="38"/>
-      <c r="X29" s="38"/>
-      <c r="Y29" s="38"/>
-      <c r="Z29" s="38"/>
-      <c r="AA29" s="37" t="e" vm="6">
+      <c r="W29" s="35"/>
+      <c r="X29" s="35"/>
+      <c r="Y29" s="35"/>
+      <c r="Z29" s="35"/>
+      <c r="AA29" s="34" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB29" s="38"/>
-      <c r="AC29" s="39"/>
-      <c r="AD29" s="37" t="e" vm="7">
+      <c r="AB29" s="35"/>
+      <c r="AC29" s="36"/>
+      <c r="AD29" s="34" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE29" s="38"/>
-      <c r="AF29" s="39"/>
-      <c r="AG29" s="37" t="e" vm="8">
+      <c r="AE29" s="35"/>
+      <c r="AF29" s="36"/>
+      <c r="AG29" s="34" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH29" s="38"/>
-      <c r="AI29" s="39"/>
-      <c r="AJ29" s="38" t="e" vm="9">
+      <c r="AH29" s="35"/>
+      <c r="AI29" s="36"/>
+      <c r="AJ29" s="35" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK29" s="38"/>
-      <c r="AL29" s="38"/>
-      <c r="AM29" s="38"/>
-      <c r="AN29" s="38"/>
-      <c r="AO29" s="37" t="e" vm="10">
+      <c r="AK29" s="35"/>
+      <c r="AL29" s="35"/>
+      <c r="AM29" s="35"/>
+      <c r="AN29" s="35"/>
+      <c r="AO29" s="34" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP29" s="38"/>
-      <c r="AQ29" s="39"/>
-      <c r="AR29" s="37" t="e" vm="11">
+      <c r="AP29" s="35"/>
+      <c r="AQ29" s="36"/>
+      <c r="AR29" s="34" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS29" s="38"/>
-      <c r="AT29" s="39"/>
-      <c r="AU29" s="38" t="e" vm="12">
+      <c r="AS29" s="35"/>
+      <c r="AT29" s="36"/>
+      <c r="AU29" s="35" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV29" s="38"/>
-      <c r="AW29" s="38"/>
-      <c r="AX29" s="38"/>
-      <c r="AY29" s="38"/>
-      <c r="AZ29" s="37" t="e" vm="13">
+      <c r="AV29" s="35"/>
+      <c r="AW29" s="35"/>
+      <c r="AX29" s="35"/>
+      <c r="AY29" s="35"/>
+      <c r="AZ29" s="34" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA29" s="38"/>
-      <c r="BB29" s="39"/>
-      <c r="BC29" s="37" t="e" vm="7">
+      <c r="BA29" s="35"/>
+      <c r="BB29" s="36"/>
+      <c r="BC29" s="34" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD29" s="38"/>
-      <c r="BE29" s="39"/>
-      <c r="BF29" s="37" t="e" vm="14">
+      <c r="BD29" s="35"/>
+      <c r="BE29" s="36"/>
+      <c r="BF29" s="34" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG29" s="38"/>
-      <c r="BH29" s="39"/>
-      <c r="BI29" s="38" t="e" vm="15">
+      <c r="BG29" s="35"/>
+      <c r="BH29" s="36"/>
+      <c r="BI29" s="35" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ29" s="38"/>
-      <c r="BK29" s="38"/>
-      <c r="BL29" s="38"/>
-      <c r="BM29" s="38"/>
-      <c r="BN29" s="37" t="e" vm="4">
+      <c r="BJ29" s="35"/>
+      <c r="BK29" s="35"/>
+      <c r="BL29" s="35"/>
+      <c r="BM29" s="35"/>
+      <c r="BN29" s="34" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO29" s="38"/>
-      <c r="BP29" s="39"/>
-      <c r="BQ29" s="37" t="e" vm="16">
+      <c r="BO29" s="35"/>
+      <c r="BP29" s="36"/>
+      <c r="BQ29" s="34" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR29" s="38"/>
-      <c r="BS29" s="39"/>
-      <c r="BT29" s="37" t="e" vm="17">
+      <c r="BR29" s="35"/>
+      <c r="BS29" s="36"/>
+      <c r="BT29" s="34" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU29" s="38"/>
-      <c r="BV29" s="39"/>
-      <c r="BW29" s="37" t="e" vm="4">
+      <c r="BU29" s="35"/>
+      <c r="BV29" s="36"/>
+      <c r="BW29" s="34" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX29" s="38"/>
-      <c r="BY29" s="39"/>
-      <c r="BZ29" s="37" t="e" vm="18">
+      <c r="BX29" s="35"/>
+      <c r="BY29" s="36"/>
+      <c r="BZ29" s="34" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA29" s="38"/>
-      <c r="CB29" s="39"/>
-      <c r="CC29" s="37" t="e" vm="19">
+      <c r="CA29" s="35"/>
+      <c r="CB29" s="36"/>
+      <c r="CC29" s="34" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD29" s="38"/>
-      <c r="CE29" s="39"/>
+      <c r="CD29" s="35"/>
+      <c r="CE29" s="36"/>
     </row>
     <row r="30" spans="1:83" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="32" t="s">
+      <c r="A30" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="32" t="s">
+      <c r="C30" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="32" t="s">
+      <c r="E30" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="F30" s="31" t="s">
+      <c r="F30" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="G30" s="32"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="32" t="s">
+      <c r="G30" s="37"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="32"/>
-      <c r="M30" s="32"/>
-      <c r="N30" s="31" t="s">
+      <c r="J30" s="37"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="37"/>
+      <c r="M30" s="37"/>
+      <c r="N30" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="O30" s="32"/>
-      <c r="P30" s="33"/>
-      <c r="Q30" s="34" t="s">
+      <c r="O30" s="37"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="R30" s="35"/>
-      <c r="S30" s="35"/>
-      <c r="T30" s="35"/>
-      <c r="U30" s="36"/>
-      <c r="V30" s="34" t="s">
+      <c r="R30" s="44"/>
+      <c r="S30" s="44"/>
+      <c r="T30" s="44"/>
+      <c r="U30" s="45"/>
+      <c r="V30" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="W30" s="35"/>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="35"/>
-      <c r="Z30" s="36"/>
-      <c r="AA30" s="31" t="s">
+      <c r="W30" s="44"/>
+      <c r="X30" s="44"/>
+      <c r="Y30" s="44"/>
+      <c r="Z30" s="45"/>
+      <c r="AA30" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="AB30" s="32"/>
-      <c r="AC30" s="33"/>
-      <c r="AD30" s="31" t="s">
+      <c r="AB30" s="37"/>
+      <c r="AC30" s="42"/>
+      <c r="AD30" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="AE30" s="32"/>
-      <c r="AF30" s="33"/>
-      <c r="AG30" s="31" t="s">
+      <c r="AE30" s="37"/>
+      <c r="AF30" s="42"/>
+      <c r="AG30" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="AH30" s="32"/>
-      <c r="AI30" s="33"/>
-      <c r="AJ30" s="32" t="s">
+      <c r="AH30" s="37"/>
+      <c r="AI30" s="42"/>
+      <c r="AJ30" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="AK30" s="32"/>
-      <c r="AL30" s="32"/>
-      <c r="AM30" s="32"/>
-      <c r="AN30" s="32"/>
-      <c r="AO30" s="31" t="s">
+      <c r="AK30" s="37"/>
+      <c r="AL30" s="37"/>
+      <c r="AM30" s="37"/>
+      <c r="AN30" s="37"/>
+      <c r="AO30" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="AP30" s="32"/>
-      <c r="AQ30" s="33"/>
-      <c r="AR30" s="31" t="s">
+      <c r="AP30" s="37"/>
+      <c r="AQ30" s="42"/>
+      <c r="AR30" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="AS30" s="32"/>
-      <c r="AT30" s="33"/>
-      <c r="AU30" s="34" t="s">
+      <c r="AS30" s="37"/>
+      <c r="AT30" s="42"/>
+      <c r="AU30" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="AV30" s="35"/>
-      <c r="AW30" s="35"/>
-      <c r="AX30" s="35"/>
-      <c r="AY30" s="36"/>
-      <c r="AZ30" s="31" t="s">
+      <c r="AV30" s="44"/>
+      <c r="AW30" s="44"/>
+      <c r="AX30" s="44"/>
+      <c r="AY30" s="45"/>
+      <c r="AZ30" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="BA30" s="32"/>
-      <c r="BB30" s="33"/>
-      <c r="BC30" s="31" t="s">
+      <c r="BA30" s="37"/>
+      <c r="BB30" s="42"/>
+      <c r="BC30" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="BD30" s="32"/>
-      <c r="BE30" s="33"/>
-      <c r="BF30" s="31" t="s">
+      <c r="BD30" s="37"/>
+      <c r="BE30" s="42"/>
+      <c r="BF30" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="BG30" s="32"/>
-      <c r="BH30" s="33"/>
-      <c r="BI30" s="34" t="s">
+      <c r="BG30" s="37"/>
+      <c r="BH30" s="42"/>
+      <c r="BI30" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="BJ30" s="35"/>
-      <c r="BK30" s="35"/>
-      <c r="BL30" s="35"/>
-      <c r="BM30" s="36"/>
-      <c r="BN30" s="31" t="s">
+      <c r="BJ30" s="44"/>
+      <c r="BK30" s="44"/>
+      <c r="BL30" s="44"/>
+      <c r="BM30" s="45"/>
+      <c r="BN30" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="BO30" s="32"/>
-      <c r="BP30" s="33"/>
-      <c r="BQ30" s="31" t="s">
+      <c r="BO30" s="37"/>
+      <c r="BP30" s="42"/>
+      <c r="BQ30" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="BR30" s="32"/>
-      <c r="BS30" s="33"/>
-      <c r="BT30" s="31" t="s">
+      <c r="BR30" s="37"/>
+      <c r="BS30" s="42"/>
+      <c r="BT30" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="BU30" s="32"/>
-      <c r="BV30" s="33"/>
-      <c r="BW30" s="31" t="s">
+      <c r="BU30" s="37"/>
+      <c r="BV30" s="42"/>
+      <c r="BW30" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="BX30" s="32"/>
-      <c r="BY30" s="33"/>
-      <c r="BZ30" s="31" t="s">
+      <c r="BX30" s="37"/>
+      <c r="BY30" s="42"/>
+      <c r="BZ30" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="CA30" s="32"/>
-      <c r="CB30" s="33"/>
-      <c r="CC30" s="31" t="s">
+      <c r="CA30" s="37"/>
+      <c r="CB30" s="42"/>
+      <c r="CC30" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="CD30" s="32"/>
-      <c r="CE30" s="33"/>
+      <c r="CD30" s="37"/>
+      <c r="CE30" s="42"/>
     </row>
     <row r="31" spans="1:83" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="32"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
       <c r="F31" s="22" t="s">
         <v>26</v>
       </c>
@@ -10782,8 +10187,8 @@
       <c r="D32" s="18" t="str">
         <v>McLaren</v>
       </c>
-      <c r="E32" s="46">
-        <v>2.1</v>
+      <c r="E32" s="31">
+        <v>2.16</v>
       </c>
       <c r="F32" s="21" t="str">
         <v>-</v>
@@ -10836,8 +10241,8 @@
       <c r="V32" s="28">
         <v>8.75</v>
       </c>
-      <c r="W32" s="23" t="str">
-        <v>-</v>
+      <c r="W32" s="23">
+        <v>9.25</v>
       </c>
       <c r="X32" s="23" t="str">
         <v>-</v>
@@ -10846,7 +10251,7 @@
         <v>-</v>
       </c>
       <c r="Z32" s="24">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AA32" s="28" t="str">
         <v>-</v>
@@ -11033,8 +10438,8 @@
       <c r="D33" s="18" t="str">
         <v>Alpine</v>
       </c>
-      <c r="E33" s="46">
-        <v>2.1</v>
+      <c r="E33" s="31">
+        <v>2.1120000000000001</v>
       </c>
       <c r="F33" s="21" t="str">
         <v>-</v>
@@ -11085,10 +10490,10 @@
         <v>-</v>
       </c>
       <c r="V33" s="28">
-        <v>8.75</v>
-      </c>
-      <c r="W33" s="23" t="str">
-        <v>-</v>
+        <v>8.5</v>
+      </c>
+      <c r="W33" s="23">
+        <v>9.1</v>
       </c>
       <c r="X33" s="23" t="str">
         <v>-</v>
@@ -11097,7 +10502,7 @@
         <v>-</v>
       </c>
       <c r="Z33" s="24">
-        <v>2.1</v>
+        <v>2.1120000000000001</v>
       </c>
       <c r="AA33" s="28" t="str">
         <v>-</v>
@@ -11284,8 +10689,8 @@
       <c r="D34" s="1" t="str">
         <v>Mercedes</v>
       </c>
-      <c r="E34" s="46">
-        <v>2.04</v>
+      <c r="E34" s="31">
+        <v>2.0699999999999998</v>
       </c>
       <c r="F34" s="21" t="str">
         <v>-</v>
@@ -11338,8 +10743,8 @@
       <c r="V34" s="28">
         <v>8.5</v>
       </c>
-      <c r="W34" s="23" t="str">
-        <v>-</v>
+      <c r="W34" s="23">
+        <v>8.75</v>
       </c>
       <c r="X34" s="23" t="str">
         <v>-</v>
@@ -11348,7 +10753,7 @@
         <v>-</v>
       </c>
       <c r="Z34" s="24">
-        <v>2.04</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="AA34" s="28" t="str">
         <v>-</v>
@@ -11527,15 +10932,15 @@
         <v>4</v>
       </c>
       <c r="B35" s="1">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="C35" s="12" t="str">
-        <v>Oscar Piastri</v>
+        <v>Liam Lawson</v>
       </c>
       <c r="D35" s="1" t="str">
-        <v>McLaren</v>
-      </c>
-      <c r="E35" s="46">
+        <v>Racing Bulls</v>
+      </c>
+      <c r="E35" s="31">
         <v>2.04</v>
       </c>
       <c r="F35" s="21" t="str">
@@ -11586,11 +10991,11 @@
       <c r="U35" s="24" t="str">
         <v>-</v>
       </c>
-      <c r="V35" s="28">
+      <c r="V35" s="28" t="str">
+        <v>-</v>
+      </c>
+      <c r="W35" s="23">
         <v>8.5</v>
-      </c>
-      <c r="W35" s="23" t="str">
-        <v>-</v>
       </c>
       <c r="X35" s="23" t="str">
         <v>-</v>
@@ -11778,16 +11183,16 @@
         <v>5</v>
       </c>
       <c r="B36" s="3">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="C36" s="12" t="str">
-        <v>Carlos Sainz</v>
+        <v>Sergio Perez</v>
       </c>
       <c r="D36" s="3" t="str">
-        <v>Williams</v>
-      </c>
-      <c r="E36" s="46">
-        <v>2.04</v>
+        <v>Cadillac</v>
+      </c>
+      <c r="E36" s="31">
+        <v>2.0279999999999996</v>
       </c>
       <c r="F36" s="21" t="str">
         <v>-</v>
@@ -11838,10 +11243,10 @@
         <v>-</v>
       </c>
       <c r="V36" s="28">
-        <v>8.5</v>
-      </c>
-      <c r="W36" s="23" t="str">
-        <v>-</v>
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="W36" s="23">
+        <v>8.6</v>
       </c>
       <c r="X36" s="23" t="str">
         <v>-</v>
@@ -11850,7 +11255,7 @@
         <v>-</v>
       </c>
       <c r="Z36" s="24">
-        <v>2.04</v>
+        <v>2.0279999999999996</v>
       </c>
       <c r="AA36" s="28" t="str">
         <v>-</v>
@@ -12029,16 +11434,16 @@
         <v>6</v>
       </c>
       <c r="B37" s="3">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C37" s="12" t="str">
-        <v>Lewis Hamilton</v>
+        <v>Carlos Sainz</v>
       </c>
       <c r="D37" s="3" t="str">
-        <v>Ferrari</v>
-      </c>
-      <c r="E37" s="46">
-        <v>1.98</v>
+        <v>Williams</v>
+      </c>
+      <c r="E37" s="31">
+        <v>2.0099999999999998</v>
       </c>
       <c r="F37" s="21" t="str">
         <v>-</v>
@@ -12089,10 +11494,10 @@
         <v>-</v>
       </c>
       <c r="V37" s="28">
-        <v>8.25</v>
-      </c>
-      <c r="W37" s="23" t="str">
-        <v>-</v>
+        <v>8.75</v>
+      </c>
+      <c r="W37" s="23">
+        <v>8</v>
       </c>
       <c r="X37" s="23" t="str">
         <v>-</v>
@@ -12101,7 +11506,7 @@
         <v>-</v>
       </c>
       <c r="Z37" s="24">
-        <v>1.98</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="AA37" s="28" t="str">
         <v>-</v>
@@ -12280,16 +11685,16 @@
         <v>7</v>
       </c>
       <c r="B38" s="4">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C38" s="12" t="str">
-        <v>Sergio Perez</v>
+        <v>Arvid Lindblad</v>
       </c>
       <c r="D38" s="4" t="str">
-        <v>Cadillac</v>
-      </c>
-      <c r="E38" s="46">
-        <v>1.98</v>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="E38" s="31">
+        <v>1.95</v>
       </c>
       <c r="F38" s="21" t="str">
         <v>-</v>
@@ -12340,10 +11745,10 @@
         <v>-</v>
       </c>
       <c r="V38" s="28">
-        <v>8.25</v>
-      </c>
-      <c r="W38" s="23" t="str">
-        <v>-</v>
+        <v>7.75</v>
+      </c>
+      <c r="W38" s="23">
+        <v>8.5</v>
       </c>
       <c r="X38" s="23" t="str">
         <v>-</v>
@@ -12352,7 +11757,7 @@
         <v>-</v>
       </c>
       <c r="Z38" s="24">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AA38" s="28" t="str">
         <v>-</v>
@@ -12531,16 +11936,16 @@
         <v>8</v>
       </c>
       <c r="B39" s="4">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C39" s="12" t="str">
-        <v>Kimi Antonelli</v>
+        <v>Max Verstappen</v>
       </c>
       <c r="D39" s="4" t="str">
-        <v>Mercedes</v>
-      </c>
-      <c r="E39" s="46">
-        <v>1.92</v>
+        <v>Red Bull</v>
+      </c>
+      <c r="E39" s="31">
+        <v>1.89</v>
       </c>
       <c r="F39" s="21" t="str">
         <v>-</v>
@@ -12591,11 +11996,11 @@
         <v>-</v>
       </c>
       <c r="V39" s="28">
+        <v>7.75</v>
+      </c>
+      <c r="W39" s="23">
         <v>8</v>
       </c>
-      <c r="W39" s="23" t="str">
-        <v>-</v>
-      </c>
       <c r="X39" s="23" t="str">
         <v>-</v>
       </c>
@@ -12603,7 +12008,7 @@
         <v>-</v>
       </c>
       <c r="Z39" s="24">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AA39" s="28" t="str">
         <v>-</v>
@@ -12782,16 +12187,16 @@
         <v>9</v>
       </c>
       <c r="B40" s="5">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C40" s="12" t="str">
-        <v>Nico Hulkenberg</v>
+        <v>Lewis Hamilton</v>
       </c>
       <c r="D40" s="5" t="str">
-        <v>Audi</v>
-      </c>
-      <c r="E40" s="46">
-        <v>1.92</v>
+        <v>Ferrari</v>
+      </c>
+      <c r="E40" s="31">
+        <v>1.8599999999999999</v>
       </c>
       <c r="F40" s="21" t="str">
         <v>-</v>
@@ -12842,10 +12247,10 @@
         <v>-</v>
       </c>
       <c r="V40" s="28">
-        <v>8</v>
-      </c>
-      <c r="W40" s="23" t="str">
-        <v>-</v>
+        <v>8.25</v>
+      </c>
+      <c r="W40" s="23">
+        <v>7.25</v>
       </c>
       <c r="X40" s="23" t="str">
         <v>-</v>
@@ -12854,7 +12259,7 @@
         <v>-</v>
       </c>
       <c r="Z40" s="24">
-        <v>1.92</v>
+        <v>1.8599999999999999</v>
       </c>
       <c r="AA40" s="28" t="str">
         <v>-</v>
@@ -13033,16 +12438,16 @@
         <v>10</v>
       </c>
       <c r="B41" s="5">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="C41" s="12" t="str">
-        <v>Max Verstappen</v>
+        <v>Oscar Piastri</v>
       </c>
       <c r="D41" s="5" t="str">
-        <v>Red Bull</v>
-      </c>
-      <c r="E41" s="46">
-        <v>1.8599999999999999</v>
+        <v>McLaren</v>
+      </c>
+      <c r="E41" s="31">
+        <v>1.8299999999999998</v>
       </c>
       <c r="F41" s="21" t="str">
         <v>-</v>
@@ -13093,10 +12498,10 @@
         <v>-</v>
       </c>
       <c r="V41" s="28">
-        <v>7.75</v>
-      </c>
-      <c r="W41" s="23" t="str">
-        <v>-</v>
+        <v>8.5</v>
+      </c>
+      <c r="W41" s="23">
+        <v>6.75</v>
       </c>
       <c r="X41" s="23" t="str">
         <v>-</v>
@@ -13105,7 +12510,7 @@
         <v>-</v>
       </c>
       <c r="Z41" s="24">
-        <v>1.8599999999999999</v>
+        <v>1.8299999999999998</v>
       </c>
       <c r="AA41" s="28" t="str">
         <v>-</v>
@@ -13284,16 +12689,16 @@
         <v>11</v>
       </c>
       <c r="B42" s="6">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="C42" s="12" t="str">
-        <v>Arvid Lindblad</v>
+        <v>Fernando Alonso</v>
       </c>
       <c r="D42" s="6" t="str">
-        <v>Racing Bulls</v>
-      </c>
-      <c r="E42" s="46">
-        <v>1.8599999999999999</v>
+        <v>Aston Martin</v>
+      </c>
+      <c r="E42" s="31">
+        <v>1.74</v>
       </c>
       <c r="F42" s="21" t="str">
         <v>-</v>
@@ -13344,10 +12749,10 @@
         <v>-</v>
       </c>
       <c r="V42" s="28">
-        <v>7.75</v>
-      </c>
-      <c r="W42" s="23" t="str">
-        <v>-</v>
+        <v>7.5</v>
+      </c>
+      <c r="W42" s="23">
+        <v>7</v>
       </c>
       <c r="X42" s="23" t="str">
         <v>-</v>
@@ -13356,7 +12761,7 @@
         <v>-</v>
       </c>
       <c r="Z42" s="24">
-        <v>1.8599999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="AA42" s="28" t="str">
         <v>-</v>
@@ -13535,16 +12940,16 @@
         <v>12</v>
       </c>
       <c r="B43" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43" s="12" t="str">
-        <v>Gabriel Bortoleto</v>
+        <v>Isack Hadjar</v>
       </c>
       <c r="D43" s="6" t="str">
-        <v>Audi</v>
-      </c>
-      <c r="E43" s="46">
-        <v>1.7999999999999998</v>
+        <v>Red Bull</v>
+      </c>
+      <c r="E43" s="31">
+        <v>1.71</v>
       </c>
       <c r="F43" s="21" t="str">
         <v>-</v>
@@ -13595,10 +13000,10 @@
         <v>-</v>
       </c>
       <c r="V43" s="28">
-        <v>7.5</v>
-      </c>
-      <c r="W43" s="23" t="str">
-        <v>-</v>
+        <v>7.25</v>
+      </c>
+      <c r="W43" s="23">
+        <v>7</v>
       </c>
       <c r="X43" s="23" t="str">
         <v>-</v>
@@ -13607,7 +13012,7 @@
         <v>-</v>
       </c>
       <c r="Z43" s="24">
-        <v>1.7999999999999998</v>
+        <v>1.71</v>
       </c>
       <c r="AA43" s="28" t="str">
         <v>-</v>
@@ -13786,16 +13191,16 @@
         <v>13</v>
       </c>
       <c r="B44" s="7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C44" s="12" t="str">
-        <v>Fernando Alonso</v>
+        <v>Gabriel Bortoleto</v>
       </c>
       <c r="D44" s="7" t="str">
-        <v>Aston Martin</v>
-      </c>
-      <c r="E44" s="46">
-        <v>1.7999999999999998</v>
+        <v>Audi</v>
+      </c>
+      <c r="E44" s="31">
+        <v>1.68</v>
       </c>
       <c r="F44" s="21" t="str">
         <v>-</v>
@@ -13848,8 +13253,8 @@
       <c r="V44" s="28">
         <v>7.5</v>
       </c>
-      <c r="W44" s="23" t="str">
-        <v>-</v>
+      <c r="W44" s="23">
+        <v>6.5</v>
       </c>
       <c r="X44" s="23" t="str">
         <v>-</v>
@@ -13858,7 +13263,7 @@
         <v>-</v>
       </c>
       <c r="Z44" s="24">
-        <v>1.7999999999999998</v>
+        <v>1.68</v>
       </c>
       <c r="AA44" s="28" t="str">
         <v>-</v>
@@ -14037,16 +13442,16 @@
         <v>14</v>
       </c>
       <c r="B45" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C45" s="12" t="str">
-        <v>Isack Hadjar</v>
+        <v>Kimi Antonelli</v>
       </c>
       <c r="D45" s="7" t="str">
-        <v>Red Bull</v>
-      </c>
-      <c r="E45" s="46">
-        <v>1.74</v>
+        <v>Mercedes</v>
+      </c>
+      <c r="E45" s="31">
+        <v>1.65</v>
       </c>
       <c r="F45" s="21" t="str">
         <v>-</v>
@@ -14097,10 +13502,10 @@
         <v>-</v>
       </c>
       <c r="V45" s="28">
-        <v>7.25</v>
-      </c>
-      <c r="W45" s="23" t="str">
-        <v>-</v>
+        <v>8</v>
+      </c>
+      <c r="W45" s="23">
+        <v>5.75</v>
       </c>
       <c r="X45" s="23" t="str">
         <v>-</v>
@@ -14109,7 +13514,7 @@
         <v>-</v>
       </c>
       <c r="Z45" s="24">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AA45" s="28" t="str">
         <v>-</v>
@@ -14288,16 +13693,16 @@
         <v>15</v>
       </c>
       <c r="B46" s="8">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C46" s="12" t="str">
-        <v>Esteban Ocon</v>
+        <v>Nico Hulkenberg</v>
       </c>
       <c r="D46" s="8" t="str">
-        <v>Hass</v>
-      </c>
-      <c r="E46" s="46">
-        <v>1.68</v>
+        <v>Audi</v>
+      </c>
+      <c r="E46" s="31">
+        <v>1.56</v>
       </c>
       <c r="F46" s="21" t="str">
         <v>-</v>
@@ -14348,10 +13753,10 @@
         <v>-</v>
       </c>
       <c r="V46" s="28">
-        <v>7</v>
-      </c>
-      <c r="W46" s="23" t="str">
-        <v>-</v>
+        <v>8</v>
+      </c>
+      <c r="W46" s="23">
+        <v>5</v>
       </c>
       <c r="X46" s="23" t="str">
         <v>-</v>
@@ -14360,7 +13765,7 @@
         <v>-</v>
       </c>
       <c r="Z46" s="24">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="AA46" s="28" t="str">
         <v>-</v>
@@ -14547,8 +13952,8 @@
       <c r="D47" s="8" t="str">
         <v>Ferrari</v>
       </c>
-      <c r="E47" s="46">
-        <v>1.44</v>
+      <c r="E47" s="31">
+        <v>1.512</v>
       </c>
       <c r="F47" s="21" t="str">
         <v>-</v>
@@ -14601,8 +14006,8 @@
       <c r="V47" s="28">
         <v>6</v>
       </c>
-      <c r="W47" s="23" t="str">
-        <v>-</v>
+      <c r="W47" s="23">
+        <v>6.6</v>
       </c>
       <c r="X47" s="23" t="str">
         <v>-</v>
@@ -14611,7 +14016,7 @@
         <v>-</v>
       </c>
       <c r="Z47" s="24">
-        <v>1.44</v>
+        <v>1.512</v>
       </c>
       <c r="AA47" s="28" t="str">
         <v>-</v>
@@ -14790,15 +14195,15 @@
         <v>17</v>
       </c>
       <c r="B48" s="9">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="C48" s="12" t="str">
-        <v>Oliver Bearman</v>
+        <v>Esteban Ocon</v>
       </c>
       <c r="D48" s="9" t="str">
         <v>Hass</v>
       </c>
-      <c r="E48" s="46">
+      <c r="E48" s="31">
         <v>1.44</v>
       </c>
       <c r="F48" s="21" t="str">
@@ -14850,10 +14255,10 @@
         <v>-</v>
       </c>
       <c r="V48" s="28">
-        <v>6</v>
-      </c>
-      <c r="W48" s="23" t="str">
-        <v>-</v>
+        <v>7</v>
+      </c>
+      <c r="W48" s="23">
+        <v>5</v>
       </c>
       <c r="X48" s="23" t="str">
         <v>-</v>
@@ -15041,16 +14446,16 @@
         <v>18</v>
       </c>
       <c r="B49" s="9">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C49" s="12" t="str">
-        <v>Lance Stroll</v>
+        <v>Alexander Albon</v>
       </c>
       <c r="D49" s="9" t="str">
-        <v>Aston Martin</v>
-      </c>
-      <c r="E49" s="46">
-        <v>1.2</v>
+        <v>Williams</v>
+      </c>
+      <c r="E49" s="31">
+        <v>1.44</v>
       </c>
       <c r="F49" s="21" t="str">
         <v>-</v>
@@ -15100,11 +14505,11 @@
       <c r="U49" s="24" t="str">
         <v>-</v>
       </c>
-      <c r="V49" s="28">
-        <v>5</v>
-      </c>
-      <c r="W49" s="23" t="str">
-        <v>-</v>
+      <c r="V49" s="28" t="str">
+        <v>-</v>
+      </c>
+      <c r="W49" s="23">
+        <v>6</v>
       </c>
       <c r="X49" s="23" t="str">
         <v>-</v>
@@ -15113,7 +14518,7 @@
         <v>-</v>
       </c>
       <c r="Z49" s="24">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AA49" s="28" t="str">
         <v>-</v>
@@ -15292,16 +14697,16 @@
         <v>19</v>
       </c>
       <c r="B50" s="10">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="C50" s="12" t="str">
-        <v>Pierre Gasly</v>
+        <v>Oliver Bearman</v>
       </c>
       <c r="D50" s="10" t="str">
-        <v>Alpine</v>
-      </c>
-      <c r="E50" s="46">
-        <v>0.84</v>
+        <v>Hass</v>
+      </c>
+      <c r="E50" s="31">
+        <v>1.38</v>
       </c>
       <c r="F50" s="21" t="str">
         <v>-</v>
@@ -15352,10 +14757,10 @@
         <v>-</v>
       </c>
       <c r="V50" s="28">
-        <v>3.5</v>
-      </c>
-      <c r="W50" s="23" t="str">
-        <v>-</v>
+        <v>6</v>
+      </c>
+      <c r="W50" s="23">
+        <v>5.5</v>
       </c>
       <c r="X50" s="23" t="str">
         <v>-</v>
@@ -15364,7 +14769,7 @@
         <v>-</v>
       </c>
       <c r="Z50" s="24">
-        <v>0.84</v>
+        <v>1.38</v>
       </c>
       <c r="AA50" s="28" t="str">
         <v>-</v>
@@ -15543,16 +14948,16 @@
         <v>20</v>
       </c>
       <c r="B51" s="10">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="C51" s="12" t="str">
-        <v>Valtteri Bottas</v>
+        <v>Pierre Gasly</v>
       </c>
       <c r="D51" s="10" t="str">
-        <v>Cadillac</v>
-      </c>
-      <c r="E51" s="46">
-        <v>0.12</v>
+        <v>Alpine</v>
+      </c>
+      <c r="E51" s="31">
+        <v>1.1399999999999999</v>
       </c>
       <c r="F51" s="21" t="str">
         <v>-</v>
@@ -15603,10 +15008,10 @@
         <v>-</v>
       </c>
       <c r="V51" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="W51" s="23" t="str">
-        <v>-</v>
+        <v>3.5</v>
+      </c>
+      <c r="W51" s="23">
+        <v>6</v>
       </c>
       <c r="X51" s="23" t="str">
         <v>-</v>
@@ -15615,7 +15020,7 @@
         <v>-</v>
       </c>
       <c r="Z51" s="24">
-        <v>0.12</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="AA51" s="28" t="str">
         <v>-</v>
@@ -15794,16 +15199,16 @@
         <v>21</v>
       </c>
       <c r="B52" s="11">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C52" s="12" t="str">
-        <v>Liam Lawson</v>
+        <v>Lance Stroll</v>
       </c>
       <c r="D52" s="11" t="str">
-        <v>Racing Bulls</v>
-      </c>
-      <c r="E52" s="46">
-        <v>-1</v>
+        <v>Aston Martin</v>
+      </c>
+      <c r="E52" s="31">
+        <v>1.08</v>
       </c>
       <c r="F52" s="21" t="str">
         <v>-</v>
@@ -15853,11 +15258,11 @@
       <c r="U52" s="24" t="str">
         <v>-</v>
       </c>
-      <c r="V52" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="W52" s="23" t="str">
-        <v>-</v>
+      <c r="V52" s="28">
+        <v>4</v>
+      </c>
+      <c r="W52" s="23">
+        <v>5</v>
       </c>
       <c r="X52" s="23" t="str">
         <v>-</v>
@@ -15865,8 +15270,8 @@
       <c r="Y52" s="23" t="str">
         <v>-</v>
       </c>
-      <c r="Z52" s="24" t="str">
-        <v>-</v>
+      <c r="Z52" s="24">
+        <v>1.08</v>
       </c>
       <c r="AA52" s="28" t="str">
         <v>-</v>
@@ -16045,16 +15450,16 @@
         <v>22</v>
       </c>
       <c r="B53" s="11">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="C53" s="12" t="str">
-        <v>Alexander Albon</v>
+        <v>Valtteri Bottas</v>
       </c>
       <c r="D53" s="11" t="str">
-        <v>Williams</v>
-      </c>
-      <c r="E53" s="46">
-        <v>-1</v>
+        <v>Cadillac</v>
+      </c>
+      <c r="E53" s="31">
+        <v>0.65999999999999992</v>
       </c>
       <c r="F53" s="21" t="str">
         <v>-</v>
@@ -16104,11 +15509,11 @@
       <c r="U53" s="24" t="str">
         <v>-</v>
       </c>
-      <c r="V53" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="W53" s="23" t="str">
-        <v>-</v>
+      <c r="V53" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="W53" s="23">
+        <v>5</v>
       </c>
       <c r="X53" s="23" t="str">
         <v>-</v>
@@ -16116,8 +15521,8 @@
       <c r="Y53" s="23" t="str">
         <v>-</v>
       </c>
-      <c r="Z53" s="24" t="str">
-        <v>-</v>
+      <c r="Z53" s="24">
+        <v>0.65999999999999992</v>
       </c>
       <c r="AA53" s="28" t="str">
         <v>-</v>
@@ -16317,33 +15722,62 @@
     </row>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="Q4:U4"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:U29"/>
-    <mergeCell ref="V29:Z29"/>
-    <mergeCell ref="V4:Z4"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AN3"/>
-    <mergeCell ref="AO3:AQ3"/>
-    <mergeCell ref="AR3:AT3"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AG4:AI4"/>
-    <mergeCell ref="AJ4:AN4"/>
-    <mergeCell ref="AO4:AQ4"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="BW30:BY30"/>
+    <mergeCell ref="BZ30:CB30"/>
+    <mergeCell ref="Q30:U30"/>
+    <mergeCell ref="V30:Z30"/>
+    <mergeCell ref="AA30:AC30"/>
+    <mergeCell ref="AD30:AF30"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AJ30:AN30"/>
+    <mergeCell ref="AO30:AQ30"/>
+    <mergeCell ref="AR30:AT30"/>
+    <mergeCell ref="AU30:AY30"/>
+    <mergeCell ref="CC30:CE30"/>
+    <mergeCell ref="AZ30:BB30"/>
+    <mergeCell ref="BC30:BE30"/>
+    <mergeCell ref="BF30:BH30"/>
+    <mergeCell ref="BI30:BM30"/>
+    <mergeCell ref="BN30:BP30"/>
+    <mergeCell ref="BQ30:BS30"/>
+    <mergeCell ref="BT30:BV30"/>
+    <mergeCell ref="BW29:BY29"/>
+    <mergeCell ref="BZ29:CB29"/>
+    <mergeCell ref="CC29:CE29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="AU29:AY29"/>
+    <mergeCell ref="AZ29:BB29"/>
+    <mergeCell ref="BC29:BE29"/>
+    <mergeCell ref="BF29:BH29"/>
+    <mergeCell ref="BI29:BM29"/>
+    <mergeCell ref="BN29:BP29"/>
+    <mergeCell ref="AA29:AC29"/>
+    <mergeCell ref="AD29:AF29"/>
+    <mergeCell ref="BQ29:BS29"/>
+    <mergeCell ref="BT29:BV29"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AN29"/>
+    <mergeCell ref="AO29:AQ29"/>
+    <mergeCell ref="AR29:AT29"/>
+    <mergeCell ref="CC4:CE4"/>
+    <mergeCell ref="AR4:AT4"/>
+    <mergeCell ref="AU4:AY4"/>
+    <mergeCell ref="AZ4:BB4"/>
+    <mergeCell ref="BC4:BE4"/>
+    <mergeCell ref="BF4:BH4"/>
+    <mergeCell ref="BI4:BM4"/>
+    <mergeCell ref="BN4:BP4"/>
+    <mergeCell ref="BQ4:BS4"/>
+    <mergeCell ref="BT4:BV4"/>
+    <mergeCell ref="BW4:BY4"/>
+    <mergeCell ref="BZ4:CB4"/>
     <mergeCell ref="BW3:BY3"/>
     <mergeCell ref="BZ3:CB3"/>
     <mergeCell ref="CC3:CE3"/>
@@ -16360,99 +15794,78 @@
     <mergeCell ref="BI3:BM3"/>
     <mergeCell ref="BN3:BP3"/>
     <mergeCell ref="BQ3:BS3"/>
-    <mergeCell ref="CC4:CE4"/>
-    <mergeCell ref="AR4:AT4"/>
-    <mergeCell ref="AU4:AY4"/>
-    <mergeCell ref="AZ4:BB4"/>
-    <mergeCell ref="BC4:BE4"/>
-    <mergeCell ref="BF4:BH4"/>
-    <mergeCell ref="BI4:BM4"/>
-    <mergeCell ref="BN4:BP4"/>
-    <mergeCell ref="BQ4:BS4"/>
-    <mergeCell ref="BT4:BV4"/>
-    <mergeCell ref="BW4:BY4"/>
-    <mergeCell ref="BZ4:CB4"/>
-    <mergeCell ref="BQ29:BS29"/>
-    <mergeCell ref="BT29:BV29"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AN29"/>
-    <mergeCell ref="AO29:AQ29"/>
-    <mergeCell ref="AR29:AT29"/>
-    <mergeCell ref="BW29:BY29"/>
-    <mergeCell ref="BZ29:CB29"/>
-    <mergeCell ref="CC29:CE29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="AU29:AY29"/>
-    <mergeCell ref="AZ29:BB29"/>
-    <mergeCell ref="BC29:BE29"/>
-    <mergeCell ref="BF29:BH29"/>
-    <mergeCell ref="BI29:BM29"/>
-    <mergeCell ref="BN29:BP29"/>
-    <mergeCell ref="AA29:AC29"/>
-    <mergeCell ref="AD29:AF29"/>
-    <mergeCell ref="CC30:CE30"/>
-    <mergeCell ref="AZ30:BB30"/>
-    <mergeCell ref="BC30:BE30"/>
-    <mergeCell ref="BF30:BH30"/>
-    <mergeCell ref="BI30:BM30"/>
-    <mergeCell ref="BN30:BP30"/>
-    <mergeCell ref="BQ30:BS30"/>
-    <mergeCell ref="BT30:BV30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="BW30:BY30"/>
-    <mergeCell ref="BZ30:CB30"/>
-    <mergeCell ref="Q30:U30"/>
-    <mergeCell ref="V30:Z30"/>
-    <mergeCell ref="AA30:AC30"/>
-    <mergeCell ref="AD30:AF30"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AJ30:AN30"/>
-    <mergeCell ref="AO30:AQ30"/>
-    <mergeCell ref="AR30:AT30"/>
-    <mergeCell ref="AU30:AY30"/>
+    <mergeCell ref="V4:Z4"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AN3"/>
+    <mergeCell ref="AO3:AQ3"/>
+    <mergeCell ref="AR3:AT3"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AG4:AI4"/>
+    <mergeCell ref="AJ4:AN4"/>
+    <mergeCell ref="AO4:AQ4"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:U29"/>
+    <mergeCell ref="V29:Z29"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="Q4:U4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B27 D6:D27 B32:B53 D32:D53">
-    <cfRule type="expression" dxfId="28" priority="335">
+    <cfRule type="expression" dxfId="69" priority="335">
       <formula>$D6="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="336">
+    <cfRule type="expression" dxfId="68" priority="336">
       <formula>$D6="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="337">
+    <cfRule type="expression" dxfId="67" priority="337">
       <formula>$D6="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="338">
+    <cfRule type="expression" dxfId="66" priority="338">
       <formula>$D6="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="339">
+    <cfRule type="expression" dxfId="65" priority="339">
       <formula>$D6="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="340">
+    <cfRule type="expression" dxfId="64" priority="340">
       <formula>$D6="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="341">
+    <cfRule type="expression" dxfId="63" priority="341">
       <formula>$D6="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="342">
+    <cfRule type="expression" dxfId="62" priority="342">
       <formula>$D6="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="343">
+    <cfRule type="expression" dxfId="61" priority="343">
       <formula>$D6="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="344">
+    <cfRule type="expression" dxfId="60" priority="344">
       <formula>$D6="Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="345">
+    <cfRule type="expression" dxfId="59" priority="345">
       <formula>$D6="Haas"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E6:E27">
+    <cfRule type="cellIs" dxfId="58" priority="3" operator="equal">
+      <formula>-1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="E32:E53">
+    <cfRule type="cellIs" dxfId="57" priority="1" operator="equal">
+      <formula>-1</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="346">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -16462,9 +15875,6 @@
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
-      <formula>-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:F6 F7:F28 G6:G28 Q6:T28 W6:Y28 AA6:AB28 AD6:AE28 AG6:AH28 AJ6:AM28 AO6:AP28 AR6:AS28 AU6:AX28 AZ6:BA28 BC6:BD28 BF6:BG28 BN6:BO28 BQ6:BR28 BT6:BU28 BW6:BX28 BZ6:CA28 CC6:CD28 H6:H27 P6:P27 AC6:AC27 AF6:AF27 AI6:AI27 AN6:AN27 AQ6:AQ27 AT6:AT27 BB6:BB27 BE6:BE27 BP6:BP27 BS6:BS27 BV6:BV27 BY6:BY27 CB6:CB27 CE6:CE27 I6:O28 U6:V27 Z6:Z27 AY6:AY27 BH6:BM27 E7:E27">
@@ -16491,6 +15901,16 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F6:CE27">
+    <cfRule type="cellIs" dxfId="56" priority="2" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32:CE53">
+    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="Q32:Z53">
     <cfRule type="colorScale" priority="277">
       <colorScale>
@@ -16513,21 +15933,6 @@
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F32:CE53">
-    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6:E27">
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
-      <formula>-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6:CE27">
-    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
-      <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16603,11 +16008,11 @@
         <v>McLaren</v>
       </c>
       <c r="E2" s="2">
-        <v>2.1</v>
-      </c>
-      <c r="G2" s="45">
+        <v>2.16</v>
+      </c>
+      <c r="G2" s="46">
         <f>K2-K3</f>
-        <v>0.12000000000000011</v>
+        <v>0.41999999999999993</v>
       </c>
       <c r="H2" s="18">
         <v>63</v>
@@ -16620,14 +16025,14 @@
       </c>
       <c r="K2" s="2">
         <f>Ratings!E6</f>
-        <v>2.04</v>
+        <v>2.0699999999999998</v>
       </c>
       <c r="M2" s="18">
         <v>63</v>
       </c>
       <c r="N2" s="29">
         <f>Simplified!G2</f>
-        <v>0.12000000000000011</v>
+        <v>0.41999999999999993</v>
       </c>
       <c r="O2" s="18">
         <v>12</v>
@@ -16647,9 +16052,9 @@
         <v>Alpine</v>
       </c>
       <c r="E3" s="2">
-        <v>2.1</v>
-      </c>
-      <c r="G3" s="45"/>
+        <v>2.1120000000000001</v>
+      </c>
+      <c r="G3" s="46"/>
       <c r="H3" s="18">
         <v>12</v>
       </c>
@@ -16661,14 +16066,14 @@
       </c>
       <c r="K3" s="2">
         <f>Ratings!E7</f>
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="M3" s="1">
         <v>1</v>
       </c>
       <c r="N3" s="29">
         <f>Simplified!G4</f>
-        <v>6.0000000000000053E-2</v>
+        <v>0.33000000000000029</v>
       </c>
       <c r="O3" s="1">
         <v>81</v>
@@ -16688,11 +16093,11 @@
         <v>Mercedes</v>
       </c>
       <c r="E4" s="2">
-        <v>2.04</v>
-      </c>
-      <c r="G4" s="45">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="G4" s="46">
         <f>K4-K5</f>
-        <v>6.0000000000000053E-2</v>
+        <v>0.33000000000000029</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -16705,14 +16110,14 @@
       </c>
       <c r="K4" s="2">
         <f>Ratings!E8</f>
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="M4" s="3">
         <v>16</v>
       </c>
       <c r="N4" s="29">
         <f>Simplified!G6</f>
-        <v>-0.54</v>
+        <v>-0.34799999999999986</v>
       </c>
       <c r="O4" s="3">
         <v>44</v>
@@ -16723,18 +16128,18 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="C5" s="12" t="str">
-        <v>Oscar Piastri</v>
+        <v>Liam Lawson</v>
       </c>
       <c r="D5" s="1" t="str">
-        <v>McLaren</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E5" s="2">
         <v>2.04</v>
       </c>
-      <c r="G5" s="45"/>
+      <c r="G5" s="46"/>
       <c r="H5" s="1">
         <v>81</v>
       </c>
@@ -16746,14 +16151,14 @@
       </c>
       <c r="K5" s="2">
         <f>Ratings!E9</f>
-        <v>2.04</v>
+        <v>1.8299999999999998</v>
       </c>
       <c r="M5" s="4">
         <v>3</v>
       </c>
       <c r="N5" s="29">
         <f>Simplified!G8</f>
-        <v>0.11999999999999988</v>
+        <v>0.17999999999999994</v>
       </c>
       <c r="O5" s="4">
         <v>6</v>
@@ -16764,20 +16169,20 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="C6" s="12" t="str">
-        <v>Carlos Sainz</v>
+        <v>Sergio Perez</v>
       </c>
       <c r="D6" s="3" t="str">
-        <v>Williams</v>
+        <v>Cadillac</v>
       </c>
       <c r="E6" s="2">
-        <v>2.04</v>
-      </c>
-      <c r="G6" s="45">
+        <v>2.0279999999999996</v>
+      </c>
+      <c r="G6" s="46">
         <f>K6-K7</f>
-        <v>-0.54</v>
+        <v>-0.34799999999999986</v>
       </c>
       <c r="H6" s="3">
         <v>16</v>
@@ -16790,14 +16195,14 @@
       </c>
       <c r="K6" s="2">
         <f>Ratings!E10</f>
-        <v>1.44</v>
+        <v>1.512</v>
       </c>
       <c r="M6" s="5">
         <v>10</v>
       </c>
       <c r="N6" s="29">
         <f>Simplified!G10</f>
-        <v>-1.2600000000000002</v>
+        <v>-0.9720000000000002</v>
       </c>
       <c r="O6" s="5">
         <v>43</v>
@@ -16808,18 +16213,18 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C7" s="12" t="str">
-        <v>Lewis Hamilton</v>
+        <v>Carlos Sainz</v>
       </c>
       <c r="D7" s="3" t="str">
-        <v>Ferrari</v>
+        <v>Williams</v>
       </c>
       <c r="E7" s="2">
-        <v>1.98</v>
-      </c>
-      <c r="G7" s="45"/>
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="G7" s="46"/>
       <c r="H7" s="3">
         <v>44</v>
       </c>
@@ -16831,14 +16236,14 @@
       </c>
       <c r="K7" s="2">
         <f>Ratings!E11</f>
-        <v>1.98</v>
+        <v>1.8599999999999999</v>
       </c>
       <c r="M7" s="6">
         <v>30</v>
       </c>
       <c r="N7" s="29">
         <f>Simplified!G12</f>
-        <v>-2.86</v>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="O7" s="6">
         <v>41</v>
@@ -16849,20 +16254,20 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C8" s="12" t="str">
-        <v>Sergio Perez</v>
+        <v>Arvid Lindblad</v>
       </c>
       <c r="D8" s="4" t="str">
-        <v>Cadillac</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E8" s="2">
-        <v>1.98</v>
-      </c>
-      <c r="G8" s="45">
+        <v>1.95</v>
+      </c>
+      <c r="G8" s="46">
         <f>K8-K9</f>
-        <v>0.11999999999999988</v>
+        <v>0.17999999999999994</v>
       </c>
       <c r="H8" s="4">
         <v>3</v>
@@ -16875,14 +16280,14 @@
       </c>
       <c r="K8" s="2">
         <f>Ratings!E12</f>
-        <v>1.8599999999999999</v>
+        <v>1.89</v>
       </c>
       <c r="M8" s="7">
         <v>31</v>
       </c>
       <c r="N8" s="29">
         <f>Simplified!G14</f>
-        <v>0.24</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="O8" s="7">
         <v>87</v>
@@ -16893,18 +16298,18 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C9" s="12" t="str">
-        <v>Kimi Antonelli</v>
+        <v>Max Verstappen</v>
       </c>
       <c r="D9" s="4" t="str">
-        <v>Mercedes</v>
+        <v>Red Bull</v>
       </c>
       <c r="E9" s="2">
-        <v>1.92</v>
-      </c>
-      <c r="G9" s="45"/>
+        <v>1.89</v>
+      </c>
+      <c r="G9" s="46"/>
       <c r="H9" s="4">
         <v>6</v>
       </c>
@@ -16916,14 +16321,14 @@
       </c>
       <c r="K9" s="2">
         <f>Ratings!E13</f>
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="M9" s="8">
         <v>55</v>
       </c>
       <c r="N9" s="29">
         <f>Simplified!G16</f>
-        <v>3.04</v>
+        <v>0.56999999999999984</v>
       </c>
       <c r="O9" s="8">
         <v>23</v>
@@ -16934,20 +16339,20 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="C10" s="12" t="str">
-        <v>Nico Hulkenberg</v>
+        <v>Lewis Hamilton</v>
       </c>
       <c r="D10" s="5" t="str">
-        <v>Audi</v>
+        <v>Ferrari</v>
       </c>
       <c r="E10" s="2">
-        <v>1.92</v>
-      </c>
-      <c r="G10" s="45">
+        <v>1.8599999999999999</v>
+      </c>
+      <c r="G10" s="46">
         <f>K10-K11</f>
-        <v>-1.2600000000000002</v>
+        <v>-0.9720000000000002</v>
       </c>
       <c r="H10" s="5">
         <v>10</v>
@@ -16960,14 +16365,14 @@
       </c>
       <c r="K10" s="2">
         <f>Ratings!E14</f>
-        <v>0.84</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="M10" s="9">
         <v>27</v>
       </c>
       <c r="N10" s="29">
         <f>Simplified!G18</f>
-        <v>0.12000000000000011</v>
+        <v>-0.11999999999999988</v>
       </c>
       <c r="O10" s="9">
         <v>5</v>
@@ -16978,18 +16383,18 @@
         <v>10</v>
       </c>
       <c r="B11" s="5">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="C11" s="12" t="str">
-        <v>Max Verstappen</v>
+        <v>Oscar Piastri</v>
       </c>
       <c r="D11" s="5" t="str">
-        <v>Red Bull</v>
+        <v>McLaren</v>
       </c>
       <c r="E11" s="2">
-        <v>1.8599999999999999</v>
-      </c>
-      <c r="G11" s="45"/>
+        <v>1.8299999999999998</v>
+      </c>
+      <c r="G11" s="46"/>
       <c r="H11" s="5">
         <v>43</v>
       </c>
@@ -17001,14 +16406,14 @@
       </c>
       <c r="K11" s="2">
         <f>Ratings!E15</f>
-        <v>2.1</v>
+        <v>2.1120000000000001</v>
       </c>
       <c r="M11" s="10">
         <v>11</v>
       </c>
       <c r="N11" s="29">
         <f>Simplified!G20</f>
-        <v>1.8599999999999999</v>
+        <v>1.3679999999999997</v>
       </c>
       <c r="O11" s="10">
         <v>77</v>
@@ -17019,20 +16424,20 @@
         <v>11</v>
       </c>
       <c r="B12" s="6">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="C12" s="12" t="str">
-        <v>Arvid Lindblad</v>
+        <v>Fernando Alonso</v>
       </c>
       <c r="D12" s="6" t="str">
-        <v>Racing Bulls</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E12" s="2">
-        <v>1.8599999999999999</v>
-      </c>
-      <c r="G12" s="45">
+        <v>1.74</v>
+      </c>
+      <c r="G12" s="46">
         <f>K12-K13</f>
-        <v>-2.86</v>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="H12" s="6">
         <v>30</v>
@@ -17045,14 +16450,14 @@
       </c>
       <c r="K12" s="2">
         <f>Ratings!E16</f>
-        <v>-1</v>
+        <v>2.04</v>
       </c>
       <c r="M12" s="11">
         <v>14</v>
       </c>
       <c r="N12" s="29">
         <f>Simplified!G22</f>
-        <v>0.59999999999999987</v>
+        <v>0.65999999999999992</v>
       </c>
       <c r="O12" s="11">
         <v>18</v>
@@ -17063,18 +16468,18 @@
         <v>12</v>
       </c>
       <c r="B13" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="12" t="str">
-        <v>Gabriel Bortoleto</v>
+        <v>Isack Hadjar</v>
       </c>
       <c r="D13" s="6" t="str">
-        <v>Audi</v>
+        <v>Red Bull</v>
       </c>
       <c r="E13" s="2">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="G13" s="45"/>
+        <v>1.71</v>
+      </c>
+      <c r="G13" s="46"/>
       <c r="H13" s="6">
         <v>41</v>
       </c>
@@ -17086,7 +16491,7 @@
       </c>
       <c r="K13" s="2">
         <f>Ratings!E17</f>
-        <v>1.8599999999999999</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
@@ -17094,20 +16499,20 @@
         <v>13</v>
       </c>
       <c r="B14" s="7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C14" s="12" t="str">
-        <v>Fernando Alonso</v>
+        <v>Gabriel Bortoleto</v>
       </c>
       <c r="D14" s="7" t="str">
-        <v>Aston Martin</v>
+        <v>Audi</v>
       </c>
       <c r="E14" s="2">
-        <v>1.7999999999999998</v>
-      </c>
-      <c r="G14" s="45">
+        <v>1.68</v>
+      </c>
+      <c r="G14" s="46">
         <f>K14-K15</f>
-        <v>0.24</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="H14" s="7">
         <v>31</v>
@@ -17120,7 +16525,7 @@
       </c>
       <c r="K14" s="2">
         <f>Ratings!E18</f>
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
@@ -17128,18 +16533,18 @@
         <v>14</v>
       </c>
       <c r="B15" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C15" s="12" t="str">
-        <v>Isack Hadjar</v>
+        <v>Kimi Antonelli</v>
       </c>
       <c r="D15" s="7" t="str">
-        <v>Red Bull</v>
+        <v>Mercedes</v>
       </c>
       <c r="E15" s="2">
-        <v>1.74</v>
-      </c>
-      <c r="G15" s="45"/>
+        <v>1.65</v>
+      </c>
+      <c r="G15" s="46"/>
       <c r="H15" s="7">
         <v>87</v>
       </c>
@@ -17151,7 +16556,7 @@
       </c>
       <c r="K15" s="2">
         <f>Ratings!E19</f>
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
@@ -17159,20 +16564,20 @@
         <v>15</v>
       </c>
       <c r="B16" s="8">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C16" s="12" t="str">
-        <v>Esteban Ocon</v>
+        <v>Nico Hulkenberg</v>
       </c>
       <c r="D16" s="8" t="str">
-        <v>Hass</v>
+        <v>Audi</v>
       </c>
       <c r="E16" s="2">
-        <v>1.68</v>
-      </c>
-      <c r="G16" s="45">
+        <v>1.56</v>
+      </c>
+      <c r="G16" s="46">
         <f>K16-K17</f>
-        <v>3.04</v>
+        <v>0.56999999999999984</v>
       </c>
       <c r="H16" s="8">
         <v>55</v>
@@ -17185,7 +16590,7 @@
       </c>
       <c r="K16" s="2">
         <f>Ratings!E20</f>
-        <v>2.04</v>
+        <v>2.0099999999999998</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -17202,9 +16607,9 @@
         <v>Ferrari</v>
       </c>
       <c r="E17" s="2">
-        <v>1.44</v>
-      </c>
-      <c r="G17" s="45"/>
+        <v>1.512</v>
+      </c>
+      <c r="G17" s="46"/>
       <c r="H17" s="8">
         <v>23</v>
       </c>
@@ -17216,7 +16621,7 @@
       </c>
       <c r="K17" s="2">
         <f>Ratings!E21</f>
-        <v>-1</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
@@ -17224,10 +16629,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="9">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="C18" s="12" t="str">
-        <v>Oliver Bearman</v>
+        <v>Esteban Ocon</v>
       </c>
       <c r="D18" s="9" t="str">
         <v>Hass</v>
@@ -17235,9 +16640,9 @@
       <c r="E18" s="2">
         <v>1.44</v>
       </c>
-      <c r="G18" s="45">
+      <c r="G18" s="46">
         <f>K18-K19</f>
-        <v>0.12000000000000011</v>
+        <v>-0.11999999999999988</v>
       </c>
       <c r="H18" s="9">
         <v>27</v>
@@ -17250,7 +16655,7 @@
       </c>
       <c r="K18" s="2">
         <f>Ratings!E22</f>
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
@@ -17258,18 +16663,18 @@
         <v>18</v>
       </c>
       <c r="B19" s="9">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C19" s="12" t="str">
-        <v>Lance Stroll</v>
+        <v>Alexander Albon</v>
       </c>
       <c r="D19" s="9" t="str">
-        <v>Aston Martin</v>
+        <v>Williams</v>
       </c>
       <c r="E19" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="G19" s="45"/>
+        <v>1.44</v>
+      </c>
+      <c r="G19" s="46"/>
       <c r="H19" s="9">
         <v>5</v>
       </c>
@@ -17281,7 +16686,7 @@
       </c>
       <c r="K19" s="2">
         <f>Ratings!E23</f>
-        <v>1.7999999999999998</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
@@ -17289,20 +16694,20 @@
         <v>19</v>
       </c>
       <c r="B20" s="10">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="C20" s="12" t="str">
-        <v>Pierre Gasly</v>
+        <v>Oliver Bearman</v>
       </c>
       <c r="D20" s="10" t="str">
-        <v>Alpine</v>
+        <v>Hass</v>
       </c>
       <c r="E20" s="2">
-        <v>0.84</v>
-      </c>
-      <c r="G20" s="45">
+        <v>1.38</v>
+      </c>
+      <c r="G20" s="46">
         <f>K20-K21</f>
-        <v>1.8599999999999999</v>
+        <v>1.3679999999999997</v>
       </c>
       <c r="H20" s="10">
         <v>11</v>
@@ -17315,7 +16720,7 @@
       </c>
       <c r="K20" s="2">
         <f>Ratings!E24</f>
-        <v>1.98</v>
+        <v>2.0279999999999996</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
@@ -17323,18 +16728,18 @@
         <v>20</v>
       </c>
       <c r="B21" s="10">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="C21" s="12" t="str">
-        <v>Valtteri Bottas</v>
+        <v>Pierre Gasly</v>
       </c>
       <c r="D21" s="10" t="str">
-        <v>Cadillac</v>
+        <v>Alpine</v>
       </c>
       <c r="E21" s="2">
-        <v>0.12</v>
-      </c>
-      <c r="G21" s="45"/>
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="G21" s="46"/>
       <c r="H21" s="10">
         <v>77</v>
       </c>
@@ -17346,7 +16751,7 @@
       </c>
       <c r="K21" s="2">
         <f>Ratings!E25</f>
-        <v>0.12</v>
+        <v>0.65999999999999992</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -17354,20 +16759,20 @@
         <v>21</v>
       </c>
       <c r="B22" s="11">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C22" s="12" t="str">
-        <v>Liam Lawson</v>
+        <v>Lance Stroll</v>
       </c>
       <c r="D22" s="11" t="str">
-        <v>Racing Bulls</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E22" s="2">
-        <v>-1</v>
-      </c>
-      <c r="G22" s="45">
+        <v>1.08</v>
+      </c>
+      <c r="G22" s="46">
         <f>K22-K23</f>
-        <v>0.59999999999999987</v>
+        <v>0.65999999999999992</v>
       </c>
       <c r="H22" s="11">
         <v>14</v>
@@ -17380,7 +16785,7 @@
       </c>
       <c r="K22" s="2">
         <f>Ratings!E26</f>
-        <v>1.7999999999999998</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
@@ -17388,18 +16793,18 @@
         <v>22</v>
       </c>
       <c r="B23" s="11">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="C23" s="12" t="str">
-        <v>Alexander Albon</v>
+        <v>Valtteri Bottas</v>
       </c>
       <c r="D23" s="11" t="str">
-        <v>Williams</v>
+        <v>Cadillac</v>
       </c>
       <c r="E23" s="2">
-        <v>-1</v>
-      </c>
-      <c r="G23" s="45"/>
+        <v>0.65999999999999992</v>
+      </c>
+      <c r="G23" s="46"/>
       <c r="H23" s="11">
         <v>18</v>
       </c>
@@ -17411,7 +16816,7 @@
       </c>
       <c r="K23" s="2">
         <f>Ratings!E27</f>
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
     </row>
   </sheetData>
@@ -17429,37 +16834,37 @@
     <mergeCell ref="G16:G17"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:B23 D2:D23">
-    <cfRule type="expression" dxfId="154" priority="8">
+    <cfRule type="expression" dxfId="54" priority="8">
       <formula>$D2="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="153" priority="2">
+    <cfRule type="expression" dxfId="53" priority="2">
       <formula>$D2="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="152" priority="3">
+    <cfRule type="expression" dxfId="52" priority="3">
       <formula>$D2="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="151" priority="4">
+    <cfRule type="expression" dxfId="51" priority="4">
       <formula>$D2="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="150" priority="5">
+    <cfRule type="expression" dxfId="50" priority="5">
       <formula>$D2="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="149" priority="6">
+    <cfRule type="expression" dxfId="49" priority="6">
       <formula>$D2="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="148" priority="7">
+    <cfRule type="expression" dxfId="48" priority="7">
       <formula>$D2="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="147" priority="9">
+    <cfRule type="expression" dxfId="47" priority="9">
       <formula>$D2="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="146" priority="10">
+    <cfRule type="expression" dxfId="46" priority="10">
       <formula>$D2="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="145" priority="11">
+    <cfRule type="expression" dxfId="45" priority="11">
       <formula>$D2="Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="144" priority="12">
+    <cfRule type="expression" dxfId="44" priority="12">
       <formula>$D2="Haas"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17475,7 +16880,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4 G2 G6 G8 G10 G12 G14 G16 G18 G20 G22">
+  <conditionalFormatting sqref="G2 G4 G6 G8 G10 G12 G14 G16 G18 G20 G22">
     <cfRule type="colorScale" priority="57">
       <colorScale>
         <cfvo type="percentile" val="0"/>
@@ -17488,37 +16893,37 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23 J4:J23">
-    <cfRule type="expression" dxfId="143" priority="59">
+    <cfRule type="expression" dxfId="43" priority="59">
       <formula>#REF!="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="142" priority="60">
+    <cfRule type="expression" dxfId="42" priority="60">
       <formula>#REF!="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="141" priority="61">
+    <cfRule type="expression" dxfId="41" priority="61">
       <formula>#REF!="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="140" priority="62">
+    <cfRule type="expression" dxfId="40" priority="62">
       <formula>#REF!="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="139" priority="63">
+    <cfRule type="expression" dxfId="39" priority="63">
       <formula>#REF!="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="64">
+    <cfRule type="expression" dxfId="38" priority="64">
       <formula>#REF!="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="65">
+    <cfRule type="expression" dxfId="37" priority="65">
       <formula>#REF!="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="66">
+    <cfRule type="expression" dxfId="36" priority="66">
       <formula>#REF!="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="135" priority="67">
+    <cfRule type="expression" dxfId="35" priority="67">
       <formula>#REF!="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="134" priority="68">
+    <cfRule type="expression" dxfId="34" priority="68">
       <formula>#REF!="Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="133" priority="69">
+    <cfRule type="expression" dxfId="33" priority="69">
       <formula>#REF!="Haas"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17535,72 +16940,72 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2 O2 H2:H3 J2:J3">
-    <cfRule type="expression" dxfId="132" priority="348">
+    <cfRule type="expression" dxfId="32" priority="348">
       <formula>$J2="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="131" priority="349">
+    <cfRule type="expression" dxfId="31" priority="349">
       <formula>$J2="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="130" priority="350">
+    <cfRule type="expression" dxfId="30" priority="350">
       <formula>$J2="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="351">
+    <cfRule type="expression" dxfId="29" priority="351">
       <formula>$J2="Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="128" priority="352">
+    <cfRule type="expression" dxfId="28" priority="352">
       <formula>$J2="Haas"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="127" priority="345">
+    <cfRule type="expression" dxfId="27" priority="345">
       <formula>$J2="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="126" priority="342">
+    <cfRule type="expression" dxfId="26" priority="342">
       <formula>$J2="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="125" priority="343">
+    <cfRule type="expression" dxfId="25" priority="343">
       <formula>$J2="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="124" priority="344">
+    <cfRule type="expression" dxfId="24" priority="344">
       <formula>$J2="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="123" priority="346">
+    <cfRule type="expression" dxfId="23" priority="346">
       <formula>$J2="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="122" priority="347">
+    <cfRule type="expression" dxfId="22" priority="347">
       <formula>$J2="Ferrari"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3:M12">
-    <cfRule type="expression" dxfId="121" priority="85">
+    <cfRule type="expression" dxfId="21" priority="85">
       <formula>$D1048555="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="120" priority="86">
+    <cfRule type="expression" dxfId="20" priority="86">
       <formula>$D1048555="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="119" priority="87">
+    <cfRule type="expression" dxfId="19" priority="87">
       <formula>$D1048555="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="88">
+    <cfRule type="expression" dxfId="18" priority="88">
       <formula>$D1048555="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="90">
+    <cfRule type="expression" dxfId="17" priority="90">
       <formula>$D1048555="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="116" priority="91">
+    <cfRule type="expression" dxfId="16" priority="91">
       <formula>$D1048555="Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="115" priority="92">
+    <cfRule type="expression" dxfId="15" priority="92">
       <formula>$D1048555="Haas"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="114" priority="82">
+    <cfRule type="expression" dxfId="14" priority="82">
       <formula>$D1048555="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="83">
+    <cfRule type="expression" dxfId="13" priority="83">
       <formula>$D1048555="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="84">
+    <cfRule type="expression" dxfId="12" priority="84">
       <formula>$D1048555="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="111" priority="89">
+    <cfRule type="expression" dxfId="11" priority="89">
       <formula>$D1048555="Red Bull"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17619,37 +17024,37 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:O12">
-    <cfRule type="expression" dxfId="110" priority="71">
+    <cfRule type="expression" dxfId="10" priority="71">
       <formula>$D1048555="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="72">
+    <cfRule type="expression" dxfId="9" priority="72">
       <formula>$D1048555="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="108" priority="73">
+    <cfRule type="expression" dxfId="8" priority="73">
       <formula>$D1048555="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="75">
+    <cfRule type="expression" dxfId="7" priority="75">
       <formula>$D1048555="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="76">
+    <cfRule type="expression" dxfId="6" priority="76">
       <formula>$D1048555="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="105" priority="77">
+    <cfRule type="expression" dxfId="5" priority="77">
       <formula>$D1048555="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="78">
+    <cfRule type="expression" dxfId="4" priority="78">
       <formula>$D1048555="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="74">
+    <cfRule type="expression" dxfId="3" priority="74">
       <formula>$D1048555="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="79">
+    <cfRule type="expression" dxfId="2" priority="79">
       <formula>$D1048555="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="80">
+    <cfRule type="expression" dxfId="1" priority="80">
       <formula>$D1048555="Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="81">
+    <cfRule type="expression" dxfId="0" priority="81">
       <formula>$D1048555="Haas"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/static/data/Ratings.xlsx
+++ b/static/data/Ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Programming\webdev\portfolio\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5723FFCB-36F9-4BDA-B804-36ED04A77BA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F89D03A-D294-4EC8-8420-F6CF6C995385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="2" xr2:uid="{BD88BCC4-2E11-4C36-830D-A75A044EF5A6}"/>
   </bookViews>
@@ -259,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1594" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="75">
   <si>
     <t>RANK</t>
   </si>
@@ -479,6 +479,12 @@
   <si>
     <t>-</t>
   </si>
+  <si>
+    <t>Haas</t>
+  </si>
+  <si>
+    <t>TEAM DRIVER AVG</t>
+  </si>
 </sst>
 </file>
 
@@ -488,7 +494,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="General;&quot;-&quot;;General;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -557,8 +563,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -634,6 +647,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -822,7 +841,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -907,10 +926,28 @@
     <xf numFmtId="164" fontId="1" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -955,14 +992,116 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="70">
+  <dxfs count="103">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFC7F00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF229870"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA7A7AA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFD2C00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF1766D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDE0E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF608CFB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00A0E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF356FC3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF26F0CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE5002C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA8A8AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF638FFD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF1767D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFA2B00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -973,7 +1112,35 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF638FFD"/>
+          <bgColor rgb="FF21976F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF26F0CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE4002C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFD7F00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF366FC3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -988,6 +1155,97 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF21976F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF26F0CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE4002C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFD7F00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF366FC3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF009FE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF638FFD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDBDFE0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA8A8AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFA2B00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF1767D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF009FE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDBDFE0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF638FFD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1022,28 +1280,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
+          <bgColor rgb="FF21976F"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1071,21 +1308,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
+          <bgColor rgb="FF009FE4"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
+          <bgColor rgb="FF366FC3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1113,7 +1343,91 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFA2B00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF21976F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA8A8AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF1767D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDBDFE0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF638FFD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF638FFD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA8A8AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF1767D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFA2B00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF21976F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF26F0CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDBDFE0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1127,7 +1441,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF26F0CE"/>
+          <bgColor rgb="FFFD7F00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF366FC3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF009FE4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1155,6 +1483,41 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF638FFD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDBDFE0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF009FE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF366FC3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFD7F00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF21976F"/>
         </patternFill>
       </fill>
@@ -1162,7 +1525,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
+          <bgColor rgb="FFE4002C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF26F0CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1197,7 +1567,77 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFE4002C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF21976F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA8A8AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFA2B00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF1767D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF26F0CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFDBDFE0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1278,195 +1718,20 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF26F0CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF21976F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF26F0CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF21976F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF21976F"/>
-      <color rgb="FFA8A8AB"/>
-      <color rgb="FFFA2B00"/>
-      <color rgb="FF1767D8"/>
-      <color rgb="FFDBDFE0"/>
-      <color rgb="FF638FFD"/>
-      <color rgb="FF009FE4"/>
-      <color rgb="FF366FC3"/>
-      <color rgb="FFFD7F00"/>
-      <color rgb="FFE4002C"/>
+      <color rgb="FF26F0CE"/>
+      <color rgb="FF229870"/>
+      <color rgb="FFA7A7AA"/>
+      <color rgb="FFFD2C00"/>
+      <color rgb="FF1766D7"/>
+      <color rgb="FFDDE0E1"/>
+      <color rgb="FF608CFB"/>
+      <color rgb="FF00A0E6"/>
+      <color rgb="FF356FC3"/>
+      <color rgb="FFE5002C"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2753,13 +3018,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:83" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
       <c r="F1" s="17"/>
       <c r="G1" s="17"/>
       <c r="H1" s="17"/>
@@ -2840,11 +3105,11 @@
       <c r="CE1" s="17"/>
     </row>
     <row r="2" spans="1:83" s="14" customFormat="1" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="33"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
+      <c r="A2" s="39"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
@@ -2930,296 +3195,296 @@
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
-      <c r="F3" s="38" t="e" vm="1">
+      <c r="F3" s="44" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="35" t="e" vm="2">
+      <c r="G3" s="45"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="41" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="38" t="e" vm="3">
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="44" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="39"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="34" t="e" vm="4">
+      <c r="O3" s="45"/>
+      <c r="P3" s="46"/>
+      <c r="Q3" s="40" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R3" s="35"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="34" t="e" vm="5">
+      <c r="R3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="40" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W3" s="35"/>
-      <c r="X3" s="35"/>
-      <c r="Y3" s="35"/>
-      <c r="Z3" s="36"/>
-      <c r="AA3" s="38" t="e" vm="6">
+      <c r="W3" s="41"/>
+      <c r="X3" s="41"/>
+      <c r="Y3" s="41"/>
+      <c r="Z3" s="42"/>
+      <c r="AA3" s="44" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="40"/>
-      <c r="AD3" s="38" t="e" vm="7">
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="46"/>
+      <c r="AD3" s="44" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="40"/>
-      <c r="AG3" s="38" t="e" vm="8">
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="46"/>
+      <c r="AG3" s="44" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH3" s="39"/>
-      <c r="AI3" s="40"/>
-      <c r="AJ3" s="34" t="e" vm="9">
+      <c r="AH3" s="45"/>
+      <c r="AI3" s="46"/>
+      <c r="AJ3" s="40" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK3" s="35"/>
-      <c r="AL3" s="35"/>
-      <c r="AM3" s="35"/>
-      <c r="AN3" s="36"/>
-      <c r="AO3" s="38" t="e" vm="10">
+      <c r="AK3" s="41"/>
+      <c r="AL3" s="41"/>
+      <c r="AM3" s="41"/>
+      <c r="AN3" s="42"/>
+      <c r="AO3" s="44" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP3" s="39"/>
-      <c r="AQ3" s="40"/>
-      <c r="AR3" s="38" t="e" vm="11">
+      <c r="AP3" s="45"/>
+      <c r="AQ3" s="46"/>
+      <c r="AR3" s="44" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS3" s="39"/>
-      <c r="AT3" s="40"/>
-      <c r="AU3" s="34" t="e" vm="12">
+      <c r="AS3" s="45"/>
+      <c r="AT3" s="46"/>
+      <c r="AU3" s="40" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV3" s="35"/>
-      <c r="AW3" s="35"/>
-      <c r="AX3" s="35"/>
-      <c r="AY3" s="36"/>
-      <c r="AZ3" s="38" t="e" vm="13">
+      <c r="AV3" s="41"/>
+      <c r="AW3" s="41"/>
+      <c r="AX3" s="41"/>
+      <c r="AY3" s="42"/>
+      <c r="AZ3" s="44" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA3" s="39"/>
-      <c r="BB3" s="40"/>
-      <c r="BC3" s="38" t="e" vm="7">
+      <c r="BA3" s="45"/>
+      <c r="BB3" s="46"/>
+      <c r="BC3" s="44" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD3" s="39"/>
-      <c r="BE3" s="40"/>
-      <c r="BF3" s="38" t="e" vm="14">
+      <c r="BD3" s="45"/>
+      <c r="BE3" s="46"/>
+      <c r="BF3" s="44" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG3" s="39"/>
-      <c r="BH3" s="40"/>
-      <c r="BI3" s="34" t="e" vm="15">
+      <c r="BG3" s="45"/>
+      <c r="BH3" s="46"/>
+      <c r="BI3" s="40" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ3" s="35"/>
-      <c r="BK3" s="35"/>
-      <c r="BL3" s="35"/>
-      <c r="BM3" s="36"/>
-      <c r="BN3" s="38" t="e" vm="4">
+      <c r="BJ3" s="41"/>
+      <c r="BK3" s="41"/>
+      <c r="BL3" s="41"/>
+      <c r="BM3" s="42"/>
+      <c r="BN3" s="44" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO3" s="39"/>
-      <c r="BP3" s="40"/>
-      <c r="BQ3" s="38" t="e" vm="16">
+      <c r="BO3" s="45"/>
+      <c r="BP3" s="46"/>
+      <c r="BQ3" s="44" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR3" s="39"/>
-      <c r="BS3" s="40"/>
-      <c r="BT3" s="38" t="e" vm="17">
+      <c r="BR3" s="45"/>
+      <c r="BS3" s="46"/>
+      <c r="BT3" s="44" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU3" s="39"/>
-      <c r="BV3" s="40"/>
-      <c r="BW3" s="38" t="e" vm="4">
+      <c r="BU3" s="45"/>
+      <c r="BV3" s="46"/>
+      <c r="BW3" s="44" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX3" s="39"/>
-      <c r="BY3" s="40"/>
-      <c r="BZ3" s="38" t="e" vm="18">
+      <c r="BX3" s="45"/>
+      <c r="BY3" s="46"/>
+      <c r="BZ3" s="44" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA3" s="39"/>
-      <c r="CB3" s="40"/>
-      <c r="CC3" s="38" t="e" vm="19">
+      <c r="CA3" s="45"/>
+      <c r="CB3" s="46"/>
+      <c r="CC3" s="44" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD3" s="39"/>
-      <c r="CE3" s="40"/>
+      <c r="CD3" s="45"/>
+      <c r="CE3" s="46"/>
     </row>
     <row r="4" spans="1:83" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="E4" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="37"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="37" t="s">
+      <c r="G4" s="43"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="41" t="s">
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="37"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="43" t="s">
+      <c r="O4" s="43"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="45"/>
-      <c r="V4" s="43" t="s">
+      <c r="R4" s="50"/>
+      <c r="S4" s="50"/>
+      <c r="T4" s="50"/>
+      <c r="U4" s="51"/>
+      <c r="V4" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="W4" s="44"/>
-      <c r="X4" s="44"/>
-      <c r="Y4" s="44"/>
-      <c r="Z4" s="45"/>
-      <c r="AA4" s="41" t="s">
+      <c r="W4" s="50"/>
+      <c r="X4" s="50"/>
+      <c r="Y4" s="50"/>
+      <c r="Z4" s="51"/>
+      <c r="AA4" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="AB4" s="37"/>
-      <c r="AC4" s="42"/>
-      <c r="AD4" s="41" t="s">
+      <c r="AB4" s="43"/>
+      <c r="AC4" s="48"/>
+      <c r="AD4" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="AE4" s="37"/>
-      <c r="AF4" s="42"/>
-      <c r="AG4" s="41" t="s">
+      <c r="AE4" s="43"/>
+      <c r="AF4" s="48"/>
+      <c r="AG4" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="AH4" s="37"/>
-      <c r="AI4" s="42"/>
-      <c r="AJ4" s="43" t="s">
+      <c r="AH4" s="43"/>
+      <c r="AI4" s="48"/>
+      <c r="AJ4" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="AK4" s="44"/>
-      <c r="AL4" s="44"/>
-      <c r="AM4" s="44"/>
-      <c r="AN4" s="45"/>
-      <c r="AO4" s="41" t="s">
+      <c r="AK4" s="50"/>
+      <c r="AL4" s="50"/>
+      <c r="AM4" s="50"/>
+      <c r="AN4" s="51"/>
+      <c r="AO4" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="AP4" s="37"/>
-      <c r="AQ4" s="42"/>
-      <c r="AR4" s="41" t="s">
+      <c r="AP4" s="43"/>
+      <c r="AQ4" s="48"/>
+      <c r="AR4" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="AS4" s="37"/>
-      <c r="AT4" s="42"/>
-      <c r="AU4" s="43" t="s">
+      <c r="AS4" s="43"/>
+      <c r="AT4" s="48"/>
+      <c r="AU4" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="AV4" s="44"/>
-      <c r="AW4" s="44"/>
-      <c r="AX4" s="44"/>
-      <c r="AY4" s="45"/>
-      <c r="AZ4" s="41" t="s">
+      <c r="AV4" s="50"/>
+      <c r="AW4" s="50"/>
+      <c r="AX4" s="50"/>
+      <c r="AY4" s="51"/>
+      <c r="AZ4" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="BA4" s="37"/>
-      <c r="BB4" s="42"/>
-      <c r="BC4" s="41" t="s">
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="48"/>
+      <c r="BC4" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="BD4" s="37"/>
-      <c r="BE4" s="42"/>
-      <c r="BF4" s="41" t="s">
+      <c r="BD4" s="43"/>
+      <c r="BE4" s="48"/>
+      <c r="BF4" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="BG4" s="37"/>
-      <c r="BH4" s="42"/>
-      <c r="BI4" s="43" t="s">
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="48"/>
+      <c r="BI4" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="BJ4" s="44"/>
-      <c r="BK4" s="44"/>
-      <c r="BL4" s="44"/>
-      <c r="BM4" s="45"/>
-      <c r="BN4" s="41" t="s">
+      <c r="BJ4" s="50"/>
+      <c r="BK4" s="50"/>
+      <c r="BL4" s="50"/>
+      <c r="BM4" s="51"/>
+      <c r="BN4" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="BO4" s="37"/>
-      <c r="BP4" s="42"/>
-      <c r="BQ4" s="41" t="s">
+      <c r="BO4" s="43"/>
+      <c r="BP4" s="48"/>
+      <c r="BQ4" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="BR4" s="37"/>
-      <c r="BS4" s="42"/>
-      <c r="BT4" s="41" t="s">
+      <c r="BR4" s="43"/>
+      <c r="BS4" s="48"/>
+      <c r="BT4" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="BU4" s="37"/>
-      <c r="BV4" s="42"/>
-      <c r="BW4" s="41" t="s">
+      <c r="BU4" s="43"/>
+      <c r="BV4" s="48"/>
+      <c r="BW4" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="BX4" s="37"/>
-      <c r="BY4" s="42"/>
-      <c r="BZ4" s="41" t="s">
+      <c r="BX4" s="43"/>
+      <c r="BY4" s="48"/>
+      <c r="BZ4" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="CA4" s="37"/>
-      <c r="CB4" s="42"/>
-      <c r="CC4" s="41" t="s">
+      <c r="CA4" s="43"/>
+      <c r="CB4" s="48"/>
+      <c r="CC4" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="CD4" s="37"/>
-      <c r="CE4" s="42"/>
+      <c r="CD4" s="43"/>
+      <c r="CE4" s="48"/>
     </row>
     <row r="5" spans="1:83" s="16" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
+      <c r="A5" s="43"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
       <c r="F5" s="22" t="s">
         <v>26</v>
       </c>
@@ -3468,9 +3733,9 @@
       <c r="D6" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <f>IFERROR(AVERAGE(H6,M6,P6,U6,Z6,AC6,AF6,AI6,AN6,AQ6,AT6,AY6,BB6,BE6,BH6,BM6,BP6,BS6,BV6,BY6,CB6,CE6),-1)</f>
-        <v>2.0699999999999998</v>
+        <v>8.6819999999999986</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>72</v>
@@ -3530,15 +3795,15 @@
       <c r="W6" s="21">
         <v>8.75</v>
       </c>
-      <c r="X6" s="21" t="s">
-        <v>72</v>
+      <c r="X6" s="21">
+        <v>8.6999999999999993</v>
       </c>
       <c r="Y6" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z6" s="24">
         <f>IF(AND(V6="-", W6="-", X6="-", Y6="-"), "-", (IFERROR(AVERAGE(V6:W6), 0)*0.24) + (IFERROR(AVERAGE(X6:Y6), 0)*0.76))</f>
-        <v>2.0699999999999998</v>
+        <v>8.6819999999999986</v>
       </c>
       <c r="AA6" s="21" t="s">
         <v>72</v>
@@ -3742,9 +4007,9 @@
       <c r="D7" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <f t="shared" ref="E7:E27" si="0">IFERROR(AVERAGE(H7,M7,P7,U7,Z7,AC7,AF7,AI7,AN7,AQ7,AT7,AY7,BB7,BE7,BH7,BM7,BP7,BS7,BV7,BY7,CB7,CE7),-1)</f>
-        <v>1.65</v>
+        <v>8.1859999999999999</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>72</v>
@@ -3804,15 +4069,15 @@
       <c r="W7" s="21">
         <v>5.75</v>
       </c>
-      <c r="X7" s="21" t="s">
-        <v>72</v>
+      <c r="X7" s="21">
+        <v>8.6</v>
       </c>
       <c r="Y7" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z7" s="24">
         <f t="shared" ref="Z7:Z27" si="5">IF(AND(V7="-", W7="-", X7="-", Y7="-"), "-", (IFERROR(AVERAGE(V7:W7), 0)*0.24) + (IFERROR(AVERAGE(X7:Y7), 0)*0.76))</f>
-        <v>1.65</v>
+        <v>8.1859999999999999</v>
       </c>
       <c r="AA7" s="21" t="s">
         <v>72</v>
@@ -4016,9 +4281,9 @@
       <c r="D8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <f t="shared" si="0"/>
-        <v>2.16</v>
+        <v>8.9359999999999999</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>72</v>
@@ -4073,20 +4338,20 @@
         <v>-</v>
       </c>
       <c r="V8" s="28">
-        <v>8.75</v>
+        <v>8.9</v>
       </c>
       <c r="W8" s="21">
-        <v>9.25</v>
-      </c>
-      <c r="X8" s="21" t="s">
-        <v>72</v>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="X8" s="21">
+        <v>8.9</v>
       </c>
       <c r="Y8" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z8" s="24">
         <f t="shared" si="5"/>
-        <v>2.16</v>
+        <v>8.9359999999999999</v>
       </c>
       <c r="AA8" s="21" t="s">
         <v>72</v>
@@ -4290,9 +4555,9 @@
       <c r="D9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <f t="shared" si="0"/>
-        <v>1.8299999999999998</v>
+        <v>8.5300000000000011</v>
       </c>
       <c r="F9" s="21" t="s">
         <v>72</v>
@@ -4347,20 +4612,20 @@
         <v>-</v>
       </c>
       <c r="V9" s="28">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="W9" s="21">
         <v>6.75</v>
       </c>
-      <c r="X9" s="21" t="s">
-        <v>72</v>
+      <c r="X9" s="21">
+        <v>8.8000000000000007</v>
       </c>
       <c r="Y9" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z9" s="24">
         <f t="shared" si="5"/>
-        <v>1.8299999999999998</v>
+        <v>8.5300000000000011</v>
       </c>
       <c r="AA9" s="21" t="s">
         <v>72</v>
@@ -4564,9 +4829,9 @@
       <c r="D10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <f t="shared" si="0"/>
-        <v>1.512</v>
+        <v>7.3780000000000001</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>72</v>
@@ -4621,20 +4886,20 @@
         <v>-</v>
       </c>
       <c r="V10" s="28">
-        <v>6</v>
+        <v>6.75</v>
       </c>
       <c r="W10" s="21">
         <v>6.6</v>
       </c>
-      <c r="X10" s="21" t="s">
-        <v>72</v>
+      <c r="X10" s="21">
+        <v>7.6</v>
       </c>
       <c r="Y10" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z10" s="24">
         <f t="shared" si="5"/>
-        <v>1.512</v>
+        <v>7.3780000000000001</v>
       </c>
       <c r="AA10" s="21" t="s">
         <v>72</v>
@@ -4838,9 +5103,9 @@
       <c r="D11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="30">
         <f t="shared" si="0"/>
-        <v>1.8599999999999999</v>
+        <v>7.9399999999999995</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>72</v>
@@ -4900,15 +5165,15 @@
       <c r="W11" s="21">
         <v>7.25</v>
       </c>
-      <c r="X11" s="21" t="s">
-        <v>72</v>
+      <c r="X11" s="21">
+        <v>8</v>
       </c>
       <c r="Y11" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z11" s="24">
         <f t="shared" si="5"/>
-        <v>1.8599999999999999</v>
+        <v>7.9399999999999995</v>
       </c>
       <c r="AA11" s="21" t="s">
         <v>72</v>
@@ -5112,9 +5377,9 @@
       <c r="D12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="30">
         <f t="shared" si="0"/>
-        <v>1.89</v>
+        <v>7.9399999999999995</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>72</v>
@@ -5169,20 +5434,20 @@
         <v>-</v>
       </c>
       <c r="V12" s="28">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="W12" s="21">
         <v>8</v>
       </c>
-      <c r="X12" s="21" t="s">
-        <v>72</v>
+      <c r="X12" s="21">
+        <v>8</v>
       </c>
       <c r="Y12" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z12" s="24">
         <f t="shared" si="5"/>
-        <v>1.89</v>
+        <v>7.9399999999999995</v>
       </c>
       <c r="AA12" s="21" t="s">
         <v>72</v>
@@ -5386,9 +5651,9 @@
       <c r="D13" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <f t="shared" si="0"/>
-        <v>1.71</v>
+        <v>7.79</v>
       </c>
       <c r="F13" s="21" t="s">
         <v>72</v>
@@ -5448,15 +5713,15 @@
       <c r="W13" s="21">
         <v>7</v>
       </c>
-      <c r="X13" s="21" t="s">
-        <v>72</v>
+      <c r="X13" s="21">
+        <v>8</v>
       </c>
       <c r="Y13" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z13" s="24">
         <f t="shared" si="5"/>
-        <v>1.71</v>
+        <v>7.79</v>
       </c>
       <c r="AA13" s="21" t="s">
         <v>72</v>
@@ -5660,9 +5925,9 @@
       <c r="D14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="30">
         <f t="shared" si="0"/>
-        <v>1.1399999999999999</v>
+        <v>6.08</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>72</v>
@@ -5722,15 +5987,15 @@
       <c r="W14" s="21">
         <v>6</v>
       </c>
-      <c r="X14" s="21" t="s">
-        <v>72</v>
+      <c r="X14" s="21">
+        <v>6.5</v>
       </c>
       <c r="Y14" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z14" s="24">
         <f t="shared" si="5"/>
-        <v>1.1399999999999999</v>
+        <v>6.08</v>
       </c>
       <c r="AA14" s="21" t="s">
         <v>72</v>
@@ -5934,9 +6199,9 @@
       <c r="D15" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="30">
         <f t="shared" si="0"/>
-        <v>2.1120000000000001</v>
+        <v>8.1980000000000004</v>
       </c>
       <c r="F15" s="21" t="s">
         <v>72</v>
@@ -5994,17 +6259,17 @@
         <v>8.5</v>
       </c>
       <c r="W15" s="21">
-        <v>9.1</v>
-      </c>
-      <c r="X15" s="21" t="s">
-        <v>72</v>
+        <v>9.15</v>
+      </c>
+      <c r="X15" s="21">
+        <v>8</v>
       </c>
       <c r="Y15" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z15" s="24">
         <f t="shared" si="5"/>
-        <v>2.1120000000000001</v>
+        <v>8.1980000000000004</v>
       </c>
       <c r="AA15" s="21" t="s">
         <v>72</v>
@@ -6208,9 +6473,9 @@
       <c r="D16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <f t="shared" si="0"/>
-        <v>2.04</v>
+        <v>7.36</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>72</v>
@@ -6270,15 +6535,15 @@
       <c r="W16" s="21">
         <v>8.5</v>
       </c>
-      <c r="X16" s="21" t="s">
-        <v>72</v>
+      <c r="X16" s="21">
+        <v>7</v>
       </c>
       <c r="Y16" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z16" s="24">
         <f t="shared" si="5"/>
-        <v>2.04</v>
+        <v>7.36</v>
       </c>
       <c r="AA16" s="21" t="s">
         <v>72</v>
@@ -6482,9 +6747,9 @@
       <c r="D17" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <f t="shared" si="0"/>
-        <v>1.95</v>
+        <v>8.1059999999999999</v>
       </c>
       <c r="F17" s="21" t="s">
         <v>72</v>
@@ -6544,15 +6809,15 @@
       <c r="W17" s="21">
         <v>8.5</v>
       </c>
-      <c r="X17" s="21" t="s">
-        <v>72</v>
+      <c r="X17" s="21">
+        <v>8.1</v>
       </c>
       <c r="Y17" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z17" s="24">
         <f t="shared" si="5"/>
-        <v>1.95</v>
+        <v>8.1059999999999999</v>
       </c>
       <c r="AA17" s="21" t="s">
         <v>72</v>
@@ -6754,11 +7019,11 @@
         <v>53</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="31">
+        <v>73</v>
+      </c>
+      <c r="E18" s="30">
         <f t="shared" si="0"/>
-        <v>1.44</v>
+        <v>5.24</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>72</v>
@@ -6818,15 +7083,15 @@
       <c r="W18" s="21">
         <v>5</v>
       </c>
-      <c r="X18" s="21" t="s">
-        <v>72</v>
+      <c r="X18" s="21">
+        <v>5</v>
       </c>
       <c r="Y18" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z18" s="24">
         <f t="shared" si="5"/>
-        <v>1.44</v>
+        <v>5.24</v>
       </c>
       <c r="AA18" s="21" t="s">
         <v>72</v>
@@ -7028,11 +7293,11 @@
         <v>54</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="31">
+        <v>73</v>
+      </c>
+      <c r="E19" s="30">
         <f t="shared" si="0"/>
-        <v>1.38</v>
+        <v>6.51</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>72</v>
@@ -7092,15 +7357,15 @@
       <c r="W19" s="21">
         <v>5.5</v>
       </c>
-      <c r="X19" s="21" t="s">
-        <v>72</v>
+      <c r="X19" s="21">
+        <v>6.75</v>
       </c>
       <c r="Y19" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z19" s="24">
         <f t="shared" si="5"/>
-        <v>1.38</v>
+        <v>6.51</v>
       </c>
       <c r="AA19" s="21" t="s">
         <v>72</v>
@@ -7304,9 +7569,9 @@
       <c r="D20" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="30">
         <f t="shared" si="0"/>
-        <v>2.0099999999999998</v>
+        <v>8.4699999999999989</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>72</v>
@@ -7366,15 +7631,15 @@
       <c r="W20" s="21">
         <v>8</v>
       </c>
-      <c r="X20" s="21" t="s">
-        <v>72</v>
+      <c r="X20" s="21">
+        <v>8.5</v>
       </c>
       <c r="Y20" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z20" s="24">
         <f t="shared" si="5"/>
-        <v>2.0099999999999998</v>
+        <v>8.4699999999999989</v>
       </c>
       <c r="AA20" s="21" t="s">
         <v>72</v>
@@ -7578,9 +7843,9 @@
       <c r="D21" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="30">
         <f t="shared" si="0"/>
-        <v>1.44</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>72</v>
@@ -7640,15 +7905,15 @@
       <c r="W21" s="21">
         <v>6</v>
       </c>
-      <c r="X21" s="21" t="s">
-        <v>72</v>
+      <c r="X21" s="21">
+        <v>4</v>
       </c>
       <c r="Y21" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z21" s="24">
         <f t="shared" si="5"/>
-        <v>1.44</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="AA21" s="21" t="s">
         <v>72</v>
@@ -7852,9 +8117,9 @@
       <c r="D22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="30">
         <f t="shared" si="0"/>
-        <v>1.56</v>
+        <v>7.61</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>72</v>
@@ -7909,20 +8174,20 @@
         <v>-</v>
       </c>
       <c r="V22" s="28">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="W22" s="21">
         <v>5</v>
       </c>
-      <c r="X22" s="21" t="s">
-        <v>72</v>
+      <c r="X22" s="21">
+        <v>8</v>
       </c>
       <c r="Y22" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z22" s="24">
         <f t="shared" si="5"/>
-        <v>1.56</v>
+        <v>7.61</v>
       </c>
       <c r="AA22" s="21" t="s">
         <v>72</v>
@@ -8126,9 +8391,9 @@
       <c r="D23" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E23" s="30">
         <f t="shared" si="0"/>
-        <v>1.68</v>
+        <v>7.5399999999999991</v>
       </c>
       <c r="F23" s="21" t="s">
         <v>72</v>
@@ -8183,20 +8448,20 @@
         <v>-</v>
       </c>
       <c r="V23" s="28">
-        <v>7.5</v>
+        <v>7.25</v>
       </c>
       <c r="W23" s="21">
         <v>6.5</v>
       </c>
-      <c r="X23" s="21" t="s">
-        <v>72</v>
+      <c r="X23" s="21">
+        <v>7.75</v>
       </c>
       <c r="Y23" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z23" s="24">
         <f t="shared" si="5"/>
-        <v>1.68</v>
+        <v>7.5399999999999991</v>
       </c>
       <c r="AA23" s="21" t="s">
         <v>72</v>
@@ -8400,9 +8665,9 @@
       <c r="D24" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="30">
         <f t="shared" si="0"/>
-        <v>2.0279999999999996</v>
+        <v>7.9179999999999993</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>72</v>
@@ -8462,15 +8727,15 @@
       <c r="W24" s="21">
         <v>8.6</v>
       </c>
-      <c r="X24" s="21" t="s">
-        <v>72</v>
+      <c r="X24" s="21">
+        <v>7.75</v>
       </c>
       <c r="Y24" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z24" s="24">
         <f t="shared" si="5"/>
-        <v>2.0279999999999996</v>
+        <v>7.9179999999999993</v>
       </c>
       <c r="AA24" s="21" t="s">
         <v>72</v>
@@ -8674,9 +8939,9 @@
       <c r="D25" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="30">
         <f t="shared" si="0"/>
-        <v>0.65999999999999992</v>
+        <v>2.36</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>72</v>
@@ -8731,20 +8996,20 @@
         <v>-</v>
       </c>
       <c r="V25" s="28">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="W25" s="21">
         <v>5</v>
       </c>
-      <c r="X25" s="21" t="s">
-        <v>72</v>
+      <c r="X25" s="21">
+        <v>2</v>
       </c>
       <c r="Y25" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z25" s="24">
         <f t="shared" si="5"/>
-        <v>0.65999999999999992</v>
+        <v>2.36</v>
       </c>
       <c r="AA25" s="21" t="s">
         <v>72</v>
@@ -8948,9 +9213,9 @@
       <c r="D26" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="30">
         <f t="shared" si="0"/>
-        <v>1.74</v>
+        <v>7.82</v>
       </c>
       <c r="F26" s="21" t="s">
         <v>72</v>
@@ -9010,15 +9275,15 @@
       <c r="W26" s="21">
         <v>7</v>
       </c>
-      <c r="X26" s="21" t="s">
-        <v>72</v>
+      <c r="X26" s="21">
+        <v>8</v>
       </c>
       <c r="Y26" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z26" s="24">
         <f t="shared" si="5"/>
-        <v>1.74</v>
+        <v>7.82</v>
       </c>
       <c r="AA26" s="21" t="s">
         <v>72</v>
@@ -9222,9 +9487,9 @@
       <c r="D27" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="30">
         <f t="shared" si="0"/>
-        <v>1.08</v>
+        <v>2.3719999999999999</v>
       </c>
       <c r="F27" s="21" t="s">
         <v>72</v>
@@ -9284,15 +9549,15 @@
       <c r="W27" s="21">
         <v>5</v>
       </c>
-      <c r="X27" s="21" t="s">
-        <v>72</v>
+      <c r="X27" s="21">
+        <v>1.7</v>
       </c>
       <c r="Y27" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z27" s="24">
         <f t="shared" si="5"/>
-        <v>1.08</v>
+        <v>2.3719999999999999</v>
       </c>
       <c r="AA27" s="21" t="s">
         <v>72</v>
@@ -9648,296 +9913,296 @@
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
-      <c r="F29" s="34" t="e" vm="1">
+      <c r="F29" s="40" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G29" s="35"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="35" t="e" vm="2">
+      <c r="G29" s="41"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="41" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="34" t="e" vm="3">
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="40" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O29" s="35"/>
-      <c r="P29" s="36"/>
-      <c r="Q29" s="35" t="e" vm="4">
+      <c r="O29" s="41"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="41" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
-      <c r="T29" s="35"/>
-      <c r="U29" s="36"/>
-      <c r="V29" s="34" t="e" vm="5">
+      <c r="R29" s="41"/>
+      <c r="S29" s="41"/>
+      <c r="T29" s="41"/>
+      <c r="U29" s="42"/>
+      <c r="V29" s="40" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W29" s="35"/>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="35"/>
-      <c r="Z29" s="35"/>
-      <c r="AA29" s="34" t="e" vm="6">
+      <c r="W29" s="41"/>
+      <c r="X29" s="41"/>
+      <c r="Y29" s="41"/>
+      <c r="Z29" s="41"/>
+      <c r="AA29" s="40" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB29" s="35"/>
-      <c r="AC29" s="36"/>
-      <c r="AD29" s="34" t="e" vm="7">
+      <c r="AB29" s="41"/>
+      <c r="AC29" s="42"/>
+      <c r="AD29" s="40" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE29" s="35"/>
-      <c r="AF29" s="36"/>
-      <c r="AG29" s="34" t="e" vm="8">
+      <c r="AE29" s="41"/>
+      <c r="AF29" s="42"/>
+      <c r="AG29" s="40" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH29" s="35"/>
-      <c r="AI29" s="36"/>
-      <c r="AJ29" s="35" t="e" vm="9">
+      <c r="AH29" s="41"/>
+      <c r="AI29" s="42"/>
+      <c r="AJ29" s="41" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK29" s="35"/>
-      <c r="AL29" s="35"/>
-      <c r="AM29" s="35"/>
-      <c r="AN29" s="35"/>
-      <c r="AO29" s="34" t="e" vm="10">
+      <c r="AK29" s="41"/>
+      <c r="AL29" s="41"/>
+      <c r="AM29" s="41"/>
+      <c r="AN29" s="41"/>
+      <c r="AO29" s="40" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP29" s="35"/>
-      <c r="AQ29" s="36"/>
-      <c r="AR29" s="34" t="e" vm="11">
+      <c r="AP29" s="41"/>
+      <c r="AQ29" s="42"/>
+      <c r="AR29" s="40" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS29" s="35"/>
-      <c r="AT29" s="36"/>
-      <c r="AU29" s="35" t="e" vm="12">
+      <c r="AS29" s="41"/>
+      <c r="AT29" s="42"/>
+      <c r="AU29" s="41" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV29" s="35"/>
-      <c r="AW29" s="35"/>
-      <c r="AX29" s="35"/>
-      <c r="AY29" s="35"/>
-      <c r="AZ29" s="34" t="e" vm="13">
+      <c r="AV29" s="41"/>
+      <c r="AW29" s="41"/>
+      <c r="AX29" s="41"/>
+      <c r="AY29" s="41"/>
+      <c r="AZ29" s="40" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA29" s="35"/>
-      <c r="BB29" s="36"/>
-      <c r="BC29" s="34" t="e" vm="7">
+      <c r="BA29" s="41"/>
+      <c r="BB29" s="42"/>
+      <c r="BC29" s="40" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD29" s="35"/>
-      <c r="BE29" s="36"/>
-      <c r="BF29" s="34" t="e" vm="14">
+      <c r="BD29" s="41"/>
+      <c r="BE29" s="42"/>
+      <c r="BF29" s="40" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG29" s="35"/>
-      <c r="BH29" s="36"/>
-      <c r="BI29" s="35" t="e" vm="15">
+      <c r="BG29" s="41"/>
+      <c r="BH29" s="42"/>
+      <c r="BI29" s="41" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ29" s="35"/>
-      <c r="BK29" s="35"/>
-      <c r="BL29" s="35"/>
-      <c r="BM29" s="35"/>
-      <c r="BN29" s="34" t="e" vm="4">
+      <c r="BJ29" s="41"/>
+      <c r="BK29" s="41"/>
+      <c r="BL29" s="41"/>
+      <c r="BM29" s="41"/>
+      <c r="BN29" s="40" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO29" s="35"/>
-      <c r="BP29" s="36"/>
-      <c r="BQ29" s="34" t="e" vm="16">
+      <c r="BO29" s="41"/>
+      <c r="BP29" s="42"/>
+      <c r="BQ29" s="40" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR29" s="35"/>
-      <c r="BS29" s="36"/>
-      <c r="BT29" s="34" t="e" vm="17">
+      <c r="BR29" s="41"/>
+      <c r="BS29" s="42"/>
+      <c r="BT29" s="40" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU29" s="35"/>
-      <c r="BV29" s="36"/>
-      <c r="BW29" s="34" t="e" vm="4">
+      <c r="BU29" s="41"/>
+      <c r="BV29" s="42"/>
+      <c r="BW29" s="40" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX29" s="35"/>
-      <c r="BY29" s="36"/>
-      <c r="BZ29" s="34" t="e" vm="18">
+      <c r="BX29" s="41"/>
+      <c r="BY29" s="42"/>
+      <c r="BZ29" s="40" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA29" s="35"/>
-      <c r="CB29" s="36"/>
-      <c r="CC29" s="34" t="e" vm="19">
+      <c r="CA29" s="41"/>
+      <c r="CB29" s="42"/>
+      <c r="CC29" s="40" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD29" s="35"/>
-      <c r="CE29" s="36"/>
+      <c r="CD29" s="41"/>
+      <c r="CE29" s="42"/>
     </row>
     <row r="30" spans="1:83" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="37" t="s">
+      <c r="A30" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="37" t="s">
+      <c r="C30" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="D30" s="37" t="s">
+      <c r="D30" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="37" t="s">
+      <c r="E30" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="F30" s="41" t="s">
+      <c r="F30" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="G30" s="37"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="37" t="s">
+      <c r="G30" s="43"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="J30" s="37"/>
-      <c r="K30" s="37"/>
-      <c r="L30" s="37"/>
-      <c r="M30" s="37"/>
-      <c r="N30" s="41" t="s">
+      <c r="J30" s="43"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="43"/>
+      <c r="M30" s="43"/>
+      <c r="N30" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="O30" s="37"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="43" t="s">
+      <c r="O30" s="43"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="R30" s="44"/>
-      <c r="S30" s="44"/>
-      <c r="T30" s="44"/>
-      <c r="U30" s="45"/>
-      <c r="V30" s="43" t="s">
+      <c r="R30" s="50"/>
+      <c r="S30" s="50"/>
+      <c r="T30" s="50"/>
+      <c r="U30" s="51"/>
+      <c r="V30" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="W30" s="44"/>
-      <c r="X30" s="44"/>
-      <c r="Y30" s="44"/>
-      <c r="Z30" s="45"/>
-      <c r="AA30" s="41" t="s">
+      <c r="W30" s="50"/>
+      <c r="X30" s="50"/>
+      <c r="Y30" s="50"/>
+      <c r="Z30" s="51"/>
+      <c r="AA30" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="AB30" s="37"/>
-      <c r="AC30" s="42"/>
-      <c r="AD30" s="41" t="s">
+      <c r="AB30" s="43"/>
+      <c r="AC30" s="48"/>
+      <c r="AD30" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="AE30" s="37"/>
-      <c r="AF30" s="42"/>
-      <c r="AG30" s="41" t="s">
+      <c r="AE30" s="43"/>
+      <c r="AF30" s="48"/>
+      <c r="AG30" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="AH30" s="37"/>
-      <c r="AI30" s="42"/>
-      <c r="AJ30" s="37" t="s">
+      <c r="AH30" s="43"/>
+      <c r="AI30" s="48"/>
+      <c r="AJ30" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="AK30" s="37"/>
-      <c r="AL30" s="37"/>
-      <c r="AM30" s="37"/>
-      <c r="AN30" s="37"/>
-      <c r="AO30" s="41" t="s">
+      <c r="AK30" s="43"/>
+      <c r="AL30" s="43"/>
+      <c r="AM30" s="43"/>
+      <c r="AN30" s="43"/>
+      <c r="AO30" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="AP30" s="37"/>
-      <c r="AQ30" s="42"/>
-      <c r="AR30" s="41" t="s">
+      <c r="AP30" s="43"/>
+      <c r="AQ30" s="48"/>
+      <c r="AR30" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="AS30" s="37"/>
-      <c r="AT30" s="42"/>
-      <c r="AU30" s="43" t="s">
+      <c r="AS30" s="43"/>
+      <c r="AT30" s="48"/>
+      <c r="AU30" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="AV30" s="44"/>
-      <c r="AW30" s="44"/>
-      <c r="AX30" s="44"/>
-      <c r="AY30" s="45"/>
-      <c r="AZ30" s="41" t="s">
+      <c r="AV30" s="50"/>
+      <c r="AW30" s="50"/>
+      <c r="AX30" s="50"/>
+      <c r="AY30" s="51"/>
+      <c r="AZ30" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="BA30" s="37"/>
-      <c r="BB30" s="42"/>
-      <c r="BC30" s="41" t="s">
+      <c r="BA30" s="43"/>
+      <c r="BB30" s="48"/>
+      <c r="BC30" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="BD30" s="37"/>
-      <c r="BE30" s="42"/>
-      <c r="BF30" s="41" t="s">
+      <c r="BD30" s="43"/>
+      <c r="BE30" s="48"/>
+      <c r="BF30" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="BG30" s="37"/>
-      <c r="BH30" s="42"/>
-      <c r="BI30" s="43" t="s">
+      <c r="BG30" s="43"/>
+      <c r="BH30" s="48"/>
+      <c r="BI30" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="BJ30" s="44"/>
-      <c r="BK30" s="44"/>
-      <c r="BL30" s="44"/>
-      <c r="BM30" s="45"/>
-      <c r="BN30" s="41" t="s">
+      <c r="BJ30" s="50"/>
+      <c r="BK30" s="50"/>
+      <c r="BL30" s="50"/>
+      <c r="BM30" s="51"/>
+      <c r="BN30" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="BO30" s="37"/>
-      <c r="BP30" s="42"/>
-      <c r="BQ30" s="41" t="s">
+      <c r="BO30" s="43"/>
+      <c r="BP30" s="48"/>
+      <c r="BQ30" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="BR30" s="37"/>
-      <c r="BS30" s="42"/>
-      <c r="BT30" s="41" t="s">
+      <c r="BR30" s="43"/>
+      <c r="BS30" s="48"/>
+      <c r="BT30" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="BU30" s="37"/>
-      <c r="BV30" s="42"/>
-      <c r="BW30" s="41" t="s">
+      <c r="BU30" s="43"/>
+      <c r="BV30" s="48"/>
+      <c r="BW30" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="BX30" s="37"/>
-      <c r="BY30" s="42"/>
-      <c r="BZ30" s="41" t="s">
+      <c r="BX30" s="43"/>
+      <c r="BY30" s="48"/>
+      <c r="BZ30" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="CA30" s="37"/>
-      <c r="CB30" s="42"/>
-      <c r="CC30" s="41" t="s">
+      <c r="CA30" s="43"/>
+      <c r="CB30" s="48"/>
+      <c r="CC30" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="CD30" s="37"/>
-      <c r="CE30" s="42"/>
+      <c r="CD30" s="43"/>
+      <c r="CE30" s="48"/>
     </row>
     <row r="31" spans="1:83" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="37"/>
-      <c r="B31" s="37"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="37"/>
+      <c r="A31" s="43"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
       <c r="F31" s="22" t="s">
         <v>26</v>
       </c>
@@ -10187,8 +10452,8 @@
       <c r="D32" s="18" t="str">
         <v>McLaren</v>
       </c>
-      <c r="E32" s="31">
-        <v>2.16</v>
+      <c r="E32" s="30">
+        <v>8.9359999999999999</v>
       </c>
       <c r="F32" s="21" t="str">
         <v>-</v>
@@ -10239,19 +10504,19 @@
         <v>-</v>
       </c>
       <c r="V32" s="28">
-        <v>8.75</v>
+        <v>8.9</v>
       </c>
       <c r="W32" s="23">
-        <v>9.25</v>
-      </c>
-      <c r="X32" s="23" t="str">
-        <v>-</v>
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="X32" s="23">
+        <v>8.9</v>
       </c>
       <c r="Y32" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z32" s="24">
-        <v>2.16</v>
+        <v>8.9359999999999999</v>
       </c>
       <c r="AA32" s="28" t="str">
         <v>-</v>
@@ -10430,16 +10695,16 @@
         <v>2</v>
       </c>
       <c r="B33" s="18">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C33" s="12" t="str">
-        <v>Franco Colapinto</v>
+        <v>George Russell</v>
       </c>
       <c r="D33" s="18" t="str">
-        <v>Alpine</v>
-      </c>
-      <c r="E33" s="31">
-        <v>2.1120000000000001</v>
+        <v>Mercedes</v>
+      </c>
+      <c r="E33" s="30">
+        <v>8.6819999999999986</v>
       </c>
       <c r="F33" s="21" t="str">
         <v>-</v>
@@ -10493,16 +10758,16 @@
         <v>8.5</v>
       </c>
       <c r="W33" s="23">
-        <v>9.1</v>
-      </c>
-      <c r="X33" s="23" t="str">
-        <v>-</v>
+        <v>8.75</v>
+      </c>
+      <c r="X33" s="23">
+        <v>8.6999999999999993</v>
       </c>
       <c r="Y33" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z33" s="24">
-        <v>2.1120000000000001</v>
+        <v>8.6819999999999986</v>
       </c>
       <c r="AA33" s="28" t="str">
         <v>-</v>
@@ -10681,16 +10946,16 @@
         <v>3</v>
       </c>
       <c r="B34" s="1">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C34" s="12" t="str">
-        <v>George Russell</v>
+        <v>Oscar Piastri</v>
       </c>
       <c r="D34" s="1" t="str">
-        <v>Mercedes</v>
-      </c>
-      <c r="E34" s="31">
-        <v>2.0699999999999998</v>
+        <v>McLaren</v>
+      </c>
+      <c r="E34" s="30">
+        <v>8.5300000000000011</v>
       </c>
       <c r="F34" s="21" t="str">
         <v>-</v>
@@ -10741,19 +11006,19 @@
         <v>-</v>
       </c>
       <c r="V34" s="28">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="W34" s="23">
-        <v>8.75</v>
-      </c>
-      <c r="X34" s="23" t="str">
-        <v>-</v>
+        <v>6.75</v>
+      </c>
+      <c r="X34" s="23">
+        <v>8.8000000000000007</v>
       </c>
       <c r="Y34" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z34" s="24">
-        <v>2.0699999999999998</v>
+        <v>8.5300000000000011</v>
       </c>
       <c r="AA34" s="28" t="str">
         <v>-</v>
@@ -10932,16 +11197,16 @@
         <v>4</v>
       </c>
       <c r="B35" s="1">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C35" s="12" t="str">
-        <v>Liam Lawson</v>
+        <v>Carlos Sainz</v>
       </c>
       <c r="D35" s="1" t="str">
-        <v>Racing Bulls</v>
-      </c>
-      <c r="E35" s="31">
-        <v>2.04</v>
+        <v>Williams</v>
+      </c>
+      <c r="E35" s="30">
+        <v>8.4699999999999989</v>
       </c>
       <c r="F35" s="21" t="str">
         <v>-</v>
@@ -10991,20 +11256,20 @@
       <c r="U35" s="24" t="str">
         <v>-</v>
       </c>
-      <c r="V35" s="28" t="str">
-        <v>-</v>
+      <c r="V35" s="28">
+        <v>8.75</v>
       </c>
       <c r="W35" s="23">
+        <v>8</v>
+      </c>
+      <c r="X35" s="23">
         <v>8.5</v>
       </c>
-      <c r="X35" s="23" t="str">
-        <v>-</v>
-      </c>
       <c r="Y35" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z35" s="24">
-        <v>2.04</v>
+        <v>8.4699999999999989</v>
       </c>
       <c r="AA35" s="28" t="str">
         <v>-</v>
@@ -11183,16 +11448,16 @@
         <v>5</v>
       </c>
       <c r="B36" s="3">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="C36" s="12" t="str">
-        <v>Sergio Perez</v>
+        <v>Franco Colapinto</v>
       </c>
       <c r="D36" s="3" t="str">
-        <v>Cadillac</v>
-      </c>
-      <c r="E36" s="31">
-        <v>2.0279999999999996</v>
+        <v>Alpine</v>
+      </c>
+      <c r="E36" s="30">
+        <v>8.1980000000000004</v>
       </c>
       <c r="F36" s="21" t="str">
         <v>-</v>
@@ -11243,19 +11508,19 @@
         <v>-</v>
       </c>
       <c r="V36" s="28">
-        <v>8.3000000000000007</v>
+        <v>8.5</v>
       </c>
       <c r="W36" s="23">
-        <v>8.6</v>
-      </c>
-      <c r="X36" s="23" t="str">
-        <v>-</v>
+        <v>9.15</v>
+      </c>
+      <c r="X36" s="23">
+        <v>8</v>
       </c>
       <c r="Y36" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z36" s="24">
-        <v>2.0279999999999996</v>
+        <v>8.1980000000000004</v>
       </c>
       <c r="AA36" s="28" t="str">
         <v>-</v>
@@ -11434,16 +11699,16 @@
         <v>6</v>
       </c>
       <c r="B37" s="3">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="C37" s="12" t="str">
-        <v>Carlos Sainz</v>
+        <v>Kimi Antonelli</v>
       </c>
       <c r="D37" s="3" t="str">
-        <v>Williams</v>
-      </c>
-      <c r="E37" s="31">
-        <v>2.0099999999999998</v>
+        <v>Mercedes</v>
+      </c>
+      <c r="E37" s="30">
+        <v>8.1859999999999999</v>
       </c>
       <c r="F37" s="21" t="str">
         <v>-</v>
@@ -11494,19 +11759,19 @@
         <v>-</v>
       </c>
       <c r="V37" s="28">
-        <v>8.75</v>
+        <v>8</v>
       </c>
       <c r="W37" s="23">
-        <v>8</v>
-      </c>
-      <c r="X37" s="23" t="str">
-        <v>-</v>
+        <v>5.75</v>
+      </c>
+      <c r="X37" s="23">
+        <v>8.6</v>
       </c>
       <c r="Y37" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z37" s="24">
-        <v>2.0099999999999998</v>
+        <v>8.1859999999999999</v>
       </c>
       <c r="AA37" s="28" t="str">
         <v>-</v>
@@ -11693,8 +11958,8 @@
       <c r="D38" s="4" t="str">
         <v>Racing Bulls</v>
       </c>
-      <c r="E38" s="31">
-        <v>1.95</v>
+      <c r="E38" s="30">
+        <v>8.1059999999999999</v>
       </c>
       <c r="F38" s="21" t="str">
         <v>-</v>
@@ -11750,14 +12015,14 @@
       <c r="W38" s="23">
         <v>8.5</v>
       </c>
-      <c r="X38" s="23" t="str">
-        <v>-</v>
+      <c r="X38" s="23">
+        <v>8.1</v>
       </c>
       <c r="Y38" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z38" s="24">
-        <v>1.95</v>
+        <v>8.1059999999999999</v>
       </c>
       <c r="AA38" s="28" t="str">
         <v>-</v>
@@ -11936,16 +12201,16 @@
         <v>8</v>
       </c>
       <c r="B39" s="4">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C39" s="12" t="str">
-        <v>Max Verstappen</v>
+        <v>Lewis Hamilton</v>
       </c>
       <c r="D39" s="4" t="str">
-        <v>Red Bull</v>
-      </c>
-      <c r="E39" s="31">
-        <v>1.89</v>
+        <v>Ferrari</v>
+      </c>
+      <c r="E39" s="30">
+        <v>7.9399999999999995</v>
       </c>
       <c r="F39" s="21" t="str">
         <v>-</v>
@@ -11996,19 +12261,19 @@
         <v>-</v>
       </c>
       <c r="V39" s="28">
-        <v>7.75</v>
+        <v>8.25</v>
       </c>
       <c r="W39" s="23">
+        <v>7.25</v>
+      </c>
+      <c r="X39" s="23">
         <v>8</v>
       </c>
-      <c r="X39" s="23" t="str">
-        <v>-</v>
-      </c>
       <c r="Y39" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z39" s="24">
-        <v>1.89</v>
+        <v>7.9399999999999995</v>
       </c>
       <c r="AA39" s="28" t="str">
         <v>-</v>
@@ -12187,16 +12452,16 @@
         <v>9</v>
       </c>
       <c r="B40" s="5">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="C40" s="12" t="str">
-        <v>Lewis Hamilton</v>
+        <v>Max Verstappen</v>
       </c>
       <c r="D40" s="5" t="str">
-        <v>Ferrari</v>
-      </c>
-      <c r="E40" s="31">
-        <v>1.8599999999999999</v>
+        <v>Red Bull</v>
+      </c>
+      <c r="E40" s="30">
+        <v>7.9399999999999995</v>
       </c>
       <c r="F40" s="21" t="str">
         <v>-</v>
@@ -12247,19 +12512,19 @@
         <v>-</v>
       </c>
       <c r="V40" s="28">
-        <v>8.25</v>
+        <v>7.5</v>
       </c>
       <c r="W40" s="23">
-        <v>7.25</v>
-      </c>
-      <c r="X40" s="23" t="str">
-        <v>-</v>
+        <v>8</v>
+      </c>
+      <c r="X40" s="23">
+        <v>8</v>
       </c>
       <c r="Y40" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z40" s="24">
-        <v>1.8599999999999999</v>
+        <v>7.9399999999999995</v>
       </c>
       <c r="AA40" s="28" t="str">
         <v>-</v>
@@ -12438,16 +12703,16 @@
         <v>10</v>
       </c>
       <c r="B41" s="5">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="C41" s="12" t="str">
-        <v>Oscar Piastri</v>
+        <v>Sergio Perez</v>
       </c>
       <c r="D41" s="5" t="str">
-        <v>McLaren</v>
-      </c>
-      <c r="E41" s="31">
-        <v>1.8299999999999998</v>
+        <v>Cadillac</v>
+      </c>
+      <c r="E41" s="30">
+        <v>7.9179999999999993</v>
       </c>
       <c r="F41" s="21" t="str">
         <v>-</v>
@@ -12498,19 +12763,19 @@
         <v>-</v>
       </c>
       <c r="V41" s="28">
-        <v>8.5</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="W41" s="23">
-        <v>6.75</v>
-      </c>
-      <c r="X41" s="23" t="str">
-        <v>-</v>
+        <v>8.6</v>
+      </c>
+      <c r="X41" s="23">
+        <v>7.75</v>
       </c>
       <c r="Y41" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z41" s="24">
-        <v>1.8299999999999998</v>
+        <v>7.9179999999999993</v>
       </c>
       <c r="AA41" s="28" t="str">
         <v>-</v>
@@ -12697,8 +12962,8 @@
       <c r="D42" s="6" t="str">
         <v>Aston Martin</v>
       </c>
-      <c r="E42" s="31">
-        <v>1.74</v>
+      <c r="E42" s="30">
+        <v>7.82</v>
       </c>
       <c r="F42" s="21" t="str">
         <v>-</v>
@@ -12754,14 +13019,14 @@
       <c r="W42" s="23">
         <v>7</v>
       </c>
-      <c r="X42" s="23" t="str">
-        <v>-</v>
+      <c r="X42" s="23">
+        <v>8</v>
       </c>
       <c r="Y42" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z42" s="24">
-        <v>1.74</v>
+        <v>7.82</v>
       </c>
       <c r="AA42" s="28" t="str">
         <v>-</v>
@@ -12948,8 +13213,8 @@
       <c r="D43" s="6" t="str">
         <v>Red Bull</v>
       </c>
-      <c r="E43" s="31">
-        <v>1.71</v>
+      <c r="E43" s="30">
+        <v>7.79</v>
       </c>
       <c r="F43" s="21" t="str">
         <v>-</v>
@@ -13005,14 +13270,14 @@
       <c r="W43" s="23">
         <v>7</v>
       </c>
-      <c r="X43" s="23" t="str">
-        <v>-</v>
+      <c r="X43" s="23">
+        <v>8</v>
       </c>
       <c r="Y43" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z43" s="24">
-        <v>1.71</v>
+        <v>7.79</v>
       </c>
       <c r="AA43" s="28" t="str">
         <v>-</v>
@@ -13191,16 +13456,16 @@
         <v>13</v>
       </c>
       <c r="B44" s="7">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C44" s="12" t="str">
-        <v>Gabriel Bortoleto</v>
+        <v>Nico Hulkenberg</v>
       </c>
       <c r="D44" s="7" t="str">
         <v>Audi</v>
       </c>
-      <c r="E44" s="31">
-        <v>1.68</v>
+      <c r="E44" s="30">
+        <v>7.61</v>
       </c>
       <c r="F44" s="21" t="str">
         <v>-</v>
@@ -13251,19 +13516,19 @@
         <v>-</v>
       </c>
       <c r="V44" s="28">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="W44" s="23">
-        <v>6.5</v>
-      </c>
-      <c r="X44" s="23" t="str">
-        <v>-</v>
+        <v>5</v>
+      </c>
+      <c r="X44" s="23">
+        <v>8</v>
       </c>
       <c r="Y44" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z44" s="24">
-        <v>1.68</v>
+        <v>7.61</v>
       </c>
       <c r="AA44" s="28" t="str">
         <v>-</v>
@@ -13442,16 +13707,16 @@
         <v>14</v>
       </c>
       <c r="B45" s="7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C45" s="12" t="str">
-        <v>Kimi Antonelli</v>
+        <v>Gabriel Bortoleto</v>
       </c>
       <c r="D45" s="7" t="str">
-        <v>Mercedes</v>
-      </c>
-      <c r="E45" s="31">
-        <v>1.65</v>
+        <v>Audi</v>
+      </c>
+      <c r="E45" s="30">
+        <v>7.5399999999999991</v>
       </c>
       <c r="F45" s="21" t="str">
         <v>-</v>
@@ -13502,19 +13767,19 @@
         <v>-</v>
       </c>
       <c r="V45" s="28">
-        <v>8</v>
+        <v>7.25</v>
       </c>
       <c r="W45" s="23">
-        <v>5.75</v>
-      </c>
-      <c r="X45" s="23" t="str">
-        <v>-</v>
+        <v>6.5</v>
+      </c>
+      <c r="X45" s="23">
+        <v>7.75</v>
       </c>
       <c r="Y45" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z45" s="24">
-        <v>1.65</v>
+        <v>7.5399999999999991</v>
       </c>
       <c r="AA45" s="28" t="str">
         <v>-</v>
@@ -13693,16 +13958,16 @@
         <v>15</v>
       </c>
       <c r="B46" s="8">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C46" s="12" t="str">
-        <v>Nico Hulkenberg</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="D46" s="8" t="str">
-        <v>Audi</v>
-      </c>
-      <c r="E46" s="31">
-        <v>1.56</v>
+        <v>Ferrari</v>
+      </c>
+      <c r="E46" s="30">
+        <v>7.3780000000000001</v>
       </c>
       <c r="F46" s="21" t="str">
         <v>-</v>
@@ -13753,19 +14018,19 @@
         <v>-</v>
       </c>
       <c r="V46" s="28">
-        <v>8</v>
+        <v>6.75</v>
       </c>
       <c r="W46" s="23">
-        <v>5</v>
-      </c>
-      <c r="X46" s="23" t="str">
-        <v>-</v>
+        <v>6.6</v>
+      </c>
+      <c r="X46" s="23">
+        <v>7.6</v>
       </c>
       <c r="Y46" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z46" s="24">
-        <v>1.56</v>
+        <v>7.3780000000000001</v>
       </c>
       <c r="AA46" s="28" t="str">
         <v>-</v>
@@ -13944,16 +14209,16 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C47" s="12" t="str">
-        <v>Charles Leclerc</v>
+        <v>Liam Lawson</v>
       </c>
       <c r="D47" s="8" t="str">
-        <v>Ferrari</v>
-      </c>
-      <c r="E47" s="31">
-        <v>1.512</v>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="E47" s="30">
+        <v>7.36</v>
       </c>
       <c r="F47" s="21" t="str">
         <v>-</v>
@@ -14003,20 +14268,20 @@
       <c r="U47" s="24" t="str">
         <v>-</v>
       </c>
-      <c r="V47" s="28">
-        <v>6</v>
+      <c r="V47" s="28" t="str">
+        <v>-</v>
       </c>
       <c r="W47" s="23">
-        <v>6.6</v>
-      </c>
-      <c r="X47" s="23" t="str">
-        <v>-</v>
+        <v>8.5</v>
+      </c>
+      <c r="X47" s="23">
+        <v>7</v>
       </c>
       <c r="Y47" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z47" s="24">
-        <v>1.512</v>
+        <v>7.36</v>
       </c>
       <c r="AA47" s="28" t="str">
         <v>-</v>
@@ -14195,16 +14460,16 @@
         <v>17</v>
       </c>
       <c r="B48" s="9">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="C48" s="12" t="str">
-        <v>Esteban Ocon</v>
+        <v>Oliver Bearman</v>
       </c>
       <c r="D48" s="9" t="str">
-        <v>Hass</v>
-      </c>
-      <c r="E48" s="31">
-        <v>1.44</v>
+        <v>Haas</v>
+      </c>
+      <c r="E48" s="30">
+        <v>6.51</v>
       </c>
       <c r="F48" s="21" t="str">
         <v>-</v>
@@ -14255,19 +14520,19 @@
         <v>-</v>
       </c>
       <c r="V48" s="28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W48" s="23">
-        <v>5</v>
-      </c>
-      <c r="X48" s="23" t="str">
-        <v>-</v>
+        <v>5.5</v>
+      </c>
+      <c r="X48" s="23">
+        <v>6.75</v>
       </c>
       <c r="Y48" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z48" s="24">
-        <v>1.44</v>
+        <v>6.51</v>
       </c>
       <c r="AA48" s="28" t="str">
         <v>-</v>
@@ -14446,16 +14711,16 @@
         <v>18</v>
       </c>
       <c r="B49" s="9">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C49" s="12" t="str">
-        <v>Alexander Albon</v>
+        <v>Pierre Gasly</v>
       </c>
       <c r="D49" s="9" t="str">
-        <v>Williams</v>
-      </c>
-      <c r="E49" s="31">
-        <v>1.44</v>
+        <v>Alpine</v>
+      </c>
+      <c r="E49" s="30">
+        <v>6.08</v>
       </c>
       <c r="F49" s="21" t="str">
         <v>-</v>
@@ -14505,20 +14770,20 @@
       <c r="U49" s="24" t="str">
         <v>-</v>
       </c>
-      <c r="V49" s="28" t="str">
-        <v>-</v>
+      <c r="V49" s="28">
+        <v>3.5</v>
       </c>
       <c r="W49" s="23">
         <v>6</v>
       </c>
-      <c r="X49" s="23" t="str">
-        <v>-</v>
+      <c r="X49" s="23">
+        <v>6.5</v>
       </c>
       <c r="Y49" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z49" s="24">
-        <v>1.44</v>
+        <v>6.08</v>
       </c>
       <c r="AA49" s="28" t="str">
         <v>-</v>
@@ -14697,16 +14962,16 @@
         <v>19</v>
       </c>
       <c r="B50" s="10">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="C50" s="12" t="str">
-        <v>Oliver Bearman</v>
+        <v>Esteban Ocon</v>
       </c>
       <c r="D50" s="10" t="str">
-        <v>Hass</v>
-      </c>
-      <c r="E50" s="31">
-        <v>1.38</v>
+        <v>Haas</v>
+      </c>
+      <c r="E50" s="30">
+        <v>5.24</v>
       </c>
       <c r="F50" s="21" t="str">
         <v>-</v>
@@ -14757,19 +15022,19 @@
         <v>-</v>
       </c>
       <c r="V50" s="28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W50" s="23">
-        <v>5.5</v>
-      </c>
-      <c r="X50" s="23" t="str">
-        <v>-</v>
+        <v>5</v>
+      </c>
+      <c r="X50" s="23">
+        <v>5</v>
       </c>
       <c r="Y50" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z50" s="24">
-        <v>1.38</v>
+        <v>5.24</v>
       </c>
       <c r="AA50" s="28" t="str">
         <v>-</v>
@@ -14948,16 +15213,16 @@
         <v>20</v>
       </c>
       <c r="B51" s="10">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C51" s="12" t="str">
-        <v>Pierre Gasly</v>
+        <v>Alexander Albon</v>
       </c>
       <c r="D51" s="10" t="str">
-        <v>Alpine</v>
-      </c>
-      <c r="E51" s="31">
-        <v>1.1399999999999999</v>
+        <v>Williams</v>
+      </c>
+      <c r="E51" s="30">
+        <v>4.4800000000000004</v>
       </c>
       <c r="F51" s="21" t="str">
         <v>-</v>
@@ -15007,20 +15272,20 @@
       <c r="U51" s="24" t="str">
         <v>-</v>
       </c>
-      <c r="V51" s="28">
-        <v>3.5</v>
+      <c r="V51" s="28" t="str">
+        <v>-</v>
       </c>
       <c r="W51" s="23">
         <v>6</v>
       </c>
-      <c r="X51" s="23" t="str">
-        <v>-</v>
+      <c r="X51" s="23">
+        <v>4</v>
       </c>
       <c r="Y51" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z51" s="24">
-        <v>1.1399999999999999</v>
+        <v>4.4800000000000004</v>
       </c>
       <c r="AA51" s="28" t="str">
         <v>-</v>
@@ -15207,8 +15472,8 @@
       <c r="D52" s="11" t="str">
         <v>Aston Martin</v>
       </c>
-      <c r="E52" s="31">
-        <v>1.08</v>
+      <c r="E52" s="30">
+        <v>2.3719999999999999</v>
       </c>
       <c r="F52" s="21" t="str">
         <v>-</v>
@@ -15264,14 +15529,14 @@
       <c r="W52" s="23">
         <v>5</v>
       </c>
-      <c r="X52" s="23" t="str">
-        <v>-</v>
+      <c r="X52" s="23">
+        <v>1.7</v>
       </c>
       <c r="Y52" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z52" s="24">
-        <v>1.08</v>
+        <v>2.3719999999999999</v>
       </c>
       <c r="AA52" s="28" t="str">
         <v>-</v>
@@ -15458,8 +15723,8 @@
       <c r="D53" s="11" t="str">
         <v>Cadillac</v>
       </c>
-      <c r="E53" s="31">
-        <v>0.65999999999999992</v>
+      <c r="E53" s="30">
+        <v>2.36</v>
       </c>
       <c r="F53" s="21" t="str">
         <v>-</v>
@@ -15510,19 +15775,19 @@
         <v>-</v>
       </c>
       <c r="V53" s="28">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="W53" s="23">
         <v>5</v>
       </c>
-      <c r="X53" s="23" t="str">
-        <v>-</v>
+      <c r="X53" s="23">
+        <v>2</v>
       </c>
       <c r="Y53" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z53" s="24">
-        <v>0.65999999999999992</v>
+        <v>2.36</v>
       </c>
       <c r="AA53" s="28" t="str">
         <v>-</v>
@@ -15823,50 +16088,50 @@
     <mergeCell ref="Q4:U4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B27 D6:D27 B32:B53 D32:D53">
-    <cfRule type="expression" dxfId="69" priority="335">
+    <cfRule type="expression" dxfId="102" priority="1">
+      <formula>$D6="Haas"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="101" priority="336">
       <formula>$D6="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="336">
+    <cfRule type="expression" dxfId="100" priority="337">
       <formula>$D6="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="337">
+    <cfRule type="expression" dxfId="99" priority="338">
       <formula>$D6="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="338">
+    <cfRule type="expression" dxfId="98" priority="339">
       <formula>$D6="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="65" priority="339">
+    <cfRule type="expression" dxfId="97" priority="340">
       <formula>$D6="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="340">
+    <cfRule type="expression" dxfId="96" priority="341">
       <formula>$D6="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="341">
+    <cfRule type="expression" dxfId="95" priority="342">
       <formula>$D6="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="342">
+    <cfRule type="expression" dxfId="94" priority="343">
       <formula>$D6="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="343">
+    <cfRule type="expression" dxfId="93" priority="344">
       <formula>$D6="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="344">
+    <cfRule type="expression" dxfId="92" priority="345">
       <formula>$D6="Racing Bulls"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="59" priority="345">
-      <formula>$D6="Haas"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E27">
-    <cfRule type="cellIs" dxfId="58" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="4" operator="equal">
       <formula>-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:E53">
-    <cfRule type="cellIs" dxfId="57" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="2" operator="equal">
       <formula>-1</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="346">
+    <cfRule type="colorScale" priority="347">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percent" val="50"/>
@@ -15878,7 +16143,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:F6 F7:F28 G6:G28 Q6:T28 W6:Y28 AA6:AB28 AD6:AE28 AG6:AH28 AJ6:AM28 AO6:AP28 AR6:AS28 AU6:AX28 AZ6:BA28 BC6:BD28 BF6:BG28 BN6:BO28 BQ6:BR28 BT6:BU28 BW6:BX28 BZ6:CA28 CC6:CD28 H6:H27 P6:P27 AC6:AC27 AF6:AF27 AI6:AI27 AN6:AN27 AQ6:AQ27 AT6:AT27 BB6:BB27 BE6:BE27 BP6:BP27 BS6:BS27 BV6:BV27 BY6:BY27 CB6:CB27 CE6:CE27 I6:O28 U6:V27 Z6:Z27 AY6:AY27 BH6:BM27 E7:E27">
-    <cfRule type="colorScale" priority="347">
+    <cfRule type="colorScale" priority="348">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percent" val="50"/>
@@ -15890,6 +16155,28 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:P53 AA32:AT53 AZ32:BH53 BN32:CE53">
+    <cfRule type="colorScale" priority="279">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="num" val="10"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6:CE27">
+    <cfRule type="cellIs" dxfId="89" priority="3" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32:CE53">
+    <cfRule type="cellIs" dxfId="88" priority="6" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q32:Z53">
     <cfRule type="colorScale" priority="278">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -15901,30 +16188,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:CE27">
-    <cfRule type="cellIs" dxfId="56" priority="2" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F32:CE53">
-    <cfRule type="cellIs" dxfId="55" priority="5" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q32:Z53">
+  <conditionalFormatting sqref="AU32:AY53">
     <cfRule type="colorScale" priority="277">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percent" val="50"/>
-        <cfvo type="num" val="10"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AU32:AY53">
-    <cfRule type="colorScale" priority="276">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percent" val="50"/>
@@ -15942,10 +16207,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA4A54E0-3364-4CB2-A64A-1895CF467E9B}">
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="5" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="4.6328125" customWidth="1"/>
     <col min="3" max="3" width="15.1796875" customWidth="1"/>
     <col min="4" max="4" width="12.7265625" customWidth="1"/>
     <col min="5" max="8" width="5" customWidth="1"/>
@@ -15954,24 +16220,27 @@
     <col min="11" max="13" width="5" customWidth="1"/>
     <col min="14" max="14" width="13.453125" customWidth="1"/>
     <col min="15" max="15" width="5" customWidth="1"/>
+    <col min="17" max="17" width="11.1796875" customWidth="1"/>
+    <col min="20" max="20" width="12.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="30" t="s">
+      <c r="D1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="30" t="s">
+      <c r="E1" s="12" t="s">
         <v>3</v>
       </c>
+      <c r="F1" s="31"/>
       <c r="G1" s="12" t="s">
         <v>65</v>
       </c>
@@ -15987,13 +16256,24 @@
       <c r="K1" s="12" t="s">
         <v>3</v>
       </c>
+      <c r="L1" s="31"/>
       <c r="M1" s="12"/>
       <c r="N1" s="12" t="s">
         <v>65</v>
       </c>
       <c r="O1" s="12"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1" s="36"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="U1" s="36"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" s="12">
         <v>1</v>
       </c>
@@ -16008,11 +16288,12 @@
         <v>McLaren</v>
       </c>
       <c r="E2" s="2">
-        <v>2.16</v>
-      </c>
-      <c r="G2" s="46">
+        <v>8.9359999999999999</v>
+      </c>
+      <c r="F2" s="31"/>
+      <c r="G2" s="37">
         <f>K2-K3</f>
-        <v>0.41999999999999993</v>
+        <v>0.49599999999999866</v>
       </c>
       <c r="H2" s="18">
         <v>63</v>
@@ -16025,36 +16306,54 @@
       </c>
       <c r="K2" s="2">
         <f>Ratings!E6</f>
-        <v>2.0699999999999998</v>
-      </c>
+        <v>8.6819999999999986</v>
+      </c>
+      <c r="L2" s="31"/>
       <c r="M2" s="18">
         <v>63</v>
       </c>
       <c r="N2" s="29">
         <f>Simplified!G2</f>
-        <v>0.41999999999999993</v>
+        <v>0.49599999999999866</v>
       </c>
       <c r="O2" s="18">
         <v>12</v>
       </c>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="32">
+        <f>AVERAGE(K2:K3)</f>
+        <v>8.4339999999999993</v>
+      </c>
+      <c r="S2" s="31"/>
+      <c r="T2" s="33" t="str" cm="1">
+        <f t="array" ref="T2:U12">_xlfn._xlws.SORT(Q2:R12,2,-1)</f>
+        <v>McLaren</v>
+      </c>
+      <c r="U2" s="33">
+        <v>8.7330000000000005</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" s="12">
         <v>2</v>
       </c>
       <c r="B3" s="18">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="C3" s="12" t="str">
-        <v>Franco Colapinto</v>
+        <v>George Russell</v>
       </c>
       <c r="D3" s="18" t="str">
-        <v>Alpine</v>
+        <v>Mercedes</v>
       </c>
       <c r="E3" s="2">
-        <v>2.1120000000000001</v>
-      </c>
-      <c r="G3" s="46"/>
+        <v>8.6819999999999986</v>
+      </c>
+      <c r="F3" s="31"/>
+      <c r="G3" s="37"/>
       <c r="H3" s="18">
         <v>12</v>
       </c>
@@ -16066,38 +16365,55 @@
       </c>
       <c r="K3" s="2">
         <f>Ratings!E7</f>
-        <v>1.65</v>
-      </c>
+        <v>8.1859999999999999</v>
+      </c>
+      <c r="L3" s="31"/>
       <c r="M3" s="1">
         <v>1</v>
       </c>
       <c r="N3" s="29">
         <f>Simplified!G4</f>
-        <v>0.33000000000000029</v>
+        <v>0.40599999999999881</v>
       </c>
       <c r="O3" s="1">
         <v>81</v>
       </c>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="32">
+        <f>AVERAGE(K4:K5)</f>
+        <v>8.7330000000000005</v>
+      </c>
+      <c r="S3" s="31"/>
+      <c r="T3" s="33" t="str">
+        <v>Mercedes</v>
+      </c>
+      <c r="U3" s="33">
+        <v>8.4339999999999993</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" s="12">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C4" s="12" t="str">
-        <v>George Russell</v>
+        <v>Oscar Piastri</v>
       </c>
       <c r="D4" s="1" t="str">
-        <v>Mercedes</v>
+        <v>McLaren</v>
       </c>
       <c r="E4" s="2">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="G4" s="46">
+        <v>8.5300000000000011</v>
+      </c>
+      <c r="F4" s="31"/>
+      <c r="G4" s="37">
         <f>K4-K5</f>
-        <v>0.33000000000000029</v>
+        <v>0.40599999999999881</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -16110,36 +16426,53 @@
       </c>
       <c r="K4" s="2">
         <f>Ratings!E8</f>
-        <v>2.16</v>
-      </c>
+        <v>8.9359999999999999</v>
+      </c>
+      <c r="L4" s="31"/>
       <c r="M4" s="3">
         <v>16</v>
       </c>
       <c r="N4" s="29">
         <f>Simplified!G6</f>
-        <v>-0.34799999999999986</v>
+        <v>-0.56199999999999939</v>
       </c>
       <c r="O4" s="3">
         <v>44</v>
       </c>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="32">
+        <f>AVERAGE(K6:K7)</f>
+        <v>7.6589999999999998</v>
+      </c>
+      <c r="S4" s="31"/>
+      <c r="T4" s="33" t="str">
+        <v>Red Bull</v>
+      </c>
+      <c r="U4" s="33">
+        <v>7.8650000000000002</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" s="12">
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C5" s="12" t="str">
-        <v>Liam Lawson</v>
+        <v>Carlos Sainz</v>
       </c>
       <c r="D5" s="1" t="str">
-        <v>Racing Bulls</v>
+        <v>Williams</v>
       </c>
       <c r="E5" s="2">
-        <v>2.04</v>
-      </c>
-      <c r="G5" s="46"/>
+        <v>8.4699999999999989</v>
+      </c>
+      <c r="F5" s="31"/>
+      <c r="G5" s="37"/>
       <c r="H5" s="1">
         <v>81</v>
       </c>
@@ -16151,38 +16484,55 @@
       </c>
       <c r="K5" s="2">
         <f>Ratings!E9</f>
-        <v>1.8299999999999998</v>
-      </c>
+        <v>8.5300000000000011</v>
+      </c>
+      <c r="L5" s="31"/>
       <c r="M5" s="4">
         <v>3</v>
       </c>
       <c r="N5" s="29">
         <f>Simplified!G8</f>
-        <v>0.17999999999999994</v>
+        <v>0.14999999999999947</v>
       </c>
       <c r="O5" s="4">
         <v>6</v>
       </c>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="R5" s="32">
+        <f>AVERAGE(K8:K9)</f>
+        <v>7.8650000000000002</v>
+      </c>
+      <c r="S5" s="31"/>
+      <c r="T5" s="33" t="str">
+        <v>Racing Bulls</v>
+      </c>
+      <c r="U5" s="33">
+        <v>7.7330000000000005</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" s="12">
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="C6" s="12" t="str">
-        <v>Sergio Perez</v>
+        <v>Franco Colapinto</v>
       </c>
       <c r="D6" s="3" t="str">
-        <v>Cadillac</v>
+        <v>Alpine</v>
       </c>
       <c r="E6" s="2">
-        <v>2.0279999999999996</v>
-      </c>
-      <c r="G6" s="46">
+        <v>8.1980000000000004</v>
+      </c>
+      <c r="F6" s="31"/>
+      <c r="G6" s="37">
         <f>K6-K7</f>
-        <v>-0.34799999999999986</v>
+        <v>-0.56199999999999939</v>
       </c>
       <c r="H6" s="3">
         <v>16</v>
@@ -16195,36 +16545,53 @@
       </c>
       <c r="K6" s="2">
         <f>Ratings!E10</f>
-        <v>1.512</v>
-      </c>
+        <v>7.3780000000000001</v>
+      </c>
+      <c r="L6" s="31"/>
       <c r="M6" s="5">
         <v>10</v>
       </c>
       <c r="N6" s="29">
         <f>Simplified!G10</f>
-        <v>-0.9720000000000002</v>
+        <v>-2.1180000000000003</v>
       </c>
       <c r="O6" s="5">
         <v>43</v>
       </c>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="R6" s="32">
+        <f>AVERAGE(K10:K11)</f>
+        <v>7.1390000000000002</v>
+      </c>
+      <c r="S6" s="31"/>
+      <c r="T6" s="33" t="str">
+        <v>Ferrari</v>
+      </c>
+      <c r="U6" s="33">
+        <v>7.6589999999999998</v>
+      </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" s="12">
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="C7" s="12" t="str">
-        <v>Carlos Sainz</v>
+        <v>Kimi Antonelli</v>
       </c>
       <c r="D7" s="3" t="str">
-        <v>Williams</v>
+        <v>Mercedes</v>
       </c>
       <c r="E7" s="2">
-        <v>2.0099999999999998</v>
-      </c>
-      <c r="G7" s="46"/>
+        <v>8.1859999999999999</v>
+      </c>
+      <c r="F7" s="31"/>
+      <c r="G7" s="37"/>
       <c r="H7" s="3">
         <v>44</v>
       </c>
@@ -16236,20 +16603,36 @@
       </c>
       <c r="K7" s="2">
         <f>Ratings!E11</f>
-        <v>1.8599999999999999</v>
-      </c>
+        <v>7.9399999999999995</v>
+      </c>
+      <c r="L7" s="31"/>
       <c r="M7" s="6">
         <v>30</v>
       </c>
       <c r="N7" s="29">
         <f>Simplified!G12</f>
-        <v>9.000000000000008E-2</v>
+        <v>-0.74599999999999955</v>
       </c>
       <c r="O7" s="6">
         <v>41</v>
       </c>
+      <c r="P7" s="31"/>
+      <c r="Q7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R7" s="32">
+        <f>AVERAGE(K12:K13)</f>
+        <v>7.7330000000000005</v>
+      </c>
+      <c r="S7" s="31"/>
+      <c r="T7" s="33" t="str">
+        <v>Audi</v>
+      </c>
+      <c r="U7" s="33">
+        <v>7.5749999999999993</v>
+      </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" s="12">
         <v>7</v>
       </c>
@@ -16263,11 +16646,12 @@
         <v>Racing Bulls</v>
       </c>
       <c r="E8" s="2">
-        <v>1.95</v>
-      </c>
-      <c r="G8" s="46">
+        <v>8.1059999999999999</v>
+      </c>
+      <c r="F8" s="31"/>
+      <c r="G8" s="37">
         <f>K8-K9</f>
-        <v>0.17999999999999994</v>
+        <v>0.14999999999999947</v>
       </c>
       <c r="H8" s="4">
         <v>3</v>
@@ -16280,36 +16664,53 @@
       </c>
       <c r="K8" s="2">
         <f>Ratings!E12</f>
-        <v>1.89</v>
-      </c>
+        <v>7.9399999999999995</v>
+      </c>
+      <c r="L8" s="31"/>
       <c r="M8" s="7">
         <v>31</v>
       </c>
       <c r="N8" s="29">
         <f>Simplified!G14</f>
-        <v>6.0000000000000053E-2</v>
+        <v>-1.2699999999999996</v>
       </c>
       <c r="O8" s="7">
         <v>87</v>
       </c>
+      <c r="P8" s="31"/>
+      <c r="Q8" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="R8" s="32">
+        <f>AVERAGE(K14:K15)</f>
+        <v>5.875</v>
+      </c>
+      <c r="S8" s="31"/>
+      <c r="T8" s="33" t="str">
+        <v>Alpine</v>
+      </c>
+      <c r="U8" s="33">
+        <v>7.1390000000000002</v>
+      </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" s="12">
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C9" s="12" t="str">
-        <v>Max Verstappen</v>
+        <v>Lewis Hamilton</v>
       </c>
       <c r="D9" s="4" t="str">
-        <v>Red Bull</v>
+        <v>Ferrari</v>
       </c>
       <c r="E9" s="2">
-        <v>1.89</v>
-      </c>
-      <c r="G9" s="46"/>
+        <v>7.9399999999999995</v>
+      </c>
+      <c r="F9" s="31"/>
+      <c r="G9" s="37"/>
       <c r="H9" s="4">
         <v>6</v>
       </c>
@@ -16321,38 +16722,55 @@
       </c>
       <c r="K9" s="2">
         <f>Ratings!E13</f>
-        <v>1.71</v>
-      </c>
+        <v>7.79</v>
+      </c>
+      <c r="L9" s="31"/>
       <c r="M9" s="8">
         <v>55</v>
       </c>
       <c r="N9" s="29">
         <f>Simplified!G16</f>
-        <v>0.56999999999999984</v>
+        <v>3.9899999999999984</v>
       </c>
       <c r="O9" s="8">
         <v>23</v>
       </c>
+      <c r="P9" s="31"/>
+      <c r="Q9" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="R9" s="32">
+        <f>AVERAGE(K16:K17)</f>
+        <v>6.4749999999999996</v>
+      </c>
+      <c r="S9" s="31"/>
+      <c r="T9" s="33" t="str">
+        <v>Williams</v>
+      </c>
+      <c r="U9" s="33">
+        <v>6.4749999999999996</v>
+      </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" s="12">
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="C10" s="12" t="str">
-        <v>Lewis Hamilton</v>
+        <v>Max Verstappen</v>
       </c>
       <c r="D10" s="5" t="str">
-        <v>Ferrari</v>
+        <v>Red Bull</v>
       </c>
       <c r="E10" s="2">
-        <v>1.8599999999999999</v>
-      </c>
-      <c r="G10" s="46">
+        <v>7.9399999999999995</v>
+      </c>
+      <c r="F10" s="31"/>
+      <c r="G10" s="37">
         <f>K10-K11</f>
-        <v>-0.9720000000000002</v>
+        <v>-2.1180000000000003</v>
       </c>
       <c r="H10" s="5">
         <v>10</v>
@@ -16365,36 +16783,53 @@
       </c>
       <c r="K10" s="2">
         <f>Ratings!E14</f>
-        <v>1.1399999999999999</v>
-      </c>
+        <v>6.08</v>
+      </c>
+      <c r="L10" s="31"/>
       <c r="M10" s="9">
         <v>27</v>
       </c>
       <c r="N10" s="29">
         <f>Simplified!G18</f>
-        <v>-0.11999999999999988</v>
+        <v>7.0000000000001172E-2</v>
       </c>
       <c r="O10" s="9">
         <v>5</v>
       </c>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="R10" s="32">
+        <f>AVERAGE(K18:K19)</f>
+        <v>7.5749999999999993</v>
+      </c>
+      <c r="S10" s="31"/>
+      <c r="T10" s="33" t="str">
+        <v>Haas</v>
+      </c>
+      <c r="U10" s="33">
+        <v>5.875</v>
+      </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" s="12">
         <v>10</v>
       </c>
       <c r="B11" s="5">
-        <v>81</v>
+        <v>11</v>
       </c>
       <c r="C11" s="12" t="str">
-        <v>Oscar Piastri</v>
+        <v>Sergio Perez</v>
       </c>
       <c r="D11" s="5" t="str">
-        <v>McLaren</v>
+        <v>Cadillac</v>
       </c>
       <c r="E11" s="2">
-        <v>1.8299999999999998</v>
-      </c>
-      <c r="G11" s="46"/>
+        <v>7.9179999999999993</v>
+      </c>
+      <c r="F11" s="31"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="5">
         <v>43</v>
       </c>
@@ -16406,20 +16841,36 @@
       </c>
       <c r="K11" s="2">
         <f>Ratings!E15</f>
-        <v>2.1120000000000001</v>
-      </c>
+        <v>8.1980000000000004</v>
+      </c>
+      <c r="L11" s="31"/>
       <c r="M11" s="10">
         <v>11</v>
       </c>
       <c r="N11" s="29">
         <f>Simplified!G20</f>
-        <v>1.3679999999999997</v>
+        <v>5.5579999999999998</v>
       </c>
       <c r="O11" s="10">
         <v>77</v>
       </c>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="R11" s="32">
+        <f>AVERAGE(K20:K21)</f>
+        <v>5.1389999999999993</v>
+      </c>
+      <c r="S11" s="31"/>
+      <c r="T11" s="33" t="str">
+        <v>Cadillac</v>
+      </c>
+      <c r="U11" s="33">
+        <v>5.1389999999999993</v>
+      </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" s="12">
         <v>11</v>
       </c>
@@ -16433,11 +16884,12 @@
         <v>Aston Martin</v>
       </c>
       <c r="E12" s="2">
-        <v>1.74</v>
-      </c>
-      <c r="G12" s="46">
+        <v>7.82</v>
+      </c>
+      <c r="F12" s="31"/>
+      <c r="G12" s="37">
         <f>K12-K13</f>
-        <v>9.000000000000008E-2</v>
+        <v>-0.74599999999999955</v>
       </c>
       <c r="H12" s="6">
         <v>30</v>
@@ -16450,20 +16902,36 @@
       </c>
       <c r="K12" s="2">
         <f>Ratings!E16</f>
-        <v>2.04</v>
-      </c>
+        <v>7.36</v>
+      </c>
+      <c r="L12" s="31"/>
       <c r="M12" s="11">
         <v>14</v>
       </c>
       <c r="N12" s="29">
         <f>Simplified!G22</f>
-        <v>0.65999999999999992</v>
+        <v>5.4480000000000004</v>
       </c>
       <c r="O12" s="11">
         <v>18</v>
       </c>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="R12" s="32">
+        <f>AVERAGE(K22:K23)</f>
+        <v>5.0960000000000001</v>
+      </c>
+      <c r="S12" s="31"/>
+      <c r="T12" s="33" t="str">
+        <v>Aston Martin</v>
+      </c>
+      <c r="U12" s="33">
+        <v>5.0960000000000001</v>
+      </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" s="12">
         <v>12</v>
       </c>
@@ -16477,9 +16945,10 @@
         <v>Red Bull</v>
       </c>
       <c r="E13" s="2">
-        <v>1.71</v>
-      </c>
-      <c r="G13" s="46"/>
+        <v>7.79</v>
+      </c>
+      <c r="F13" s="31"/>
+      <c r="G13" s="37"/>
       <c r="H13" s="6">
         <v>41</v>
       </c>
@@ -16491,28 +16960,39 @@
       </c>
       <c r="K13" s="2">
         <f>Ratings!E17</f>
-        <v>1.95</v>
-      </c>
+        <v>8.1059999999999999</v>
+      </c>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="31"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" s="12">
         <v>13</v>
       </c>
       <c r="B14" s="7">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C14" s="12" t="str">
-        <v>Gabriel Bortoleto</v>
+        <v>Nico Hulkenberg</v>
       </c>
       <c r="D14" s="7" t="str">
         <v>Audi</v>
       </c>
       <c r="E14" s="2">
-        <v>1.68</v>
-      </c>
-      <c r="G14" s="46">
+        <v>7.61</v>
+      </c>
+      <c r="F14" s="31"/>
+      <c r="G14" s="37">
         <f>K14-K15</f>
-        <v>6.0000000000000053E-2</v>
+        <v>-1.2699999999999996</v>
       </c>
       <c r="H14" s="7">
         <v>31</v>
@@ -16521,30 +17001,41 @@
         <v>53</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="K14" s="2">
         <f>Ratings!E18</f>
-        <v>1.44</v>
-      </c>
+        <v>5.24</v>
+      </c>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="31"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" s="12">
         <v>14</v>
       </c>
       <c r="B15" s="7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C15" s="12" t="str">
-        <v>Kimi Antonelli</v>
+        <v>Gabriel Bortoleto</v>
       </c>
       <c r="D15" s="7" t="str">
-        <v>Mercedes</v>
+        <v>Audi</v>
       </c>
       <c r="E15" s="2">
-        <v>1.65</v>
-      </c>
-      <c r="G15" s="46"/>
+        <v>7.5399999999999991</v>
+      </c>
+      <c r="F15" s="31"/>
+      <c r="G15" s="37"/>
       <c r="H15" s="7">
         <v>87</v>
       </c>
@@ -16552,32 +17043,43 @@
         <v>54</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="K15" s="2">
         <f>Ratings!E19</f>
-        <v>1.38</v>
-      </c>
+        <v>6.51</v>
+      </c>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="31"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="31"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" s="12">
         <v>15</v>
       </c>
       <c r="B16" s="8">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C16" s="12" t="str">
-        <v>Nico Hulkenberg</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="D16" s="8" t="str">
-        <v>Audi</v>
+        <v>Ferrari</v>
       </c>
       <c r="E16" s="2">
-        <v>1.56</v>
-      </c>
-      <c r="G16" s="46">
+        <v>7.3780000000000001</v>
+      </c>
+      <c r="F16" s="31"/>
+      <c r="G16" s="37">
         <f>K16-K17</f>
-        <v>0.56999999999999984</v>
+        <v>3.9899999999999984</v>
       </c>
       <c r="H16" s="8">
         <v>55</v>
@@ -16590,26 +17092,37 @@
       </c>
       <c r="K16" s="2">
         <f>Ratings!E20</f>
-        <v>2.0099999999999998</v>
-      </c>
+        <v>8.4699999999999989</v>
+      </c>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="31"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="12">
         <v>16</v>
       </c>
       <c r="B17" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C17" s="12" t="str">
-        <v>Charles Leclerc</v>
+        <v>Liam Lawson</v>
       </c>
       <c r="D17" s="8" t="str">
-        <v>Ferrari</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E17" s="2">
-        <v>1.512</v>
-      </c>
-      <c r="G17" s="46"/>
+        <v>7.36</v>
+      </c>
+      <c r="F17" s="31"/>
+      <c r="G17" s="37"/>
       <c r="H17" s="8">
         <v>23</v>
       </c>
@@ -16621,28 +17134,39 @@
       </c>
       <c r="K17" s="2">
         <f>Ratings!E21</f>
-        <v>1.44</v>
-      </c>
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" s="12">
         <v>17</v>
       </c>
       <c r="B18" s="9">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="C18" s="12" t="str">
-        <v>Esteban Ocon</v>
+        <v>Oliver Bearman</v>
       </c>
       <c r="D18" s="9" t="str">
-        <v>Hass</v>
+        <v>Haas</v>
       </c>
       <c r="E18" s="2">
-        <v>1.44</v>
-      </c>
-      <c r="G18" s="46">
+        <v>6.51</v>
+      </c>
+      <c r="F18" s="31"/>
+      <c r="G18" s="37">
         <f>K18-K19</f>
-        <v>-0.11999999999999988</v>
+        <v>7.0000000000001172E-2</v>
       </c>
       <c r="H18" s="9">
         <v>27</v>
@@ -16655,26 +17179,37 @@
       </c>
       <c r="K18" s="2">
         <f>Ratings!E22</f>
-        <v>1.56</v>
-      </c>
+        <v>7.61</v>
+      </c>
+      <c r="L18" s="31"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="31"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" s="12">
         <v>18</v>
       </c>
       <c r="B19" s="9">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C19" s="12" t="str">
-        <v>Alexander Albon</v>
+        <v>Pierre Gasly</v>
       </c>
       <c r="D19" s="9" t="str">
-        <v>Williams</v>
+        <v>Alpine</v>
       </c>
       <c r="E19" s="2">
-        <v>1.44</v>
-      </c>
-      <c r="G19" s="46"/>
+        <v>6.08</v>
+      </c>
+      <c r="F19" s="31"/>
+      <c r="G19" s="37"/>
       <c r="H19" s="9">
         <v>5</v>
       </c>
@@ -16686,28 +17221,39 @@
       </c>
       <c r="K19" s="2">
         <f>Ratings!E23</f>
-        <v>1.68</v>
-      </c>
+        <v>7.5399999999999991</v>
+      </c>
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="31"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" s="12">
         <v>19</v>
       </c>
       <c r="B20" s="10">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="C20" s="12" t="str">
-        <v>Oliver Bearman</v>
+        <v>Esteban Ocon</v>
       </c>
       <c r="D20" s="10" t="str">
-        <v>Hass</v>
+        <v>Haas</v>
       </c>
       <c r="E20" s="2">
-        <v>1.38</v>
-      </c>
-      <c r="G20" s="46">
+        <v>5.24</v>
+      </c>
+      <c r="F20" s="31"/>
+      <c r="G20" s="37">
         <f>K20-K21</f>
-        <v>1.3679999999999997</v>
+        <v>5.5579999999999998</v>
       </c>
       <c r="H20" s="10">
         <v>11</v>
@@ -16720,26 +17266,37 @@
       </c>
       <c r="K20" s="2">
         <f>Ratings!E24</f>
-        <v>2.0279999999999996</v>
-      </c>
+        <v>7.9179999999999993</v>
+      </c>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" s="12">
         <v>20</v>
       </c>
       <c r="B21" s="10">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C21" s="12" t="str">
-        <v>Pierre Gasly</v>
+        <v>Alexander Albon</v>
       </c>
       <c r="D21" s="10" t="str">
-        <v>Alpine</v>
+        <v>Williams</v>
       </c>
       <c r="E21" s="2">
-        <v>1.1399999999999999</v>
-      </c>
-      <c r="G21" s="46"/>
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="F21" s="31"/>
+      <c r="G21" s="37"/>
       <c r="H21" s="10">
         <v>77</v>
       </c>
@@ -16751,10 +17308,20 @@
       </c>
       <c r="K21" s="2">
         <f>Ratings!E25</f>
-        <v>0.65999999999999992</v>
-      </c>
+        <v>2.36</v>
+      </c>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="31"/>
+      <c r="P21" s="31"/>
+      <c r="Q21" s="31"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="31"/>
+      <c r="T21" s="31"/>
+      <c r="U21" s="31"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" s="12">
         <v>21</v>
       </c>
@@ -16768,11 +17335,12 @@
         <v>Aston Martin</v>
       </c>
       <c r="E22" s="2">
-        <v>1.08</v>
-      </c>
-      <c r="G22" s="46">
+        <v>2.3719999999999999</v>
+      </c>
+      <c r="F22" s="31"/>
+      <c r="G22" s="37">
         <f>K22-K23</f>
-        <v>0.65999999999999992</v>
+        <v>5.4480000000000004</v>
       </c>
       <c r="H22" s="11">
         <v>14</v>
@@ -16785,10 +17353,20 @@
       </c>
       <c r="K22" s="2">
         <f>Ratings!E26</f>
-        <v>1.74</v>
-      </c>
+        <v>7.82</v>
+      </c>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" s="12">
         <v>22</v>
       </c>
@@ -16802,9 +17380,10 @@
         <v>Cadillac</v>
       </c>
       <c r="E23" s="2">
-        <v>0.65999999999999992</v>
-      </c>
-      <c r="G23" s="46"/>
+        <v>2.36</v>
+      </c>
+      <c r="F23" s="31"/>
+      <c r="G23" s="37"/>
       <c r="H23" s="11">
         <v>18</v>
       </c>
@@ -16816,11 +17395,23 @@
       </c>
       <c r="K23" s="2">
         <f>Ratings!E27</f>
-        <v>1.08</v>
-      </c>
+        <v>2.3719999999999999</v>
+      </c>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="G20:G21"/>
     <mergeCell ref="G22:G23"/>
@@ -16834,42 +17425,42 @@
     <mergeCell ref="G16:G17"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:B23 D2:D23">
-    <cfRule type="expression" dxfId="54" priority="8">
+    <cfRule type="expression" dxfId="87" priority="147">
+      <formula>$D2="Haas"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="86" priority="141">
+      <formula>$D2="Mercedes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="137">
+      <formula>$D2="Williams"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="138">
+      <formula>$D2="Audi"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="139">
+      <formula>$D2="Cadillac"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="82" priority="140">
+      <formula>$D2="Aston Martin"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="81" priority="142">
+      <formula>$D2="Ferrari"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="80" priority="143">
       <formula>$D2="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="2">
-      <formula>$D2="Williams"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="3">
-      <formula>$D2="Audi"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="51" priority="4">
-      <formula>$D2="Cadillac"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="50" priority="5">
-      <formula>$D2="Aston Martin"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="6">
-      <formula>$D2="Mercedes"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="7">
-      <formula>$D2="Ferrari"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="47" priority="9">
+    <cfRule type="expression" dxfId="79" priority="144">
       <formula>$D2="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="10">
+    <cfRule type="expression" dxfId="78" priority="145">
       <formula>$D2="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="11">
+    <cfRule type="expression" dxfId="77" priority="146">
       <formula>$D2="Racing Bulls"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="12">
-      <formula>$D2="Haas"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E23">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="136">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percent" val="50"/>
@@ -16880,55 +17471,55 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2 G4 G6 G8 G10 G12 G14 G16 G18 G20 G22">
-    <cfRule type="colorScale" priority="57">
+  <conditionalFormatting sqref="G4 G2 G6 G8 G10 G12 G14 G16 G18 G20 G22">
+    <cfRule type="colorScale" priority="192">
       <colorScale>
         <cfvo type="percentile" val="0"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="percentile" val="100"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23 J4:J23">
-    <cfRule type="expression" dxfId="43" priority="59">
+    <cfRule type="expression" dxfId="76" priority="198">
+      <formula>#REF!="Mercedes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="199">
+      <formula>#REF!="Ferrari"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="197">
+      <formula>#REF!="Aston Martin"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="200">
+      <formula>#REF!="McLaren"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="201">
+      <formula>#REF!="Red Bull"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="71" priority="202">
+      <formula>#REF!="Alpine"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="204">
+      <formula>#REF!="Haas"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="69" priority="203">
+      <formula>#REF!="Racing Bulls"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="194">
       <formula>#REF!="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="60">
+    <cfRule type="expression" dxfId="67" priority="195">
       <formula>#REF!="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="61">
+    <cfRule type="expression" dxfId="66" priority="196">
       <formula>#REF!="Cadillac"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="62">
-      <formula>#REF!="Aston Martin"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="39" priority="63">
-      <formula>#REF!="Mercedes"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="64">
-      <formula>#REF!="Ferrari"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="65">
-      <formula>#REF!="McLaren"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="66">
-      <formula>#REF!="Red Bull"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="67">
-      <formula>#REF!="Alpine"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="68">
-      <formula>#REF!="Racing Bulls"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="69">
-      <formula>#REF!="Haas"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K23">
-    <cfRule type="colorScale" priority="58">
+    <cfRule type="colorScale" priority="193">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percent" val="50"/>
@@ -16940,77 +17531,77 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2 O2 H2:H3 J2:J3">
-    <cfRule type="expression" dxfId="32" priority="348">
+    <cfRule type="expression" dxfId="65" priority="485">
+      <formula>$J2="Alpine"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="484">
+      <formula>$J2="Red Bull"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="63" priority="483">
       <formula>$J2="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="349">
-      <formula>$J2="Red Bull"</formula>
+    <cfRule type="expression" dxfId="62" priority="482">
+      <formula>$J2="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="350">
-      <formula>$J2="Alpine"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="351">
-      <formula>$J2="Racing Bulls"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="352">
+    <cfRule type="expression" dxfId="61" priority="487">
       <formula>$J2="Haas"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="345">
+    <cfRule type="expression" dxfId="60" priority="481">
+      <formula>$J2="Mercedes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="480">
       <formula>$J2="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="342">
+    <cfRule type="expression" dxfId="58" priority="478">
+      <formula>$J2="Audi"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="57" priority="477">
       <formula>$J2="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="343">
-      <formula>$J2="Audi"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="344">
+    <cfRule type="expression" dxfId="56" priority="479">
       <formula>$J2="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="346">
-      <formula>$J2="Mercedes"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="347">
-      <formula>$J2="Ferrari"</formula>
+    <cfRule type="expression" dxfId="55" priority="486">
+      <formula>$J2="Racing Bulls"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3:M12">
-    <cfRule type="expression" dxfId="21" priority="85">
+    <cfRule type="expression" dxfId="54" priority="226">
+      <formula>$D1048555="Racing Bulls"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="227">
+      <formula>$D1048555="Haas"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="217">
+      <formula>$D1048555="Williams"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="51" priority="219">
+      <formula>$D1048555="Cadillac"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="220">
       <formula>$D1048555="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="86">
+    <cfRule type="expression" dxfId="49" priority="218">
+      <formula>$D1048555="Audi"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="221">
       <formula>$D1048555="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="87">
+    <cfRule type="expression" dxfId="47" priority="222">
       <formula>$D1048555="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="88">
+    <cfRule type="expression" dxfId="46" priority="223">
       <formula>$D1048555="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="90">
+    <cfRule type="expression" dxfId="45" priority="224">
+      <formula>$D1048555="Red Bull"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="225">
       <formula>$D1048555="Alpine"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="91">
-      <formula>$D1048555="Racing Bulls"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="92">
-      <formula>$D1048555="Haas"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="82">
-      <formula>$D1048555="Williams"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="83">
-      <formula>$D1048555="Audi"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="84">
-      <formula>$D1048555="Cadillac"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="89">
-      <formula>$D1048555="Red Bull"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N12">
-    <cfRule type="dataBar" priority="70">
+    <cfRule type="dataBar" priority="205">
       <dataBar showValue="0">
         <cfvo type="num" val="-10"/>
         <cfvo type="num" val="10"/>
@@ -17024,38 +17615,167 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:O12">
-    <cfRule type="expression" dxfId="10" priority="71">
+    <cfRule type="expression" dxfId="43" priority="206">
       <formula>$D1048555="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="72">
+    <cfRule type="expression" dxfId="42" priority="207">
       <formula>$D1048555="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="73">
+    <cfRule type="expression" dxfId="41" priority="208">
       <formula>$D1048555="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="75">
+    <cfRule type="expression" dxfId="40" priority="209">
+      <formula>$D1048555="Aston Martin"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="210">
       <formula>$D1048555="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="76">
+    <cfRule type="expression" dxfId="38" priority="211">
       <formula>$D1048555="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="77">
+    <cfRule type="expression" dxfId="37" priority="212">
       <formula>$D1048555="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="78">
+    <cfRule type="expression" dxfId="36" priority="213">
       <formula>$D1048555="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="74">
-      <formula>$D1048555="Aston Martin"</formula>
+    <cfRule type="expression" dxfId="35" priority="215">
+      <formula>$D1048555="Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="79">
+    <cfRule type="expression" dxfId="34" priority="216">
+      <formula>$D1048555="Haas"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="214">
       <formula>$D1048555="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="80">
-      <formula>$D1048555="Racing Bulls"</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2">
+    <cfRule type="expression" dxfId="32" priority="125">
+      <formula>$J2="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="81">
-      <formula>$D1048555="Haas"</formula>
+    <cfRule type="expression" dxfId="31" priority="126">
+      <formula>$J2="Audi"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="127">
+      <formula>$J2="Cadillac"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="135">
+      <formula>$J2="Haas"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="134">
+      <formula>$J2="Racing Bulls"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="133">
+      <formula>$J2="Alpine"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="132">
+      <formula>$J2="Red Bull"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="131">
+      <formula>$J2="McLaren"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="130">
+      <formula>$J2="Ferrari"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="129">
+      <formula>$J2="Mercedes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="128">
+      <formula>$J2="Aston Martin"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q3:Q12">
+    <cfRule type="expression" dxfId="21" priority="23">
+      <formula>#REF!="Alpine"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="22">
+      <formula>#REF!="Red Bull"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="21">
+      <formula>#REF!="McLaren"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="20">
+      <formula>#REF!="Ferrari"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="19">
+      <formula>#REF!="Mercedes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="18">
+      <formula>#REF!="Aston Martin"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="15" priority="25">
+      <formula>#REF!="Haas"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="16">
+      <formula>#REF!="Audi"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="15">
+      <formula>#REF!="Williams"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="24">
+      <formula>#REF!="Racing Bulls"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="17">
+      <formula>#REF!="Cadillac"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R12">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T12">
+    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+      <formula>"Ferrari"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+      <formula>"Mercedes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+      <formula>"Red Bull"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+      <formula>"Alpine"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"Racing Bulls"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"Haas"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"Williams"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"Audi"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Cadillac"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"Aston Martin"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="11" operator="equal">
+      <formula>"McLaren"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U2:U12">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17065,7 +17785,7 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{36AB2FEB-256E-4F86-BFF6-3B16CDA9DDCE}">
-            <x14:dataBar minLength="0" maxLength="100" border="1" gradient="0" axisPosition="middle">
+            <x14:dataBar minLength="0" maxLength="100" border="1" gradient="0" direction="rightToLeft" axisPosition="middle">
               <x14:cfvo type="num">
                 <xm:f>-10</xm:f>
               </x14:cfvo>

--- a/static/data/Ratings.xlsx
+++ b/static/data/Ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Programming\webdev\portfolio\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F89D03A-D294-4EC8-8420-F6CF6C995385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A882DC6-58AA-43DA-9DFE-1731D5023EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="2" xr2:uid="{BD88BCC4-2E11-4C36-830D-A75A044EF5A6}"/>
   </bookViews>
@@ -941,43 +941,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -992,18 +959,44 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="103">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFC7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1063,6 +1056,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFE5002C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFC7F00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF26F0CE"/>
         </patternFill>
       </fill>
@@ -1070,21 +1077,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFE5002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
+          <bgColor rgb="FF21976F"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1105,6 +1098,286 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFA8A8AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF26F0CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE4002C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFD7F00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF366FC3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDBDFE0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF638FFD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF009FE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFA2B00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF1767D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDBDFE0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF638FFD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF009FE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF366FC3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFD7F00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE4002C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF26F0CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF21976F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA8A8AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDBDFE0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFD7F00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE4002C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF26F0CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF21976F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA8A8AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFA2B00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF1767D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF009FE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF638FFD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF366FC3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF638FFD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF009FE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF366FC3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFD7F00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE4002C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF26F0CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF21976F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA8A8AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFA2B00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF1767D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFDBDFE0"/>
         </patternFill>
       </fill>
@@ -1113,6 +1386,34 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF21976F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDBDFE0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF1767D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFA2B00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA8A8AB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1148,6 +1449,34 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF009FE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF638FFD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF1767D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFA2B00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA8A8AB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1210,34 +1539,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFDBDFE0"/>
         </patternFill>
       </fill>
@@ -1246,6 +1547,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF638FFD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF009FE4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1302,314 +1610,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF26F0CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF21976F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF21976F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF26F0CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF21976F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF26F0CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF21976F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF26F0CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3018,13 +3018,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:83" s="14" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
       <c r="F1" s="17"/>
       <c r="G1" s="17"/>
       <c r="H1" s="17"/>
@@ -3105,11 +3105,11 @@
       <c r="CE1" s="17"/>
     </row>
     <row r="2" spans="1:83" s="14" customFormat="1" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="39"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
@@ -3201,36 +3201,36 @@
       </c>
       <c r="G3" s="45"/>
       <c r="H3" s="46"/>
-      <c r="I3" s="41" t="e" vm="2">
+      <c r="I3" s="42" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
       <c r="N3" s="44" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
       <c r="O3" s="45"/>
       <c r="P3" s="46"/>
-      <c r="Q3" s="40" t="e" vm="4">
+      <c r="Q3" s="41" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="42"/>
-      <c r="V3" s="40" t="e" vm="5">
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="42"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="41" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="42"/>
+      <c r="W3" s="42"/>
+      <c r="X3" s="42"/>
+      <c r="Y3" s="42"/>
+      <c r="Z3" s="43"/>
       <c r="AA3" s="44" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
@@ -3249,14 +3249,14 @@
       </c>
       <c r="AH3" s="45"/>
       <c r="AI3" s="46"/>
-      <c r="AJ3" s="40" t="e" vm="9">
+      <c r="AJ3" s="41" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK3" s="41"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="41"/>
-      <c r="AN3" s="42"/>
+      <c r="AK3" s="42"/>
+      <c r="AL3" s="42"/>
+      <c r="AM3" s="42"/>
+      <c r="AN3" s="43"/>
       <c r="AO3" s="44" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
@@ -3269,14 +3269,14 @@
       </c>
       <c r="AS3" s="45"/>
       <c r="AT3" s="46"/>
-      <c r="AU3" s="40" t="e" vm="12">
+      <c r="AU3" s="41" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV3" s="41"/>
-      <c r="AW3" s="41"/>
-      <c r="AX3" s="41"/>
-      <c r="AY3" s="42"/>
+      <c r="AV3" s="42"/>
+      <c r="AW3" s="42"/>
+      <c r="AX3" s="42"/>
+      <c r="AY3" s="43"/>
       <c r="AZ3" s="44" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
@@ -3295,14 +3295,14 @@
       </c>
       <c r="BG3" s="45"/>
       <c r="BH3" s="46"/>
-      <c r="BI3" s="40" t="e" vm="15">
+      <c r="BI3" s="41" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ3" s="41"/>
-      <c r="BK3" s="41"/>
-      <c r="BL3" s="41"/>
-      <c r="BM3" s="42"/>
+      <c r="BJ3" s="42"/>
+      <c r="BK3" s="42"/>
+      <c r="BL3" s="42"/>
+      <c r="BM3" s="43"/>
       <c r="BN3" s="44" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
@@ -3341,150 +3341,150 @@
       <c r="CE3" s="46"/>
     </row>
     <row r="4" spans="1:83" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="43"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="43" t="s">
+      <c r="G4" s="36"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="47" t="s">
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="43"/>
-      <c r="P4" s="48"/>
-      <c r="Q4" s="49" t="s">
+      <c r="O4" s="36"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="51"/>
-      <c r="V4" s="49" t="s">
+      <c r="R4" s="39"/>
+      <c r="S4" s="39"/>
+      <c r="T4" s="39"/>
+      <c r="U4" s="40"/>
+      <c r="V4" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="W4" s="50"/>
-      <c r="X4" s="50"/>
-      <c r="Y4" s="50"/>
-      <c r="Z4" s="51"/>
-      <c r="AA4" s="47" t="s">
+      <c r="W4" s="39"/>
+      <c r="X4" s="39"/>
+      <c r="Y4" s="39"/>
+      <c r="Z4" s="40"/>
+      <c r="AA4" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="AB4" s="43"/>
-      <c r="AC4" s="48"/>
-      <c r="AD4" s="47" t="s">
+      <c r="AB4" s="36"/>
+      <c r="AC4" s="37"/>
+      <c r="AD4" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="AE4" s="43"/>
-      <c r="AF4" s="48"/>
-      <c r="AG4" s="47" t="s">
+      <c r="AE4" s="36"/>
+      <c r="AF4" s="37"/>
+      <c r="AG4" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="AH4" s="43"/>
-      <c r="AI4" s="48"/>
-      <c r="AJ4" s="49" t="s">
+      <c r="AH4" s="36"/>
+      <c r="AI4" s="37"/>
+      <c r="AJ4" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="AK4" s="50"/>
-      <c r="AL4" s="50"/>
-      <c r="AM4" s="50"/>
-      <c r="AN4" s="51"/>
-      <c r="AO4" s="47" t="s">
+      <c r="AK4" s="39"/>
+      <c r="AL4" s="39"/>
+      <c r="AM4" s="39"/>
+      <c r="AN4" s="40"/>
+      <c r="AO4" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="AP4" s="43"/>
-      <c r="AQ4" s="48"/>
-      <c r="AR4" s="47" t="s">
+      <c r="AP4" s="36"/>
+      <c r="AQ4" s="37"/>
+      <c r="AR4" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="AS4" s="43"/>
-      <c r="AT4" s="48"/>
-      <c r="AU4" s="49" t="s">
+      <c r="AS4" s="36"/>
+      <c r="AT4" s="37"/>
+      <c r="AU4" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="AV4" s="50"/>
-      <c r="AW4" s="50"/>
-      <c r="AX4" s="50"/>
-      <c r="AY4" s="51"/>
-      <c r="AZ4" s="47" t="s">
+      <c r="AV4" s="39"/>
+      <c r="AW4" s="39"/>
+      <c r="AX4" s="39"/>
+      <c r="AY4" s="40"/>
+      <c r="AZ4" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="BA4" s="43"/>
-      <c r="BB4" s="48"/>
-      <c r="BC4" s="47" t="s">
+      <c r="BA4" s="36"/>
+      <c r="BB4" s="37"/>
+      <c r="BC4" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="BD4" s="43"/>
-      <c r="BE4" s="48"/>
-      <c r="BF4" s="47" t="s">
+      <c r="BD4" s="36"/>
+      <c r="BE4" s="37"/>
+      <c r="BF4" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="BG4" s="43"/>
-      <c r="BH4" s="48"/>
-      <c r="BI4" s="49" t="s">
+      <c r="BG4" s="36"/>
+      <c r="BH4" s="37"/>
+      <c r="BI4" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="BJ4" s="50"/>
-      <c r="BK4" s="50"/>
-      <c r="BL4" s="50"/>
-      <c r="BM4" s="51"/>
-      <c r="BN4" s="47" t="s">
+      <c r="BJ4" s="39"/>
+      <c r="BK4" s="39"/>
+      <c r="BL4" s="39"/>
+      <c r="BM4" s="40"/>
+      <c r="BN4" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="BO4" s="43"/>
-      <c r="BP4" s="48"/>
-      <c r="BQ4" s="47" t="s">
+      <c r="BO4" s="36"/>
+      <c r="BP4" s="37"/>
+      <c r="BQ4" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="BR4" s="43"/>
-      <c r="BS4" s="48"/>
-      <c r="BT4" s="47" t="s">
+      <c r="BR4" s="36"/>
+      <c r="BS4" s="37"/>
+      <c r="BT4" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="BU4" s="43"/>
-      <c r="BV4" s="48"/>
-      <c r="BW4" s="47" t="s">
+      <c r="BU4" s="36"/>
+      <c r="BV4" s="37"/>
+      <c r="BW4" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="BX4" s="43"/>
-      <c r="BY4" s="48"/>
-      <c r="BZ4" s="47" t="s">
+      <c r="BX4" s="36"/>
+      <c r="BY4" s="37"/>
+      <c r="BZ4" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="CA4" s="43"/>
-      <c r="CB4" s="48"/>
-      <c r="CC4" s="47" t="s">
+      <c r="CA4" s="36"/>
+      <c r="CB4" s="37"/>
+      <c r="CC4" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="CD4" s="43"/>
-      <c r="CE4" s="48"/>
+      <c r="CD4" s="36"/>
+      <c r="CE4" s="37"/>
     </row>
     <row r="5" spans="1:83" s="16" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="43"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
       <c r="F5" s="22" t="s">
         <v>26</v>
       </c>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="E27" s="30">
         <f t="shared" si="0"/>
-        <v>2.3719999999999999</v>
+        <v>2.2960000000000003</v>
       </c>
       <c r="F27" s="21" t="s">
         <v>72</v>
@@ -9550,14 +9550,14 @@
         <v>5</v>
       </c>
       <c r="X27" s="21">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Y27" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z27" s="24">
         <f t="shared" si="5"/>
-        <v>2.3719999999999999</v>
+        <v>2.2960000000000003</v>
       </c>
       <c r="AA27" s="21" t="s">
         <v>72</v>
@@ -9913,296 +9913,296 @@
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
-      <c r="F29" s="40" t="e" vm="1">
+      <c r="F29" s="41" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G29" s="41"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="41" t="e" vm="2">
+      <c r="G29" s="42"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="42" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="41"/>
-      <c r="M29" s="41"/>
-      <c r="N29" s="40" t="e" vm="3">
+      <c r="J29" s="42"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="42"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="41" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O29" s="41"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="41" t="e" vm="4">
+      <c r="O29" s="42"/>
+      <c r="P29" s="43"/>
+      <c r="Q29" s="42" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R29" s="41"/>
-      <c r="S29" s="41"/>
-      <c r="T29" s="41"/>
-      <c r="U29" s="42"/>
-      <c r="V29" s="40" t="e" vm="5">
+      <c r="R29" s="42"/>
+      <c r="S29" s="42"/>
+      <c r="T29" s="42"/>
+      <c r="U29" s="43"/>
+      <c r="V29" s="41" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W29" s="41"/>
-      <c r="X29" s="41"/>
-      <c r="Y29" s="41"/>
-      <c r="Z29" s="41"/>
-      <c r="AA29" s="40" t="e" vm="6">
+      <c r="W29" s="42"/>
+      <c r="X29" s="42"/>
+      <c r="Y29" s="42"/>
+      <c r="Z29" s="42"/>
+      <c r="AA29" s="41" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB29" s="41"/>
-      <c r="AC29" s="42"/>
-      <c r="AD29" s="40" t="e" vm="7">
+      <c r="AB29" s="42"/>
+      <c r="AC29" s="43"/>
+      <c r="AD29" s="41" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE29" s="41"/>
-      <c r="AF29" s="42"/>
-      <c r="AG29" s="40" t="e" vm="8">
+      <c r="AE29" s="42"/>
+      <c r="AF29" s="43"/>
+      <c r="AG29" s="41" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH29" s="41"/>
-      <c r="AI29" s="42"/>
-      <c r="AJ29" s="41" t="e" vm="9">
+      <c r="AH29" s="42"/>
+      <c r="AI29" s="43"/>
+      <c r="AJ29" s="42" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK29" s="41"/>
-      <c r="AL29" s="41"/>
-      <c r="AM29" s="41"/>
-      <c r="AN29" s="41"/>
-      <c r="AO29" s="40" t="e" vm="10">
+      <c r="AK29" s="42"/>
+      <c r="AL29" s="42"/>
+      <c r="AM29" s="42"/>
+      <c r="AN29" s="42"/>
+      <c r="AO29" s="41" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP29" s="41"/>
-      <c r="AQ29" s="42"/>
-      <c r="AR29" s="40" t="e" vm="11">
+      <c r="AP29" s="42"/>
+      <c r="AQ29" s="43"/>
+      <c r="AR29" s="41" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS29" s="41"/>
-      <c r="AT29" s="42"/>
-      <c r="AU29" s="41" t="e" vm="12">
+      <c r="AS29" s="42"/>
+      <c r="AT29" s="43"/>
+      <c r="AU29" s="42" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV29" s="41"/>
-      <c r="AW29" s="41"/>
-      <c r="AX29" s="41"/>
-      <c r="AY29" s="41"/>
-      <c r="AZ29" s="40" t="e" vm="13">
+      <c r="AV29" s="42"/>
+      <c r="AW29" s="42"/>
+      <c r="AX29" s="42"/>
+      <c r="AY29" s="42"/>
+      <c r="AZ29" s="41" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA29" s="41"/>
-      <c r="BB29" s="42"/>
-      <c r="BC29" s="40" t="e" vm="7">
+      <c r="BA29" s="42"/>
+      <c r="BB29" s="43"/>
+      <c r="BC29" s="41" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD29" s="41"/>
-      <c r="BE29" s="42"/>
-      <c r="BF29" s="40" t="e" vm="14">
+      <c r="BD29" s="42"/>
+      <c r="BE29" s="43"/>
+      <c r="BF29" s="41" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG29" s="41"/>
-      <c r="BH29" s="42"/>
-      <c r="BI29" s="41" t="e" vm="15">
+      <c r="BG29" s="42"/>
+      <c r="BH29" s="43"/>
+      <c r="BI29" s="42" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ29" s="41"/>
-      <c r="BK29" s="41"/>
-      <c r="BL29" s="41"/>
-      <c r="BM29" s="41"/>
-      <c r="BN29" s="40" t="e" vm="4">
+      <c r="BJ29" s="42"/>
+      <c r="BK29" s="42"/>
+      <c r="BL29" s="42"/>
+      <c r="BM29" s="42"/>
+      <c r="BN29" s="41" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO29" s="41"/>
-      <c r="BP29" s="42"/>
-      <c r="BQ29" s="40" t="e" vm="16">
+      <c r="BO29" s="42"/>
+      <c r="BP29" s="43"/>
+      <c r="BQ29" s="41" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR29" s="41"/>
-      <c r="BS29" s="42"/>
-      <c r="BT29" s="40" t="e" vm="17">
+      <c r="BR29" s="42"/>
+      <c r="BS29" s="43"/>
+      <c r="BT29" s="41" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU29" s="41"/>
-      <c r="BV29" s="42"/>
-      <c r="BW29" s="40" t="e" vm="4">
+      <c r="BU29" s="42"/>
+      <c r="BV29" s="43"/>
+      <c r="BW29" s="41" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX29" s="41"/>
-      <c r="BY29" s="42"/>
-      <c r="BZ29" s="40" t="e" vm="18">
+      <c r="BX29" s="42"/>
+      <c r="BY29" s="43"/>
+      <c r="BZ29" s="41" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA29" s="41"/>
-      <c r="CB29" s="42"/>
-      <c r="CC29" s="40" t="e" vm="19">
+      <c r="CA29" s="42"/>
+      <c r="CB29" s="43"/>
+      <c r="CC29" s="41" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD29" s="41"/>
-      <c r="CE29" s="42"/>
+      <c r="CD29" s="42"/>
+      <c r="CE29" s="43"/>
     </row>
     <row r="30" spans="1:83" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="43" t="s">
+      <c r="A30" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="43" t="s">
+      <c r="B30" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="43" t="s">
+      <c r="C30" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="D30" s="43" t="s">
+      <c r="D30" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="43" t="s">
+      <c r="E30" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="F30" s="47" t="s">
+      <c r="F30" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="G30" s="43"/>
-      <c r="H30" s="48"/>
-      <c r="I30" s="43" t="s">
+      <c r="G30" s="36"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="43"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="47" t="s">
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="O30" s="43"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="49" t="s">
+      <c r="O30" s="36"/>
+      <c r="P30" s="37"/>
+      <c r="Q30" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="R30" s="50"/>
-      <c r="S30" s="50"/>
-      <c r="T30" s="50"/>
-      <c r="U30" s="51"/>
-      <c r="V30" s="49" t="s">
+      <c r="R30" s="39"/>
+      <c r="S30" s="39"/>
+      <c r="T30" s="39"/>
+      <c r="U30" s="40"/>
+      <c r="V30" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="W30" s="50"/>
-      <c r="X30" s="50"/>
-      <c r="Y30" s="50"/>
-      <c r="Z30" s="51"/>
-      <c r="AA30" s="47" t="s">
+      <c r="W30" s="39"/>
+      <c r="X30" s="39"/>
+      <c r="Y30" s="39"/>
+      <c r="Z30" s="40"/>
+      <c r="AA30" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="AB30" s="43"/>
-      <c r="AC30" s="48"/>
-      <c r="AD30" s="47" t="s">
+      <c r="AB30" s="36"/>
+      <c r="AC30" s="37"/>
+      <c r="AD30" s="35" t="s">
         <v>10</v>
       </c>
-      <c r="AE30" s="43"/>
-      <c r="AF30" s="48"/>
-      <c r="AG30" s="47" t="s">
+      <c r="AE30" s="36"/>
+      <c r="AF30" s="37"/>
+      <c r="AG30" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="AH30" s="43"/>
-      <c r="AI30" s="48"/>
-      <c r="AJ30" s="43" t="s">
+      <c r="AH30" s="36"/>
+      <c r="AI30" s="37"/>
+      <c r="AJ30" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="AK30" s="43"/>
-      <c r="AL30" s="43"/>
-      <c r="AM30" s="43"/>
-      <c r="AN30" s="43"/>
-      <c r="AO30" s="47" t="s">
+      <c r="AK30" s="36"/>
+      <c r="AL30" s="36"/>
+      <c r="AM30" s="36"/>
+      <c r="AN30" s="36"/>
+      <c r="AO30" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="AP30" s="43"/>
-      <c r="AQ30" s="48"/>
-      <c r="AR30" s="47" t="s">
+      <c r="AP30" s="36"/>
+      <c r="AQ30" s="37"/>
+      <c r="AR30" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="AS30" s="43"/>
-      <c r="AT30" s="48"/>
-      <c r="AU30" s="49" t="s">
+      <c r="AS30" s="36"/>
+      <c r="AT30" s="37"/>
+      <c r="AU30" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="AV30" s="50"/>
-      <c r="AW30" s="50"/>
-      <c r="AX30" s="50"/>
-      <c r="AY30" s="51"/>
-      <c r="AZ30" s="47" t="s">
+      <c r="AV30" s="39"/>
+      <c r="AW30" s="39"/>
+      <c r="AX30" s="39"/>
+      <c r="AY30" s="40"/>
+      <c r="AZ30" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="BA30" s="43"/>
-      <c r="BB30" s="48"/>
-      <c r="BC30" s="47" t="s">
+      <c r="BA30" s="36"/>
+      <c r="BB30" s="37"/>
+      <c r="BC30" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="BD30" s="43"/>
-      <c r="BE30" s="48"/>
-      <c r="BF30" s="47" t="s">
+      <c r="BD30" s="36"/>
+      <c r="BE30" s="37"/>
+      <c r="BF30" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="BG30" s="43"/>
-      <c r="BH30" s="48"/>
-      <c r="BI30" s="49" t="s">
+      <c r="BG30" s="36"/>
+      <c r="BH30" s="37"/>
+      <c r="BI30" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="BJ30" s="50"/>
-      <c r="BK30" s="50"/>
-      <c r="BL30" s="50"/>
-      <c r="BM30" s="51"/>
-      <c r="BN30" s="47" t="s">
+      <c r="BJ30" s="39"/>
+      <c r="BK30" s="39"/>
+      <c r="BL30" s="39"/>
+      <c r="BM30" s="40"/>
+      <c r="BN30" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="BO30" s="43"/>
-      <c r="BP30" s="48"/>
-      <c r="BQ30" s="47" t="s">
+      <c r="BO30" s="36"/>
+      <c r="BP30" s="37"/>
+      <c r="BQ30" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="BR30" s="43"/>
-      <c r="BS30" s="48"/>
-      <c r="BT30" s="47" t="s">
+      <c r="BR30" s="36"/>
+      <c r="BS30" s="37"/>
+      <c r="BT30" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="BU30" s="43"/>
-      <c r="BV30" s="48"/>
-      <c r="BW30" s="47" t="s">
+      <c r="BU30" s="36"/>
+      <c r="BV30" s="37"/>
+      <c r="BW30" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="BX30" s="43"/>
-      <c r="BY30" s="48"/>
-      <c r="BZ30" s="47" t="s">
+      <c r="BX30" s="36"/>
+      <c r="BY30" s="37"/>
+      <c r="BZ30" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="CA30" s="43"/>
-      <c r="CB30" s="48"/>
-      <c r="CC30" s="47" t="s">
+      <c r="CA30" s="36"/>
+      <c r="CB30" s="37"/>
+      <c r="CC30" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="CD30" s="43"/>
-      <c r="CE30" s="48"/>
+      <c r="CD30" s="36"/>
+      <c r="CE30" s="37"/>
     </row>
     <row r="31" spans="1:83" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="43"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
+      <c r="A31" s="36"/>
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
       <c r="F31" s="22" t="s">
         <v>26</v>
       </c>
@@ -15464,16 +15464,16 @@
         <v>21</v>
       </c>
       <c r="B52" s="11">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="C52" s="12" t="str">
-        <v>Lance Stroll</v>
+        <v>Valtteri Bottas</v>
       </c>
       <c r="D52" s="11" t="str">
-        <v>Aston Martin</v>
+        <v>Cadillac</v>
       </c>
       <c r="E52" s="30">
-        <v>2.3719999999999999</v>
+        <v>2.36</v>
       </c>
       <c r="F52" s="21" t="str">
         <v>-</v>
@@ -15524,19 +15524,19 @@
         <v>-</v>
       </c>
       <c r="V52" s="28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W52" s="23">
         <v>5</v>
       </c>
       <c r="X52" s="23">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Y52" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z52" s="24">
-        <v>2.3719999999999999</v>
+        <v>2.36</v>
       </c>
       <c r="AA52" s="28" t="str">
         <v>-</v>
@@ -15715,16 +15715,16 @@
         <v>22</v>
       </c>
       <c r="B53" s="11">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="C53" s="12" t="str">
-        <v>Valtteri Bottas</v>
+        <v>Lance Stroll</v>
       </c>
       <c r="D53" s="11" t="str">
-        <v>Cadillac</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E53" s="30">
-        <v>2.36</v>
+        <v>2.2960000000000003</v>
       </c>
       <c r="F53" s="21" t="str">
         <v>-</v>
@@ -15775,19 +15775,19 @@
         <v>-</v>
       </c>
       <c r="V53" s="28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W53" s="23">
         <v>5</v>
       </c>
       <c r="X53" s="23">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="Y53" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z53" s="24">
-        <v>2.36</v>
+        <v>2.2960000000000003</v>
       </c>
       <c r="AA53" s="28" t="str">
         <v>-</v>
@@ -15987,28 +15987,67 @@
     </row>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="BW30:BY30"/>
-    <mergeCell ref="BZ30:CB30"/>
-    <mergeCell ref="Q30:U30"/>
-    <mergeCell ref="V30:Z30"/>
-    <mergeCell ref="AA30:AC30"/>
-    <mergeCell ref="AD30:AF30"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AJ30:AN30"/>
-    <mergeCell ref="AO30:AQ30"/>
-    <mergeCell ref="AR30:AT30"/>
-    <mergeCell ref="AU30:AY30"/>
-    <mergeCell ref="CC30:CE30"/>
-    <mergeCell ref="AZ30:BB30"/>
-    <mergeCell ref="BC30:BE30"/>
-    <mergeCell ref="BF30:BH30"/>
-    <mergeCell ref="BI30:BM30"/>
-    <mergeCell ref="BN30:BP30"/>
-    <mergeCell ref="BQ30:BS30"/>
-    <mergeCell ref="BT30:BV30"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="Q4:U4"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:U29"/>
+    <mergeCell ref="V29:Z29"/>
+    <mergeCell ref="V4:Z4"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AN3"/>
+    <mergeCell ref="AO3:AQ3"/>
+    <mergeCell ref="AR3:AT3"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AG4:AI4"/>
+    <mergeCell ref="AJ4:AN4"/>
+    <mergeCell ref="AO4:AQ4"/>
+    <mergeCell ref="BW3:BY3"/>
+    <mergeCell ref="BZ3:CB3"/>
+    <mergeCell ref="CC3:CE3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="V3:Z3"/>
+    <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="BT3:BV3"/>
+    <mergeCell ref="AU3:AY3"/>
+    <mergeCell ref="AZ3:BB3"/>
+    <mergeCell ref="BC3:BE3"/>
+    <mergeCell ref="BF3:BH3"/>
+    <mergeCell ref="BI3:BM3"/>
+    <mergeCell ref="BN3:BP3"/>
+    <mergeCell ref="BQ3:BS3"/>
+    <mergeCell ref="CC4:CE4"/>
+    <mergeCell ref="AR4:AT4"/>
+    <mergeCell ref="AU4:AY4"/>
+    <mergeCell ref="AZ4:BB4"/>
+    <mergeCell ref="BC4:BE4"/>
+    <mergeCell ref="BF4:BH4"/>
+    <mergeCell ref="BI4:BM4"/>
+    <mergeCell ref="BN4:BP4"/>
+    <mergeCell ref="BQ4:BS4"/>
+    <mergeCell ref="BT4:BV4"/>
+    <mergeCell ref="BW4:BY4"/>
+    <mergeCell ref="BZ4:CB4"/>
+    <mergeCell ref="BQ29:BS29"/>
+    <mergeCell ref="BT29:BV29"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AN29"/>
+    <mergeCell ref="AO29:AQ29"/>
+    <mergeCell ref="AR29:AT29"/>
     <mergeCell ref="BW29:BY29"/>
     <mergeCell ref="BZ29:CB29"/>
     <mergeCell ref="CC29:CE29"/>
@@ -16025,67 +16064,28 @@
     <mergeCell ref="BN29:BP29"/>
     <mergeCell ref="AA29:AC29"/>
     <mergeCell ref="AD29:AF29"/>
-    <mergeCell ref="BQ29:BS29"/>
-    <mergeCell ref="BT29:BV29"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AN29"/>
-    <mergeCell ref="AO29:AQ29"/>
-    <mergeCell ref="AR29:AT29"/>
-    <mergeCell ref="CC4:CE4"/>
-    <mergeCell ref="AR4:AT4"/>
-    <mergeCell ref="AU4:AY4"/>
-    <mergeCell ref="AZ4:BB4"/>
-    <mergeCell ref="BC4:BE4"/>
-    <mergeCell ref="BF4:BH4"/>
-    <mergeCell ref="BI4:BM4"/>
-    <mergeCell ref="BN4:BP4"/>
-    <mergeCell ref="BQ4:BS4"/>
-    <mergeCell ref="BT4:BV4"/>
-    <mergeCell ref="BW4:BY4"/>
-    <mergeCell ref="BZ4:CB4"/>
-    <mergeCell ref="BW3:BY3"/>
-    <mergeCell ref="BZ3:CB3"/>
-    <mergeCell ref="CC3:CE3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="V3:Z3"/>
-    <mergeCell ref="AA3:AC3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="BT3:BV3"/>
-    <mergeCell ref="AU3:AY3"/>
-    <mergeCell ref="AZ3:BB3"/>
-    <mergeCell ref="BC3:BE3"/>
-    <mergeCell ref="BF3:BH3"/>
-    <mergeCell ref="BI3:BM3"/>
-    <mergeCell ref="BN3:BP3"/>
-    <mergeCell ref="BQ3:BS3"/>
-    <mergeCell ref="V4:Z4"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AN3"/>
-    <mergeCell ref="AO3:AQ3"/>
-    <mergeCell ref="AR3:AT3"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AG4:AI4"/>
-    <mergeCell ref="AJ4:AN4"/>
-    <mergeCell ref="AO4:AQ4"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:U29"/>
-    <mergeCell ref="V29:Z29"/>
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="Q4:U4"/>
+    <mergeCell ref="CC30:CE30"/>
+    <mergeCell ref="AZ30:BB30"/>
+    <mergeCell ref="BC30:BE30"/>
+    <mergeCell ref="BF30:BH30"/>
+    <mergeCell ref="BI30:BM30"/>
+    <mergeCell ref="BN30:BP30"/>
+    <mergeCell ref="BQ30:BS30"/>
+    <mergeCell ref="BT30:BV30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="BW30:BY30"/>
+    <mergeCell ref="BZ30:CB30"/>
+    <mergeCell ref="Q30:U30"/>
+    <mergeCell ref="V30:Z30"/>
+    <mergeCell ref="AA30:AC30"/>
+    <mergeCell ref="AD30:AF30"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AJ30:AN30"/>
+    <mergeCell ref="AO30:AQ30"/>
+    <mergeCell ref="AR30:AT30"/>
+    <mergeCell ref="AU30:AY30"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B27 D6:D27 B32:B53 D32:D53">
     <cfRule type="expression" dxfId="102" priority="1">
@@ -16263,15 +16263,15 @@
       </c>
       <c r="O1" s="12"/>
       <c r="P1" s="31"/>
-      <c r="Q1" s="35" t="s">
+      <c r="Q1" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="R1" s="36"/>
+      <c r="R1" s="50"/>
       <c r="S1" s="31"/>
-      <c r="T1" s="35" t="s">
+      <c r="T1" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="U1" s="36"/>
+      <c r="U1" s="50"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" s="12">
@@ -16291,7 +16291,7 @@
         <v>8.9359999999999999</v>
       </c>
       <c r="F2" s="31"/>
-      <c r="G2" s="37">
+      <c r="G2" s="51">
         <f>K2-K3</f>
         <v>0.49599999999999866</v>
       </c>
@@ -16353,7 +16353,7 @@
         <v>8.6819999999999986</v>
       </c>
       <c r="F3" s="31"/>
-      <c r="G3" s="37"/>
+      <c r="G3" s="51"/>
       <c r="H3" s="18">
         <v>12</v>
       </c>
@@ -16411,7 +16411,7 @@
         <v>8.5300000000000011</v>
       </c>
       <c r="F4" s="31"/>
-      <c r="G4" s="37">
+      <c r="G4" s="51">
         <f>K4-K5</f>
         <v>0.40599999999999881</v>
       </c>
@@ -16472,7 +16472,7 @@
         <v>8.4699999999999989</v>
       </c>
       <c r="F5" s="31"/>
-      <c r="G5" s="37"/>
+      <c r="G5" s="51"/>
       <c r="H5" s="1">
         <v>81</v>
       </c>
@@ -16530,7 +16530,7 @@
         <v>8.1980000000000004</v>
       </c>
       <c r="F6" s="31"/>
-      <c r="G6" s="37">
+      <c r="G6" s="51">
         <f>K6-K7</f>
         <v>-0.56199999999999939</v>
       </c>
@@ -16591,7 +16591,7 @@
         <v>8.1859999999999999</v>
       </c>
       <c r="F7" s="31"/>
-      <c r="G7" s="37"/>
+      <c r="G7" s="51"/>
       <c r="H7" s="3">
         <v>44</v>
       </c>
@@ -16649,7 +16649,7 @@
         <v>8.1059999999999999</v>
       </c>
       <c r="F8" s="31"/>
-      <c r="G8" s="37">
+      <c r="G8" s="51">
         <f>K8-K9</f>
         <v>0.14999999999999947</v>
       </c>
@@ -16710,7 +16710,7 @@
         <v>7.9399999999999995</v>
       </c>
       <c r="F9" s="31"/>
-      <c r="G9" s="37"/>
+      <c r="G9" s="51"/>
       <c r="H9" s="4">
         <v>6</v>
       </c>
@@ -16768,7 +16768,7 @@
         <v>7.9399999999999995</v>
       </c>
       <c r="F10" s="31"/>
-      <c r="G10" s="37">
+      <c r="G10" s="51">
         <f>K10-K11</f>
         <v>-2.1180000000000003</v>
       </c>
@@ -16829,7 +16829,7 @@
         <v>7.9179999999999993</v>
       </c>
       <c r="F11" s="31"/>
-      <c r="G11" s="37"/>
+      <c r="G11" s="51"/>
       <c r="H11" s="5">
         <v>43</v>
       </c>
@@ -16887,7 +16887,7 @@
         <v>7.82</v>
       </c>
       <c r="F12" s="31"/>
-      <c r="G12" s="37">
+      <c r="G12" s="51">
         <f>K12-K13</f>
         <v>-0.74599999999999955</v>
       </c>
@@ -16910,7 +16910,7 @@
       </c>
       <c r="N12" s="29">
         <f>Simplified!G22</f>
-        <v>5.4480000000000004</v>
+        <v>5.524</v>
       </c>
       <c r="O12" s="11">
         <v>18</v>
@@ -16921,14 +16921,14 @@
       </c>
       <c r="R12" s="32">
         <f>AVERAGE(K22:K23)</f>
-        <v>5.0960000000000001</v>
+        <v>5.0579999999999998</v>
       </c>
       <c r="S12" s="31"/>
       <c r="T12" s="33" t="str">
         <v>Aston Martin</v>
       </c>
       <c r="U12" s="33">
-        <v>5.0960000000000001</v>
+        <v>5.0579999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
@@ -16948,7 +16948,7 @@
         <v>7.79</v>
       </c>
       <c r="F13" s="31"/>
-      <c r="G13" s="37"/>
+      <c r="G13" s="51"/>
       <c r="H13" s="6">
         <v>41</v>
       </c>
@@ -16990,7 +16990,7 @@
         <v>7.61</v>
       </c>
       <c r="F14" s="31"/>
-      <c r="G14" s="37">
+      <c r="G14" s="51">
         <f>K14-K15</f>
         <v>-1.2699999999999996</v>
       </c>
@@ -17035,7 +17035,7 @@
         <v>7.5399999999999991</v>
       </c>
       <c r="F15" s="31"/>
-      <c r="G15" s="37"/>
+      <c r="G15" s="51"/>
       <c r="H15" s="7">
         <v>87</v>
       </c>
@@ -17077,7 +17077,7 @@
         <v>7.3780000000000001</v>
       </c>
       <c r="F16" s="31"/>
-      <c r="G16" s="37">
+      <c r="G16" s="51">
         <f>K16-K17</f>
         <v>3.9899999999999984</v>
       </c>
@@ -17122,7 +17122,7 @@
         <v>7.36</v>
       </c>
       <c r="F17" s="31"/>
-      <c r="G17" s="37"/>
+      <c r="G17" s="51"/>
       <c r="H17" s="8">
         <v>23</v>
       </c>
@@ -17164,7 +17164,7 @@
         <v>6.51</v>
       </c>
       <c r="F18" s="31"/>
-      <c r="G18" s="37">
+      <c r="G18" s="51">
         <f>K18-K19</f>
         <v>7.0000000000001172E-2</v>
       </c>
@@ -17209,7 +17209,7 @@
         <v>6.08</v>
       </c>
       <c r="F19" s="31"/>
-      <c r="G19" s="37"/>
+      <c r="G19" s="51"/>
       <c r="H19" s="9">
         <v>5</v>
       </c>
@@ -17251,7 +17251,7 @@
         <v>5.24</v>
       </c>
       <c r="F20" s="31"/>
-      <c r="G20" s="37">
+      <c r="G20" s="51">
         <f>K20-K21</f>
         <v>5.5579999999999998</v>
       </c>
@@ -17296,7 +17296,7 @@
         <v>4.4800000000000004</v>
       </c>
       <c r="F21" s="31"/>
-      <c r="G21" s="37"/>
+      <c r="G21" s="51"/>
       <c r="H21" s="10">
         <v>77</v>
       </c>
@@ -17326,21 +17326,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="11">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="C22" s="12" t="str">
-        <v>Lance Stroll</v>
+        <v>Valtteri Bottas</v>
       </c>
       <c r="D22" s="11" t="str">
-        <v>Aston Martin</v>
+        <v>Cadillac</v>
       </c>
       <c r="E22" s="2">
-        <v>2.3719999999999999</v>
+        <v>2.36</v>
       </c>
       <c r="F22" s="31"/>
-      <c r="G22" s="37">
+      <c r="G22" s="51">
         <f>K22-K23</f>
-        <v>5.4480000000000004</v>
+        <v>5.524</v>
       </c>
       <c r="H22" s="11">
         <v>14</v>
@@ -17371,19 +17371,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="11">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="C23" s="12" t="str">
-        <v>Valtteri Bottas</v>
+        <v>Lance Stroll</v>
       </c>
       <c r="D23" s="11" t="str">
-        <v>Cadillac</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E23" s="2">
-        <v>2.36</v>
+        <v>2.2960000000000003</v>
       </c>
       <c r="F23" s="31"/>
-      <c r="G23" s="37"/>
+      <c r="G23" s="51"/>
       <c r="H23" s="11">
         <v>18</v>
       </c>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="K23" s="2">
         <f>Ratings!E27</f>
-        <v>2.3719999999999999</v>
+        <v>2.2960000000000003</v>
       </c>
       <c r="L23" s="31"/>
       <c r="M23" s="31"/>
@@ -17425,38 +17425,38 @@
     <mergeCell ref="G16:G17"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:B23 D2:D23">
-    <cfRule type="expression" dxfId="87" priority="147">
-      <formula>$D2="Haas"</formula>
+    <cfRule type="expression" dxfId="87" priority="137">
+      <formula>$D2="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="141">
+    <cfRule type="expression" dxfId="86" priority="138">
+      <formula>$D2="Audi"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="85" priority="139">
+      <formula>$D2="Cadillac"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="84" priority="140">
+      <formula>$D2="Aston Martin"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="83" priority="141">
       <formula>$D2="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="137">
-      <formula>$D2="Williams"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="84" priority="138">
-      <formula>$D2="Audi"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="83" priority="139">
-      <formula>$D2="Cadillac"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="82" priority="140">
-      <formula>$D2="Aston Martin"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="81" priority="142">
+    <cfRule type="expression" dxfId="82" priority="142">
       <formula>$D2="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="143">
+    <cfRule type="expression" dxfId="81" priority="143">
       <formula>$D2="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="144">
+    <cfRule type="expression" dxfId="80" priority="144">
       <formula>$D2="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="145">
+    <cfRule type="expression" dxfId="79" priority="145">
       <formula>$D2="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="146">
+    <cfRule type="expression" dxfId="78" priority="146">
       <formula>$D2="Racing Bulls"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="147">
+      <formula>$D2="Haas"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E23">
@@ -17471,7 +17471,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4 G2 G6 G8 G10 G12 G14 G16 G18 G20 G22">
+  <conditionalFormatting sqref="G2 G4 G6 G8 G10 G12 G14 G16 G18 G20 G22">
     <cfRule type="colorScale" priority="192">
       <colorScale>
         <cfvo type="percentile" val="0"/>
@@ -17484,38 +17484,38 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23 J4:J23">
-    <cfRule type="expression" dxfId="76" priority="198">
+    <cfRule type="expression" dxfId="76" priority="204">
+      <formula>#REF!="Haas"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="75" priority="203">
+      <formula>#REF!="Racing Bulls"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="202">
+      <formula>#REF!="Alpine"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="73" priority="201">
+      <formula>#REF!="Red Bull"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="200">
+      <formula>#REF!="McLaren"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="71" priority="199">
+      <formula>#REF!="Ferrari"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="198">
       <formula>#REF!="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="199">
-      <formula>#REF!="Ferrari"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="74" priority="197">
+    <cfRule type="expression" dxfId="69" priority="197">
       <formula>#REF!="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="200">
-      <formula>#REF!="McLaren"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="201">
-      <formula>#REF!="Red Bull"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="71" priority="202">
-      <formula>#REF!="Alpine"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="70" priority="204">
-      <formula>#REF!="Haas"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="69" priority="203">
-      <formula>#REF!="Racing Bulls"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="68" priority="194">
-      <formula>#REF!="Williams"</formula>
+    <cfRule type="expression" dxfId="68" priority="196">
+      <formula>#REF!="Cadillac"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="67" priority="195">
       <formula>#REF!="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="196">
-      <formula>#REF!="Cadillac"</formula>
+    <cfRule type="expression" dxfId="66" priority="194">
+      <formula>#REF!="Williams"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K23">
@@ -17531,26 +17531,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2 O2 H2:H3 J2:J3">
-    <cfRule type="expression" dxfId="65" priority="485">
+    <cfRule type="expression" dxfId="65" priority="486">
+      <formula>$J2="Racing Bulls"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="485">
       <formula>$J2="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="484">
+    <cfRule type="expression" dxfId="63" priority="484">
       <formula>$J2="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="483">
+    <cfRule type="expression" dxfId="62" priority="483">
       <formula>$J2="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="482">
+    <cfRule type="expression" dxfId="61" priority="482">
       <formula>$J2="Ferrari"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="487">
-      <formula>$J2="Haas"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="60" priority="481">
       <formula>$J2="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="59" priority="480">
-      <formula>$J2="Aston Martin"</formula>
+    <cfRule type="expression" dxfId="59" priority="479">
+      <formula>$J2="Cadillac"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="58" priority="478">
       <formula>$J2="Audi"</formula>
@@ -17558,22 +17558,22 @@
     <cfRule type="expression" dxfId="57" priority="477">
       <formula>$J2="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="479">
-      <formula>$J2="Cadillac"</formula>
+    <cfRule type="expression" dxfId="56" priority="487">
+      <formula>$J2="Haas"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="486">
-      <formula>$J2="Racing Bulls"</formula>
+    <cfRule type="expression" dxfId="55" priority="480">
+      <formula>$J2="Aston Martin"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3:M12">
-    <cfRule type="expression" dxfId="54" priority="226">
-      <formula>$D1048555="Racing Bulls"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="227">
+    <cfRule type="expression" dxfId="54" priority="227">
       <formula>$D1048555="Haas"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="217">
+    <cfRule type="expression" dxfId="53" priority="217">
       <formula>$D1048555="Williams"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="218">
+      <formula>$D1048555="Audi"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="51" priority="219">
       <formula>$D1048555="Cadillac"</formula>
@@ -17581,23 +17581,23 @@
     <cfRule type="expression" dxfId="50" priority="220">
       <formula>$D1048555="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="218">
-      <formula>$D1048555="Audi"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="221">
+    <cfRule type="expression" dxfId="49" priority="221">
       <formula>$D1048555="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="222">
+    <cfRule type="expression" dxfId="48" priority="222">
       <formula>$D1048555="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="223">
+    <cfRule type="expression" dxfId="47" priority="223">
       <formula>$D1048555="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="224">
+    <cfRule type="expression" dxfId="46" priority="224">
       <formula>$D1048555="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="225">
+    <cfRule type="expression" dxfId="45" priority="225">
       <formula>$D1048555="Alpine"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="226">
+      <formula>$D1048555="Racing Bulls"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N12">
@@ -17615,108 +17615,108 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:O12">
-    <cfRule type="expression" dxfId="43" priority="206">
+    <cfRule type="expression" dxfId="43" priority="213">
+      <formula>$D1048555="Red Bull"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="215">
+      <formula>$D1048555="Racing Bulls"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="214">
+      <formula>$D1048555="Alpine"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="206">
       <formula>$D1048555="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="207">
+    <cfRule type="expression" dxfId="39" priority="207">
       <formula>$D1048555="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="208">
+    <cfRule type="expression" dxfId="38" priority="208">
       <formula>$D1048555="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="209">
+    <cfRule type="expression" dxfId="37" priority="209">
       <formula>$D1048555="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="210">
+    <cfRule type="expression" dxfId="36" priority="210">
       <formula>$D1048555="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="211">
+    <cfRule type="expression" dxfId="35" priority="211">
       <formula>$D1048555="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="212">
+    <cfRule type="expression" dxfId="34" priority="212">
       <formula>$D1048555="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="213">
-      <formula>$D1048555="Red Bull"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="215">
-      <formula>$D1048555="Racing Bulls"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="216">
+    <cfRule type="expression" dxfId="33" priority="216">
       <formula>$D1048555="Haas"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="214">
-      <formula>$D1048555="Alpine"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2">
-    <cfRule type="expression" dxfId="32" priority="125">
+    <cfRule type="expression" dxfId="32" priority="127">
+      <formula>$J2="Cadillac"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="128">
+      <formula>$J2="Aston Martin"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="129">
+      <formula>$J2="Mercedes"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="130">
+      <formula>$J2="Ferrari"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="131">
+      <formula>$J2="McLaren"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="132">
+      <formula>$J2="Red Bull"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="133">
+      <formula>$J2="Alpine"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="134">
+      <formula>$J2="Racing Bulls"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="135">
+      <formula>$J2="Haas"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="125">
       <formula>$J2="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="126">
+    <cfRule type="expression" dxfId="22" priority="126">
       <formula>$J2="Audi"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="127">
-      <formula>$J2="Cadillac"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="135">
-      <formula>$J2="Haas"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="134">
-      <formula>$J2="Racing Bulls"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="133">
-      <formula>$J2="Alpine"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="132">
-      <formula>$J2="Red Bull"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="131">
-      <formula>$J2="McLaren"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="130">
-      <formula>$J2="Ferrari"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="129">
-      <formula>$J2="Mercedes"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="128">
-      <formula>$J2="Aston Martin"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q3:Q12">
     <cfRule type="expression" dxfId="21" priority="23">
       <formula>#REF!="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="22">
+    <cfRule type="expression" dxfId="20" priority="24">
+      <formula>#REF!="Racing Bulls"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="25">
+      <formula>#REF!="Haas"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="22">
       <formula>#REF!="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="21">
+    <cfRule type="expression" dxfId="17" priority="21">
       <formula>#REF!="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="20">
+    <cfRule type="expression" dxfId="16" priority="20">
       <formula>#REF!="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="15" priority="19">
       <formula>#REF!="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="18">
-      <formula>#REF!="Aston Martin"</formula>
+    <cfRule type="expression" dxfId="14" priority="17">
+      <formula>#REF!="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="25">
-      <formula>#REF!="Haas"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="16">
+    <cfRule type="expression" dxfId="13" priority="16">
       <formula>#REF!="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="15">
+    <cfRule type="expression" dxfId="12" priority="15">
       <formula>#REF!="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="24">
-      <formula>#REF!="Racing Bulls"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="17">
-      <formula>#REF!="Cadillac"</formula>
+    <cfRule type="expression" dxfId="11" priority="18">
+      <formula>#REF!="Aston Martin"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R12">
@@ -17732,38 +17732,38 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T12">
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+      <formula>"Mercedes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+      <formula>"McLaren"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"Ferrari"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
-      <formula>"Mercedes"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"Red Bull"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>"Alpine"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"Haas"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"Williams"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"Audi"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"Cadillac"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"Aston Martin"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="11" operator="equal">
-      <formula>"McLaren"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U12">

--- a/static/data/Ratings.xlsx
+++ b/static/data/Ratings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Programming\webdev\portfolio\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A882DC6-58AA-43DA-9DFE-1731D5023EF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95C47A8-CECE-4EEE-AA11-21812C6BD690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" firstSheet="2" activeTab="2" xr2:uid="{BD88BCC4-2E11-4C36-830D-A75A044EF5A6}"/>
   </bookViews>
@@ -259,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1544" uniqueCount="77">
   <si>
     <t>RANK</t>
   </si>
@@ -485,6 +485,12 @@
   <si>
     <t>TEAM DRIVER AVG</t>
   </si>
+  <si>
+    <t>NR</t>
+  </si>
+  <si>
+    <t>Sno</t>
+  </si>
 </sst>
 </file>
 
@@ -494,7 +500,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="General;&quot;-&quot;;General;@"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -566,6 +572,23 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -841,7 +864,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -992,11 +1015,169 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="103">
+  <dxfs count="105">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF34C8DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF34C8DC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF638FFD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF009FE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF366FC3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFD7F00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE4002C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF26F0CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF21976F"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFA8A8AB"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFA2B00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF1767D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDBDFE0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1613,125 +1794,20 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF638FFD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF009FE4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF366FC3"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFD7F00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE4002C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF26F0CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF21976F"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA8A8AB"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFA2B00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF1767D8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDBDFE0"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF34C8DC"/>
+      <color rgb="FFAAE8F0"/>
+      <color rgb="FFF8696B"/>
+      <color rgb="FF63BE7B"/>
       <color rgb="FF26F0CE"/>
       <color rgb="FF229870"/>
       <color rgb="FFA7A7AA"/>
       <color rgb="FFFD2C00"/>
       <color rgb="FF1766D7"/>
       <color rgb="FFDDE0E1"/>
-      <color rgb="FF608CFB"/>
-      <color rgb="FF00A0E6"/>
-      <color rgb="FF356FC3"/>
-      <color rgb="FFE5002C"/>
     </mruColors>
   </colors>
   <extLst>
@@ -3342,7 +3418,7 @@
     </row>
     <row r="4" spans="1:83" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="36" t="s">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="B4" s="36" t="s">
         <v>63</v>
@@ -3724,7 +3800,7 @@
       <c r="A6" s="12">
         <v>1</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="54">
         <v>63</v>
       </c>
       <c r="C6" s="12" t="s">
@@ -3735,7 +3811,7 @@
       </c>
       <c r="E6" s="30">
         <f>IFERROR(AVERAGE(H6,M6,P6,U6,Z6,AC6,AF6,AI6,AN6,AQ6,AT6,AY6,BB6,BE6,BH6,BM6,BP6,BS6,BV6,BY6,CB6,CE6),-1)</f>
-        <v>8.6819999999999986</v>
+        <v>7.0583333333333336</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>72</v>
@@ -3744,7 +3820,7 @@
         <v>72</v>
       </c>
       <c r="H6" s="24" t="str">
-        <f>IF(AND(F6="-", G6="-"), "-", AVERAGE(F6, G6))</f>
+        <f>IF(AND(OR(F6="-", F6="NR"), OR(G6="-", G6="NR")), IF(OR(F6="NR", G6="NR"), "NR", "-"), ((IFERROR(F6*0.3, 0) + IFERROR(G6*0.7, 0)) / (IF(OR(F6="-", F6="NR"), 0, 0.3) + IF(OR(G6="-", G6="NR"), 0, 0.7))) - (IF(F6="NR", 0.3, 0) + IF(G6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="I6" s="21" t="s">
@@ -3760,7 +3836,7 @@
         <v>72</v>
       </c>
       <c r="M6" s="24" t="str">
-        <f>IF(AND(I6="-", J6="-", K6="-", L6="-"), "-", (IFERROR(AVERAGE(I6:J6), 0)*0.24) + (IFERROR(AVERAGE(K6:L6), 0)*0.76))</f>
+        <f>IF(AND(OR(I6="-", I6="NR"), OR(J6="-", J6="NR"), OR(K6="-", K6="NR"), OR(L6="-", L6="NR")), IF(OR(I6="NR", J6="NR", K6="NR", L6="NR"), "NR", "-"), ((IFERROR(I6*0.1, 0) + IFERROR(J6*0.15, 0) + IFERROR(K6*0.2, 0) + IFERROR(L6*0.55, 0)) / (IF(OR(I6="-", I6="NR"), 0, 0.1) + IF(OR(J6="-", J6="NR"), 0, 0.15) + IF(OR(K6="-", K6="NR"), 0, 0.2) + IF(OR(L6="-", L6="NR"), 0, 0.55))) - (IF(I6="NR", 0.1, 0) + IF(J6="NR", 0.15, 0) + IF(K6="NR", 0.2, 0) + IF(L6="NR", 0.55, 0)))</f>
         <v>-</v>
       </c>
       <c r="N6" s="21" t="s">
@@ -3770,7 +3846,7 @@
         <v>72</v>
       </c>
       <c r="P6" s="24" t="str">
-        <f>IF(AND(N6="-", O6="-"), "-", AVERAGE(N6, O6))</f>
+        <f>IF(AND(OR(N6="-", N6="NR"), OR(O6="-", O6="NR")), IF(OR(N6="NR", O6="NR"), "NR", "-"), ((IFERROR(N6*0.3, 0) + IFERROR(O6*0.7, 0)) / (IF(OR(N6="-", N6="NR"), 0, 0.3) + IF(OR(O6="-", O6="NR"), 0, 0.7))) - (IF(N6="NR", 0.3, 0) + IF(O6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="Q6" s="21" t="s">
@@ -3786,34 +3862,34 @@
         <v>72</v>
       </c>
       <c r="U6" s="24" t="str">
-        <f>IF(AND(Q6="-", R6="-", S6="-", T6="-"), "-", (IFERROR(AVERAGE(Q6:R6), 0)*0.24) + (IFERROR(AVERAGE(S6:T6), 0)*0.76))</f>
+        <f>IF(AND(OR(Q6="-", Q6="NR"), OR(R6="-", R6="NR"), OR(S6="-", S6="NR"), OR(T6="-", T6="NR")), IF(OR(Q6="NR", R6="NR", S6="NR", T6="NR"), "NR", "-"), ((IFERROR(Q6*0.1, 0) + IFERROR(R6*0.15, 0) + IFERROR(S6*0.2, 0) + IFERROR(T6*0.55, 0)) / (IF(OR(Q6="-", Q6="NR"), 0, 0.1) + IF(OR(R6="-", R6="NR"), 0, 0.15) + IF(OR(S6="-", S6="NR"), 0, 0.2) + IF(OR(T6="-", T6="NR"), 0, 0.55))) - (IF(Q6="NR", 0.1, 0) + IF(R6="NR", 0.15, 0) + IF(S6="NR", 0.2, 0) + IF(T6="NR", 0.55, 0)))</f>
         <v>-</v>
       </c>
       <c r="V6" s="28">
+        <v>8.75</v>
+      </c>
+      <c r="W6" s="21">
         <v>8.5</v>
       </c>
-      <c r="W6" s="21">
+      <c r="X6" s="21">
         <v>8.75</v>
       </c>
-      <c r="X6" s="21">
-        <v>8.6999999999999993</v>
-      </c>
       <c r="Y6" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z6" s="24">
-        <f>IF(AND(V6="-", W6="-", X6="-", Y6="-"), "-", (IFERROR(AVERAGE(V6:W6), 0)*0.24) + (IFERROR(AVERAGE(X6:Y6), 0)*0.76))</f>
-        <v>8.6819999999999986</v>
-      </c>
-      <c r="AA6" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB6" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC6" s="24" t="str">
-        <f>IF(AND(AA6="-", AB6="-"), "-", AVERAGE(AA6, AB6))</f>
-        <v>-</v>
+        <f>IF(AND(OR(V6="-", V6="NR"), OR(W6="-", W6="NR"), OR(X6="-", X6="NR"), OR(Y6="-", Y6="NR")), IF(OR(V6="NR", W6="NR", X6="NR", Y6="NR"), "NR", "-"), ((IFERROR(V6*0.1, 0) + IFERROR(W6*0.15, 0) + IFERROR(X6*0.2, 0) + IFERROR(Y6*0.55, 0)) / (IF(OR(V6="-", V6="NR"), 0, 0.1) + IF(OR(W6="-", W6="NR"), 0, 0.15) + IF(OR(X6="-", X6="NR"), 0, 0.2) + IF(OR(Y6="-", Y6="NR"), 0, 0.55))) - (IF(V6="NR", 0.1, 0) + IF(W6="NR", 0.15, 0) + IF(X6="NR", 0.2, 0) + IF(Y6="NR", 0.55, 0)))</f>
+        <v>8.6666666666666661</v>
+      </c>
+      <c r="AA6" s="21">
+        <v>6</v>
+      </c>
+      <c r="AB6" s="21">
+        <v>5</v>
+      </c>
+      <c r="AC6" s="24">
+        <f>IF(AND(OR(AA6="-", AA6="NR"), OR(AB6="-", AB6="NR")), IF(OR(AA6="NR", AB6="NR"), "NR", "-"), ((IFERROR(AA6*0.45, 0) + IFERROR(AB6*0.55, 0)) / (IF(OR(AA6="-", AA6="NR"), 0, 0.45) + IF(OR(AB6="-", AB6="NR"), 0, 0.55))) - (IF(AA6="NR", 0.45, 0) + IF(AB6="NR", 0.55, 0)))</f>
+        <v>5.45</v>
       </c>
       <c r="AD6" s="21" t="s">
         <v>72</v>
@@ -3822,7 +3898,7 @@
         <v>72</v>
       </c>
       <c r="AF6" s="24" t="str">
-        <f>IF(AND(AD6="-", AE6="-"), "-", AVERAGE(AD6, AE6))</f>
+        <f>IF(AND(OR(AD6="-", AD6="NR"), OR(AE6="-", AE6="NR")), IF(OR(AD6="NR", AE6="NR"), "NR", "-"), ((IFERROR(AD6*0.3, 0) + IFERROR(AE6*0.7, 0)) / (IF(OR(AD6="-", AD6="NR"), 0, 0.3) + IF(OR(AE6="-", AE6="NR"), 0, 0.7))) - (IF(AD6="NR", 0.3, 0) + IF(AE6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="AG6" s="21" t="s">
@@ -3832,7 +3908,7 @@
         <v>72</v>
       </c>
       <c r="AI6" s="24" t="str">
-        <f>IF(AND(AG6="-", AH6="-"), "-", AVERAGE(AG6, AH6))</f>
+        <f>IF(AND(OR(AG6="-", AG6="NR"), OR(AH6="-", AH6="NR")), IF(OR(AG6="NR", AH6="NR"), "NR", "-"), ((IFERROR(AG6*0.3, 0) + IFERROR(AH6*0.7, 0)) / (IF(OR(AG6="-", AG6="NR"), 0, 0.3) + IF(OR(AH6="-", AH6="NR"), 0, 0.7))) - (IF(AG6="NR", 0.3, 0) + IF(AH6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="AJ6" s="21" t="s">
@@ -3848,7 +3924,7 @@
         <v>72</v>
       </c>
       <c r="AN6" s="24" t="str">
-        <f>IF(AND(AL6="-", AM6="-"), "-", AVERAGE(AL6, AM6))</f>
+        <f>IF(AND(OR(AJ6="-", AJ6="NR"), OR(AK6="-", AK6="NR"), OR(AL6="-", AL6="NR"), OR(AM6="-", AM6="NR")), IF(OR(AJ6="NR", AK6="NR", AL6="NR", AM6="NR"), "NR", "-"), ((IFERROR(AJ6*0.1, 0) + IFERROR(AK6*0.15, 0) + IFERROR(AL6*0.2, 0) + IFERROR(AM6*0.55, 0)) / (IF(OR(AJ6="-", AJ6="NR"), 0, 0.1) + IF(OR(AK6="-", AK6="NR"), 0, 0.15) + IF(OR(AL6="-", AL6="NR"), 0, 0.2) + IF(OR(AM6="-", AM6="NR"), 0, 0.55))) - (IF(AJ6="NR", 0.1, 0) + IF(AK6="NR", 0.15, 0) + IF(AL6="NR", 0.2, 0) + IF(AM6="NR", 0.55, 0)))</f>
         <v>-</v>
       </c>
       <c r="AO6" s="21" t="s">
@@ -3858,7 +3934,7 @@
         <v>72</v>
       </c>
       <c r="AQ6" s="24" t="str">
-        <f>IF(AND(AO6="-", AP6="-"), "-", AVERAGE(AO6, AP6))</f>
+        <f>IF(AND(OR(AO6="-", AO6="NR"), OR(AP6="-", AP6="NR")), IF(OR(AO6="NR", AP6="NR"), "NR", "-"), ((IFERROR(AO6*0.3, 0) + IFERROR(AP6*0.7, 0)) / (IF(OR(AO6="-", AO6="NR"), 0, 0.3) + IF(OR(AP6="-", AP6="NR"), 0, 0.7))) - (IF(AO6="NR", 0.3, 0) + IF(AP6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="AR6" s="21" t="s">
@@ -3868,7 +3944,7 @@
         <v>72</v>
       </c>
       <c r="AT6" s="24" t="str">
-        <f>IF(AND(AR6="-", AS6="-"), "-", AVERAGE(AR6, AS6))</f>
+        <f>IF(AND(OR(AR6="-", AR6="NR"), OR(AS6="-", AS6="NR")), IF(OR(AR6="NR", AS6="NR"), "NR", "-"), ((IFERROR(AR6*0.3, 0) + IFERROR(AS6*0.7, 0)) / (IF(OR(AR6="-", AR6="NR"), 0, 0.3) + IF(OR(AS6="-", AS6="NR"), 0, 0.7))) - (IF(AR6="NR", 0.3, 0) + IF(AS6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="AU6" s="21" t="s">
@@ -3884,7 +3960,7 @@
         <v>72</v>
       </c>
       <c r="AY6" s="24" t="str">
-        <f>IF(AND(AU6="-", AV6="-", AW6="-", AX6="-"), "-", (IFERROR(AVERAGE(AU6:AV6), 0)*0.24) + (IFERROR(AVERAGE(AW6:AX6), 0)*0.76))</f>
+        <f>IF(AND(OR(AU6="-", AU6="NR"), OR(AV6="-", AV6="NR"), OR(AW6="-", AW6="NR"), OR(AX6="-", AX6="NR")), IF(OR(AU6="NR", AV6="NR", AW6="NR", AX6="NR"), "NR", "-"), ((IFERROR(AU6*0.1, 0) + IFERROR(AV6*0.15, 0) + IFERROR(AW6*0.2, 0) + IFERROR(AX6*0.55, 0)) / (IF(OR(AU6="-", AU6="NR"), 0, 0.1) + IF(OR(AV6="-", AV6="NR"), 0, 0.15) + IF(OR(AW6="-", AW6="NR"), 0, 0.2) + IF(OR(AX6="-", AX6="NR"), 0, 0.55))) - (IF(AU6="NR", 0.1, 0) + IF(AV6="NR", 0.15, 0) + IF(AW6="NR", 0.2, 0) + IF(AX6="NR", 0.55, 0)))</f>
         <v>-</v>
       </c>
       <c r="AZ6" s="21" t="s">
@@ -3894,7 +3970,7 @@
         <v>72</v>
       </c>
       <c r="BB6" s="24" t="str">
-        <f>IF(AND(AZ6="-", BA6="-"), "-", AVERAGE(AZ6, BA6))</f>
+        <f>IF(AND(OR(AZ6="-", AZ6="NR"), OR(BA6="-", BA6="NR")), IF(OR(AZ6="NR", BA6="NR"), "NR", "-"), ((IFERROR(AZ6*0.3, 0) + IFERROR(BA6*0.7, 0)) / (IF(OR(AZ6="-", AZ6="NR"), 0, 0.3) + IF(OR(BA6="-", BA6="NR"), 0, 0.7))) - (IF(AZ6="NR", 0.3, 0) + IF(BA6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="BC6" s="21" t="s">
@@ -3904,7 +3980,7 @@
         <v>72</v>
       </c>
       <c r="BE6" s="24" t="str">
-        <f>IF(AND(BC6="-", BD6="-"), "-", AVERAGE(BC6, BD6))</f>
+        <f>IF(AND(OR(BC6="-", BC6="NR"), OR(BD6="-", BD6="NR")), IF(OR(BC6="NR", BD6="NR"), "NR", "-"), ((IFERROR(BC6*0.3, 0) + IFERROR(BD6*0.7, 0)) / (IF(OR(BC6="-", BC6="NR"), 0, 0.3) + IF(OR(BD6="-", BD6="NR"), 0, 0.7))) - (IF(BC6="NR", 0.3, 0) + IF(BD6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="BF6" s="21" t="s">
@@ -3914,7 +3990,7 @@
         <v>72</v>
       </c>
       <c r="BH6" s="24" t="str">
-        <f>IF(AND(BF6="-", BG6="-"), "-", AVERAGE(BF6, BG6))</f>
+        <f>IF(AND(OR(BF6="-", BF6="NR"), OR(BG6="-", BG6="NR")), IF(OR(BF6="NR", BG6="NR"), "NR", "-"), ((IFERROR(BF6*0.3, 0) + IFERROR(BG6*0.7, 0)) / (IF(OR(BF6="-", BF6="NR"), 0, 0.3) + IF(OR(BG6="-", BG6="NR"), 0, 0.7))) - (IF(BF6="NR", 0.3, 0) + IF(BG6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="BI6" s="21" t="s">
@@ -3930,7 +4006,7 @@
         <v>72</v>
       </c>
       <c r="BM6" s="24" t="str">
-        <f>IF(AND(BI6="-", BJ6="-", BK6="-", BL6="-"), "-", (IFERROR(AVERAGE(BI6:BJ6), 0)*0.24) + (IFERROR(AVERAGE(BK6:BL6), 0)*0.76))</f>
+        <f>IF(AND(OR(BI6="-", BI6="NR"), OR(BJ6="-", BJ6="NR"), OR(BK6="-", BK6="NR"), OR(BL6="-", BL6="NR")), IF(OR(BI6="NR", BJ6="NR", BK6="NR", BL6="NR"), "NR", "-"), ((IFERROR(BI6*0.1, 0) + IFERROR(BJ6*0.15, 0) + IFERROR(BK6*0.2, 0) + IFERROR(BL6*0.55, 0)) / (IF(OR(BI6="-", BI6="NR"), 0, 0.1) + IF(OR(BJ6="-", BJ6="NR"), 0, 0.15) + IF(OR(BK6="-", BK6="NR"), 0, 0.2) + IF(OR(BL6="-", BL6="NR"), 0, 0.55))) - (IF(BI6="NR", 0.1, 0) + IF(BJ6="NR", 0.15, 0) + IF(BK6="NR", 0.2, 0) + IF(BL6="NR", 0.55, 0)))</f>
         <v>-</v>
       </c>
       <c r="BN6" s="21" t="s">
@@ -3940,7 +4016,7 @@
         <v>72</v>
       </c>
       <c r="BP6" s="24" t="str">
-        <f>IF(AND(BN6="-", BO6="-"), "-", AVERAGE(BN6, BO6))</f>
+        <f>IF(AND(OR(BN6="-", BN6="NR"), OR(BO6="-", BO6="NR")), IF(OR(BN6="NR", BO6="NR"), "NR", "-"), ((IFERROR(BN6*0.3, 0) + IFERROR(BO6*0.7, 0)) / (IF(OR(BN6="-", BN6="NR"), 0, 0.3) + IF(OR(BO6="-", BO6="NR"), 0, 0.7))) - (IF(BN6="NR", 0.3, 0) + IF(BO6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="BQ6" s="21" t="s">
@@ -3950,7 +4026,7 @@
         <v>72</v>
       </c>
       <c r="BS6" s="24" t="str">
-        <f>IF(AND(BQ6="-", BR6="-"), "-", AVERAGE(BQ6, BR6))</f>
+        <f>IF(AND(OR(BQ6="-", BQ6="NR"), OR(BR6="-", BR6="NR")), IF(OR(BQ6="NR", BR6="NR"), "NR", "-"), ((IFERROR(BQ6*0.3, 0) + IFERROR(BR6*0.7, 0)) / (IF(OR(BQ6="-", BQ6="NR"), 0, 0.3) + IF(OR(BR6="-", BR6="NR"), 0, 0.7))) - (IF(BQ6="NR", 0.3, 0) + IF(BR6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="BT6" s="21" t="s">
@@ -3960,7 +4036,7 @@
         <v>72</v>
       </c>
       <c r="BV6" s="24" t="str">
-        <f>IF(AND(BT6="-", BU6="-"), "-", AVERAGE(BT6, BU6))</f>
+        <f>IF(AND(OR(BT6="-", BT6="NR"), OR(BU6="-", BU6="NR")), IF(OR(BT6="NR", BU6="NR"), "NR", "-"), ((IFERROR(BT6*0.3, 0) + IFERROR(BU6*0.7, 0)) / (IF(OR(BT6="-", BT6="NR"), 0, 0.3) + IF(OR(BU6="-", BU6="NR"), 0, 0.7))) - (IF(BT6="NR", 0.3, 0) + IF(BU6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="BW6" s="21" t="s">
@@ -3970,7 +4046,7 @@
         <v>72</v>
       </c>
       <c r="BY6" s="24" t="str">
-        <f>IF(AND(BW6="-", BX6="-"), "-", AVERAGE(BW6, BX6))</f>
+        <f>IF(AND(OR(BW6="-", BW6="NR"), OR(BX6="-", BX6="NR")), IF(OR(BW6="NR", BX6="NR"), "NR", "-"), ((IFERROR(BW6*0.3, 0) + IFERROR(BX6*0.7, 0)) / (IF(OR(BW6="-", BW6="NR"), 0, 0.3) + IF(OR(BX6="-", BX6="NR"), 0, 0.7))) - (IF(BW6="NR", 0.3, 0) + IF(BX6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="BZ6" s="21" t="s">
@@ -3980,7 +4056,7 @@
         <v>72</v>
       </c>
       <c r="CB6" s="24" t="str">
-        <f>IF(AND(BZ6="-", CA6="-"), "-", AVERAGE(BZ6, CA6))</f>
+        <f>IF(AND(OR(BZ6="-", BZ6="NR"), OR(CA6="-", CA6="NR")), IF(OR(BZ6="NR", CA6="NR"), "NR", "-"), ((IFERROR(BZ6*0.3, 0) + IFERROR(CA6*0.7, 0)) / (IF(OR(BZ6="-", BZ6="NR"), 0, 0.3) + IF(OR(CA6="-", CA6="NR"), 0, 0.7))) - (IF(BZ6="NR", 0.3, 0) + IF(CA6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="CC6" s="21" t="s">
@@ -3990,7 +4066,7 @@
         <v>72</v>
       </c>
       <c r="CE6" s="24" t="str">
-        <f>IF(AND(CC6="-", CD6="-"), "-", AVERAGE(CC6, CD6))</f>
+        <f>IF(AND(OR(CC6="-", CC6="NR"), OR(CD6="-", CD6="NR")), IF(OR(CC6="NR", CD6="NR"), "NR", "-"), ((IFERROR(CC6*0.3, 0) + IFERROR(CD6*0.7, 0)) / (IF(OR(CC6="-", CC6="NR"), 0, 0.3) + IF(OR(CD6="-", CD6="NR"), 0, 0.7))) - (IF(CC6="NR", 0.3, 0) + IF(CD6="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
     </row>
@@ -3998,7 +4074,7 @@
       <c r="A7" s="12">
         <v>2</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="54">
         <v>12</v>
       </c>
       <c r="C7" s="12" t="s">
@@ -4009,7 +4085,7 @@
       </c>
       <c r="E7" s="30">
         <f t="shared" ref="E7:E27" si="0">IFERROR(AVERAGE(H7,M7,P7,U7,Z7,AC7,AF7,AI7,AN7,AQ7,AT7,AY7,BB7,BE7,BH7,BM7,BP7,BS7,BV7,BY7,CB7,CE7),-1)</f>
-        <v>8.1859999999999999</v>
+        <v>8.37638888888889</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>72</v>
@@ -4018,7 +4094,7 @@
         <v>72</v>
       </c>
       <c r="H7" s="24" t="str">
-        <f t="shared" ref="H7:H27" si="1">IF(AND(F7="-", G7="-"), "-", AVERAGE(F7, G7))</f>
+        <f t="shared" ref="H7:H27" si="1">IF(AND(OR(F7="-", F7="NR"), OR(G7="-", G7="NR")), IF(OR(F7="NR", G7="NR"), "NR", "-"), ((IFERROR(F7*0.3, 0) + IFERROR(G7*0.7, 0)) / (IF(OR(F7="-", F7="NR"), 0, 0.3) + IF(OR(G7="-", G7="NR"), 0, 0.7))) - (IF(F7="NR", 0.3, 0) + IF(G7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="I7" s="21" t="s">
@@ -4034,7 +4110,7 @@
         <v>72</v>
       </c>
       <c r="M7" s="24" t="str">
-        <f t="shared" ref="M7:M27" si="2">IF(AND(I7="-", J7="-", K7="-", L7="-"), "-", (IFERROR(AVERAGE(I7:J7), 0)*0.24) + (IFERROR(AVERAGE(K7:L7), 0)*0.76))</f>
+        <f t="shared" ref="M7:M27" si="2">IF(AND(OR(I7="-", I7="NR"), OR(J7="-", J7="NR"), OR(K7="-", K7="NR"), OR(L7="-", L7="NR")), IF(OR(I7="NR", J7="NR", K7="NR", L7="NR"), "NR", "-"), ((IFERROR(I7*0.1, 0) + IFERROR(J7*0.15, 0) + IFERROR(K7*0.2, 0) + IFERROR(L7*0.55, 0)) / (IF(OR(I7="-", I7="NR"), 0, 0.1) + IF(OR(J7="-", J7="NR"), 0, 0.15) + IF(OR(K7="-", K7="NR"), 0, 0.2) + IF(OR(L7="-", L7="NR"), 0, 0.55))) - (IF(I7="NR", 0.1, 0) + IF(J7="NR", 0.15, 0) + IF(K7="NR", 0.2, 0) + IF(L7="NR", 0.55, 0)))</f>
         <v>-</v>
       </c>
       <c r="N7" s="21" t="s">
@@ -4044,7 +4120,7 @@
         <v>72</v>
       </c>
       <c r="P7" s="24" t="str">
-        <f t="shared" ref="P7:P27" si="3">IF(AND(N7="-", O7="-"), "-", AVERAGE(N7, O7))</f>
+        <f t="shared" ref="P7:P27" si="3">IF(AND(OR(N7="-", N7="NR"), OR(O7="-", O7="NR")), IF(OR(N7="NR", O7="NR"), "NR", "-"), ((IFERROR(N7*0.3, 0) + IFERROR(O7*0.7, 0)) / (IF(OR(N7="-", N7="NR"), 0, 0.3) + IF(OR(O7="-", O7="NR"), 0, 0.7))) - (IF(N7="NR", 0.3, 0) + IF(O7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="Q7" s="21" t="s">
@@ -4060,34 +4136,34 @@
         <v>72</v>
       </c>
       <c r="U7" s="24" t="str">
-        <f t="shared" ref="U7:U27" si="4">IF(AND(Q7="-", R7="-", S7="-", T7="-"), "-", (IFERROR(AVERAGE(Q7:R7), 0)*0.24) + (IFERROR(AVERAGE(S7:T7), 0)*0.76))</f>
+        <f t="shared" ref="U7:U27" si="4">IF(AND(OR(Q7="-", Q7="NR"), OR(R7="-", R7="NR"), OR(S7="-", S7="NR"), OR(T7="-", T7="NR")), IF(OR(Q7="NR", R7="NR", S7="NR", T7="NR"), "NR", "-"), ((IFERROR(Q7*0.1, 0) + IFERROR(R7*0.15, 0) + IFERROR(S7*0.2, 0) + IFERROR(T7*0.55, 0)) / (IF(OR(Q7="-", Q7="NR"), 0, 0.1) + IF(OR(R7="-", R7="NR"), 0, 0.15) + IF(OR(S7="-", S7="NR"), 0, 0.2) + IF(OR(T7="-", T7="NR"), 0, 0.55))) - (IF(Q7="NR", 0.1, 0) + IF(R7="NR", 0.15, 0) + IF(S7="NR", 0.2, 0) + IF(T7="NR", 0.55, 0)))</f>
         <v>-</v>
       </c>
       <c r="V7" s="28">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="W7" s="21">
         <v>5.75</v>
       </c>
       <c r="X7" s="21">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="Y7" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z7" s="24">
-        <f t="shared" ref="Z7:Z27" si="5">IF(AND(V7="-", W7="-", X7="-", Y7="-"), "-", (IFERROR(AVERAGE(V7:W7), 0)*0.24) + (IFERROR(AVERAGE(X7:Y7), 0)*0.76))</f>
-        <v>8.1859999999999999</v>
-      </c>
-      <c r="AA7" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB7" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC7" s="24" t="str">
-        <f t="shared" ref="AC7:AC27" si="6">IF(AND(AA7="-", AB7="-"), "-", AVERAGE(AA7, AB7))</f>
-        <v>-</v>
+        <f t="shared" ref="Z7:Z28" si="5">IF(AND(OR(V7="-", V7="NR"), OR(W7="-", W7="NR"), OR(X7="-", X7="NR"), OR(Y7="-", Y7="NR")), IF(OR(V7="NR", W7="NR", X7="NR", Y7="NR"), "NR", "-"), ((IFERROR(V7*0.1, 0) + IFERROR(W7*0.15, 0) + IFERROR(X7*0.2, 0) + IFERROR(Y7*0.55, 0)) / (IF(OR(V7="-", V7="NR"), 0, 0.1) + IF(OR(W7="-", W7="NR"), 0, 0.15) + IF(OR(X7="-", X7="NR"), 0, 0.2) + IF(OR(Y7="-", Y7="NR"), 0, 0.55))) - (IF(V7="NR", 0.1, 0) + IF(W7="NR", 0.15, 0) + IF(X7="NR", 0.2, 0) + IF(Y7="NR", 0.55, 0)))</f>
+        <v>7.5277777777777777</v>
+      </c>
+      <c r="AA7" s="21">
+        <v>9.5</v>
+      </c>
+      <c r="AB7" s="21">
+        <v>9</v>
+      </c>
+      <c r="AC7" s="24">
+        <f t="shared" ref="AC7:AC27" si="6">IF(AND(OR(AA7="-", AA7="NR"), OR(AB7="-", AB7="NR")), IF(OR(AA7="NR", AB7="NR"), "NR", "-"), ((IFERROR(AA7*0.45, 0) + IFERROR(AB7*0.55, 0)) / (IF(OR(AA7="-", AA7="NR"), 0, 0.45) + IF(OR(AB7="-", AB7="NR"), 0, 0.55))) - (IF(AA7="NR", 0.45, 0) + IF(AB7="NR", 0.55, 0)))</f>
+        <v>9.2250000000000014</v>
       </c>
       <c r="AD7" s="21" t="s">
         <v>72</v>
@@ -4096,7 +4172,7 @@
         <v>72</v>
       </c>
       <c r="AF7" s="24" t="str">
-        <f t="shared" ref="AF7:AF27" si="7">IF(AND(AD7="-", AE7="-"), "-", AVERAGE(AD7, AE7))</f>
+        <f t="shared" ref="AF7:AF27" si="7">IF(AND(OR(AD7="-", AD7="NR"), OR(AE7="-", AE7="NR")), IF(OR(AD7="NR", AE7="NR"), "NR", "-"), ((IFERROR(AD7*0.3, 0) + IFERROR(AE7*0.7, 0)) / (IF(OR(AD7="-", AD7="NR"), 0, 0.3) + IF(OR(AE7="-", AE7="NR"), 0, 0.7))) - (IF(AD7="NR", 0.3, 0) + IF(AE7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="AG7" s="21" t="s">
@@ -4106,7 +4182,7 @@
         <v>72</v>
       </c>
       <c r="AI7" s="24" t="str">
-        <f t="shared" ref="AI7:AI27" si="8">IF(AND(AG7="-", AH7="-"), "-", AVERAGE(AG7, AH7))</f>
+        <f t="shared" ref="AI7:AI27" si="8">IF(AND(OR(AG7="-", AG7="NR"), OR(AH7="-", AH7="NR")), IF(OR(AG7="NR", AH7="NR"), "NR", "-"), ((IFERROR(AG7*0.3, 0) + IFERROR(AH7*0.7, 0)) / (IF(OR(AG7="-", AG7="NR"), 0, 0.3) + IF(OR(AH7="-", AH7="NR"), 0, 0.7))) - (IF(AG7="NR", 0.3, 0) + IF(AH7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="AJ7" s="21" t="s">
@@ -4122,7 +4198,7 @@
         <v>72</v>
       </c>
       <c r="AN7" s="24" t="str">
-        <f t="shared" ref="AN7:AN27" si="9">IF(AND(AL7="-", AM7="-"), "-", AVERAGE(AL7, AM7))</f>
+        <f t="shared" ref="AN7:AN27" si="9">IF(AND(OR(AJ7="-", AJ7="NR"), OR(AK7="-", AK7="NR"), OR(AL7="-", AL7="NR"), OR(AM7="-", AM7="NR")), IF(OR(AJ7="NR", AK7="NR", AL7="NR", AM7="NR"), "NR", "-"), ((IFERROR(AJ7*0.1, 0) + IFERROR(AK7*0.15, 0) + IFERROR(AL7*0.2, 0) + IFERROR(AM7*0.55, 0)) / (IF(OR(AJ7="-", AJ7="NR"), 0, 0.1) + IF(OR(AK7="-", AK7="NR"), 0, 0.15) + IF(OR(AL7="-", AL7="NR"), 0, 0.2) + IF(OR(AM7="-", AM7="NR"), 0, 0.55))) - (IF(AJ7="NR", 0.1, 0) + IF(AK7="NR", 0.15, 0) + IF(AL7="NR", 0.2, 0) + IF(AM7="NR", 0.55, 0)))</f>
         <v>-</v>
       </c>
       <c r="AO7" s="21" t="s">
@@ -4132,7 +4208,7 @@
         <v>72</v>
       </c>
       <c r="AQ7" s="24" t="str">
-        <f t="shared" ref="AQ7:AQ27" si="10">IF(AND(AO7="-", AP7="-"), "-", AVERAGE(AO7, AP7))</f>
+        <f t="shared" ref="AQ7:AQ27" si="10">IF(AND(OR(AO7="-", AO7="NR"), OR(AP7="-", AP7="NR")), IF(OR(AO7="NR", AP7="NR"), "NR", "-"), ((IFERROR(AO7*0.3, 0) + IFERROR(AP7*0.7, 0)) / (IF(OR(AO7="-", AO7="NR"), 0, 0.3) + IF(OR(AP7="-", AP7="NR"), 0, 0.7))) - (IF(AO7="NR", 0.3, 0) + IF(AP7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="AR7" s="21" t="s">
@@ -4142,7 +4218,7 @@
         <v>72</v>
       </c>
       <c r="AT7" s="24" t="str">
-        <f t="shared" ref="AT7:AT27" si="11">IF(AND(AR7="-", AS7="-"), "-", AVERAGE(AR7, AS7))</f>
+        <f t="shared" ref="AT7:AT27" si="11">IF(AND(OR(AR7="-", AR7="NR"), OR(AS7="-", AS7="NR")), IF(OR(AR7="NR", AS7="NR"), "NR", "-"), ((IFERROR(AR7*0.3, 0) + IFERROR(AS7*0.7, 0)) / (IF(OR(AR7="-", AR7="NR"), 0, 0.3) + IF(OR(AS7="-", AS7="NR"), 0, 0.7))) - (IF(AR7="NR", 0.3, 0) + IF(AS7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="AU7" s="21" t="s">
@@ -4158,7 +4234,7 @@
         <v>72</v>
       </c>
       <c r="AY7" s="24" t="str">
-        <f t="shared" ref="AY7:AY27" si="12">IF(AND(AU7="-", AV7="-", AW7="-", AX7="-"), "-", (IFERROR(AVERAGE(AU7:AV7), 0)*0.24) + (IFERROR(AVERAGE(AW7:AX7), 0)*0.76))</f>
+        <f t="shared" ref="AY7:AY27" si="12">IF(AND(OR(AU7="-", AU7="NR"), OR(AV7="-", AV7="NR"), OR(AW7="-", AW7="NR"), OR(AX7="-", AX7="NR")), IF(OR(AU7="NR", AV7="NR", AW7="NR", AX7="NR"), "NR", "-"), ((IFERROR(AU7*0.1, 0) + IFERROR(AV7*0.15, 0) + IFERROR(AW7*0.2, 0) + IFERROR(AX7*0.55, 0)) / (IF(OR(AU7="-", AU7="NR"), 0, 0.1) + IF(OR(AV7="-", AV7="NR"), 0, 0.15) + IF(OR(AW7="-", AW7="NR"), 0, 0.2) + IF(OR(AX7="-", AX7="NR"), 0, 0.55))) - (IF(AU7="NR", 0.1, 0) + IF(AV7="NR", 0.15, 0) + IF(AW7="NR", 0.2, 0) + IF(AX7="NR", 0.55, 0)))</f>
         <v>-</v>
       </c>
       <c r="AZ7" s="21" t="s">
@@ -4168,7 +4244,7 @@
         <v>72</v>
       </c>
       <c r="BB7" s="24" t="str">
-        <f t="shared" ref="BB7:BB27" si="13">IF(AND(AZ7="-", BA7="-"), "-", AVERAGE(AZ7, BA7))</f>
+        <f t="shared" ref="BB7:BB27" si="13">IF(AND(OR(AZ7="-", AZ7="NR"), OR(BA7="-", BA7="NR")), IF(OR(AZ7="NR", BA7="NR"), "NR", "-"), ((IFERROR(AZ7*0.3, 0) + IFERROR(BA7*0.7, 0)) / (IF(OR(AZ7="-", AZ7="NR"), 0, 0.3) + IF(OR(BA7="-", BA7="NR"), 0, 0.7))) - (IF(AZ7="NR", 0.3, 0) + IF(BA7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="BC7" s="21" t="s">
@@ -4178,7 +4254,7 @@
         <v>72</v>
       </c>
       <c r="BE7" s="24" t="str">
-        <f t="shared" ref="BE7:BE27" si="14">IF(AND(BC7="-", BD7="-"), "-", AVERAGE(BC7, BD7))</f>
+        <f t="shared" ref="BE7:BE27" si="14">IF(AND(OR(BC7="-", BC7="NR"), OR(BD7="-", BD7="NR")), IF(OR(BC7="NR", BD7="NR"), "NR", "-"), ((IFERROR(BC7*0.3, 0) + IFERROR(BD7*0.7, 0)) / (IF(OR(BC7="-", BC7="NR"), 0, 0.3) + IF(OR(BD7="-", BD7="NR"), 0, 0.7))) - (IF(BC7="NR", 0.3, 0) + IF(BD7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="BF7" s="21" t="s">
@@ -4188,7 +4264,7 @@
         <v>72</v>
       </c>
       <c r="BH7" s="24" t="str">
-        <f t="shared" ref="BH7:BH27" si="15">IF(AND(BF7="-", BG7="-"), "-", AVERAGE(BF7, BG7))</f>
+        <f t="shared" ref="BH7:BH27" si="15">IF(AND(OR(BF7="-", BF7="NR"), OR(BG7="-", BG7="NR")), IF(OR(BF7="NR", BG7="NR"), "NR", "-"), ((IFERROR(BF7*0.3, 0) + IFERROR(BG7*0.7, 0)) / (IF(OR(BF7="-", BF7="NR"), 0, 0.3) + IF(OR(BG7="-", BG7="NR"), 0, 0.7))) - (IF(BF7="NR", 0.3, 0) + IF(BG7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="BI7" s="21" t="s">
@@ -4204,7 +4280,7 @@
         <v>72</v>
       </c>
       <c r="BM7" s="24" t="str">
-        <f t="shared" ref="BM7:BM27" si="16">IF(AND(BI7="-", BJ7="-", BK7="-", BL7="-"), "-", (IFERROR(AVERAGE(BI7:BJ7), 0)*0.24) + (IFERROR(AVERAGE(BK7:BL7), 0)*0.76))</f>
+        <f t="shared" ref="BM7:BM27" si="16">IF(AND(OR(BI7="-", BI7="NR"), OR(BJ7="-", BJ7="NR"), OR(BK7="-", BK7="NR"), OR(BL7="-", BL7="NR")), IF(OR(BI7="NR", BJ7="NR", BK7="NR", BL7="NR"), "NR", "-"), ((IFERROR(BI7*0.1, 0) + IFERROR(BJ7*0.15, 0) + IFERROR(BK7*0.2, 0) + IFERROR(BL7*0.55, 0)) / (IF(OR(BI7="-", BI7="NR"), 0, 0.1) + IF(OR(BJ7="-", BJ7="NR"), 0, 0.15) + IF(OR(BK7="-", BK7="NR"), 0, 0.2) + IF(OR(BL7="-", BL7="NR"), 0, 0.55))) - (IF(BI7="NR", 0.1, 0) + IF(BJ7="NR", 0.15, 0) + IF(BK7="NR", 0.2, 0) + IF(BL7="NR", 0.55, 0)))</f>
         <v>-</v>
       </c>
       <c r="BN7" s="21" t="s">
@@ -4214,7 +4290,7 @@
         <v>72</v>
       </c>
       <c r="BP7" s="24" t="str">
-        <f t="shared" ref="BP7:BP27" si="17">IF(AND(BN7="-", BO7="-"), "-", AVERAGE(BN7, BO7))</f>
+        <f t="shared" ref="BP7:BP27" si="17">IF(AND(OR(BN7="-", BN7="NR"), OR(BO7="-", BO7="NR")), IF(OR(BN7="NR", BO7="NR"), "NR", "-"), ((IFERROR(BN7*0.3, 0) + IFERROR(BO7*0.7, 0)) / (IF(OR(BN7="-", BN7="NR"), 0, 0.3) + IF(OR(BO7="-", BO7="NR"), 0, 0.7))) - (IF(BN7="NR", 0.3, 0) + IF(BO7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="BQ7" s="21" t="s">
@@ -4224,7 +4300,7 @@
         <v>72</v>
       </c>
       <c r="BS7" s="24" t="str">
-        <f t="shared" ref="BS7:BS27" si="18">IF(AND(BQ7="-", BR7="-"), "-", AVERAGE(BQ7, BR7))</f>
+        <f t="shared" ref="BS7:BS27" si="18">IF(AND(OR(BQ7="-", BQ7="NR"), OR(BR7="-", BR7="NR")), IF(OR(BQ7="NR", BR7="NR"), "NR", "-"), ((IFERROR(BQ7*0.3, 0) + IFERROR(BR7*0.7, 0)) / (IF(OR(BQ7="-", BQ7="NR"), 0, 0.3) + IF(OR(BR7="-", BR7="NR"), 0, 0.7))) - (IF(BQ7="NR", 0.3, 0) + IF(BR7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="BT7" s="21" t="s">
@@ -4234,7 +4310,7 @@
         <v>72</v>
       </c>
       <c r="BV7" s="24" t="str">
-        <f t="shared" ref="BV7:BV27" si="19">IF(AND(BT7="-", BU7="-"), "-", AVERAGE(BT7, BU7))</f>
+        <f t="shared" ref="BV7:BV27" si="19">IF(AND(OR(BT7="-", BT7="NR"), OR(BU7="-", BU7="NR")), IF(OR(BT7="NR", BU7="NR"), "NR", "-"), ((IFERROR(BT7*0.3, 0) + IFERROR(BU7*0.7, 0)) / (IF(OR(BT7="-", BT7="NR"), 0, 0.3) + IF(OR(BU7="-", BU7="NR"), 0, 0.7))) - (IF(BT7="NR", 0.3, 0) + IF(BU7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="BW7" s="21" t="s">
@@ -4244,7 +4320,7 @@
         <v>72</v>
       </c>
       <c r="BY7" s="24" t="str">
-        <f t="shared" ref="BY7:BY27" si="20">IF(AND(BW7="-", BX7="-"), "-", AVERAGE(BW7, BX7))</f>
+        <f t="shared" ref="BY7:BY27" si="20">IF(AND(OR(BW7="-", BW7="NR"), OR(BX7="-", BX7="NR")), IF(OR(BW7="NR", BX7="NR"), "NR", "-"), ((IFERROR(BW7*0.3, 0) + IFERROR(BX7*0.7, 0)) / (IF(OR(BW7="-", BW7="NR"), 0, 0.3) + IF(OR(BX7="-", BX7="NR"), 0, 0.7))) - (IF(BW7="NR", 0.3, 0) + IF(BX7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="BZ7" s="21" t="s">
@@ -4254,7 +4330,7 @@
         <v>72</v>
       </c>
       <c r="CB7" s="24" t="str">
-        <f t="shared" ref="CB7:CB27" si="21">IF(AND(BZ7="-", CA7="-"), "-", AVERAGE(BZ7, CA7))</f>
+        <f t="shared" ref="CB7:CB27" si="21">IF(AND(OR(BZ7="-", BZ7="NR"), OR(CA7="-", CA7="NR")), IF(OR(BZ7="NR", CA7="NR"), "NR", "-"), ((IFERROR(BZ7*0.3, 0) + IFERROR(CA7*0.7, 0)) / (IF(OR(BZ7="-", BZ7="NR"), 0, 0.3) + IF(OR(CA7="-", CA7="NR"), 0, 0.7))) - (IF(BZ7="NR", 0.3, 0) + IF(CA7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
       <c r="CC7" s="21" t="s">
@@ -4264,7 +4340,7 @@
         <v>72</v>
       </c>
       <c r="CE7" s="24" t="str">
-        <f t="shared" ref="CE7:CE27" si="22">IF(AND(CC7="-", CD7="-"), "-", AVERAGE(CC7, CD7))</f>
+        <f t="shared" ref="CE7:CE27" si="22">IF(AND(OR(CC7="-", CC7="NR"), OR(CD7="-", CD7="NR")), IF(OR(CC7="NR", CD7="NR"), "NR", "-"), ((IFERROR(CC7*0.3, 0) + IFERROR(CD7*0.7, 0)) / (IF(OR(CC7="-", CC7="NR"), 0, 0.3) + IF(OR(CD7="-", CD7="NR"), 0, 0.7))) - (IF(CC7="NR", 0.3, 0) + IF(CD7="NR", 0.7, 0)))</f>
         <v>-</v>
       </c>
     </row>
@@ -4272,7 +4348,7 @@
       <c r="A8" s="12">
         <v>3</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="55">
         <v>1</v>
       </c>
       <c r="C8" s="12" t="s">
@@ -4283,7 +4359,7 @@
       </c>
       <c r="E8" s="30">
         <f t="shared" si="0"/>
-        <v>8.9359999999999999</v>
+        <v>8.4611111111111104</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>72</v>
@@ -4338,30 +4414,30 @@
         <v>-</v>
       </c>
       <c r="V8" s="28">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="W8" s="21">
+        <v>9.75</v>
+      </c>
+      <c r="X8" s="21">
         <v>9.1999999999999993</v>
-      </c>
-      <c r="X8" s="21">
-        <v>8.9</v>
       </c>
       <c r="Y8" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z8" s="24">
         <f t="shared" si="5"/>
-        <v>8.9359999999999999</v>
-      </c>
-      <c r="AA8" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB8" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC8" s="24" t="str">
+        <v>9.4722222222222197</v>
+      </c>
+      <c r="AA8" s="21">
+        <v>8</v>
+      </c>
+      <c r="AB8" s="21">
+        <v>7</v>
+      </c>
+      <c r="AC8" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>7.4500000000000011</v>
       </c>
       <c r="AD8" s="21" t="s">
         <v>72</v>
@@ -4546,7 +4622,7 @@
       <c r="A9" s="12">
         <v>4</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="55">
         <v>81</v>
       </c>
       <c r="C9" s="12" t="s">
@@ -4557,7 +4633,7 @@
       </c>
       <c r="E9" s="30">
         <f t="shared" si="0"/>
-        <v>8.5300000000000011</v>
+        <v>8.2319444444444443</v>
       </c>
       <c r="F9" s="21" t="s">
         <v>72</v>
@@ -4612,30 +4688,30 @@
         <v>-</v>
       </c>
       <c r="V9" s="28">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="W9" s="21">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="X9" s="21">
-        <v>8.8000000000000007</v>
+        <v>9.1</v>
       </c>
       <c r="Y9" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z9" s="24">
         <f t="shared" si="5"/>
-        <v>8.5300000000000011</v>
-      </c>
-      <c r="AA9" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB9" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC9" s="24" t="str">
+        <v>8.7388888888888889</v>
+      </c>
+      <c r="AA9" s="21">
+        <v>8</v>
+      </c>
+      <c r="AB9" s="21">
+        <v>7.5</v>
+      </c>
+      <c r="AC9" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>7.7249999999999996</v>
       </c>
       <c r="AD9" s="21" t="s">
         <v>72</v>
@@ -4820,7 +4896,7 @@
       <c r="A10" s="12">
         <v>5</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="56">
         <v>16</v>
       </c>
       <c r="C10" s="12" t="s">
@@ -4831,7 +4907,7 @@
       </c>
       <c r="E10" s="30">
         <f t="shared" si="0"/>
-        <v>7.3780000000000001</v>
+        <v>7.110555555555556</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>72</v>
@@ -4889,27 +4965,27 @@
         <v>6.75</v>
       </c>
       <c r="W10" s="21">
-        <v>6.6</v>
+        <v>6.75</v>
       </c>
       <c r="X10" s="21">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="Y10" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z10" s="24">
         <f t="shared" si="5"/>
-        <v>7.3780000000000001</v>
-      </c>
-      <c r="AA10" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB10" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC10" s="24" t="str">
+        <v>6.8611111111111116</v>
+      </c>
+      <c r="AA10" s="21">
+        <v>7.8</v>
+      </c>
+      <c r="AB10" s="21">
+        <v>7</v>
+      </c>
+      <c r="AC10" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>7.36</v>
       </c>
       <c r="AD10" s="21" t="s">
         <v>72</v>
@@ -5094,7 +5170,7 @@
       <c r="A11" s="12">
         <v>6</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="56">
         <v>44</v>
       </c>
       <c r="C11" s="12" t="s">
@@ -5105,7 +5181,7 @@
       </c>
       <c r="E11" s="30">
         <f t="shared" si="0"/>
-        <v>7.9399999999999995</v>
+        <v>8.2431944444444447</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>72</v>
@@ -5163,7 +5239,7 @@
         <v>8.25</v>
       </c>
       <c r="W11" s="21">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="X11" s="21">
         <v>8</v>
@@ -5173,17 +5249,17 @@
       </c>
       <c r="Z11" s="24">
         <f t="shared" si="5"/>
-        <v>7.9399999999999995</v>
-      </c>
-      <c r="AA11" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB11" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC11" s="24" t="str">
+        <v>7.8888888888888893</v>
+      </c>
+      <c r="AA11" s="21">
+        <v>8.9</v>
+      </c>
+      <c r="AB11" s="21">
+        <v>8.35</v>
+      </c>
+      <c r="AC11" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>8.5975000000000001</v>
       </c>
       <c r="AD11" s="21" t="s">
         <v>72</v>
@@ -5368,7 +5444,7 @@
       <c r="A12" s="12">
         <v>7</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="57">
         <v>3</v>
       </c>
       <c r="C12" s="12" t="s">
@@ -5379,7 +5455,7 @@
       </c>
       <c r="E12" s="30">
         <f t="shared" si="0"/>
-        <v>7.9399999999999995</v>
+        <v>8.5694444444444446</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>72</v>
@@ -5447,17 +5523,17 @@
       </c>
       <c r="Z12" s="24">
         <f t="shared" si="5"/>
-        <v>7.9399999999999995</v>
-      </c>
-      <c r="AA12" s="21" t="s">
-        <v>72</v>
+        <v>7.8888888888888884</v>
+      </c>
+      <c r="AA12" s="21">
+        <v>9.8000000000000007</v>
       </c>
       <c r="AB12" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC12" s="24" t="str">
+        <v>75</v>
+      </c>
+      <c r="AC12" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>9.25</v>
       </c>
       <c r="AD12" s="21" t="s">
         <v>72</v>
@@ -5642,7 +5718,7 @@
       <c r="A13" s="12">
         <v>8</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13" s="57">
         <v>6</v>
       </c>
       <c r="C13" s="12" t="s">
@@ -5653,7 +5729,7 @@
       </c>
       <c r="E13" s="30">
         <f t="shared" si="0"/>
-        <v>7.79</v>
+        <v>7.9041666666666668</v>
       </c>
       <c r="F13" s="21" t="s">
         <v>72</v>
@@ -5710,28 +5786,28 @@
       <c r="V13" s="28">
         <v>7.25</v>
       </c>
-      <c r="W13" s="21">
-        <v>7</v>
+      <c r="W13" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="X13" s="21">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="Y13" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z13" s="24">
         <f t="shared" si="5"/>
-        <v>7.79</v>
-      </c>
-      <c r="AA13" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB13" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC13" s="24" t="str">
+        <v>7.5333333333333323</v>
+      </c>
+      <c r="AA13" s="21">
+        <v>8</v>
+      </c>
+      <c r="AB13" s="21">
+        <v>8.5</v>
+      </c>
+      <c r="AC13" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>8.2750000000000004</v>
       </c>
       <c r="AD13" s="21" t="s">
         <v>72</v>
@@ -5916,7 +5992,7 @@
       <c r="A14" s="12">
         <v>9</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="58">
         <v>10</v>
       </c>
       <c r="C14" s="12" t="s">
@@ -5927,7 +6003,7 @@
       </c>
       <c r="E14" s="30">
         <f t="shared" si="0"/>
-        <v>6.08</v>
+        <v>6.3365277777777784</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>72</v>
@@ -5982,10 +6058,10 @@
         <v>-</v>
       </c>
       <c r="V14" s="28">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="W14" s="21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X14" s="21">
         <v>6.5</v>
@@ -5995,17 +6071,17 @@
       </c>
       <c r="Z14" s="24">
         <f t="shared" si="5"/>
-        <v>6.08</v>
-      </c>
-      <c r="AA14" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB14" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC14" s="24" t="str">
+        <v>4.9555555555555557</v>
+      </c>
+      <c r="AA14" s="21">
+        <v>8.9</v>
+      </c>
+      <c r="AB14" s="21">
+        <v>6.75</v>
+      </c>
+      <c r="AC14" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>7.7175000000000002</v>
       </c>
       <c r="AD14" s="21" t="s">
         <v>72</v>
@@ -6190,7 +6266,7 @@
       <c r="A15" s="12">
         <v>10</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="58">
         <v>43</v>
       </c>
       <c r="C15" s="12" t="s">
@@ -6201,7 +6277,7 @@
       </c>
       <c r="E15" s="30">
         <f t="shared" si="0"/>
-        <v>8.1980000000000004</v>
+        <v>7.5841666666666665</v>
       </c>
       <c r="F15" s="21" t="s">
         <v>72</v>
@@ -6256,30 +6332,30 @@
         <v>-</v>
       </c>
       <c r="V15" s="28">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="W15" s="21">
-        <v>9.15</v>
+        <v>9</v>
       </c>
       <c r="X15" s="21">
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="Y15" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z15" s="24">
         <f t="shared" si="5"/>
-        <v>8.1980000000000004</v>
-      </c>
-      <c r="AA15" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB15" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC15" s="24" t="str">
+        <v>8.8333333333333321</v>
+      </c>
+      <c r="AA15" s="21">
+        <v>6.5</v>
+      </c>
+      <c r="AB15" s="21">
+        <v>6.2</v>
+      </c>
+      <c r="AC15" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>6.3350000000000009</v>
       </c>
       <c r="AD15" s="21" t="s">
         <v>72</v>
@@ -6464,7 +6540,7 @@
       <c r="A16" s="12">
         <v>11</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="59">
         <v>30</v>
       </c>
       <c r="C16" s="12" t="s">
@@ -6475,7 +6551,7 @@
       </c>
       <c r="E16" s="30">
         <f t="shared" si="0"/>
-        <v>7.36</v>
+        <v>8.4160714285714295</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>72</v>
@@ -6530,30 +6606,30 @@
         <v>-</v>
       </c>
       <c r="V16" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="W16" s="21">
-        <v>8.5</v>
+        <v>75</v>
+      </c>
+      <c r="W16" s="53">
+        <v>8.75</v>
       </c>
       <c r="X16" s="21">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="Y16" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z16" s="24">
         <f t="shared" si="5"/>
-        <v>7.36</v>
-      </c>
-      <c r="AA16" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB16" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC16" s="24" t="str">
+        <v>8.1071428571428577</v>
+      </c>
+      <c r="AA16" s="21">
+        <v>9</v>
+      </c>
+      <c r="AB16" s="21">
+        <v>8.5</v>
+      </c>
+      <c r="AC16" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>8.7250000000000014</v>
       </c>
       <c r="AD16" s="21" t="s">
         <v>72</v>
@@ -6738,7 +6814,7 @@
       <c r="A17" s="12">
         <v>12</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="59">
         <v>41</v>
       </c>
       <c r="C17" s="12" t="s">
@@ -6749,7 +6825,7 @@
       </c>
       <c r="E17" s="30">
         <f t="shared" si="0"/>
-        <v>8.1059999999999999</v>
+        <v>7.648194444444445</v>
       </c>
       <c r="F17" s="21" t="s">
         <v>72</v>
@@ -6804,30 +6880,30 @@
         <v>-</v>
       </c>
       <c r="V17" s="28">
-        <v>7.75</v>
-      </c>
-      <c r="W17" s="21">
+        <v>8.75</v>
+      </c>
+      <c r="W17" s="53">
+        <v>8.75</v>
+      </c>
+      <c r="X17" s="21">
         <v>8.5</v>
       </c>
-      <c r="X17" s="21">
-        <v>8.1</v>
-      </c>
       <c r="Y17" s="21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Z17" s="24">
         <f t="shared" si="5"/>
-        <v>8.1059999999999999</v>
-      </c>
-      <c r="AA17" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB17" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC17" s="24" t="str">
+        <v>8.0888888888888886</v>
+      </c>
+      <c r="AA17" s="21">
+        <v>5.75</v>
+      </c>
+      <c r="AB17" s="21">
+        <v>8.4</v>
+      </c>
+      <c r="AC17" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>7.2075000000000014</v>
       </c>
       <c r="AD17" s="21" t="s">
         <v>72</v>
@@ -7012,7 +7088,7 @@
       <c r="A18" s="12">
         <v>13</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="60">
         <v>31</v>
       </c>
       <c r="C18" s="12" t="s">
@@ -7023,7 +7099,7 @@
       </c>
       <c r="E18" s="30">
         <f t="shared" si="0"/>
-        <v>5.24</v>
+        <v>6.8611111111111107</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>72</v>
@@ -7081,27 +7157,27 @@
         <v>7</v>
       </c>
       <c r="W18" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18" s="21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z18" s="24">
         <f t="shared" si="5"/>
-        <v>5.24</v>
-      </c>
-      <c r="AA18" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB18" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC18" s="24" t="str">
+        <v>6.2222222222222223</v>
+      </c>
+      <c r="AA18" s="21">
+        <v>7.5</v>
+      </c>
+      <c r="AB18" s="21">
+        <v>7.5</v>
+      </c>
+      <c r="AC18" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>7.5</v>
       </c>
       <c r="AD18" s="21" t="s">
         <v>72</v>
@@ -7286,7 +7362,7 @@
       <c r="A19" s="12">
         <v>14</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="60">
         <v>87</v>
       </c>
       <c r="C19" s="12" t="s">
@@ -7297,7 +7373,7 @@
       </c>
       <c r="E19" s="30">
         <f t="shared" si="0"/>
-        <v>6.51</v>
+        <v>6.0555555555555554</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>72</v>
@@ -7352,10 +7428,10 @@
         <v>-</v>
       </c>
       <c r="V19" s="28">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W19" s="21">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="X19" s="21">
         <v>6.75</v>
@@ -7365,17 +7441,17 @@
       </c>
       <c r="Z19" s="24">
         <f t="shared" si="5"/>
-        <v>6.51</v>
-      </c>
-      <c r="AA19" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB19" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC19" s="24" t="str">
+        <v>6.1111111111111107</v>
+      </c>
+      <c r="AA19" s="21">
+        <v>6</v>
+      </c>
+      <c r="AB19" s="21">
+        <v>6</v>
+      </c>
+      <c r="AC19" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>6</v>
       </c>
       <c r="AD19" s="21" t="s">
         <v>72</v>
@@ -7560,7 +7636,7 @@
       <c r="A20" s="12">
         <v>15</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="61">
         <v>55</v>
       </c>
       <c r="C20" s="12" t="s">
@@ -7571,7 +7647,7 @@
       </c>
       <c r="E20" s="30">
         <f t="shared" si="0"/>
-        <v>8.4699999999999989</v>
+        <v>8.2451388888888886</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>72</v>
@@ -7626,30 +7702,30 @@
         <v>-</v>
       </c>
       <c r="V20" s="28">
+        <v>9</v>
+      </c>
+      <c r="W20" s="21">
         <v>8.75</v>
       </c>
-      <c r="W20" s="21">
-        <v>8</v>
-      </c>
       <c r="X20" s="21">
-        <v>8.5</v>
+        <v>8.35</v>
       </c>
       <c r="Y20" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z20" s="24">
         <f t="shared" si="5"/>
-        <v>8.4699999999999989</v>
-      </c>
-      <c r="AA20" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB20" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC20" s="24" t="str">
+        <v>8.6277777777777764</v>
+      </c>
+      <c r="AA20" s="21">
+        <v>8</v>
+      </c>
+      <c r="AB20" s="21">
+        <v>7.75</v>
+      </c>
+      <c r="AC20" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>7.8625000000000007</v>
       </c>
       <c r="AD20" s="21" t="s">
         <v>72</v>
@@ -7834,7 +7910,7 @@
       <c r="A21" s="12">
         <v>16</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="61">
         <v>23</v>
       </c>
       <c r="C21" s="12" t="s">
@@ -7845,7 +7921,7 @@
       </c>
       <c r="E21" s="30">
         <f t="shared" si="0"/>
-        <v>4.4800000000000004</v>
+        <v>6.4342857142857142</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>72</v>
@@ -7900,30 +7976,30 @@
         <v>-</v>
       </c>
       <c r="V21" s="28" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="W21" s="21">
         <v>6</v>
       </c>
       <c r="X21" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y21" s="21" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Z21" s="24">
         <f t="shared" si="5"/>
-        <v>4.4800000000000004</v>
-      </c>
-      <c r="AA21" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB21" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC21" s="24" t="str">
+        <v>4.7785714285714285</v>
+      </c>
+      <c r="AA21" s="21">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AB21" s="21">
+        <v>8</v>
+      </c>
+      <c r="AC21" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>8.09</v>
       </c>
       <c r="AD21" s="21" t="s">
         <v>72</v>
@@ -8108,7 +8184,7 @@
       <c r="A22" s="12">
         <v>17</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="62">
         <v>27</v>
       </c>
       <c r="C22" s="12" t="s">
@@ -8119,7 +8195,7 @@
       </c>
       <c r="E22" s="30">
         <f t="shared" si="0"/>
-        <v>7.61</v>
+        <v>6.6902777777777782</v>
       </c>
       <c r="F22" s="21" t="s">
         <v>72</v>
@@ -8174,10 +8250,10 @@
         <v>-</v>
       </c>
       <c r="V22" s="28">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="W22" s="21">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="X22" s="21">
         <v>8</v>
@@ -8187,17 +8263,17 @@
       </c>
       <c r="Z22" s="24">
         <f t="shared" si="5"/>
-        <v>7.61</v>
-      </c>
-      <c r="AA22" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB22" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC22" s="24" t="str">
+        <v>6.8055555555555554</v>
+      </c>
+      <c r="AA22" s="21">
+        <v>8.5</v>
+      </c>
+      <c r="AB22" s="21">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>6.5750000000000002</v>
       </c>
       <c r="AD22" s="21" t="s">
         <v>72</v>
@@ -8382,7 +8458,7 @@
       <c r="A23" s="12">
         <v>18</v>
       </c>
-      <c r="B23" s="9">
+      <c r="B23" s="62">
         <v>5</v>
       </c>
       <c r="C23" s="12" t="s">
@@ -8393,7 +8469,7 @@
       </c>
       <c r="E23" s="30">
         <f t="shared" si="0"/>
-        <v>7.5399999999999991</v>
+        <v>6.9708333333333332</v>
       </c>
       <c r="F23" s="21" t="s">
         <v>72</v>
@@ -8448,7 +8524,7 @@
         <v>-</v>
       </c>
       <c r="V23" s="28">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="W23" s="21">
         <v>6.5</v>
@@ -8461,17 +8537,17 @@
       </c>
       <c r="Z23" s="24">
         <f t="shared" si="5"/>
-        <v>7.5399999999999991</v>
-      </c>
-      <c r="AA23" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB23" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC23" s="24" t="str">
+        <v>7.166666666666667</v>
+      </c>
+      <c r="AA23" s="21">
+        <v>6.5</v>
+      </c>
+      <c r="AB23" s="21">
+        <v>7</v>
+      </c>
+      <c r="AC23" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>6.7750000000000004</v>
       </c>
       <c r="AD23" s="21" t="s">
         <v>72</v>
@@ -8656,7 +8732,7 @@
       <c r="A24" s="12">
         <v>19</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="63">
         <v>11</v>
       </c>
       <c r="C24" s="12" t="s">
@@ -8667,7 +8743,7 @@
       </c>
       <c r="E24" s="30">
         <f t="shared" si="0"/>
-        <v>7.9179999999999993</v>
+        <v>7.8322222222222226</v>
       </c>
       <c r="F24" s="21" t="s">
         <v>72</v>
@@ -8722,30 +8798,30 @@
         <v>-</v>
       </c>
       <c r="V24" s="28">
-        <v>8.3000000000000007</v>
+        <v>8.75</v>
       </c>
       <c r="W24" s="21">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="X24" s="21">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="Y24" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z24" s="24">
         <f t="shared" si="5"/>
-        <v>7.9179999999999993</v>
-      </c>
-      <c r="AA24" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB24" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC24" s="24" t="str">
+        <v>7.9444444444444446</v>
+      </c>
+      <c r="AA24" s="21">
+        <v>8.6</v>
+      </c>
+      <c r="AB24" s="21">
+        <v>7</v>
+      </c>
+      <c r="AC24" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>7.7200000000000006</v>
       </c>
       <c r="AD24" s="21" t="s">
         <v>72</v>
@@ -8930,7 +9006,7 @@
       <c r="A25" s="12">
         <v>20</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="63">
         <v>77</v>
       </c>
       <c r="C25" s="12" t="s">
@@ -8941,7 +9017,7 @@
       </c>
       <c r="E25" s="30">
         <f t="shared" si="0"/>
-        <v>2.36</v>
+        <v>5.5083333333333337</v>
       </c>
       <c r="F25" s="21" t="s">
         <v>72</v>
@@ -8999,7 +9075,7 @@
         <v>2</v>
       </c>
       <c r="W25" s="21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X25" s="21">
         <v>2</v>
@@ -9009,17 +9085,17 @@
       </c>
       <c r="Z25" s="24">
         <f t="shared" si="5"/>
-        <v>2.36</v>
-      </c>
-      <c r="AA25" s="21" t="s">
-        <v>72</v>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="AA25" s="21">
+        <v>7.9</v>
       </c>
       <c r="AB25" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC25" s="24" t="str">
+        <v>75</v>
+      </c>
+      <c r="AC25" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>7.3500000000000005</v>
       </c>
       <c r="AD25" s="21" t="s">
         <v>72</v>
@@ -9204,7 +9280,7 @@
       <c r="A26" s="12">
         <v>21</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="64">
         <v>14</v>
       </c>
       <c r="C26" s="12" t="s">
@@ -9215,7 +9291,7 @@
       </c>
       <c r="E26" s="30">
         <f t="shared" si="0"/>
-        <v>7.82</v>
+        <v>7.8008333333333333</v>
       </c>
       <c r="F26" s="21" t="s">
         <v>72</v>
@@ -9275,25 +9351,25 @@
       <c r="W26" s="21">
         <v>7</v>
       </c>
-      <c r="X26" s="21">
-        <v>8</v>
+      <c r="X26" s="52">
+        <v>8.25</v>
       </c>
       <c r="Y26" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z26" s="24">
         <f t="shared" si="5"/>
-        <v>7.82</v>
-      </c>
-      <c r="AA26" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB26" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC26" s="24" t="str">
+        <v>7.666666666666667</v>
+      </c>
+      <c r="AA26" s="21">
+        <v>7</v>
+      </c>
+      <c r="AB26" s="21">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="AC26" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>7.9350000000000005</v>
       </c>
       <c r="AD26" s="21" t="s">
         <v>72</v>
@@ -9478,7 +9554,7 @@
       <c r="A27" s="12">
         <v>22</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="64">
         <v>18</v>
       </c>
       <c r="C27" s="12" t="s">
@@ -9489,7 +9565,7 @@
       </c>
       <c r="E27" s="30">
         <f t="shared" si="0"/>
-        <v>2.2960000000000003</v>
+        <v>3.776388888888889</v>
       </c>
       <c r="F27" s="21" t="s">
         <v>72</v>
@@ -9546,28 +9622,28 @@
       <c r="V27" s="28">
         <v>4</v>
       </c>
-      <c r="W27" s="21">
-        <v>5</v>
+      <c r="W27" s="53">
+        <v>4.5</v>
       </c>
       <c r="X27" s="21">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Y27" s="21" t="s">
         <v>72</v>
       </c>
       <c r="Z27" s="24">
         <f t="shared" si="5"/>
-        <v>2.2960000000000003</v>
-      </c>
-      <c r="AA27" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AB27" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC27" s="24" t="str">
+        <v>3.2777777777777777</v>
+      </c>
+      <c r="AA27" s="21">
+        <v>4</v>
+      </c>
+      <c r="AB27" s="21">
+        <v>4.5</v>
+      </c>
+      <c r="AC27" s="24">
         <f t="shared" si="6"/>
-        <v>-</v>
+        <v>4.2750000000000004</v>
       </c>
       <c r="AD27" s="21" t="s">
         <v>72</v>
@@ -9777,6 +9853,10 @@
       <c r="O28" s="21" t="s">
         <v>72</v>
       </c>
+      <c r="P28" s="24" t="str">
+        <f t="shared" ref="P12:P28" si="24">IF(AND(N28="-", O28="-"), "-", ((IFERROR(N28*0.3, 0) + IFERROR(O28*0.7, 0)) / (IF(N28="-", 0, 0.3) + IF(O28="-", 0, 0.7))) - (1 - (IF(N28="-", 0, 0.3) + IF(O28="-", 0, 0.7))))</f>
+        <v>-</v>
+      </c>
       <c r="Q28" s="21" t="s">
         <v>72</v>
       </c>
@@ -9798,11 +9878,19 @@
       <c r="Y28" s="21" t="s">
         <v>72</v>
       </c>
+      <c r="Z28" s="24">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="AA28" s="21" t="s">
         <v>72</v>
       </c>
       <c r="AB28" s="21" t="s">
         <v>72</v>
+      </c>
+      <c r="AC28" s="24" t="str">
+        <f t="shared" ref="AC28" si="25">IF(AND(AA28="-", AB28="-"), "-", IFERROR(AA28*0.45, 0) + IFERROR(AB28*0.55, 0))</f>
+        <v>-</v>
       </c>
       <c r="AD28" s="21" t="s">
         <v>72</v>
@@ -10442,18 +10530,18 @@
       <c r="A32" s="12">
         <v>1</v>
       </c>
-      <c r="B32" s="18" cm="1">
+      <c r="B32" s="54" cm="1">
         <f t="array" ref="B32:CE53">_xlfn._xlws.SORT(B6:CE27,4,-1)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="12" t="str">
-        <v>Lando Norris</v>
+        <v>Max Verstappen</v>
       </c>
       <c r="D32" s="18" t="str">
-        <v>McLaren</v>
+        <v>Red Bull</v>
       </c>
       <c r="E32" s="30">
-        <v>8.9359999999999999</v>
+        <v>8.5694444444444446</v>
       </c>
       <c r="F32" s="21" t="str">
         <v>-</v>
@@ -10504,28 +10592,28 @@
         <v>-</v>
       </c>
       <c r="V32" s="28">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="W32" s="23">
-        <v>9.1999999999999993</v>
+        <v>8</v>
       </c>
       <c r="X32" s="23">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="Y32" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z32" s="24">
-        <v>8.9359999999999999</v>
-      </c>
-      <c r="AA32" s="28" t="str">
-        <v>-</v>
+        <v>7.8888888888888884</v>
+      </c>
+      <c r="AA32" s="28">
+        <v>9.8000000000000007</v>
       </c>
       <c r="AB32" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC32" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
+      </c>
+      <c r="AC32" s="24">
+        <v>9.25</v>
       </c>
       <c r="AD32" s="28" t="str">
         <v>-</v>
@@ -10694,17 +10782,17 @@
       <c r="A33" s="12">
         <v>2</v>
       </c>
-      <c r="B33" s="18">
-        <v>63</v>
+      <c r="B33" s="54">
+        <v>1</v>
       </c>
       <c r="C33" s="12" t="str">
-        <v>George Russell</v>
+        <v>Lando Norris</v>
       </c>
       <c r="D33" s="18" t="str">
-        <v>Mercedes</v>
+        <v>McLaren</v>
       </c>
       <c r="E33" s="30">
-        <v>8.6819999999999986</v>
+        <v>8.4611111111111104</v>
       </c>
       <c r="F33" s="21" t="str">
         <v>-</v>
@@ -10755,28 +10843,28 @@
         <v>-</v>
       </c>
       <c r="V33" s="28">
-        <v>8.5</v>
+        <v>9.6</v>
       </c>
       <c r="W33" s="23">
-        <v>8.75</v>
+        <v>9.75</v>
       </c>
       <c r="X33" s="23">
-        <v>8.6999999999999993</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="Y33" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z33" s="24">
-        <v>8.6819999999999986</v>
-      </c>
-      <c r="AA33" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB33" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC33" s="24" t="str">
-        <v>-</v>
+        <v>9.4722222222222197</v>
+      </c>
+      <c r="AA33" s="28">
+        <v>8</v>
+      </c>
+      <c r="AB33" s="23">
+        <v>7</v>
+      </c>
+      <c r="AC33" s="24">
+        <v>7.4500000000000011</v>
       </c>
       <c r="AD33" s="28" t="str">
         <v>-</v>
@@ -10945,17 +11033,17 @@
       <c r="A34" s="12">
         <v>3</v>
       </c>
-      <c r="B34" s="1">
-        <v>81</v>
+      <c r="B34" s="55">
+        <v>30</v>
       </c>
       <c r="C34" s="12" t="str">
-        <v>Oscar Piastri</v>
+        <v>Liam Lawson</v>
       </c>
       <c r="D34" s="1" t="str">
-        <v>McLaren</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E34" s="30">
-        <v>8.5300000000000011</v>
+        <v>8.4160714285714295</v>
       </c>
       <c r="F34" s="21" t="str">
         <v>-</v>
@@ -11005,29 +11093,29 @@
       <c r="U34" s="24" t="str">
         <v>-</v>
       </c>
-      <c r="V34" s="28">
-        <v>8.6</v>
+      <c r="V34" s="28" t="str">
+        <v>NR</v>
       </c>
       <c r="W34" s="23">
-        <v>6.75</v>
+        <v>8.75</v>
       </c>
       <c r="X34" s="23">
-        <v>8.8000000000000007</v>
+        <v>7.8</v>
       </c>
       <c r="Y34" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z34" s="24">
-        <v>8.5300000000000011</v>
-      </c>
-      <c r="AA34" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB34" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC34" s="24" t="str">
-        <v>-</v>
+        <v>8.1071428571428577</v>
+      </c>
+      <c r="AA34" s="28">
+        <v>9</v>
+      </c>
+      <c r="AB34" s="23">
+        <v>8.5</v>
+      </c>
+      <c r="AC34" s="24">
+        <v>8.7250000000000014</v>
       </c>
       <c r="AD34" s="28" t="str">
         <v>-</v>
@@ -11196,17 +11284,17 @@
       <c r="A35" s="12">
         <v>4</v>
       </c>
-      <c r="B35" s="1">
-        <v>55</v>
+      <c r="B35" s="55">
+        <v>12</v>
       </c>
       <c r="C35" s="12" t="str">
-        <v>Carlos Sainz</v>
+        <v>Kimi Antonelli</v>
       </c>
       <c r="D35" s="1" t="str">
-        <v>Williams</v>
+        <v>Mercedes</v>
       </c>
       <c r="E35" s="30">
-        <v>8.4699999999999989</v>
+        <v>8.37638888888889</v>
       </c>
       <c r="F35" s="21" t="str">
         <v>-</v>
@@ -11257,10 +11345,10 @@
         <v>-</v>
       </c>
       <c r="V35" s="28">
-        <v>8.75</v>
+        <v>8.25</v>
       </c>
       <c r="W35" s="23">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="X35" s="23">
         <v>8.5</v>
@@ -11269,16 +11357,16 @@
         <v>-</v>
       </c>
       <c r="Z35" s="24">
-        <v>8.4699999999999989</v>
-      </c>
-      <c r="AA35" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB35" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC35" s="24" t="str">
-        <v>-</v>
+        <v>7.5277777777777777</v>
+      </c>
+      <c r="AA35" s="28">
+        <v>9.5</v>
+      </c>
+      <c r="AB35" s="23">
+        <v>9</v>
+      </c>
+      <c r="AC35" s="24">
+        <v>9.2250000000000014</v>
       </c>
       <c r="AD35" s="28" t="str">
         <v>-</v>
@@ -11447,17 +11535,17 @@
       <c r="A36" s="12">
         <v>5</v>
       </c>
-      <c r="B36" s="3">
-        <v>43</v>
+      <c r="B36" s="56">
+        <v>55</v>
       </c>
       <c r="C36" s="12" t="str">
-        <v>Franco Colapinto</v>
+        <v>Carlos Sainz</v>
       </c>
       <c r="D36" s="3" t="str">
-        <v>Alpine</v>
+        <v>Williams</v>
       </c>
       <c r="E36" s="30">
-        <v>8.1980000000000004</v>
+        <v>8.2451388888888886</v>
       </c>
       <c r="F36" s="21" t="str">
         <v>-</v>
@@ -11508,28 +11596,28 @@
         <v>-</v>
       </c>
       <c r="V36" s="28">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W36" s="23">
-        <v>9.15</v>
+        <v>8.75</v>
       </c>
       <c r="X36" s="23">
+        <v>8.35</v>
+      </c>
+      <c r="Y36" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z36" s="24">
+        <v>8.6277777777777764</v>
+      </c>
+      <c r="AA36" s="28">
         <v>8</v>
       </c>
-      <c r="Y36" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="Z36" s="24">
-        <v>8.1980000000000004</v>
-      </c>
-      <c r="AA36" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB36" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC36" s="24" t="str">
-        <v>-</v>
+      <c r="AB36" s="23">
+        <v>7.75</v>
+      </c>
+      <c r="AC36" s="24">
+        <v>7.8625000000000007</v>
       </c>
       <c r="AD36" s="28" t="str">
         <v>-</v>
@@ -11698,17 +11786,17 @@
       <c r="A37" s="12">
         <v>6</v>
       </c>
-      <c r="B37" s="3">
-        <v>12</v>
+      <c r="B37" s="56">
+        <v>44</v>
       </c>
       <c r="C37" s="12" t="str">
-        <v>Kimi Antonelli</v>
+        <v>Lewis Hamilton</v>
       </c>
       <c r="D37" s="3" t="str">
-        <v>Mercedes</v>
+        <v>Ferrari</v>
       </c>
       <c r="E37" s="30">
-        <v>8.1859999999999999</v>
+        <v>8.2431944444444447</v>
       </c>
       <c r="F37" s="21" t="str">
         <v>-</v>
@@ -11759,28 +11847,28 @@
         <v>-</v>
       </c>
       <c r="V37" s="28">
+        <v>8.25</v>
+      </c>
+      <c r="W37" s="23">
+        <v>7.5</v>
+      </c>
+      <c r="X37" s="23">
         <v>8</v>
       </c>
-      <c r="W37" s="23">
-        <v>5.75</v>
-      </c>
-      <c r="X37" s="23">
-        <v>8.6</v>
-      </c>
       <c r="Y37" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z37" s="24">
-        <v>8.1859999999999999</v>
-      </c>
-      <c r="AA37" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB37" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC37" s="24" t="str">
-        <v>-</v>
+        <v>7.8888888888888893</v>
+      </c>
+      <c r="AA37" s="28">
+        <v>8.9</v>
+      </c>
+      <c r="AB37" s="23">
+        <v>8.35</v>
+      </c>
+      <c r="AC37" s="24">
+        <v>8.5975000000000001</v>
       </c>
       <c r="AD37" s="28" t="str">
         <v>-</v>
@@ -11949,17 +12037,17 @@
       <c r="A38" s="12">
         <v>7</v>
       </c>
-      <c r="B38" s="4">
-        <v>41</v>
+      <c r="B38" s="57">
+        <v>81</v>
       </c>
       <c r="C38" s="12" t="str">
-        <v>Arvid Lindblad</v>
+        <v>Oscar Piastri</v>
       </c>
       <c r="D38" s="4" t="str">
-        <v>Racing Bulls</v>
+        <v>McLaren</v>
       </c>
       <c r="E38" s="30">
-        <v>8.1059999999999999</v>
+        <v>8.2319444444444443</v>
       </c>
       <c r="F38" s="21" t="str">
         <v>-</v>
@@ -12010,28 +12098,28 @@
         <v>-</v>
       </c>
       <c r="V38" s="28">
+        <v>9.5</v>
+      </c>
+      <c r="W38" s="23">
         <v>7.75</v>
       </c>
-      <c r="W38" s="23">
-        <v>8.5</v>
-      </c>
       <c r="X38" s="23">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="Y38" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z38" s="24">
-        <v>8.1059999999999999</v>
-      </c>
-      <c r="AA38" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB38" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC38" s="24" t="str">
-        <v>-</v>
+        <v>8.7388888888888889</v>
+      </c>
+      <c r="AA38" s="28">
+        <v>8</v>
+      </c>
+      <c r="AB38" s="23">
+        <v>7.5</v>
+      </c>
+      <c r="AC38" s="24">
+        <v>7.7249999999999996</v>
       </c>
       <c r="AD38" s="28" t="str">
         <v>-</v>
@@ -12200,17 +12288,17 @@
       <c r="A39" s="12">
         <v>8</v>
       </c>
-      <c r="B39" s="4">
-        <v>44</v>
+      <c r="B39" s="57">
+        <v>6</v>
       </c>
       <c r="C39" s="12" t="str">
-        <v>Lewis Hamilton</v>
+        <v>Isack Hadjar</v>
       </c>
       <c r="D39" s="4" t="str">
-        <v>Ferrari</v>
+        <v>Red Bull</v>
       </c>
       <c r="E39" s="30">
-        <v>7.9399999999999995</v>
+        <v>7.9041666666666668</v>
       </c>
       <c r="F39" s="21" t="str">
         <v>-</v>
@@ -12261,28 +12349,28 @@
         <v>-</v>
       </c>
       <c r="V39" s="28">
-        <v>8.25</v>
-      </c>
-      <c r="W39" s="23">
         <v>7.25</v>
       </c>
+      <c r="W39" s="23" t="str">
+        <v>NR</v>
+      </c>
       <c r="X39" s="23">
+        <v>7.9</v>
+      </c>
+      <c r="Y39" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z39" s="24">
+        <v>7.5333333333333323</v>
+      </c>
+      <c r="AA39" s="28">
         <v>8</v>
       </c>
-      <c r="Y39" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="Z39" s="24">
-        <v>7.9399999999999995</v>
-      </c>
-      <c r="AA39" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB39" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC39" s="24" t="str">
-        <v>-</v>
+      <c r="AB39" s="23">
+        <v>8.5</v>
+      </c>
+      <c r="AC39" s="24">
+        <v>8.2750000000000004</v>
       </c>
       <c r="AD39" s="28" t="str">
         <v>-</v>
@@ -12451,17 +12539,17 @@
       <c r="A40" s="12">
         <v>9</v>
       </c>
-      <c r="B40" s="5">
-        <v>3</v>
+      <c r="B40" s="58">
+        <v>11</v>
       </c>
       <c r="C40" s="12" t="str">
-        <v>Max Verstappen</v>
+        <v>Sergio Perez</v>
       </c>
       <c r="D40" s="5" t="str">
-        <v>Red Bull</v>
+        <v>Cadillac</v>
       </c>
       <c r="E40" s="30">
-        <v>7.9399999999999995</v>
+        <v>7.8322222222222226</v>
       </c>
       <c r="F40" s="21" t="str">
         <v>-</v>
@@ -12512,28 +12600,28 @@
         <v>-</v>
       </c>
       <c r="V40" s="28">
-        <v>7.5</v>
+        <v>8.75</v>
       </c>
       <c r="W40" s="23">
         <v>8</v>
       </c>
       <c r="X40" s="23">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Y40" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z40" s="24">
-        <v>7.9399999999999995</v>
-      </c>
-      <c r="AA40" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB40" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC40" s="24" t="str">
-        <v>-</v>
+        <v>7.9444444444444446</v>
+      </c>
+      <c r="AA40" s="28">
+        <v>8.6</v>
+      </c>
+      <c r="AB40" s="23">
+        <v>7</v>
+      </c>
+      <c r="AC40" s="24">
+        <v>7.7200000000000006</v>
       </c>
       <c r="AD40" s="28" t="str">
         <v>-</v>
@@ -12702,17 +12790,17 @@
       <c r="A41" s="12">
         <v>10</v>
       </c>
-      <c r="B41" s="5">
-        <v>11</v>
+      <c r="B41" s="58">
+        <v>14</v>
       </c>
       <c r="C41" s="12" t="str">
-        <v>Sergio Perez</v>
+        <v>Fernando Alonso</v>
       </c>
       <c r="D41" s="5" t="str">
-        <v>Cadillac</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E41" s="30">
-        <v>7.9179999999999993</v>
+        <v>7.8008333333333333</v>
       </c>
       <c r="F41" s="21" t="str">
         <v>-</v>
@@ -12763,28 +12851,28 @@
         <v>-</v>
       </c>
       <c r="V41" s="28">
-        <v>8.3000000000000007</v>
+        <v>7.5</v>
       </c>
       <c r="W41" s="23">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="X41" s="23">
-        <v>7.75</v>
+        <v>8.25</v>
       </c>
       <c r="Y41" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z41" s="24">
-        <v>7.9179999999999993</v>
-      </c>
-      <c r="AA41" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB41" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC41" s="24" t="str">
-        <v>-</v>
+        <v>7.666666666666667</v>
+      </c>
+      <c r="AA41" s="28">
+        <v>7</v>
+      </c>
+      <c r="AB41" s="23">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="AC41" s="24">
+        <v>7.9350000000000005</v>
       </c>
       <c r="AD41" s="28" t="str">
         <v>-</v>
@@ -12953,17 +13041,17 @@
       <c r="A42" s="12">
         <v>11</v>
       </c>
-      <c r="B42" s="6">
-        <v>14</v>
+      <c r="B42" s="59">
+        <v>41</v>
       </c>
       <c r="C42" s="12" t="str">
-        <v>Fernando Alonso</v>
+        <v>Arvid Lindblad</v>
       </c>
       <c r="D42" s="6" t="str">
-        <v>Aston Martin</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E42" s="30">
-        <v>7.82</v>
+        <v>7.648194444444445</v>
       </c>
       <c r="F42" s="21" t="str">
         <v>-</v>
@@ -13014,28 +13102,28 @@
         <v>-</v>
       </c>
       <c r="V42" s="28">
-        <v>7.5</v>
+        <v>8.75</v>
       </c>
       <c r="W42" s="23">
-        <v>7</v>
+        <v>8.75</v>
       </c>
       <c r="X42" s="23">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="Y42" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="Z42" s="24">
-        <v>7.82</v>
-      </c>
-      <c r="AA42" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB42" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC42" s="24" t="str">
-        <v>-</v>
+        <v>8.0888888888888886</v>
+      </c>
+      <c r="AA42" s="28">
+        <v>5.75</v>
+      </c>
+      <c r="AB42" s="23">
+        <v>8.4</v>
+      </c>
+      <c r="AC42" s="24">
+        <v>7.2075000000000014</v>
       </c>
       <c r="AD42" s="28" t="str">
         <v>-</v>
@@ -13204,17 +13292,17 @@
       <c r="A43" s="12">
         <v>12</v>
       </c>
-      <c r="B43" s="6">
-        <v>6</v>
+      <c r="B43" s="59">
+        <v>43</v>
       </c>
       <c r="C43" s="12" t="str">
-        <v>Isack Hadjar</v>
+        <v>Franco Colapinto</v>
       </c>
       <c r="D43" s="6" t="str">
-        <v>Red Bull</v>
+        <v>Alpine</v>
       </c>
       <c r="E43" s="30">
-        <v>7.79</v>
+        <v>7.5841666666666665</v>
       </c>
       <c r="F43" s="21" t="str">
         <v>-</v>
@@ -13265,28 +13353,28 @@
         <v>-</v>
       </c>
       <c r="V43" s="28">
-        <v>7.25</v>
+        <v>8.75</v>
       </c>
       <c r="W43" s="23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X43" s="23">
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="Y43" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z43" s="24">
-        <v>7.79</v>
-      </c>
-      <c r="AA43" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB43" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC43" s="24" t="str">
-        <v>-</v>
+        <v>8.8333333333333321</v>
+      </c>
+      <c r="AA43" s="28">
+        <v>6.5</v>
+      </c>
+      <c r="AB43" s="23">
+        <v>6.2</v>
+      </c>
+      <c r="AC43" s="24">
+        <v>6.3350000000000009</v>
       </c>
       <c r="AD43" s="28" t="str">
         <v>-</v>
@@ -13455,17 +13543,17 @@
       <c r="A44" s="12">
         <v>13</v>
       </c>
-      <c r="B44" s="7">
-        <v>27</v>
+      <c r="B44" s="60">
+        <v>16</v>
       </c>
       <c r="C44" s="12" t="str">
-        <v>Nico Hulkenberg</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="D44" s="7" t="str">
-        <v>Audi</v>
+        <v>Ferrari</v>
       </c>
       <c r="E44" s="30">
-        <v>7.61</v>
+        <v>7.110555555555556</v>
       </c>
       <c r="F44" s="21" t="str">
         <v>-</v>
@@ -13516,28 +13604,28 @@
         <v>-</v>
       </c>
       <c r="V44" s="28">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
       <c r="W44" s="23">
-        <v>5</v>
+        <v>6.75</v>
       </c>
       <c r="X44" s="23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y44" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z44" s="24">
-        <v>7.61</v>
-      </c>
-      <c r="AA44" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB44" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC44" s="24" t="str">
-        <v>-</v>
+        <v>6.8611111111111116</v>
+      </c>
+      <c r="AA44" s="28">
+        <v>7.8</v>
+      </c>
+      <c r="AB44" s="23">
+        <v>7</v>
+      </c>
+      <c r="AC44" s="24">
+        <v>7.36</v>
       </c>
       <c r="AD44" s="28" t="str">
         <v>-</v>
@@ -13706,89 +13794,89 @@
       <c r="A45" s="12">
         <v>14</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="60">
+        <v>63</v>
+      </c>
+      <c r="C45" s="12" t="str">
+        <v>George Russell</v>
+      </c>
+      <c r="D45" s="7" t="str">
+        <v>Mercedes</v>
+      </c>
+      <c r="E45" s="30">
+        <v>7.0583333333333336</v>
+      </c>
+      <c r="F45" s="21" t="str">
+        <v>-</v>
+      </c>
+      <c r="G45" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="H45" s="24" t="str">
+        <v>-</v>
+      </c>
+      <c r="I45" s="28" t="str">
+        <v>-</v>
+      </c>
+      <c r="J45" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="K45" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="L45" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="M45" s="24" t="str">
+        <v>-</v>
+      </c>
+      <c r="N45" s="28" t="str">
+        <v>-</v>
+      </c>
+      <c r="O45" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="P45" s="24" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q45" s="28" t="str">
+        <v>-</v>
+      </c>
+      <c r="R45" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="S45" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="T45" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="U45" s="24" t="str">
+        <v>-</v>
+      </c>
+      <c r="V45" s="28">
+        <v>8.75</v>
+      </c>
+      <c r="W45" s="23">
+        <v>8.5</v>
+      </c>
+      <c r="X45" s="23">
+        <v>8.75</v>
+      </c>
+      <c r="Y45" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z45" s="24">
+        <v>8.6666666666666661</v>
+      </c>
+      <c r="AA45" s="28">
+        <v>6</v>
+      </c>
+      <c r="AB45" s="23">
         <v>5</v>
       </c>
-      <c r="C45" s="12" t="str">
-        <v>Gabriel Bortoleto</v>
-      </c>
-      <c r="D45" s="7" t="str">
-        <v>Audi</v>
-      </c>
-      <c r="E45" s="30">
-        <v>7.5399999999999991</v>
-      </c>
-      <c r="F45" s="21" t="str">
-        <v>-</v>
-      </c>
-      <c r="G45" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="H45" s="24" t="str">
-        <v>-</v>
-      </c>
-      <c r="I45" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="J45" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="K45" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="L45" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="M45" s="24" t="str">
-        <v>-</v>
-      </c>
-      <c r="N45" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="O45" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="P45" s="24" t="str">
-        <v>-</v>
-      </c>
-      <c r="Q45" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="R45" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="S45" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="T45" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="U45" s="24" t="str">
-        <v>-</v>
-      </c>
-      <c r="V45" s="28">
-        <v>7.25</v>
-      </c>
-      <c r="W45" s="23">
-        <v>6.5</v>
-      </c>
-      <c r="X45" s="23">
-        <v>7.75</v>
-      </c>
-      <c r="Y45" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="Z45" s="24">
-        <v>7.5399999999999991</v>
-      </c>
-      <c r="AA45" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB45" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC45" s="24" t="str">
-        <v>-</v>
+      <c r="AC45" s="24">
+        <v>5.45</v>
       </c>
       <c r="AD45" s="28" t="str">
         <v>-</v>
@@ -13957,17 +14045,17 @@
       <c r="A46" s="12">
         <v>15</v>
       </c>
-      <c r="B46" s="8">
-        <v>16</v>
+      <c r="B46" s="61">
+        <v>5</v>
       </c>
       <c r="C46" s="12" t="str">
-        <v>Charles Leclerc</v>
+        <v>Gabriel Bortoleto</v>
       </c>
       <c r="D46" s="8" t="str">
-        <v>Ferrari</v>
+        <v>Audi</v>
       </c>
       <c r="E46" s="30">
-        <v>7.3780000000000001</v>
+        <v>6.9708333333333332</v>
       </c>
       <c r="F46" s="21" t="str">
         <v>-</v>
@@ -14018,28 +14106,28 @@
         <v>-</v>
       </c>
       <c r="V46" s="28">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W46" s="23">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="X46" s="23">
-        <v>7.6</v>
+        <v>7.75</v>
       </c>
       <c r="Y46" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z46" s="24">
-        <v>7.3780000000000001</v>
-      </c>
-      <c r="AA46" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB46" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC46" s="24" t="str">
-        <v>-</v>
+        <v>7.166666666666667</v>
+      </c>
+      <c r="AA46" s="28">
+        <v>6.5</v>
+      </c>
+      <c r="AB46" s="23">
+        <v>7</v>
+      </c>
+      <c r="AC46" s="24">
+        <v>6.7750000000000004</v>
       </c>
       <c r="AD46" s="28" t="str">
         <v>-</v>
@@ -14208,17 +14296,17 @@
       <c r="A47" s="12">
         <v>16</v>
       </c>
-      <c r="B47" s="8">
-        <v>30</v>
+      <c r="B47" s="61">
+        <v>31</v>
       </c>
       <c r="C47" s="12" t="str">
-        <v>Liam Lawson</v>
+        <v>Esteban Ocon</v>
       </c>
       <c r="D47" s="8" t="str">
-        <v>Racing Bulls</v>
+        <v>Haas</v>
       </c>
       <c r="E47" s="30">
-        <v>7.36</v>
+        <v>6.8611111111111107</v>
       </c>
       <c r="F47" s="21" t="str">
         <v>-</v>
@@ -14268,29 +14356,29 @@
       <c r="U47" s="24" t="str">
         <v>-</v>
       </c>
-      <c r="V47" s="28" t="str">
-        <v>-</v>
+      <c r="V47" s="28">
+        <v>7</v>
       </c>
       <c r="W47" s="23">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="X47" s="23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y47" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z47" s="24">
-        <v>7.36</v>
-      </c>
-      <c r="AA47" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB47" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC47" s="24" t="str">
-        <v>-</v>
+        <v>6.2222222222222223</v>
+      </c>
+      <c r="AA47" s="28">
+        <v>7.5</v>
+      </c>
+      <c r="AB47" s="23">
+        <v>7.5</v>
+      </c>
+      <c r="AC47" s="24">
+        <v>7.5</v>
       </c>
       <c r="AD47" s="28" t="str">
         <v>-</v>
@@ -14459,17 +14547,17 @@
       <c r="A48" s="12">
         <v>17</v>
       </c>
-      <c r="B48" s="9">
-        <v>87</v>
+      <c r="B48" s="62">
+        <v>27</v>
       </c>
       <c r="C48" s="12" t="str">
-        <v>Oliver Bearman</v>
+        <v>Nico Hulkenberg</v>
       </c>
       <c r="D48" s="9" t="str">
-        <v>Haas</v>
+        <v>Audi</v>
       </c>
       <c r="E48" s="30">
-        <v>6.51</v>
+        <v>6.6902777777777782</v>
       </c>
       <c r="F48" s="21" t="str">
         <v>-</v>
@@ -14520,28 +14608,28 @@
         <v>-</v>
       </c>
       <c r="V48" s="28">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="W48" s="23">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="X48" s="23">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="Y48" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z48" s="24">
-        <v>6.51</v>
-      </c>
-      <c r="AA48" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB48" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC48" s="24" t="str">
-        <v>-</v>
+        <v>6.8055555555555554</v>
+      </c>
+      <c r="AA48" s="28">
+        <v>8.5</v>
+      </c>
+      <c r="AB48" s="23">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="24">
+        <v>6.5750000000000002</v>
       </c>
       <c r="AD48" s="28" t="str">
         <v>-</v>
@@ -14710,17 +14798,17 @@
       <c r="A49" s="12">
         <v>18</v>
       </c>
-      <c r="B49" s="9">
-        <v>10</v>
+      <c r="B49" s="62">
+        <v>23</v>
       </c>
       <c r="C49" s="12" t="str">
-        <v>Pierre Gasly</v>
+        <v>Alexander Albon</v>
       </c>
       <c r="D49" s="9" t="str">
-        <v>Alpine</v>
+        <v>Williams</v>
       </c>
       <c r="E49" s="30">
-        <v>6.08</v>
+        <v>6.4342857142857142</v>
       </c>
       <c r="F49" s="21" t="str">
         <v>-</v>
@@ -14770,29 +14858,29 @@
       <c r="U49" s="24" t="str">
         <v>-</v>
       </c>
-      <c r="V49" s="28">
-        <v>3.5</v>
+      <c r="V49" s="28" t="str">
+        <v>NR</v>
       </c>
       <c r="W49" s="23">
         <v>6</v>
       </c>
       <c r="X49" s="23">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="Y49" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="Z49" s="24">
-        <v>6.08</v>
-      </c>
-      <c r="AA49" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB49" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC49" s="24" t="str">
-        <v>-</v>
+        <v>4.7785714285714285</v>
+      </c>
+      <c r="AA49" s="28">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AB49" s="23">
+        <v>8</v>
+      </c>
+      <c r="AC49" s="24">
+        <v>8.09</v>
       </c>
       <c r="AD49" s="28" t="str">
         <v>-</v>
@@ -14961,17 +15049,17 @@
       <c r="A50" s="12">
         <v>19</v>
       </c>
-      <c r="B50" s="10">
-        <v>31</v>
+      <c r="B50" s="63">
+        <v>10</v>
       </c>
       <c r="C50" s="12" t="str">
-        <v>Esteban Ocon</v>
+        <v>Pierre Gasly</v>
       </c>
       <c r="D50" s="10" t="str">
-        <v>Haas</v>
+        <v>Alpine</v>
       </c>
       <c r="E50" s="30">
-        <v>5.24</v>
+        <v>6.3365277777777784</v>
       </c>
       <c r="F50" s="21" t="str">
         <v>-</v>
@@ -15022,28 +15110,28 @@
         <v>-</v>
       </c>
       <c r="V50" s="28">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="W50" s="23">
         <v>5</v>
       </c>
       <c r="X50" s="23">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="Y50" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z50" s="24">
-        <v>5.24</v>
-      </c>
-      <c r="AA50" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB50" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC50" s="24" t="str">
-        <v>-</v>
+        <v>4.9555555555555557</v>
+      </c>
+      <c r="AA50" s="28">
+        <v>8.9</v>
+      </c>
+      <c r="AB50" s="23">
+        <v>6.75</v>
+      </c>
+      <c r="AC50" s="24">
+        <v>7.7175000000000002</v>
       </c>
       <c r="AD50" s="28" t="str">
         <v>-</v>
@@ -15212,17 +15300,17 @@
       <c r="A51" s="12">
         <v>20</v>
       </c>
-      <c r="B51" s="10">
-        <v>23</v>
+      <c r="B51" s="63">
+        <v>87</v>
       </c>
       <c r="C51" s="12" t="str">
-        <v>Alexander Albon</v>
+        <v>Oliver Bearman</v>
       </c>
       <c r="D51" s="10" t="str">
-        <v>Williams</v>
+        <v>Haas</v>
       </c>
       <c r="E51" s="30">
-        <v>4.4800000000000004</v>
+        <v>6.0555555555555554</v>
       </c>
       <c r="F51" s="21" t="str">
         <v>-</v>
@@ -15272,29 +15360,29 @@
       <c r="U51" s="24" t="str">
         <v>-</v>
       </c>
-      <c r="V51" s="28" t="str">
-        <v>-</v>
+      <c r="V51" s="28">
+        <v>6.5</v>
       </c>
       <c r="W51" s="23">
+        <v>5</v>
+      </c>
+      <c r="X51" s="23">
+        <v>6.75</v>
+      </c>
+      <c r="Y51" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z51" s="24">
+        <v>6.1111111111111107</v>
+      </c>
+      <c r="AA51" s="28">
         <v>6</v>
       </c>
-      <c r="X51" s="23">
-        <v>4</v>
-      </c>
-      <c r="Y51" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="Z51" s="24">
-        <v>4.4800000000000004</v>
-      </c>
-      <c r="AA51" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB51" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC51" s="24" t="str">
-        <v>-</v>
+      <c r="AB51" s="23">
+        <v>6</v>
+      </c>
+      <c r="AC51" s="24">
+        <v>6</v>
       </c>
       <c r="AD51" s="28" t="str">
         <v>-</v>
@@ -15463,7 +15551,7 @@
       <c r="A52" s="12">
         <v>21</v>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="64">
         <v>77</v>
       </c>
       <c r="C52" s="12" t="str">
@@ -15473,7 +15561,7 @@
         <v>Cadillac</v>
       </c>
       <c r="E52" s="30">
-        <v>2.36</v>
+        <v>5.5083333333333337</v>
       </c>
       <c r="F52" s="21" t="str">
         <v>-</v>
@@ -15527,7 +15615,7 @@
         <v>2</v>
       </c>
       <c r="W52" s="23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X52" s="23">
         <v>2</v>
@@ -15536,16 +15624,16 @@
         <v>-</v>
       </c>
       <c r="Z52" s="24">
-        <v>2.36</v>
-      </c>
-      <c r="AA52" s="28" t="str">
-        <v>-</v>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="AA52" s="28">
+        <v>7.9</v>
       </c>
       <c r="AB52" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC52" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
+      </c>
+      <c r="AC52" s="24">
+        <v>7.3500000000000005</v>
       </c>
       <c r="AD52" s="28" t="str">
         <v>-</v>
@@ -15714,7 +15802,7 @@
       <c r="A53" s="12">
         <v>22</v>
       </c>
-      <c r="B53" s="11">
+      <c r="B53" s="64">
         <v>18</v>
       </c>
       <c r="C53" s="12" t="str">
@@ -15724,7 +15812,7 @@
         <v>Aston Martin</v>
       </c>
       <c r="E53" s="30">
-        <v>2.2960000000000003</v>
+        <v>3.776388888888889</v>
       </c>
       <c r="F53" s="21" t="str">
         <v>-</v>
@@ -15778,25 +15866,25 @@
         <v>4</v>
       </c>
       <c r="W53" s="23">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="X53" s="23">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Y53" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z53" s="24">
-        <v>2.2960000000000003</v>
-      </c>
-      <c r="AA53" s="28" t="str">
-        <v>-</v>
-      </c>
-      <c r="AB53" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="AC53" s="24" t="str">
-        <v>-</v>
+        <v>3.2777777777777777</v>
+      </c>
+      <c r="AA53" s="28">
+        <v>4</v>
+      </c>
+      <c r="AB53" s="23">
+        <v>4.5</v>
+      </c>
+      <c r="AC53" s="24">
+        <v>4.2750000000000004</v>
       </c>
       <c r="AD53" s="28" t="str">
         <v>-</v>
@@ -16088,50 +16176,50 @@
     <mergeCell ref="AU30:AY30"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B27 D6:D27 B32:B53 D32:D53">
-    <cfRule type="expression" dxfId="102" priority="1">
+    <cfRule type="expression" dxfId="16" priority="3">
       <formula>$D6="Haas"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="336">
+    <cfRule type="expression" dxfId="15" priority="338">
       <formula>$D6="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="337">
+    <cfRule type="expression" dxfId="14" priority="339">
       <formula>$D6="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="99" priority="338">
+    <cfRule type="expression" dxfId="13" priority="340">
       <formula>$D6="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="339">
+    <cfRule type="expression" dxfId="12" priority="341">
       <formula>$D6="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="340">
+    <cfRule type="expression" dxfId="11" priority="342">
       <formula>$D6="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="96" priority="341">
+    <cfRule type="expression" dxfId="10" priority="343">
       <formula>$D6="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="95" priority="342">
+    <cfRule type="expression" dxfId="9" priority="344">
       <formula>$D6="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="343">
+    <cfRule type="expression" dxfId="8" priority="345">
       <formula>$D6="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="344">
+    <cfRule type="expression" dxfId="7" priority="346">
       <formula>$D6="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="345">
+    <cfRule type="expression" dxfId="6" priority="347">
       <formula>$D6="Racing Bulls"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6:E27">
-    <cfRule type="cellIs" dxfId="91" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E32:E53">
-    <cfRule type="cellIs" dxfId="90" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>-1</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="347">
+    <cfRule type="colorScale" priority="349">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percent" val="50"/>
@@ -16142,8 +16230,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:F6 F7:F28 G6:G28 Q6:T28 W6:Y28 AA6:AB28 AD6:AE28 AG6:AH28 AJ6:AM28 AO6:AP28 AR6:AS28 AU6:AX28 AZ6:BA28 BC6:BD28 BF6:BG28 BN6:BO28 BQ6:BR28 BT6:BU28 BW6:BX28 BZ6:CA28 CC6:CD28 H6:H27 P6:P27 AC6:AC27 AF6:AF27 AI6:AI27 AN6:AN27 AQ6:AQ27 AT6:AT27 BB6:BB27 BE6:BE27 BP6:BP27 BS6:BS27 BV6:BV27 BY6:BY27 CB6:CB27 CE6:CE27 I6:O28 U6:V27 Z6:Z27 AY6:AY27 BH6:BM27 E7:E27">
-    <cfRule type="colorScale" priority="348">
+  <conditionalFormatting sqref="E6:F6 F7:F28 G6:G28 AG6:AH28 AJ6:AM28 AO6:AP28 AR6:AS28 AU6:AX28 AZ6:BA28 BC6:BD28 BF6:BG28 BN6:BO28 BQ6:BR28 BT6:BU28 BW6:BX28 BZ6:CA28 CC6:CD28 E7:E27 W6:AE28 U6:V27 AN6:AN27 AY6:AY27 H6:H27 I6:T28 AF6:AF27 AI6:AI27 AQ6:AQ27 AT6:AT27 BB6:BB27 BE6:BE27 BH6:BM27 BP6:BP27 BS6:BS27 BV6:BV27 BY6:BY27 CB6:CB27 CE6:CE27">
+    <cfRule type="colorScale" priority="350">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="percent" val="50"/>
@@ -16155,6 +16243,43 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:P53 AA32:AT53 AZ32:BH53 BN32:CE53">
+    <cfRule type="colorScale" priority="281">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="num" val="10"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F6:CE6 AC6:AC28 F7:Y11 F12:O27 Q12:Y27 AA7:CE27 Z7:Z28 U6:U27 M6:M27 AN6:AN27 AY6:AY27 BM6:BM27 H6:H27 P6:P28 AF6:AF27 AI6:AI27 AQ6:AQ27 AT6:AT27 BB6:BB27 BE6:BE27 BH6:BH27 BP6:BP27 BS6:BS27 BV6:BV27 BY6:BY27 CB6:CB27 CE6:CE27">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32:CE53">
+    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
+      <formula>"-"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"NR"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q32:Z53">
+    <cfRule type="colorScale" priority="280">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="num" val="10"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AU32:AY53">
     <cfRule type="colorScale" priority="279">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -16166,38 +16291,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:CE27">
-    <cfRule type="cellIs" dxfId="89" priority="3" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F32:CE53">
-    <cfRule type="cellIs" dxfId="88" priority="6" operator="equal">
-      <formula>"-"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q32:Z53">
-    <cfRule type="colorScale" priority="278">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percent" val="50"/>
-        <cfvo type="num" val="10"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AU32:AY53">
-    <cfRule type="colorScale" priority="277">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="percent" val="50"/>
-        <cfvo type="num" val="10"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
+  <conditionalFormatting sqref="F6:CE6 F7:Y27 AA7:CE27 Z7:Z28 U6:U27 M6:M27 AN6:AN27 AY6:AY27 BM6:BM27 H6:H27 P6:P27 AF6:AF27 AI6:AI27 AQ6:AQ27 AT6:AT27 BB6:BB27 BE6:BE27 BH6:BH27 BP6:BP27 BS6:BS27 BV6:BV27 BY6:BY27 CB6:CB27 CE6:CE27">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"NR"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16279,21 +16375,21 @@
       </c>
       <c r="B2" s="18" cm="1">
         <f t="array" ref="B2:E23">_xlfn._xlws.SORT(Ratings!B6:E27,4,-1)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="12" t="str">
-        <v>Lando Norris</v>
+        <v>Max Verstappen</v>
       </c>
       <c r="D2" s="18" t="str">
-        <v>McLaren</v>
+        <v>Red Bull</v>
       </c>
       <c r="E2" s="2">
-        <v>8.9359999999999999</v>
+        <v>8.5694444444444446</v>
       </c>
       <c r="F2" s="31"/>
       <c r="G2" s="51">
         <f>K2-K3</f>
-        <v>0.49599999999999866</v>
+        <v>-1.3180555555555564</v>
       </c>
       <c r="H2" s="18">
         <v>63</v>
@@ -16306,7 +16402,7 @@
       </c>
       <c r="K2" s="2">
         <f>Ratings!E6</f>
-        <v>8.6819999999999986</v>
+        <v>7.0583333333333336</v>
       </c>
       <c r="L2" s="31"/>
       <c r="M2" s="18">
@@ -16314,7 +16410,7 @@
       </c>
       <c r="N2" s="29">
         <f>Simplified!G2</f>
-        <v>0.49599999999999866</v>
+        <v>-1.3180555555555564</v>
       </c>
       <c r="O2" s="18">
         <v>12</v>
@@ -16325,7 +16421,7 @@
       </c>
       <c r="R2" s="32">
         <f>AVERAGE(K2:K3)</f>
-        <v>8.4339999999999993</v>
+        <v>7.7173611111111118</v>
       </c>
       <c r="S2" s="31"/>
       <c r="T2" s="33" t="str" cm="1">
@@ -16333,7 +16429,7 @@
         <v>McLaren</v>
       </c>
       <c r="U2" s="33">
-        <v>8.7330000000000005</v>
+        <v>8.3465277777777764</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
@@ -16341,16 +16437,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="18">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="C3" s="12" t="str">
-        <v>George Russell</v>
+        <v>Lando Norris</v>
       </c>
       <c r="D3" s="18" t="str">
-        <v>Mercedes</v>
+        <v>McLaren</v>
       </c>
       <c r="E3" s="2">
-        <v>8.6819999999999986</v>
+        <v>8.4611111111111104</v>
       </c>
       <c r="F3" s="31"/>
       <c r="G3" s="51"/>
@@ -16365,7 +16461,7 @@
       </c>
       <c r="K3" s="2">
         <f>Ratings!E7</f>
-        <v>8.1859999999999999</v>
+        <v>8.37638888888889</v>
       </c>
       <c r="L3" s="31"/>
       <c r="M3" s="1">
@@ -16373,7 +16469,7 @@
       </c>
       <c r="N3" s="29">
         <f>Simplified!G4</f>
-        <v>0.40599999999999881</v>
+        <v>0.22916666666666607</v>
       </c>
       <c r="O3" s="1">
         <v>81</v>
@@ -16384,14 +16480,14 @@
       </c>
       <c r="R3" s="32">
         <f>AVERAGE(K4:K5)</f>
-        <v>8.7330000000000005</v>
+        <v>8.3465277777777764</v>
       </c>
       <c r="S3" s="31"/>
       <c r="T3" s="33" t="str">
-        <v>Mercedes</v>
+        <v>Red Bull</v>
       </c>
       <c r="U3" s="33">
-        <v>8.4339999999999993</v>
+        <v>8.2368055555555557</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
@@ -16399,21 +16495,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="C4" s="12" t="str">
-        <v>Oscar Piastri</v>
+        <v>Liam Lawson</v>
       </c>
       <c r="D4" s="1" t="str">
-        <v>McLaren</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E4" s="2">
-        <v>8.5300000000000011</v>
+        <v>8.4160714285714295</v>
       </c>
       <c r="F4" s="31"/>
       <c r="G4" s="51">
         <f>K4-K5</f>
-        <v>0.40599999999999881</v>
+        <v>0.22916666666666607</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -16426,7 +16522,7 @@
       </c>
       <c r="K4" s="2">
         <f>Ratings!E8</f>
-        <v>8.9359999999999999</v>
+        <v>8.4611111111111104</v>
       </c>
       <c r="L4" s="31"/>
       <c r="M4" s="3">
@@ -16434,7 +16530,7 @@
       </c>
       <c r="N4" s="29">
         <f>Simplified!G6</f>
-        <v>-0.56199999999999939</v>
+        <v>-1.1326388888888888</v>
       </c>
       <c r="O4" s="3">
         <v>44</v>
@@ -16445,14 +16541,14 @@
       </c>
       <c r="R4" s="32">
         <f>AVERAGE(K6:K7)</f>
-        <v>7.6589999999999998</v>
+        <v>7.6768750000000008</v>
       </c>
       <c r="S4" s="31"/>
       <c r="T4" s="33" t="str">
-        <v>Red Bull</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="U4" s="33">
-        <v>7.8650000000000002</v>
+        <v>8.0321329365079368</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
@@ -16460,16 +16556,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="C5" s="12" t="str">
-        <v>Carlos Sainz</v>
+        <v>Kimi Antonelli</v>
       </c>
       <c r="D5" s="1" t="str">
-        <v>Williams</v>
+        <v>Mercedes</v>
       </c>
       <c r="E5" s="2">
-        <v>8.4699999999999989</v>
+        <v>8.37638888888889</v>
       </c>
       <c r="F5" s="31"/>
       <c r="G5" s="51"/>
@@ -16484,7 +16580,7 @@
       </c>
       <c r="K5" s="2">
         <f>Ratings!E9</f>
-        <v>8.5300000000000011</v>
+        <v>8.2319444444444443</v>
       </c>
       <c r="L5" s="31"/>
       <c r="M5" s="4">
@@ -16492,7 +16588,7 @@
       </c>
       <c r="N5" s="29">
         <f>Simplified!G8</f>
-        <v>0.14999999999999947</v>
+        <v>0.66527777777777786</v>
       </c>
       <c r="O5" s="4">
         <v>6</v>
@@ -16503,14 +16599,14 @@
       </c>
       <c r="R5" s="32">
         <f>AVERAGE(K8:K9)</f>
-        <v>7.8650000000000002</v>
+        <v>8.2368055555555557</v>
       </c>
       <c r="S5" s="31"/>
       <c r="T5" s="33" t="str">
-        <v>Racing Bulls</v>
+        <v>Mercedes</v>
       </c>
       <c r="U5" s="33">
-        <v>7.7330000000000005</v>
+        <v>7.7173611111111118</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
@@ -16518,21 +16614,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C6" s="12" t="str">
-        <v>Franco Colapinto</v>
+        <v>Carlos Sainz</v>
       </c>
       <c r="D6" s="3" t="str">
-        <v>Alpine</v>
+        <v>Williams</v>
       </c>
       <c r="E6" s="2">
-        <v>8.1980000000000004</v>
+        <v>8.2451388888888886</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="51">
         <f>K6-K7</f>
-        <v>-0.56199999999999939</v>
+        <v>-1.1326388888888888</v>
       </c>
       <c r="H6" s="3">
         <v>16</v>
@@ -16545,7 +16641,7 @@
       </c>
       <c r="K6" s="2">
         <f>Ratings!E10</f>
-        <v>7.3780000000000001</v>
+        <v>7.110555555555556</v>
       </c>
       <c r="L6" s="31"/>
       <c r="M6" s="5">
@@ -16553,7 +16649,7 @@
       </c>
       <c r="N6" s="29">
         <f>Simplified!G10</f>
-        <v>-2.1180000000000003</v>
+        <v>-1.2476388888888881</v>
       </c>
       <c r="O6" s="5">
         <v>43</v>
@@ -16564,14 +16660,14 @@
       </c>
       <c r="R6" s="32">
         <f>AVERAGE(K10:K11)</f>
-        <v>7.1390000000000002</v>
+        <v>6.9603472222222225</v>
       </c>
       <c r="S6" s="31"/>
       <c r="T6" s="33" t="str">
         <v>Ferrari</v>
       </c>
       <c r="U6" s="33">
-        <v>7.6589999999999998</v>
+        <v>7.6768750000000008</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
@@ -16579,16 +16675,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="C7" s="12" t="str">
-        <v>Kimi Antonelli</v>
+        <v>Lewis Hamilton</v>
       </c>
       <c r="D7" s="3" t="str">
-        <v>Mercedes</v>
+        <v>Ferrari</v>
       </c>
       <c r="E7" s="2">
-        <v>8.1859999999999999</v>
+        <v>8.2431944444444447</v>
       </c>
       <c r="F7" s="31"/>
       <c r="G7" s="51"/>
@@ -16603,7 +16699,7 @@
       </c>
       <c r="K7" s="2">
         <f>Ratings!E11</f>
-        <v>7.9399999999999995</v>
+        <v>8.2431944444444447</v>
       </c>
       <c r="L7" s="31"/>
       <c r="M7" s="6">
@@ -16611,7 +16707,7 @@
       </c>
       <c r="N7" s="29">
         <f>Simplified!G12</f>
-        <v>-0.74599999999999955</v>
+        <v>0.76787698412698457</v>
       </c>
       <c r="O7" s="6">
         <v>41</v>
@@ -16622,14 +16718,14 @@
       </c>
       <c r="R7" s="32">
         <f>AVERAGE(K12:K13)</f>
-        <v>7.7330000000000005</v>
+        <v>8.0321329365079368</v>
       </c>
       <c r="S7" s="31"/>
       <c r="T7" s="33" t="str">
-        <v>Audi</v>
+        <v>Williams</v>
       </c>
       <c r="U7" s="33">
-        <v>7.5749999999999993</v>
+        <v>7.3397123015873014</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
@@ -16637,21 +16733,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="C8" s="12" t="str">
-        <v>Arvid Lindblad</v>
+        <v>Oscar Piastri</v>
       </c>
       <c r="D8" s="4" t="str">
-        <v>Racing Bulls</v>
+        <v>McLaren</v>
       </c>
       <c r="E8" s="2">
-        <v>8.1059999999999999</v>
+        <v>8.2319444444444443</v>
       </c>
       <c r="F8" s="31"/>
       <c r="G8" s="51">
         <f>K8-K9</f>
-        <v>0.14999999999999947</v>
+        <v>0.66527777777777786</v>
       </c>
       <c r="H8" s="4">
         <v>3</v>
@@ -16664,7 +16760,7 @@
       </c>
       <c r="K8" s="2">
         <f>Ratings!E12</f>
-        <v>7.9399999999999995</v>
+        <v>8.5694444444444446</v>
       </c>
       <c r="L8" s="31"/>
       <c r="M8" s="7">
@@ -16672,7 +16768,7 @@
       </c>
       <c r="N8" s="29">
         <f>Simplified!G14</f>
-        <v>-1.2699999999999996</v>
+        <v>0.80555555555555536</v>
       </c>
       <c r="O8" s="7">
         <v>87</v>
@@ -16683,14 +16779,14 @@
       </c>
       <c r="R8" s="32">
         <f>AVERAGE(K14:K15)</f>
-        <v>5.875</v>
+        <v>6.458333333333333</v>
       </c>
       <c r="S8" s="31"/>
       <c r="T8" s="33" t="str">
         <v>Alpine</v>
       </c>
       <c r="U8" s="33">
-        <v>7.1390000000000002</v>
+        <v>6.9603472222222225</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
@@ -16698,16 +16794,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="C9" s="12" t="str">
-        <v>Lewis Hamilton</v>
+        <v>Isack Hadjar</v>
       </c>
       <c r="D9" s="4" t="str">
-        <v>Ferrari</v>
+        <v>Red Bull</v>
       </c>
       <c r="E9" s="2">
-        <v>7.9399999999999995</v>
+        <v>7.9041666666666668</v>
       </c>
       <c r="F9" s="31"/>
       <c r="G9" s="51"/>
@@ -16722,7 +16818,7 @@
       </c>
       <c r="K9" s="2">
         <f>Ratings!E13</f>
-        <v>7.79</v>
+        <v>7.9041666666666668</v>
       </c>
       <c r="L9" s="31"/>
       <c r="M9" s="8">
@@ -16730,7 +16826,7 @@
       </c>
       <c r="N9" s="29">
         <f>Simplified!G16</f>
-        <v>3.9899999999999984</v>
+        <v>1.8108531746031744</v>
       </c>
       <c r="O9" s="8">
         <v>23</v>
@@ -16741,14 +16837,14 @@
       </c>
       <c r="R9" s="32">
         <f>AVERAGE(K16:K17)</f>
-        <v>6.4749999999999996</v>
+        <v>7.3397123015873014</v>
       </c>
       <c r="S9" s="31"/>
       <c r="T9" s="33" t="str">
-        <v>Williams</v>
+        <v>Audi</v>
       </c>
       <c r="U9" s="33">
-        <v>6.4749999999999996</v>
+        <v>6.8305555555555557</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
@@ -16756,21 +16852,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C10" s="12" t="str">
-        <v>Max Verstappen</v>
+        <v>Sergio Perez</v>
       </c>
       <c r="D10" s="5" t="str">
-        <v>Red Bull</v>
+        <v>Cadillac</v>
       </c>
       <c r="E10" s="2">
-        <v>7.9399999999999995</v>
+        <v>7.8322222222222226</v>
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="51">
         <f>K10-K11</f>
-        <v>-2.1180000000000003</v>
+        <v>-1.2476388888888881</v>
       </c>
       <c r="H10" s="5">
         <v>10</v>
@@ -16783,7 +16879,7 @@
       </c>
       <c r="K10" s="2">
         <f>Ratings!E14</f>
-        <v>6.08</v>
+        <v>6.3365277777777784</v>
       </c>
       <c r="L10" s="31"/>
       <c r="M10" s="9">
@@ -16791,7 +16887,7 @@
       </c>
       <c r="N10" s="29">
         <f>Simplified!G18</f>
-        <v>7.0000000000001172E-2</v>
+        <v>-0.280555555555555</v>
       </c>
       <c r="O10" s="9">
         <v>5</v>
@@ -16802,14 +16898,14 @@
       </c>
       <c r="R10" s="32">
         <f>AVERAGE(K18:K19)</f>
-        <v>7.5749999999999993</v>
+        <v>6.8305555555555557</v>
       </c>
       <c r="S10" s="31"/>
       <c r="T10" s="33" t="str">
-        <v>Haas</v>
+        <v>Cadillac</v>
       </c>
       <c r="U10" s="33">
-        <v>5.875</v>
+        <v>6.6702777777777786</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
@@ -16817,16 +16913,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="5">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" s="12" t="str">
-        <v>Sergio Perez</v>
+        <v>Fernando Alonso</v>
       </c>
       <c r="D11" s="5" t="str">
-        <v>Cadillac</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E11" s="2">
-        <v>7.9179999999999993</v>
+        <v>7.8008333333333333</v>
       </c>
       <c r="F11" s="31"/>
       <c r="G11" s="51"/>
@@ -16841,7 +16937,7 @@
       </c>
       <c r="K11" s="2">
         <f>Ratings!E15</f>
-        <v>8.1980000000000004</v>
+        <v>7.5841666666666665</v>
       </c>
       <c r="L11" s="31"/>
       <c r="M11" s="10">
@@ -16849,7 +16945,7 @@
       </c>
       <c r="N11" s="29">
         <f>Simplified!G20</f>
-        <v>5.5579999999999998</v>
+        <v>2.3238888888888889</v>
       </c>
       <c r="O11" s="10">
         <v>77</v>
@@ -16860,14 +16956,14 @@
       </c>
       <c r="R11" s="32">
         <f>AVERAGE(K20:K21)</f>
-        <v>5.1389999999999993</v>
+        <v>6.6702777777777786</v>
       </c>
       <c r="S11" s="31"/>
       <c r="T11" s="33" t="str">
-        <v>Cadillac</v>
+        <v>Haas</v>
       </c>
       <c r="U11" s="33">
-        <v>5.1389999999999993</v>
+        <v>6.458333333333333</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
@@ -16875,21 +16971,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="6">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C12" s="12" t="str">
-        <v>Fernando Alonso</v>
+        <v>Arvid Lindblad</v>
       </c>
       <c r="D12" s="6" t="str">
-        <v>Aston Martin</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E12" s="2">
-        <v>7.82</v>
+        <v>7.648194444444445</v>
       </c>
       <c r="F12" s="31"/>
       <c r="G12" s="51">
         <f>K12-K13</f>
-        <v>-0.74599999999999955</v>
+        <v>0.76787698412698457</v>
       </c>
       <c r="H12" s="6">
         <v>30</v>
@@ -16902,7 +16998,7 @@
       </c>
       <c r="K12" s="2">
         <f>Ratings!E16</f>
-        <v>7.36</v>
+        <v>8.4160714285714295</v>
       </c>
       <c r="L12" s="31"/>
       <c r="M12" s="11">
@@ -16910,7 +17006,7 @@
       </c>
       <c r="N12" s="29">
         <f>Simplified!G22</f>
-        <v>5.524</v>
+        <v>4.0244444444444447</v>
       </c>
       <c r="O12" s="11">
         <v>18</v>
@@ -16921,14 +17017,14 @@
       </c>
       <c r="R12" s="32">
         <f>AVERAGE(K22:K23)</f>
-        <v>5.0579999999999998</v>
+        <v>5.7886111111111109</v>
       </c>
       <c r="S12" s="31"/>
       <c r="T12" s="33" t="str">
         <v>Aston Martin</v>
       </c>
       <c r="U12" s="33">
-        <v>5.0579999999999998</v>
+        <v>5.7886111111111109</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
@@ -16936,16 +17032,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="C13" s="12" t="str">
-        <v>Isack Hadjar</v>
+        <v>Franco Colapinto</v>
       </c>
       <c r="D13" s="6" t="str">
-        <v>Red Bull</v>
+        <v>Alpine</v>
       </c>
       <c r="E13" s="2">
-        <v>7.79</v>
+        <v>7.5841666666666665</v>
       </c>
       <c r="F13" s="31"/>
       <c r="G13" s="51"/>
@@ -16960,7 +17056,7 @@
       </c>
       <c r="K13" s="2">
         <f>Ratings!E17</f>
-        <v>8.1059999999999999</v>
+        <v>7.648194444444445</v>
       </c>
       <c r="L13" s="31"/>
       <c r="M13" s="31"/>
@@ -16978,21 +17074,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="7">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C14" s="12" t="str">
-        <v>Nico Hulkenberg</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="D14" s="7" t="str">
-        <v>Audi</v>
+        <v>Ferrari</v>
       </c>
       <c r="E14" s="2">
-        <v>7.61</v>
+        <v>7.110555555555556</v>
       </c>
       <c r="F14" s="31"/>
       <c r="G14" s="51">
         <f>K14-K15</f>
-        <v>-1.2699999999999996</v>
+        <v>0.80555555555555536</v>
       </c>
       <c r="H14" s="7">
         <v>31</v>
@@ -17005,7 +17101,7 @@
       </c>
       <c r="K14" s="2">
         <f>Ratings!E18</f>
-        <v>5.24</v>
+        <v>6.8611111111111107</v>
       </c>
       <c r="L14" s="31"/>
       <c r="M14" s="31"/>
@@ -17023,16 +17119,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="7">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="C15" s="12" t="str">
-        <v>Gabriel Bortoleto</v>
+        <v>George Russell</v>
       </c>
       <c r="D15" s="7" t="str">
-        <v>Audi</v>
+        <v>Mercedes</v>
       </c>
       <c r="E15" s="2">
-        <v>7.5399999999999991</v>
+        <v>7.0583333333333336</v>
       </c>
       <c r="F15" s="31"/>
       <c r="G15" s="51"/>
@@ -17047,7 +17143,7 @@
       </c>
       <c r="K15" s="2">
         <f>Ratings!E19</f>
-        <v>6.51</v>
+        <v>6.0555555555555554</v>
       </c>
       <c r="L15" s="31"/>
       <c r="M15" s="31"/>
@@ -17065,21 +17161,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="8">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C16" s="12" t="str">
-        <v>Charles Leclerc</v>
+        <v>Gabriel Bortoleto</v>
       </c>
       <c r="D16" s="8" t="str">
-        <v>Ferrari</v>
+        <v>Audi</v>
       </c>
       <c r="E16" s="2">
-        <v>7.3780000000000001</v>
+        <v>6.9708333333333332</v>
       </c>
       <c r="F16" s="31"/>
       <c r="G16" s="51">
         <f>K16-K17</f>
-        <v>3.9899999999999984</v>
+        <v>1.8108531746031744</v>
       </c>
       <c r="H16" s="8">
         <v>55</v>
@@ -17092,7 +17188,7 @@
       </c>
       <c r="K16" s="2">
         <f>Ratings!E20</f>
-        <v>8.4699999999999989</v>
+        <v>8.2451388888888886</v>
       </c>
       <c r="L16" s="31"/>
       <c r="M16" s="31"/>
@@ -17110,16 +17206,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C17" s="12" t="str">
-        <v>Liam Lawson</v>
+        <v>Esteban Ocon</v>
       </c>
       <c r="D17" s="8" t="str">
-        <v>Racing Bulls</v>
+        <v>Haas</v>
       </c>
       <c r="E17" s="2">
-        <v>7.36</v>
+        <v>6.8611111111111107</v>
       </c>
       <c r="F17" s="31"/>
       <c r="G17" s="51"/>
@@ -17134,7 +17230,7 @@
       </c>
       <c r="K17" s="2">
         <f>Ratings!E21</f>
-        <v>4.4800000000000004</v>
+        <v>6.4342857142857142</v>
       </c>
       <c r="L17" s="31"/>
       <c r="M17" s="31"/>
@@ -17152,21 +17248,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="9">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="C18" s="12" t="str">
-        <v>Oliver Bearman</v>
+        <v>Nico Hulkenberg</v>
       </c>
       <c r="D18" s="9" t="str">
-        <v>Haas</v>
+        <v>Audi</v>
       </c>
       <c r="E18" s="2">
-        <v>6.51</v>
+        <v>6.6902777777777782</v>
       </c>
       <c r="F18" s="31"/>
       <c r="G18" s="51">
         <f>K18-K19</f>
-        <v>7.0000000000001172E-2</v>
+        <v>-0.280555555555555</v>
       </c>
       <c r="H18" s="9">
         <v>27</v>
@@ -17179,7 +17275,7 @@
       </c>
       <c r="K18" s="2">
         <f>Ratings!E22</f>
-        <v>7.61</v>
+        <v>6.6902777777777782</v>
       </c>
       <c r="L18" s="31"/>
       <c r="M18" s="31"/>
@@ -17197,16 +17293,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="9">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C19" s="12" t="str">
-        <v>Pierre Gasly</v>
+        <v>Alexander Albon</v>
       </c>
       <c r="D19" s="9" t="str">
-        <v>Alpine</v>
+        <v>Williams</v>
       </c>
       <c r="E19" s="2">
-        <v>6.08</v>
+        <v>6.4342857142857142</v>
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="51"/>
@@ -17221,7 +17317,7 @@
       </c>
       <c r="K19" s="2">
         <f>Ratings!E23</f>
-        <v>7.5399999999999991</v>
+        <v>6.9708333333333332</v>
       </c>
       <c r="L19" s="31"/>
       <c r="M19" s="31"/>
@@ -17239,21 +17335,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="10">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C20" s="12" t="str">
-        <v>Esteban Ocon</v>
+        <v>Pierre Gasly</v>
       </c>
       <c r="D20" s="10" t="str">
-        <v>Haas</v>
+        <v>Alpine</v>
       </c>
       <c r="E20" s="2">
-        <v>5.24</v>
+        <v>6.3365277777777784</v>
       </c>
       <c r="F20" s="31"/>
       <c r="G20" s="51">
         <f>K20-K21</f>
-        <v>5.5579999999999998</v>
+        <v>2.3238888888888889</v>
       </c>
       <c r="H20" s="10">
         <v>11</v>
@@ -17266,7 +17362,7 @@
       </c>
       <c r="K20" s="2">
         <f>Ratings!E24</f>
-        <v>7.9179999999999993</v>
+        <v>7.8322222222222226</v>
       </c>
       <c r="L20" s="31"/>
       <c r="M20" s="31"/>
@@ -17284,16 +17380,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="10">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="C21" s="12" t="str">
-        <v>Alexander Albon</v>
+        <v>Oliver Bearman</v>
       </c>
       <c r="D21" s="10" t="str">
-        <v>Williams</v>
+        <v>Haas</v>
       </c>
       <c r="E21" s="2">
-        <v>4.4800000000000004</v>
+        <v>6.0555555555555554</v>
       </c>
       <c r="F21" s="31"/>
       <c r="G21" s="51"/>
@@ -17308,7 +17404,7 @@
       </c>
       <c r="K21" s="2">
         <f>Ratings!E25</f>
-        <v>2.36</v>
+        <v>5.5083333333333337</v>
       </c>
       <c r="L21" s="31"/>
       <c r="M21" s="31"/>
@@ -17335,12 +17431,12 @@
         <v>Cadillac</v>
       </c>
       <c r="E22" s="2">
-        <v>2.36</v>
+        <v>5.5083333333333337</v>
       </c>
       <c r="F22" s="31"/>
       <c r="G22" s="51">
         <f>K22-K23</f>
-        <v>5.524</v>
+        <v>4.0244444444444447</v>
       </c>
       <c r="H22" s="11">
         <v>14</v>
@@ -17353,7 +17449,7 @@
       </c>
       <c r="K22" s="2">
         <f>Ratings!E26</f>
-        <v>7.82</v>
+        <v>7.8008333333333333</v>
       </c>
       <c r="L22" s="31"/>
       <c r="M22" s="31"/>
@@ -17380,7 +17476,7 @@
         <v>Aston Martin</v>
       </c>
       <c r="E23" s="2">
-        <v>2.2960000000000003</v>
+        <v>3.776388888888889</v>
       </c>
       <c r="F23" s="31"/>
       <c r="G23" s="51"/>
@@ -17395,7 +17491,7 @@
       </c>
       <c r="K23" s="2">
         <f>Ratings!E27</f>
-        <v>2.2960000000000003</v>
+        <v>3.776388888888889</v>
       </c>
       <c r="L23" s="31"/>
       <c r="M23" s="31"/>
@@ -17425,37 +17521,37 @@
     <mergeCell ref="G16:G17"/>
   </mergeCells>
   <conditionalFormatting sqref="B2:B23 D2:D23">
-    <cfRule type="expression" dxfId="87" priority="137">
+    <cfRule type="expression" dxfId="104" priority="137">
       <formula>$D2="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="138">
+    <cfRule type="expression" dxfId="103" priority="138">
       <formula>$D2="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="139">
+    <cfRule type="expression" dxfId="102" priority="139">
       <formula>$D2="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="140">
+    <cfRule type="expression" dxfId="101" priority="140">
       <formula>$D2="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="141">
+    <cfRule type="expression" dxfId="100" priority="141">
       <formula>$D2="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="142">
+    <cfRule type="expression" dxfId="99" priority="142">
       <formula>$D2="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="143">
+    <cfRule type="expression" dxfId="98" priority="143">
       <formula>$D2="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="144">
+    <cfRule type="expression" dxfId="97" priority="144">
       <formula>$D2="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="145">
+    <cfRule type="expression" dxfId="96" priority="145">
       <formula>$D2="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="146">
+    <cfRule type="expression" dxfId="95" priority="146">
       <formula>$D2="Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="147">
+    <cfRule type="expression" dxfId="94" priority="147">
       <formula>$D2="Haas"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17474,47 +17570,47 @@
   <conditionalFormatting sqref="G2 G4 G6 G8 G10 G12 G14 G16 G18 G20 G22">
     <cfRule type="colorScale" priority="192">
       <colorScale>
-        <cfvo type="percentile" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="percentile" val="100"/>
+        <cfvo type="percentile" val="1"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="99"/>
+        <color rgb="FFF8696B"/>
         <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H23 J4:J23">
-    <cfRule type="expression" dxfId="76" priority="204">
+    <cfRule type="expression" dxfId="93" priority="204">
       <formula>#REF!="Haas"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="203">
+    <cfRule type="expression" dxfId="92" priority="203">
       <formula>#REF!="Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="202">
+    <cfRule type="expression" dxfId="91" priority="202">
       <formula>#REF!="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="201">
+    <cfRule type="expression" dxfId="90" priority="201">
       <formula>#REF!="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="200">
+    <cfRule type="expression" dxfId="89" priority="200">
       <formula>#REF!="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="199">
+    <cfRule type="expression" dxfId="88" priority="199">
       <formula>#REF!="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="198">
+    <cfRule type="expression" dxfId="87" priority="198">
       <formula>#REF!="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="197">
+    <cfRule type="expression" dxfId="86" priority="197">
       <formula>#REF!="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="196">
+    <cfRule type="expression" dxfId="85" priority="196">
       <formula>#REF!="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="195">
+    <cfRule type="expression" dxfId="84" priority="195">
       <formula>#REF!="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="194">
+    <cfRule type="expression" dxfId="83" priority="194">
       <formula>#REF!="Williams"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17531,72 +17627,72 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2 O2 H2:H3 J2:J3">
-    <cfRule type="expression" dxfId="65" priority="486">
+    <cfRule type="expression" dxfId="82" priority="486">
       <formula>$J2="Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="485">
+    <cfRule type="expression" dxfId="81" priority="485">
       <formula>$J2="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="484">
+    <cfRule type="expression" dxfId="80" priority="484">
       <formula>$J2="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="483">
+    <cfRule type="expression" dxfId="79" priority="483">
       <formula>$J2="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="482">
+    <cfRule type="expression" dxfId="78" priority="482">
       <formula>$J2="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="481">
+    <cfRule type="expression" dxfId="77" priority="481">
       <formula>$J2="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="59" priority="479">
+    <cfRule type="expression" dxfId="76" priority="479">
       <formula>$J2="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="478">
+    <cfRule type="expression" dxfId="75" priority="478">
       <formula>$J2="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="477">
+    <cfRule type="expression" dxfId="74" priority="477">
       <formula>$J2="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="56" priority="487">
+    <cfRule type="expression" dxfId="73" priority="487">
       <formula>$J2="Haas"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="480">
+    <cfRule type="expression" dxfId="72" priority="480">
       <formula>$J2="Aston Martin"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3:M12">
-    <cfRule type="expression" dxfId="54" priority="227">
+    <cfRule type="expression" dxfId="71" priority="227">
       <formula>$D1048555="Haas"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="217">
+    <cfRule type="expression" dxfId="70" priority="217">
       <formula>$D1048555="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="218">
+    <cfRule type="expression" dxfId="69" priority="218">
       <formula>$D1048555="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="219">
+    <cfRule type="expression" dxfId="68" priority="219">
       <formula>$D1048555="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="220">
+    <cfRule type="expression" dxfId="67" priority="220">
       <formula>$D1048555="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="221">
+    <cfRule type="expression" dxfId="66" priority="221">
       <formula>$D1048555="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="222">
+    <cfRule type="expression" dxfId="65" priority="222">
       <formula>$D1048555="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="223">
+    <cfRule type="expression" dxfId="64" priority="223">
       <formula>$D1048555="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="224">
+    <cfRule type="expression" dxfId="63" priority="224">
       <formula>$D1048555="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="225">
+    <cfRule type="expression" dxfId="62" priority="225">
       <formula>$D1048555="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="226">
+    <cfRule type="expression" dxfId="61" priority="226">
       <formula>$D1048555="Racing Bulls"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17615,107 +17711,107 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O3:O12">
-    <cfRule type="expression" dxfId="43" priority="213">
+    <cfRule type="expression" dxfId="60" priority="213">
       <formula>$D1048555="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="215">
+    <cfRule type="expression" dxfId="59" priority="215">
       <formula>$D1048555="Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="214">
+    <cfRule type="expression" dxfId="58" priority="214">
       <formula>$D1048555="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="206">
+    <cfRule type="expression" dxfId="57" priority="206">
       <formula>$D1048555="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="207">
+    <cfRule type="expression" dxfId="56" priority="207">
       <formula>$D1048555="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="208">
+    <cfRule type="expression" dxfId="55" priority="208">
       <formula>$D1048555="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="209">
+    <cfRule type="expression" dxfId="54" priority="209">
       <formula>$D1048555="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="210">
+    <cfRule type="expression" dxfId="53" priority="210">
       <formula>$D1048555="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="211">
+    <cfRule type="expression" dxfId="52" priority="211">
       <formula>$D1048555="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="212">
+    <cfRule type="expression" dxfId="51" priority="212">
       <formula>$D1048555="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="216">
+    <cfRule type="expression" dxfId="50" priority="216">
       <formula>$D1048555="Haas"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q2">
-    <cfRule type="expression" dxfId="32" priority="127">
+    <cfRule type="expression" dxfId="49" priority="127">
       <formula>$J2="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="128">
+    <cfRule type="expression" dxfId="48" priority="128">
       <formula>$J2="Aston Martin"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="129">
+    <cfRule type="expression" dxfId="47" priority="129">
       <formula>$J2="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="130">
+    <cfRule type="expression" dxfId="46" priority="130">
       <formula>$J2="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="131">
+    <cfRule type="expression" dxfId="45" priority="131">
       <formula>$J2="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="132">
+    <cfRule type="expression" dxfId="44" priority="132">
       <formula>$J2="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="133">
+    <cfRule type="expression" dxfId="43" priority="133">
       <formula>$J2="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="134">
+    <cfRule type="expression" dxfId="42" priority="134">
       <formula>$J2="Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="135">
+    <cfRule type="expression" dxfId="41" priority="135">
       <formula>$J2="Haas"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="125">
+    <cfRule type="expression" dxfId="40" priority="125">
       <formula>$J2="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="126">
+    <cfRule type="expression" dxfId="39" priority="126">
       <formula>$J2="Audi"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q3:Q12">
-    <cfRule type="expression" dxfId="21" priority="23">
+    <cfRule type="expression" dxfId="38" priority="23">
       <formula>#REF!="Alpine"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="24">
+    <cfRule type="expression" dxfId="37" priority="24">
       <formula>#REF!="Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="25">
+    <cfRule type="expression" dxfId="36" priority="25">
       <formula>#REF!="Haas"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="22">
+    <cfRule type="expression" dxfId="35" priority="22">
       <formula>#REF!="Red Bull"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="21">
+    <cfRule type="expression" dxfId="34" priority="21">
       <formula>#REF!="McLaren"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="20">
+    <cfRule type="expression" dxfId="33" priority="20">
       <formula>#REF!="Ferrari"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="19">
+    <cfRule type="expression" dxfId="32" priority="19">
       <formula>#REF!="Mercedes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="17">
+    <cfRule type="expression" dxfId="31" priority="17">
       <formula>#REF!="Cadillac"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="16">
+    <cfRule type="expression" dxfId="30" priority="16">
       <formula>#REF!="Audi"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="15">
+    <cfRule type="expression" dxfId="29" priority="15">
       <formula>#REF!="Williams"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="18">
+    <cfRule type="expression" dxfId="28" priority="18">
       <formula>#REF!="Aston Martin"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17732,37 +17828,37 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T12">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
       <formula>"Mercedes"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="11" operator="equal">
       <formula>"McLaren"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="10" operator="equal">
       <formula>"Ferrari"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="9" operator="equal">
       <formula>"Red Bull"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="8" operator="equal">
       <formula>"Alpine"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="7" operator="equal">
       <formula>"Racing Bulls"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="6" operator="equal">
       <formula>"Haas"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="5" operator="equal">
       <formula>"Williams"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
       <formula>"Audi"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
       <formula>"Cadillac"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>"Aston Martin"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/static/data/Ratings.xlsx
+++ b/static/data/Ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Programming\webdev\portfolio\static\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF19A9E-3CC0-4856-9543-5A2CABDE9017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEB19F1-B806-4256-95C3-D8BD5634CB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="2" activeTab="2" xr2:uid="{BD88BCC4-2E11-4C36-830D-A75A044EF5A6}"/>
   </bookViews>
@@ -259,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1522" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="77">
   <si>
     <t>RANK</t>
   </si>
@@ -1012,34 +1012,10 @@
     <xf numFmtId="4" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1052,6 +1028,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3103,13 +3103,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:83" s="14" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
       <c r="F1" s="17"/>
       <c r="G1" s="17"/>
       <c r="H1" s="17"/>
@@ -3190,11 +3190,11 @@
       <c r="CE1" s="17"/>
     </row>
     <row r="2" spans="1:83" s="14" customFormat="1" ht="19.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
@@ -3280,296 +3280,296 @@
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
-      <c r="F3" s="57" t="e" vm="1">
+      <c r="F3" s="60" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G3" s="58"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="54" t="e" vm="2">
+      <c r="G3" s="61"/>
+      <c r="H3" s="62"/>
+      <c r="I3" s="58" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="57" t="e" vm="3">
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="60" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="58"/>
-      <c r="P3" s="59"/>
-      <c r="Q3" s="53" t="e" vm="4">
+      <c r="O3" s="61"/>
+      <c r="P3" s="62"/>
+      <c r="Q3" s="57" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R3" s="54"/>
-      <c r="S3" s="54"/>
-      <c r="T3" s="54"/>
-      <c r="U3" s="55"/>
-      <c r="V3" s="53" t="e" vm="5">
+      <c r="R3" s="58"/>
+      <c r="S3" s="58"/>
+      <c r="T3" s="58"/>
+      <c r="U3" s="59"/>
+      <c r="V3" s="57" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W3" s="54"/>
-      <c r="X3" s="54"/>
-      <c r="Y3" s="54"/>
-      <c r="Z3" s="55"/>
-      <c r="AA3" s="57" t="e" vm="6">
+      <c r="W3" s="58"/>
+      <c r="X3" s="58"/>
+      <c r="Y3" s="58"/>
+      <c r="Z3" s="59"/>
+      <c r="AA3" s="60" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB3" s="58"/>
-      <c r="AC3" s="59"/>
-      <c r="AD3" s="57" t="e" vm="7">
+      <c r="AB3" s="61"/>
+      <c r="AC3" s="62"/>
+      <c r="AD3" s="60" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE3" s="58"/>
-      <c r="AF3" s="59"/>
-      <c r="AG3" s="57" t="e" vm="8">
+      <c r="AE3" s="61"/>
+      <c r="AF3" s="62"/>
+      <c r="AG3" s="60" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH3" s="58"/>
-      <c r="AI3" s="59"/>
-      <c r="AJ3" s="53" t="e" vm="9">
+      <c r="AH3" s="61"/>
+      <c r="AI3" s="62"/>
+      <c r="AJ3" s="57" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="55"/>
-      <c r="AO3" s="57" t="e" vm="10">
+      <c r="AK3" s="58"/>
+      <c r="AL3" s="58"/>
+      <c r="AM3" s="58"/>
+      <c r="AN3" s="59"/>
+      <c r="AO3" s="60" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP3" s="58"/>
-      <c r="AQ3" s="59"/>
-      <c r="AR3" s="57" t="e" vm="11">
+      <c r="AP3" s="61"/>
+      <c r="AQ3" s="62"/>
+      <c r="AR3" s="60" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS3" s="58"/>
-      <c r="AT3" s="59"/>
-      <c r="AU3" s="53" t="e" vm="12">
+      <c r="AS3" s="61"/>
+      <c r="AT3" s="62"/>
+      <c r="AU3" s="57" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV3" s="54"/>
-      <c r="AW3" s="54"/>
-      <c r="AX3" s="54"/>
-      <c r="AY3" s="55"/>
-      <c r="AZ3" s="57" t="e" vm="13">
+      <c r="AV3" s="58"/>
+      <c r="AW3" s="58"/>
+      <c r="AX3" s="58"/>
+      <c r="AY3" s="59"/>
+      <c r="AZ3" s="60" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA3" s="58"/>
-      <c r="BB3" s="59"/>
-      <c r="BC3" s="57" t="e" vm="7">
+      <c r="BA3" s="61"/>
+      <c r="BB3" s="62"/>
+      <c r="BC3" s="60" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD3" s="58"/>
-      <c r="BE3" s="59"/>
-      <c r="BF3" s="57" t="e" vm="14">
+      <c r="BD3" s="61"/>
+      <c r="BE3" s="62"/>
+      <c r="BF3" s="60" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG3" s="58"/>
-      <c r="BH3" s="59"/>
-      <c r="BI3" s="53" t="e" vm="15">
+      <c r="BG3" s="61"/>
+      <c r="BH3" s="62"/>
+      <c r="BI3" s="57" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ3" s="54"/>
-      <c r="BK3" s="54"/>
-      <c r="BL3" s="54"/>
-      <c r="BM3" s="55"/>
-      <c r="BN3" s="57" t="e" vm="4">
+      <c r="BJ3" s="58"/>
+      <c r="BK3" s="58"/>
+      <c r="BL3" s="58"/>
+      <c r="BM3" s="59"/>
+      <c r="BN3" s="60" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO3" s="58"/>
-      <c r="BP3" s="59"/>
-      <c r="BQ3" s="57" t="e" vm="16">
+      <c r="BO3" s="61"/>
+      <c r="BP3" s="62"/>
+      <c r="BQ3" s="60" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR3" s="58"/>
-      <c r="BS3" s="59"/>
-      <c r="BT3" s="57" t="e" vm="17">
+      <c r="BR3" s="61"/>
+      <c r="BS3" s="62"/>
+      <c r="BT3" s="60" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU3" s="58"/>
-      <c r="BV3" s="59"/>
-      <c r="BW3" s="57" t="e" vm="4">
+      <c r="BU3" s="61"/>
+      <c r="BV3" s="62"/>
+      <c r="BW3" s="60" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX3" s="58"/>
-      <c r="BY3" s="59"/>
-      <c r="BZ3" s="57" t="e" vm="18">
+      <c r="BX3" s="61"/>
+      <c r="BY3" s="62"/>
+      <c r="BZ3" s="60" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA3" s="58"/>
-      <c r="CB3" s="59"/>
-      <c r="CC3" s="57" t="e" vm="19">
+      <c r="CA3" s="61"/>
+      <c r="CB3" s="62"/>
+      <c r="CC3" s="60" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD3" s="58"/>
-      <c r="CE3" s="59"/>
+      <c r="CD3" s="61"/>
+      <c r="CE3" s="62"/>
     </row>
     <row r="4" spans="1:83" s="16" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="56" t="s">
+      <c r="C4" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="56" t="s">
+      <c r="D4" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="56" t="s">
+      <c r="E4" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="60" t="s">
+      <c r="F4" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="56"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="56" t="s">
+      <c r="G4" s="52"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="60" t="s">
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="O4" s="56"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="62" t="s">
+      <c r="O4" s="52"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="62" t="s">
+      <c r="R4" s="55"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="55"/>
+      <c r="U4" s="56"/>
+      <c r="V4" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="W4" s="63"/>
-      <c r="X4" s="63"/>
-      <c r="Y4" s="63"/>
-      <c r="Z4" s="64"/>
-      <c r="AA4" s="60" t="s">
+      <c r="W4" s="55"/>
+      <c r="X4" s="55"/>
+      <c r="Y4" s="55"/>
+      <c r="Z4" s="56"/>
+      <c r="AA4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="AB4" s="56"/>
-      <c r="AC4" s="61"/>
-      <c r="AD4" s="60" t="s">
+      <c r="AB4" s="52"/>
+      <c r="AC4" s="53"/>
+      <c r="AD4" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="AE4" s="56"/>
-      <c r="AF4" s="61"/>
-      <c r="AG4" s="60" t="s">
+      <c r="AE4" s="52"/>
+      <c r="AF4" s="53"/>
+      <c r="AG4" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="AH4" s="56"/>
-      <c r="AI4" s="61"/>
-      <c r="AJ4" s="62" t="s">
+      <c r="AH4" s="52"/>
+      <c r="AI4" s="53"/>
+      <c r="AJ4" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="AK4" s="63"/>
-      <c r="AL4" s="63"/>
-      <c r="AM4" s="63"/>
-      <c r="AN4" s="64"/>
-      <c r="AO4" s="60" t="s">
+      <c r="AK4" s="55"/>
+      <c r="AL4" s="55"/>
+      <c r="AM4" s="55"/>
+      <c r="AN4" s="56"/>
+      <c r="AO4" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="AP4" s="56"/>
-      <c r="AQ4" s="61"/>
-      <c r="AR4" s="60" t="s">
+      <c r="AP4" s="52"/>
+      <c r="AQ4" s="53"/>
+      <c r="AR4" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="AS4" s="56"/>
-      <c r="AT4" s="61"/>
-      <c r="AU4" s="62" t="s">
+      <c r="AS4" s="52"/>
+      <c r="AT4" s="53"/>
+      <c r="AU4" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="AV4" s="63"/>
-      <c r="AW4" s="63"/>
-      <c r="AX4" s="63"/>
-      <c r="AY4" s="64"/>
-      <c r="AZ4" s="60" t="s">
+      <c r="AV4" s="55"/>
+      <c r="AW4" s="55"/>
+      <c r="AX4" s="55"/>
+      <c r="AY4" s="56"/>
+      <c r="AZ4" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="BA4" s="56"/>
-      <c r="BB4" s="61"/>
-      <c r="BC4" s="60" t="s">
+      <c r="BA4" s="52"/>
+      <c r="BB4" s="53"/>
+      <c r="BC4" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="BD4" s="56"/>
-      <c r="BE4" s="61"/>
-      <c r="BF4" s="60" t="s">
+      <c r="BD4" s="52"/>
+      <c r="BE4" s="53"/>
+      <c r="BF4" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="BG4" s="56"/>
-      <c r="BH4" s="61"/>
-      <c r="BI4" s="62" t="s">
+      <c r="BG4" s="52"/>
+      <c r="BH4" s="53"/>
+      <c r="BI4" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="BJ4" s="63"/>
-      <c r="BK4" s="63"/>
-      <c r="BL4" s="63"/>
-      <c r="BM4" s="64"/>
-      <c r="BN4" s="60" t="s">
+      <c r="BJ4" s="55"/>
+      <c r="BK4" s="55"/>
+      <c r="BL4" s="55"/>
+      <c r="BM4" s="56"/>
+      <c r="BN4" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="BO4" s="56"/>
-      <c r="BP4" s="61"/>
-      <c r="BQ4" s="60" t="s">
+      <c r="BO4" s="52"/>
+      <c r="BP4" s="53"/>
+      <c r="BQ4" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="BR4" s="56"/>
-      <c r="BS4" s="61"/>
-      <c r="BT4" s="60" t="s">
+      <c r="BR4" s="52"/>
+      <c r="BS4" s="53"/>
+      <c r="BT4" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="BU4" s="56"/>
-      <c r="BV4" s="61"/>
-      <c r="BW4" s="60" t="s">
+      <c r="BU4" s="52"/>
+      <c r="BV4" s="53"/>
+      <c r="BW4" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="BX4" s="56"/>
-      <c r="BY4" s="61"/>
-      <c r="BZ4" s="60" t="s">
+      <c r="BX4" s="52"/>
+      <c r="BY4" s="53"/>
+      <c r="BZ4" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="CA4" s="56"/>
-      <c r="CB4" s="61"/>
-      <c r="CC4" s="60" t="s">
+      <c r="CA4" s="52"/>
+      <c r="CB4" s="53"/>
+      <c r="CC4" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="CD4" s="56"/>
-      <c r="CE4" s="61"/>
+      <c r="CD4" s="52"/>
+      <c r="CE4" s="53"/>
     </row>
     <row r="5" spans="1:83" s="16" customFormat="1" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="56"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
       <c r="F5" s="22" t="s">
         <v>26</v>
       </c>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="E6" s="30">
         <f>IFERROR(AVERAGE(H6,M6,P6,U6,Z6,AC6,AF6,AI6,AN6,AQ6,AT6,AY6,BB6,BE6,BH6,BM6,BP6,BS6,BV6,BY6,CB6,CE6),-1)</f>
-        <v>7.7055555555555557</v>
+        <v>7.3822222222222225</v>
       </c>
       <c r="F6" s="46" t="s">
         <v>72</v>
@@ -3884,11 +3884,11 @@
         <v>8.75</v>
       </c>
       <c r="Y6" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Z6" s="47">
         <f>IF(AND(OR(V6="-", V6="NR"), OR(W6="-", W6="NR"), OR(X6="-", X6="NR"), OR(Y6="-", Y6="NR")), IF(OR(V6="NR", W6="NR", X6="NR", Y6="NR"), "NR", "-"), ((IFERROR(V6*0.1, 0) + IFERROR(W6*0.15, 0) + IFERROR(X6*0.2, 0) + IFERROR(Y6*0.55, 0)) / (IF(OR(V6="-", V6="NR"), 0, 0.1) + IF(OR(W6="-", W6="NR"), 0, 0.15) + IF(OR(X6="-", X6="NR"), 0, 0.2) + IF(OR(Y6="-", Y6="NR"), 0, 0.55))) - (IF(V6="NR", 0.1, 0) + IF(W6="NR", 0.15, 0) + IF(X6="NR", 0.2, 0) + IF(Y6="NR", 0.55, 0)))</f>
-        <v>8.6666666666666661</v>
+        <v>8.1166666666666654</v>
       </c>
       <c r="AA6" s="46">
         <v>6</v>
@@ -3903,12 +3903,12 @@
       <c r="AD6" s="46">
         <v>9</v>
       </c>
-      <c r="AE6" s="46" t="s">
-        <v>72</v>
+      <c r="AE6" s="46">
+        <v>8.4</v>
       </c>
       <c r="AF6" s="47">
         <f>IF(AND(OR(AD6="-", AD6="NR"), OR(AE6="-", AE6="NR")), IF(OR(AD6="NR", AE6="NR"), "NR", "-"), ((IFERROR(AD6*0.3, 0) + IFERROR(AE6*0.7, 0)) / (IF(OR(AD6="-", AD6="NR"), 0, 0.3) + IF(OR(AE6="-", AE6="NR"), 0, 0.7))) - (IF(AD6="NR", 0.3, 0) + IF(AE6="NR", 0.7, 0)))</f>
-        <v>9</v>
+        <v>8.58</v>
       </c>
       <c r="AG6" s="46" t="s">
         <v>72</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E7" s="30">
         <f t="shared" ref="E7:E27" si="0">IFERROR(AVERAGE(H7,M7,P7,U7,Z7,AC7,AF7,AI7,AN7,AQ7,AT7,AY7,BB7,BE7,BH7,BM7,BP7,BS7,BV7,BY7,CB7,CE7),-1)</f>
-        <v>8.4175925925925927</v>
+        <v>8.357592592592594</v>
       </c>
       <c r="F7" s="46" t="s">
         <v>72</v>
@@ -4175,14 +4175,14 @@
         <v>9.2250000000000014</v>
       </c>
       <c r="AD7" s="46">
+        <v>7.9</v>
+      </c>
+      <c r="AE7" s="46">
         <v>8.5</v>
-      </c>
-      <c r="AE7" s="46" t="s">
-        <v>72</v>
       </c>
       <c r="AF7" s="47">
         <f t="shared" ref="AF7:AF27" si="7">IF(AND(OR(AD7="-", AD7="NR"), OR(AE7="-", AE7="NR")), IF(OR(AD7="NR", AE7="NR"), "NR", "-"), ((IFERROR(AD7*0.3, 0) + IFERROR(AE7*0.7, 0)) / (IF(OR(AD7="-", AD7="NR"), 0, 0.3) + IF(OR(AE7="-", AE7="NR"), 0, 0.7))) - (IF(AD7="NR", 0.3, 0) + IF(AE7="NR", 0.7, 0)))</f>
-        <v>8.5</v>
+        <v>8.32</v>
       </c>
       <c r="AG7" s="46" t="s">
         <v>72</v>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="E8" s="30">
         <f t="shared" si="0"/>
-        <v>8.5574074074074069</v>
+        <v>8.7032407407407408</v>
       </c>
       <c r="F8" s="46" t="s">
         <v>72</v>
@@ -4390,11 +4390,11 @@
         <v>72</v>
       </c>
       <c r="L8" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M8" s="47" t="str">
         <f t="shared" si="2"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="N8" s="46" t="s">
         <v>72</v>
@@ -4439,24 +4439,24 @@
         <v>9.4722222222222197</v>
       </c>
       <c r="AA8" s="46">
-        <v>8</v>
+        <v>7.85</v>
       </c>
       <c r="AB8" s="46">
         <v>7</v>
       </c>
       <c r="AC8" s="47">
         <f t="shared" si="6"/>
-        <v>7.4500000000000011</v>
+        <v>7.3825000000000003</v>
       </c>
       <c r="AD8" s="46">
-        <v>8.75</v>
-      </c>
-      <c r="AE8" s="46" t="s">
-        <v>72</v>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AE8" s="46">
+        <v>9.4499999999999993</v>
       </c>
       <c r="AF8" s="47">
         <f t="shared" si="7"/>
-        <v>8.75</v>
+        <v>9.254999999999999</v>
       </c>
       <c r="AG8" s="46" t="s">
         <v>72</v>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="E9" s="30">
         <f t="shared" si="0"/>
-        <v>7.9879629629629632</v>
+        <v>7.9529629629629639</v>
       </c>
       <c r="F9" s="46" t="s">
         <v>72</v>
@@ -4664,11 +4664,11 @@
         <v>72</v>
       </c>
       <c r="L9" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M9" s="47" t="str">
         <f t="shared" si="2"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="N9" s="46" t="s">
         <v>72</v>
@@ -4700,7 +4700,7 @@
         <v>9.5</v>
       </c>
       <c r="W9" s="46">
-        <v>7.75</v>
+        <v>7.9</v>
       </c>
       <c r="X9" s="46">
         <v>9.1</v>
@@ -4710,27 +4710,27 @@
       </c>
       <c r="Z9" s="47">
         <f t="shared" si="5"/>
-        <v>8.7388888888888889</v>
+        <v>8.7888888888888896</v>
       </c>
       <c r="AA9" s="46">
         <v>8</v>
       </c>
       <c r="AB9" s="46">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC9" s="47">
         <f t="shared" si="6"/>
-        <v>7.7249999999999996</v>
+        <v>7.8900000000000006</v>
       </c>
       <c r="AD9" s="46">
-        <v>7.5</v>
-      </c>
-      <c r="AE9" s="46" t="s">
-        <v>72</v>
+        <v>7.6</v>
+      </c>
+      <c r="AE9" s="46">
+        <v>7</v>
       </c>
       <c r="AF9" s="47">
         <f t="shared" si="7"/>
-        <v>7.5</v>
+        <v>7.18</v>
       </c>
       <c r="AG9" s="46" t="s">
         <v>72</v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="E10" s="30">
         <f t="shared" si="0"/>
-        <v>6.4070370370370382</v>
+        <v>7.2353703703703713</v>
       </c>
       <c r="F10" s="46" t="s">
         <v>72</v>
@@ -4999,12 +4999,12 @@
       <c r="AD10" s="46">
         <v>5</v>
       </c>
-      <c r="AE10" s="46" t="s">
-        <v>72</v>
+      <c r="AE10" s="46">
+        <v>8.5500000000000007</v>
       </c>
       <c r="AF10" s="47">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>7.4850000000000003</v>
       </c>
       <c r="AG10" s="46" t="s">
         <v>72</v>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="E11" s="30">
         <f t="shared" si="0"/>
-        <v>8.7454629629629625</v>
+        <v>8.76212962962963</v>
       </c>
       <c r="F11" s="46" t="s">
         <v>72</v>
@@ -5271,14 +5271,14 @@
         <v>8.5975000000000001</v>
       </c>
       <c r="AD11" s="46">
-        <v>9.75</v>
-      </c>
-      <c r="AE11" s="46" t="s">
-        <v>72</v>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AE11" s="46">
+        <v>9.8000000000000007</v>
       </c>
       <c r="AF11" s="47">
-        <f t="shared" si="7"/>
-        <v>9.75</v>
+        <f>IF(AND(OR(AD11="-", AD11="NR"), OR(AE11="-", AE11="NR")), IF(OR(AD11="NR", AE11="NR"), "NR", "-"), ((IFERROR(AD11*0.3, 0) + IFERROR(AE11*0.7, 0)) / (IF(OR(AD11="-", AD11="NR"), 0, 0.3) + IF(OR(AE11="-", AE11="NR"), 0, 0.7))) - (IF(AD11="NR", 0.3, 0) + IF(AE11="NR", 0.7, 0)))</f>
+        <v>9.8000000000000007</v>
       </c>
       <c r="AG11" s="46" t="s">
         <v>72</v>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="E12" s="30">
         <f t="shared" si="0"/>
-        <v>8.7962962962962958</v>
+        <v>8.5575925925925933</v>
       </c>
       <c r="F12" s="46" t="s">
         <v>72</v>
@@ -5519,7 +5519,7 @@
         <v>-</v>
       </c>
       <c r="V12" s="48">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W12" s="46">
         <v>8</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="Z12" s="47">
         <f t="shared" si="5"/>
-        <v>7.8888888888888884</v>
+        <v>7.7777777777777777</v>
       </c>
       <c r="AA12" s="46">
         <v>9.8000000000000007</v>
@@ -5545,14 +5545,14 @@
         <v>9.25</v>
       </c>
       <c r="AD12" s="46">
-        <v>9.25</v>
-      </c>
-      <c r="AE12" s="46" t="s">
-        <v>72</v>
+        <v>9.1</v>
+      </c>
+      <c r="AE12" s="46">
+        <v>8.4499999999999993</v>
       </c>
       <c r="AF12" s="47">
         <f t="shared" si="7"/>
-        <v>9.25</v>
+        <v>8.6449999999999996</v>
       </c>
       <c r="AG12" s="46" t="s">
         <v>72</v>
@@ -5738,17 +5738,17 @@
       </c>
       <c r="E13" s="30">
         <f t="shared" si="0"/>
-        <v>8.1402777777777775</v>
+        <v>7.5819444444444448</v>
       </c>
       <c r="F13" s="46" t="s">
         <v>72</v>
       </c>
       <c r="G13" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H13" s="47" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="I13" s="46" t="s">
         <v>72</v>
@@ -5786,14 +5786,14 @@
         <v>72</v>
       </c>
       <c r="T13" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="U13" s="47" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="V13" s="48">
-        <v>7.25</v>
+        <v>6.95</v>
       </c>
       <c r="W13" s="46" t="s">
         <v>75</v>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="Z13" s="47">
         <f t="shared" si="5"/>
-        <v>7.5333333333333323</v>
+        <v>7.4333333333333327</v>
       </c>
       <c r="AA13" s="46">
         <v>8</v>
@@ -5821,12 +5821,12 @@
       <c r="AD13" s="46">
         <v>8.75</v>
       </c>
-      <c r="AE13" s="46" t="s">
-        <v>72</v>
+      <c r="AE13" s="46">
+        <v>6.5</v>
       </c>
       <c r="AF13" s="47">
         <f t="shared" si="7"/>
-        <v>8.75</v>
+        <v>7.1749999999999998</v>
       </c>
       <c r="AG13" s="46" t="s">
         <v>72</v>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="E14" s="30">
         <f t="shared" si="0"/>
-        <v>7.2701851851851851</v>
+        <v>7.4235185185185175</v>
       </c>
       <c r="F14" s="46" t="s">
         <v>72</v>
@@ -6060,11 +6060,11 @@
         <v>72</v>
       </c>
       <c r="T14" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="U14" s="47" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="V14" s="48">
         <v>1.8</v>
@@ -6086,21 +6086,21 @@
         <v>8.9</v>
       </c>
       <c r="AB14" s="46">
-        <v>9</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AC14" s="47">
         <f t="shared" si="6"/>
-        <v>8.9550000000000001</v>
+        <v>9.0649999999999995</v>
       </c>
       <c r="AD14" s="46">
         <v>7.9</v>
       </c>
-      <c r="AE14" s="46" t="s">
-        <v>72</v>
+      <c r="AE14" s="46">
+        <v>8.4</v>
       </c>
       <c r="AF14" s="47">
         <f t="shared" si="7"/>
-        <v>7.9</v>
+        <v>8.25</v>
       </c>
       <c r="AG14" s="46" t="s">
         <v>72</v>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="E15" s="30">
         <f t="shared" si="0"/>
-        <v>7.722777777777778</v>
+        <v>7.6761111111111111</v>
       </c>
       <c r="F15" s="46" t="s">
         <v>72</v>
@@ -6369,12 +6369,12 @@
       <c r="AD15" s="46">
         <v>8</v>
       </c>
-      <c r="AE15" s="46" t="s">
-        <v>72</v>
+      <c r="AE15" s="46">
+        <v>7.8</v>
       </c>
       <c r="AF15" s="47">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>7.8599999999999994</v>
       </c>
       <c r="AG15" s="46" t="s">
         <v>72</v>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="E16" s="30">
         <f t="shared" si="0"/>
-        <v>8.4440476190476197</v>
+        <v>8.2340476190476206</v>
       </c>
       <c r="F16" s="46" t="s">
         <v>72</v>
@@ -6608,11 +6608,11 @@
         <v>72</v>
       </c>
       <c r="T16" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="U16" s="47" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="V16" s="48" t="s">
         <v>75</v>
@@ -6643,12 +6643,12 @@
       <c r="AD16" s="46">
         <v>8.5</v>
       </c>
-      <c r="AE16" s="46" t="s">
-        <v>72</v>
+      <c r="AE16" s="46">
+        <v>7.6</v>
       </c>
       <c r="AF16" s="47">
         <f t="shared" si="7"/>
-        <v>8.5</v>
+        <v>7.8699999999999992</v>
       </c>
       <c r="AG16" s="46" t="s">
         <v>72</v>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="E17" s="30">
         <f t="shared" si="0"/>
-        <v>7.8321296296296294</v>
+        <v>7.6737962962962962</v>
       </c>
       <c r="F17" s="46" t="s">
         <v>72</v>
@@ -6876,7 +6876,7 @@
         <v>72</v>
       </c>
       <c r="R17" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="S17" s="46" t="s">
         <v>72</v>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="U17" s="47" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="V17" s="48">
         <v>8.75</v>
@@ -6915,14 +6915,14 @@
         <v>7.2075000000000014</v>
       </c>
       <c r="AD17" s="46">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="AE17" s="46" t="s">
-        <v>72</v>
+        <v>8.25</v>
+      </c>
+      <c r="AE17" s="46">
+        <v>7.5</v>
       </c>
       <c r="AF17" s="47">
         <f t="shared" si="7"/>
-        <v>8.1999999999999993</v>
+        <v>7.7249999999999996</v>
       </c>
       <c r="AG17" s="46" t="s">
         <v>72</v>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="E18" s="30">
         <f t="shared" si="0"/>
-        <v>6.4074074074074074</v>
+        <v>6.6507407407407406</v>
       </c>
       <c r="F18" s="46" t="s">
         <v>72</v>
@@ -7189,14 +7189,14 @@
         <v>7.5</v>
       </c>
       <c r="AD18" s="46">
-        <v>5.5</v>
-      </c>
-      <c r="AE18" s="46" t="s">
-        <v>72</v>
+        <v>5.6</v>
+      </c>
+      <c r="AE18" s="46">
+        <v>6.5</v>
       </c>
       <c r="AF18" s="47">
         <f t="shared" si="7"/>
-        <v>5.5</v>
+        <v>6.2299999999999995</v>
       </c>
       <c r="AG18" s="46" t="s">
         <v>72</v>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="E19" s="30">
         <f t="shared" si="0"/>
-        <v>6.6370370370370368</v>
+        <v>6.383703703703703</v>
       </c>
       <c r="F19" s="46" t="s">
         <v>72</v>
@@ -7414,11 +7414,11 @@
         <v>72</v>
       </c>
       <c r="O19" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P19" s="47" t="str">
         <f t="shared" si="3"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="Q19" s="46" t="s">
         <v>72</v>
@@ -7455,22 +7455,22 @@
       <c r="AA19" s="46">
         <v>6</v>
       </c>
-      <c r="AB19" s="46">
-        <v>6</v>
+      <c r="AB19" s="46" t="s">
+        <v>75</v>
       </c>
       <c r="AC19" s="47">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>5.45</v>
       </c>
       <c r="AD19" s="46">
         <v>7.8</v>
       </c>
-      <c r="AE19" s="46" t="s">
-        <v>72</v>
+      <c r="AE19" s="46">
+        <v>7.5</v>
       </c>
       <c r="AF19" s="47">
         <f t="shared" si="7"/>
-        <v>7.8</v>
+        <v>7.59</v>
       </c>
       <c r="AG19" s="46" t="s">
         <v>72</v>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="E20" s="30">
         <f t="shared" si="0"/>
-        <v>8.0967592592592599</v>
+        <v>7.9567592592592584</v>
       </c>
       <c r="F20" s="46" t="s">
         <v>72</v>
@@ -7739,12 +7739,12 @@
       <c r="AD20" s="46">
         <v>7.8</v>
       </c>
-      <c r="AE20" s="46" t="s">
-        <v>72</v>
+      <c r="AE20" s="46">
+        <v>7.2</v>
       </c>
       <c r="AF20" s="47">
         <f t="shared" si="7"/>
-        <v>7.8</v>
+        <v>7.38</v>
       </c>
       <c r="AG20" s="46" t="s">
         <v>72</v>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="E21" s="30">
         <f t="shared" si="0"/>
-        <v>6.2061904761904758</v>
+        <v>6.2645238095238085</v>
       </c>
       <c r="F21" s="46" t="s">
         <v>72</v>
@@ -7952,11 +7952,11 @@
         <v>72</v>
       </c>
       <c r="L21" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M21" s="47" t="str">
         <f t="shared" si="2"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="N21" s="46" t="s">
         <v>72</v>
@@ -8013,12 +8013,12 @@
       <c r="AD21" s="46">
         <v>5.75</v>
       </c>
-      <c r="AE21" s="46" t="s">
-        <v>72</v>
+      <c r="AE21" s="46">
+        <v>6</v>
       </c>
       <c r="AF21" s="47">
         <f t="shared" si="7"/>
-        <v>5.75</v>
+        <v>5.9249999999999989</v>
       </c>
       <c r="AG21" s="46" t="s">
         <v>72</v>
@@ -8204,17 +8204,17 @@
       </c>
       <c r="E22" s="30">
         <f t="shared" si="0"/>
-        <v>7.3768518518518524</v>
+        <v>7.143518518518519</v>
       </c>
       <c r="F22" s="46" t="s">
         <v>72</v>
       </c>
       <c r="G22" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H22" s="47" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="I22" s="46" t="s">
         <v>72</v>
@@ -8246,17 +8246,17 @@
         <v>72</v>
       </c>
       <c r="R22" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="S22" s="46" t="s">
         <v>72</v>
       </c>
       <c r="T22" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="U22" s="47" t="str">
         <f t="shared" si="4"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="V22" s="48">
         <v>7.5</v>
@@ -8288,11 +8288,11 @@
         <v>8.75</v>
       </c>
       <c r="AE22" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AF22" s="47">
         <f t="shared" si="7"/>
-        <v>8.75</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="AG22" s="46" t="s">
         <v>72</v>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="E23" s="30">
         <f t="shared" si="0"/>
-        <v>7.2805555555555559</v>
+        <v>6.7905555555555557</v>
       </c>
       <c r="F23" s="46" t="s">
         <v>72</v>
@@ -8500,11 +8500,11 @@
         <v>72</v>
       </c>
       <c r="L23" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M23" s="47" t="str">
         <f t="shared" si="2"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="N23" s="46" t="s">
         <v>72</v>
@@ -8561,12 +8561,12 @@
       <c r="AD23" s="46">
         <v>7.9</v>
       </c>
-      <c r="AE23" s="46" t="s">
-        <v>72</v>
+      <c r="AE23" s="46">
+        <v>5.8</v>
       </c>
       <c r="AF23" s="47">
         <f t="shared" si="7"/>
-        <v>7.9</v>
+        <v>6.43</v>
       </c>
       <c r="AG23" s="46" t="s">
         <v>72</v>
@@ -8752,7 +8752,7 @@
       </c>
       <c r="E24" s="30">
         <f t="shared" si="0"/>
-        <v>7.8881481481481481</v>
+        <v>7.6048148148148149</v>
       </c>
       <c r="F24" s="46" t="s">
         <v>72</v>
@@ -8833,14 +8833,14 @@
         <v>7.7200000000000006</v>
       </c>
       <c r="AD24" s="46">
-        <v>8</v>
-      </c>
-      <c r="AE24" s="46" t="s">
-        <v>72</v>
+        <v>7.5</v>
+      </c>
+      <c r="AE24" s="46">
+        <v>7</v>
       </c>
       <c r="AF24" s="47">
         <f t="shared" si="7"/>
-        <v>8</v>
+        <v>7.1499999999999995</v>
       </c>
       <c r="AG24" s="46" t="s">
         <v>72</v>
@@ -9026,17 +9026,17 @@
       </c>
       <c r="E25" s="30">
         <f t="shared" si="0"/>
-        <v>6.1722222222222216</v>
+        <v>5.9388888888888891</v>
       </c>
       <c r="F25" s="46" t="s">
         <v>72</v>
       </c>
       <c r="G25" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H25" s="47" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="I25" s="46" t="s">
         <v>72</v>
@@ -9110,11 +9110,11 @@
         <v>7.5</v>
       </c>
       <c r="AE25" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AF25" s="47">
         <f t="shared" si="7"/>
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AG25" s="46" t="s">
         <v>72</v>
@@ -9300,17 +9300,17 @@
       </c>
       <c r="E26" s="30">
         <f t="shared" si="0"/>
-        <v>7.5338888888888889</v>
+        <v>7.3505555555555562</v>
       </c>
       <c r="F26" s="46" t="s">
         <v>72</v>
       </c>
       <c r="G26" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H26" s="47" t="str">
         <f t="shared" si="1"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="I26" s="46" t="s">
         <v>72</v>
@@ -9364,11 +9364,11 @@
         <v>8.25</v>
       </c>
       <c r="Y26" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="Z26" s="47">
         <f t="shared" si="5"/>
-        <v>7.666666666666667</v>
+        <v>7.1166666666666671</v>
       </c>
       <c r="AA26" s="46">
         <v>7</v>
@@ -9383,12 +9383,12 @@
       <c r="AD26" s="46">
         <v>7</v>
       </c>
-      <c r="AE26" s="46" t="s">
-        <v>72</v>
+      <c r="AE26" s="46">
+        <v>7</v>
       </c>
       <c r="AF26" s="47">
         <f t="shared" si="7"/>
-        <v>7.0000000000000009</v>
+        <v>7</v>
       </c>
       <c r="AG26" s="46" t="s">
         <v>72</v>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="E27" s="30">
         <f t="shared" si="0"/>
-        <v>5.0175925925925924</v>
+        <v>4.784259259259259</v>
       </c>
       <c r="F27" s="46" t="s">
         <v>72</v>
@@ -9596,11 +9596,11 @@
         <v>72</v>
       </c>
       <c r="L27" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M27" s="47" t="str">
         <f t="shared" si="2"/>
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="N27" s="46" t="s">
         <v>72</v>
@@ -9658,11 +9658,11 @@
         <v>7.5</v>
       </c>
       <c r="AE27" s="46" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="AF27" s="47">
         <f t="shared" si="7"/>
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AG27" s="46" t="s">
         <v>72</v>
@@ -10010,296 +10010,296 @@
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
-      <c r="F29" s="53" t="e" vm="1">
+      <c r="F29" s="57" t="e" vm="1">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/au.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G29" s="54"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="54" t="e" vm="2">
+      <c r="G29" s="58"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="58" t="e" vm="2">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/cn.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J29" s="54"/>
-      <c r="K29" s="54"/>
-      <c r="L29" s="54"/>
-      <c r="M29" s="54"/>
-      <c r="N29" s="53" t="e" vm="3">
+      <c r="J29" s="58"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="57" t="e" vm="3">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/jp.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="O29" s="54"/>
-      <c r="P29" s="55"/>
-      <c r="Q29" s="54" t="e" vm="4">
+      <c r="O29" s="58"/>
+      <c r="P29" s="59"/>
+      <c r="Q29" s="58" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="R29" s="54"/>
-      <c r="S29" s="54"/>
-      <c r="T29" s="54"/>
-      <c r="U29" s="55"/>
-      <c r="V29" s="53" t="e" vm="5">
+      <c r="R29" s="58"/>
+      <c r="S29" s="58"/>
+      <c r="T29" s="58"/>
+      <c r="U29" s="59"/>
+      <c r="V29" s="57" t="e" vm="5">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ca.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="W29" s="54"/>
-      <c r="X29" s="54"/>
-      <c r="Y29" s="54"/>
-      <c r="Z29" s="54"/>
-      <c r="AA29" s="53" t="e" vm="6">
+      <c r="W29" s="58"/>
+      <c r="X29" s="58"/>
+      <c r="Y29" s="58"/>
+      <c r="Z29" s="58"/>
+      <c r="AA29" s="57" t="e" vm="6">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mc.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AB29" s="54"/>
-      <c r="AC29" s="55"/>
-      <c r="AD29" s="53" t="e" vm="7">
+      <c r="AB29" s="58"/>
+      <c r="AC29" s="59"/>
+      <c r="AD29" s="57" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE29" s="54"/>
-      <c r="AF29" s="55"/>
-      <c r="AG29" s="53" t="e" vm="8">
+      <c r="AE29" s="58"/>
+      <c r="AF29" s="59"/>
+      <c r="AG29" s="57" t="e" vm="8">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/at.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH29" s="54"/>
-      <c r="AI29" s="55"/>
-      <c r="AJ29" s="54" t="e" vm="9">
+      <c r="AH29" s="58"/>
+      <c r="AI29" s="59"/>
+      <c r="AJ29" s="58" t="e" vm="9">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/gb.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AK29" s="54"/>
-      <c r="AL29" s="54"/>
-      <c r="AM29" s="54"/>
-      <c r="AN29" s="54"/>
-      <c r="AO29" s="53" t="e" vm="10">
+      <c r="AK29" s="58"/>
+      <c r="AL29" s="58"/>
+      <c r="AM29" s="58"/>
+      <c r="AN29" s="58"/>
+      <c r="AO29" s="57" t="e" vm="10">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/be.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AP29" s="54"/>
-      <c r="AQ29" s="55"/>
-      <c r="AR29" s="53" t="e" vm="11">
+      <c r="AP29" s="58"/>
+      <c r="AQ29" s="59"/>
+      <c r="AR29" s="57" t="e" vm="11">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/hu.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AS29" s="54"/>
-      <c r="AT29" s="55"/>
-      <c r="AU29" s="54" t="e" vm="12">
+      <c r="AS29" s="58"/>
+      <c r="AT29" s="59"/>
+      <c r="AU29" s="58" t="e" vm="12">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/nl.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AV29" s="54"/>
-      <c r="AW29" s="54"/>
-      <c r="AX29" s="54"/>
-      <c r="AY29" s="54"/>
-      <c r="AZ29" s="53" t="e" vm="13">
+      <c r="AV29" s="58"/>
+      <c r="AW29" s="58"/>
+      <c r="AX29" s="58"/>
+      <c r="AY29" s="58"/>
+      <c r="AZ29" s="57" t="e" vm="13">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/it.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BA29" s="54"/>
-      <c r="BB29" s="55"/>
-      <c r="BC29" s="53" t="e" vm="7">
+      <c r="BA29" s="58"/>
+      <c r="BB29" s="59"/>
+      <c r="BC29" s="57" t="e" vm="7">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/es.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BD29" s="54"/>
-      <c r="BE29" s="55"/>
-      <c r="BF29" s="53" t="e" vm="14">
+      <c r="BD29" s="58"/>
+      <c r="BE29" s="59"/>
+      <c r="BF29" s="57" t="e" vm="14">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/az.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BG29" s="54"/>
-      <c r="BH29" s="55"/>
-      <c r="BI29" s="54" t="e" vm="15">
+      <c r="BG29" s="58"/>
+      <c r="BH29" s="59"/>
+      <c r="BI29" s="58" t="e" vm="15">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/sg.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BJ29" s="54"/>
-      <c r="BK29" s="54"/>
-      <c r="BL29" s="54"/>
-      <c r="BM29" s="54"/>
-      <c r="BN29" s="53" t="e" vm="4">
+      <c r="BJ29" s="58"/>
+      <c r="BK29" s="58"/>
+      <c r="BL29" s="58"/>
+      <c r="BM29" s="58"/>
+      <c r="BN29" s="57" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BO29" s="54"/>
-      <c r="BP29" s="55"/>
-      <c r="BQ29" s="53" t="e" vm="16">
+      <c r="BO29" s="58"/>
+      <c r="BP29" s="59"/>
+      <c r="BQ29" s="57" t="e" vm="16">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/mx.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BR29" s="54"/>
-      <c r="BS29" s="55"/>
-      <c r="BT29" s="53" t="e" vm="17">
+      <c r="BR29" s="58"/>
+      <c r="BS29" s="59"/>
+      <c r="BT29" s="57" t="e" vm="17">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/br.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BU29" s="54"/>
-      <c r="BV29" s="55"/>
-      <c r="BW29" s="53" t="e" vm="4">
+      <c r="BU29" s="58"/>
+      <c r="BV29" s="59"/>
+      <c r="BW29" s="57" t="e" vm="4">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/us.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="BX29" s="54"/>
-      <c r="BY29" s="55"/>
-      <c r="BZ29" s="53" t="e" vm="18">
+      <c r="BX29" s="58"/>
+      <c r="BY29" s="59"/>
+      <c r="BZ29" s="57" t="e" vm="18">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/qa.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CA29" s="54"/>
-      <c r="CB29" s="55"/>
-      <c r="CC29" s="53" t="e" vm="19">
+      <c r="CA29" s="58"/>
+      <c r="CB29" s="59"/>
+      <c r="CC29" s="57" t="e" vm="19">
         <f>_xlfn.IMAGE("https://flagcdn.com/w640/ae.png")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="CD29" s="54"/>
-      <c r="CE29" s="55"/>
+      <c r="CD29" s="58"/>
+      <c r="CE29" s="59"/>
     </row>
     <row r="30" spans="1:83" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="56" t="s">
+      <c r="A30" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="56" t="s">
+      <c r="B30" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="56" t="s">
+      <c r="C30" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="D30" s="56" t="s">
+      <c r="D30" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="56" t="s">
+      <c r="E30" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="F30" s="60" t="s">
+      <c r="F30" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="G30" s="56"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="56" t="s">
+      <c r="G30" s="52"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="J30" s="56"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="56"/>
-      <c r="M30" s="56"/>
-      <c r="N30" s="60" t="s">
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="O30" s="56"/>
-      <c r="P30" s="61"/>
-      <c r="Q30" s="62" t="s">
+      <c r="O30" s="52"/>
+      <c r="P30" s="53"/>
+      <c r="Q30" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="R30" s="63"/>
-      <c r="S30" s="63"/>
-      <c r="T30" s="63"/>
-      <c r="U30" s="64"/>
-      <c r="V30" s="62" t="s">
+      <c r="R30" s="55"/>
+      <c r="S30" s="55"/>
+      <c r="T30" s="55"/>
+      <c r="U30" s="56"/>
+      <c r="V30" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="W30" s="63"/>
-      <c r="X30" s="63"/>
-      <c r="Y30" s="63"/>
-      <c r="Z30" s="64"/>
-      <c r="AA30" s="60" t="s">
+      <c r="W30" s="55"/>
+      <c r="X30" s="55"/>
+      <c r="Y30" s="55"/>
+      <c r="Z30" s="56"/>
+      <c r="AA30" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="AB30" s="56"/>
-      <c r="AC30" s="61"/>
-      <c r="AD30" s="60" t="s">
+      <c r="AB30" s="52"/>
+      <c r="AC30" s="53"/>
+      <c r="AD30" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="AE30" s="56"/>
-      <c r="AF30" s="61"/>
-      <c r="AG30" s="60" t="s">
+      <c r="AE30" s="52"/>
+      <c r="AF30" s="53"/>
+      <c r="AG30" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="AH30" s="56"/>
-      <c r="AI30" s="61"/>
-      <c r="AJ30" s="56" t="s">
+      <c r="AH30" s="52"/>
+      <c r="AI30" s="53"/>
+      <c r="AJ30" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="AK30" s="56"/>
-      <c r="AL30" s="56"/>
-      <c r="AM30" s="56"/>
-      <c r="AN30" s="56"/>
-      <c r="AO30" s="60" t="s">
+      <c r="AK30" s="52"/>
+      <c r="AL30" s="52"/>
+      <c r="AM30" s="52"/>
+      <c r="AN30" s="52"/>
+      <c r="AO30" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="AP30" s="56"/>
-      <c r="AQ30" s="61"/>
-      <c r="AR30" s="60" t="s">
+      <c r="AP30" s="52"/>
+      <c r="AQ30" s="53"/>
+      <c r="AR30" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="AS30" s="56"/>
-      <c r="AT30" s="61"/>
-      <c r="AU30" s="62" t="s">
+      <c r="AS30" s="52"/>
+      <c r="AT30" s="53"/>
+      <c r="AU30" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="AV30" s="63"/>
-      <c r="AW30" s="63"/>
-      <c r="AX30" s="63"/>
-      <c r="AY30" s="64"/>
-      <c r="AZ30" s="60" t="s">
+      <c r="AV30" s="55"/>
+      <c r="AW30" s="55"/>
+      <c r="AX30" s="55"/>
+      <c r="AY30" s="56"/>
+      <c r="AZ30" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="BA30" s="56"/>
-      <c r="BB30" s="61"/>
-      <c r="BC30" s="60" t="s">
+      <c r="BA30" s="52"/>
+      <c r="BB30" s="53"/>
+      <c r="BC30" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="BD30" s="56"/>
-      <c r="BE30" s="61"/>
-      <c r="BF30" s="60" t="s">
+      <c r="BD30" s="52"/>
+      <c r="BE30" s="53"/>
+      <c r="BF30" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="BG30" s="56"/>
-      <c r="BH30" s="61"/>
-      <c r="BI30" s="62" t="s">
+      <c r="BG30" s="52"/>
+      <c r="BH30" s="53"/>
+      <c r="BI30" s="54" t="s">
         <v>19</v>
       </c>
-      <c r="BJ30" s="63"/>
-      <c r="BK30" s="63"/>
-      <c r="BL30" s="63"/>
-      <c r="BM30" s="64"/>
-      <c r="BN30" s="60" t="s">
+      <c r="BJ30" s="55"/>
+      <c r="BK30" s="55"/>
+      <c r="BL30" s="55"/>
+      <c r="BM30" s="56"/>
+      <c r="BN30" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="BO30" s="56"/>
-      <c r="BP30" s="61"/>
-      <c r="BQ30" s="60" t="s">
+      <c r="BO30" s="52"/>
+      <c r="BP30" s="53"/>
+      <c r="BQ30" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="BR30" s="56"/>
-      <c r="BS30" s="61"/>
-      <c r="BT30" s="60" t="s">
+      <c r="BR30" s="52"/>
+      <c r="BS30" s="53"/>
+      <c r="BT30" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="BU30" s="56"/>
-      <c r="BV30" s="61"/>
-      <c r="BW30" s="60" t="s">
+      <c r="BU30" s="52"/>
+      <c r="BV30" s="53"/>
+      <c r="BW30" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="BX30" s="56"/>
-      <c r="BY30" s="61"/>
-      <c r="BZ30" s="60" t="s">
+      <c r="BX30" s="52"/>
+      <c r="BY30" s="53"/>
+      <c r="BZ30" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="CA30" s="56"/>
-      <c r="CB30" s="61"/>
-      <c r="CC30" s="60" t="s">
+      <c r="CA30" s="52"/>
+      <c r="CB30" s="53"/>
+      <c r="CC30" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="CD30" s="56"/>
-      <c r="CE30" s="61"/>
+      <c r="CD30" s="52"/>
+      <c r="CE30" s="53"/>
     </row>
     <row r="31" spans="1:83" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="56"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
+      <c r="A31" s="52"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
       <c r="F31" s="22" t="s">
         <v>26</v>
       </c>
@@ -10541,16 +10541,16 @@
       </c>
       <c r="B32" s="35" cm="1">
         <f t="array" ref="B32:CE53">_xlfn._xlws.SORT(B6:CE27,4,-1)</f>
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C32" s="12" t="str">
-        <v>Max Verstappen</v>
+        <v>Lewis Hamilton</v>
       </c>
       <c r="D32" s="18" t="str">
-        <v>Red Bull</v>
+        <v>Ferrari</v>
       </c>
       <c r="E32" s="30">
-        <v>8.7962962962962958</v>
+        <v>8.76212962962963</v>
       </c>
       <c r="F32" s="21" t="str">
         <v>-</v>
@@ -10601,10 +10601,10 @@
         <v>-</v>
       </c>
       <c r="V32" s="28">
+        <v>8.25</v>
+      </c>
+      <c r="W32" s="23">
         <v>7.5</v>
-      </c>
-      <c r="W32" s="23">
-        <v>8</v>
       </c>
       <c r="X32" s="23">
         <v>8</v>
@@ -10613,25 +10613,25 @@
         <v>-</v>
       </c>
       <c r="Z32" s="24">
-        <v>7.8888888888888884</v>
+        <v>7.8888888888888893</v>
       </c>
       <c r="AA32" s="28">
+        <v>8.9</v>
+      </c>
+      <c r="AB32" s="23">
+        <v>8.35</v>
+      </c>
+      <c r="AC32" s="24">
+        <v>8.5975000000000001</v>
+      </c>
+      <c r="AD32" s="28">
         <v>9.8000000000000007</v>
       </c>
-      <c r="AB32" s="23" t="str">
-        <v>NR</v>
-      </c>
-      <c r="AC32" s="24">
-        <v>9.25</v>
-      </c>
-      <c r="AD32" s="28">
-        <v>9.25</v>
-      </c>
-      <c r="AE32" s="23" t="str">
-        <v>-</v>
+      <c r="AE32" s="23">
+        <v>9.8000000000000007</v>
       </c>
       <c r="AF32" s="24">
-        <v>9.25</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="AG32" s="28" t="str">
         <v>-</v>
@@ -10792,16 +10792,16 @@
         <v>2</v>
       </c>
       <c r="B33" s="35">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C33" s="12" t="str">
-        <v>Lewis Hamilton</v>
+        <v>Lando Norris</v>
       </c>
       <c r="D33" s="18" t="str">
-        <v>Ferrari</v>
+        <v>McLaren</v>
       </c>
       <c r="E33" s="30">
-        <v>8.7454629629629625</v>
+        <v>8.7032407407407408</v>
       </c>
       <c r="F33" s="21" t="str">
         <v>-</v>
@@ -10822,10 +10822,10 @@
         <v>-</v>
       </c>
       <c r="L33" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="M33" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="N33" s="28" t="str">
         <v>-</v>
@@ -10852,37 +10852,37 @@
         <v>-</v>
       </c>
       <c r="V33" s="28">
-        <v>8.25</v>
+        <v>9.6</v>
       </c>
       <c r="W33" s="23">
-        <v>7.5</v>
+        <v>9.75</v>
       </c>
       <c r="X33" s="23">
-        <v>8</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="Y33" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z33" s="24">
-        <v>7.8888888888888893</v>
+        <v>9.4722222222222197</v>
       </c>
       <c r="AA33" s="28">
-        <v>8.9</v>
+        <v>7.85</v>
       </c>
       <c r="AB33" s="23">
-        <v>8.35</v>
+        <v>7</v>
       </c>
       <c r="AC33" s="24">
-        <v>8.5975000000000001</v>
+        <v>7.3825000000000003</v>
       </c>
       <c r="AD33" s="28">
-        <v>9.75</v>
-      </c>
-      <c r="AE33" s="23" t="str">
-        <v>-</v>
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AE33" s="23">
+        <v>9.4499999999999993</v>
       </c>
       <c r="AF33" s="24">
-        <v>9.75</v>
+        <v>9.254999999999999</v>
       </c>
       <c r="AG33" s="28" t="str">
         <v>-</v>
@@ -11043,16 +11043,16 @@
         <v>3</v>
       </c>
       <c r="B34" s="36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C34" s="12" t="str">
-        <v>Lando Norris</v>
+        <v>Max Verstappen</v>
       </c>
       <c r="D34" s="1" t="str">
-        <v>McLaren</v>
+        <v>Red Bull</v>
       </c>
       <c r="E34" s="30">
-        <v>8.5574074074074069</v>
+        <v>8.5575925925925933</v>
       </c>
       <c r="F34" s="21" t="str">
         <v>-</v>
@@ -11103,37 +11103,37 @@
         <v>-</v>
       </c>
       <c r="V34" s="28">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="W34" s="23">
-        <v>9.75</v>
+        <v>8</v>
       </c>
       <c r="X34" s="23">
-        <v>9.1999999999999993</v>
+        <v>8</v>
       </c>
       <c r="Y34" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z34" s="24">
-        <v>9.4722222222222197</v>
+        <v>7.7777777777777777</v>
       </c>
       <c r="AA34" s="28">
-        <v>8</v>
-      </c>
-      <c r="AB34" s="23">
-        <v>7</v>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AB34" s="23" t="str">
+        <v>NR</v>
       </c>
       <c r="AC34" s="24">
-        <v>7.4500000000000011</v>
+        <v>9.25</v>
       </c>
       <c r="AD34" s="28">
-        <v>8.75</v>
-      </c>
-      <c r="AE34" s="23" t="str">
-        <v>-</v>
+        <v>9.1</v>
+      </c>
+      <c r="AE34" s="23">
+        <v>8.4499999999999993</v>
       </c>
       <c r="AF34" s="24">
-        <v>8.75</v>
+        <v>8.6449999999999996</v>
       </c>
       <c r="AG34" s="28" t="str">
         <v>-</v>
@@ -11294,16 +11294,16 @@
         <v>4</v>
       </c>
       <c r="B35" s="36">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C35" s="12" t="str">
-        <v>Liam Lawson</v>
+        <v>Kimi Antonelli</v>
       </c>
       <c r="D35" s="1" t="str">
-        <v>Racing Bulls</v>
+        <v>Mercedes</v>
       </c>
       <c r="E35" s="30">
-        <v>8.4440476190476197</v>
+        <v>8.357592592592594</v>
       </c>
       <c r="F35" s="21" t="str">
         <v>-</v>
@@ -11353,38 +11353,38 @@
       <c r="U35" s="24" t="str">
         <v>-</v>
       </c>
-      <c r="V35" s="28" t="str">
-        <v>NR</v>
+      <c r="V35" s="28">
+        <v>8.25</v>
       </c>
       <c r="W35" s="23">
-        <v>8.75</v>
+        <v>5.75</v>
       </c>
       <c r="X35" s="23">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="Y35" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z35" s="24">
-        <v>8.1071428571428577</v>
+        <v>7.5277777777777777</v>
       </c>
       <c r="AA35" s="28">
+        <v>9.5</v>
+      </c>
+      <c r="AB35" s="23">
         <v>9</v>
       </c>
-      <c r="AB35" s="23">
+      <c r="AC35" s="24">
+        <v>9.2250000000000014</v>
+      </c>
+      <c r="AD35" s="28">
+        <v>7.9</v>
+      </c>
+      <c r="AE35" s="23">
         <v>8.5</v>
       </c>
-      <c r="AC35" s="24">
-        <v>8.7250000000000014</v>
-      </c>
-      <c r="AD35" s="28">
-        <v>8.5</v>
-      </c>
-      <c r="AE35" s="23" t="str">
-        <v>-</v>
-      </c>
       <c r="AF35" s="24">
-        <v>8.5</v>
+        <v>8.32</v>
       </c>
       <c r="AG35" s="28" t="str">
         <v>-</v>
@@ -11545,16 +11545,16 @@
         <v>5</v>
       </c>
       <c r="B36" s="37">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C36" s="12" t="str">
-        <v>Kimi Antonelli</v>
+        <v>Liam Lawson</v>
       </c>
       <c r="D36" s="3" t="str">
-        <v>Mercedes</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E36" s="30">
-        <v>8.4175925925925927</v>
+        <v>8.2340476190476206</v>
       </c>
       <c r="F36" s="21" t="str">
         <v>-</v>
@@ -11599,43 +11599,43 @@
         <v>-</v>
       </c>
       <c r="T36" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="U36" s="24" t="str">
-        <v>-</v>
-      </c>
-      <c r="V36" s="28">
-        <v>8.25</v>
+        <v>NR</v>
+      </c>
+      <c r="V36" s="28" t="str">
+        <v>NR</v>
       </c>
       <c r="W36" s="23">
-        <v>5.75</v>
+        <v>8.75</v>
       </c>
       <c r="X36" s="23">
+        <v>7.8</v>
+      </c>
+      <c r="Y36" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z36" s="24">
+        <v>8.1071428571428577</v>
+      </c>
+      <c r="AA36" s="28">
+        <v>9</v>
+      </c>
+      <c r="AB36" s="23">
         <v>8.5</v>
       </c>
-      <c r="Y36" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="Z36" s="24">
-        <v>7.5277777777777777</v>
-      </c>
-      <c r="AA36" s="28">
-        <v>9.5</v>
-      </c>
-      <c r="AB36" s="23">
-        <v>9</v>
-      </c>
       <c r="AC36" s="24">
-        <v>9.2250000000000014</v>
+        <v>8.7250000000000014</v>
       </c>
       <c r="AD36" s="28">
         <v>8.5</v>
       </c>
-      <c r="AE36" s="23" t="str">
-        <v>-</v>
+      <c r="AE36" s="23">
+        <v>7.6</v>
       </c>
       <c r="AF36" s="24">
-        <v>8.5</v>
+        <v>7.8699999999999992</v>
       </c>
       <c r="AG36" s="28" t="str">
         <v>-</v>
@@ -11796,16 +11796,16 @@
         <v>6</v>
       </c>
       <c r="B37" s="37">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C37" s="12" t="str">
-        <v>Isack Hadjar</v>
+        <v>Carlos Sainz</v>
       </c>
       <c r="D37" s="3" t="str">
-        <v>Red Bull</v>
+        <v>Williams</v>
       </c>
       <c r="E37" s="30">
-        <v>8.1402777777777775</v>
+        <v>7.9567592592592584</v>
       </c>
       <c r="F37" s="21" t="str">
         <v>-</v>
@@ -11856,37 +11856,37 @@
         <v>-</v>
       </c>
       <c r="V37" s="28">
-        <v>7.25</v>
-      </c>
-      <c r="W37" s="23" t="str">
-        <v>NR</v>
+        <v>9</v>
+      </c>
+      <c r="W37" s="23">
+        <v>8.75</v>
       </c>
       <c r="X37" s="23">
-        <v>7.9</v>
+        <v>8.35</v>
       </c>
       <c r="Y37" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z37" s="24">
-        <v>7.5333333333333323</v>
+        <v>8.6277777777777764</v>
       </c>
       <c r="AA37" s="28">
         <v>8</v>
       </c>
       <c r="AB37" s="23">
-        <v>8.25</v>
+        <v>7.75</v>
       </c>
       <c r="AC37" s="24">
-        <v>8.1375000000000011</v>
+        <v>7.8625000000000007</v>
       </c>
       <c r="AD37" s="28">
-        <v>8.75</v>
-      </c>
-      <c r="AE37" s="23" t="str">
-        <v>-</v>
+        <v>7.8</v>
+      </c>
+      <c r="AE37" s="23">
+        <v>7.2</v>
       </c>
       <c r="AF37" s="24">
-        <v>8.75</v>
+        <v>7.38</v>
       </c>
       <c r="AG37" s="28" t="str">
         <v>-</v>
@@ -12047,16 +12047,16 @@
         <v>7</v>
       </c>
       <c r="B38" s="38">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C38" s="12" t="str">
-        <v>Carlos Sainz</v>
+        <v>Oscar Piastri</v>
       </c>
       <c r="D38" s="4" t="str">
-        <v>Williams</v>
+        <v>McLaren</v>
       </c>
       <c r="E38" s="30">
-        <v>8.0967592592592599</v>
+        <v>7.9529629629629639</v>
       </c>
       <c r="F38" s="21" t="str">
         <v>-</v>
@@ -12077,10 +12077,10 @@
         <v>-</v>
       </c>
       <c r="L38" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="M38" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="N38" s="28" t="str">
         <v>-</v>
@@ -12107,37 +12107,37 @@
         <v>-</v>
       </c>
       <c r="V38" s="28">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="W38" s="23">
-        <v>8.75</v>
+        <v>7.9</v>
       </c>
       <c r="X38" s="23">
-        <v>8.35</v>
+        <v>9.1</v>
       </c>
       <c r="Y38" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z38" s="24">
-        <v>8.6277777777777764</v>
+        <v>8.7888888888888896</v>
       </c>
       <c r="AA38" s="28">
         <v>8</v>
       </c>
       <c r="AB38" s="23">
-        <v>7.75</v>
+        <v>7.8</v>
       </c>
       <c r="AC38" s="24">
-        <v>7.8625000000000007</v>
+        <v>7.8900000000000006</v>
       </c>
       <c r="AD38" s="28">
-        <v>7.8</v>
-      </c>
-      <c r="AE38" s="23" t="str">
-        <v>-</v>
+        <v>7.6</v>
+      </c>
+      <c r="AE38" s="23">
+        <v>7</v>
       </c>
       <c r="AF38" s="24">
-        <v>7.8</v>
+        <v>7.18</v>
       </c>
       <c r="AG38" s="28" t="str">
         <v>-</v>
@@ -12298,16 +12298,16 @@
         <v>8</v>
       </c>
       <c r="B39" s="38">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="C39" s="12" t="str">
-        <v>Oscar Piastri</v>
+        <v>Franco Colapinto</v>
       </c>
       <c r="D39" s="4" t="str">
-        <v>McLaren</v>
+        <v>Alpine</v>
       </c>
       <c r="E39" s="30">
-        <v>7.9879629629629632</v>
+        <v>7.6761111111111111</v>
       </c>
       <c r="F39" s="21" t="str">
         <v>-</v>
@@ -12358,37 +12358,37 @@
         <v>-</v>
       </c>
       <c r="V39" s="28">
-        <v>9.5</v>
+        <v>8.75</v>
       </c>
       <c r="W39" s="23">
-        <v>7.75</v>
+        <v>9</v>
       </c>
       <c r="X39" s="23">
-        <v>9.1</v>
+        <v>8.75</v>
       </c>
       <c r="Y39" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z39" s="24">
-        <v>8.7388888888888889</v>
+        <v>8.8333333333333321</v>
       </c>
       <c r="AA39" s="28">
+        <v>6.5</v>
+      </c>
+      <c r="AB39" s="23">
+        <v>6.2</v>
+      </c>
+      <c r="AC39" s="24">
+        <v>6.3350000000000009</v>
+      </c>
+      <c r="AD39" s="28">
         <v>8</v>
       </c>
-      <c r="AB39" s="23">
-        <v>7.5</v>
-      </c>
-      <c r="AC39" s="24">
-        <v>7.7249999999999996</v>
-      </c>
-      <c r="AD39" s="28">
-        <v>7.5</v>
-      </c>
-      <c r="AE39" s="23" t="str">
-        <v>-</v>
+      <c r="AE39" s="23">
+        <v>7.8</v>
       </c>
       <c r="AF39" s="24">
-        <v>7.5</v>
+        <v>7.8599999999999994</v>
       </c>
       <c r="AG39" s="28" t="str">
         <v>-</v>
@@ -12549,16 +12549,16 @@
         <v>9</v>
       </c>
       <c r="B40" s="39">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C40" s="12" t="str">
-        <v>Sergio Perez</v>
+        <v>Arvid Lindblad</v>
       </c>
       <c r="D40" s="5" t="str">
-        <v>Cadillac</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E40" s="30">
-        <v>7.8881481481481481</v>
+        <v>7.6737962962962962</v>
       </c>
       <c r="F40" s="21" t="str">
         <v>-</v>
@@ -12597,7 +12597,7 @@
         <v>-</v>
       </c>
       <c r="R40" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="S40" s="23" t="str">
         <v>-</v>
@@ -12606,40 +12606,40 @@
         <v>-</v>
       </c>
       <c r="U40" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="V40" s="28">
         <v>8.75</v>
       </c>
       <c r="W40" s="23">
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="X40" s="23">
+        <v>8.5</v>
+      </c>
+      <c r="Y40" s="23" t="str">
+        <v>NR</v>
+      </c>
+      <c r="Z40" s="24">
+        <v>8.0888888888888886</v>
+      </c>
+      <c r="AA40" s="28">
+        <v>5.75</v>
+      </c>
+      <c r="AB40" s="23">
+        <v>8.4</v>
+      </c>
+      <c r="AC40" s="24">
+        <v>7.2075000000000014</v>
+      </c>
+      <c r="AD40" s="28">
+        <v>8.25</v>
+      </c>
+      <c r="AE40" s="23">
         <v>7.5</v>
       </c>
-      <c r="Y40" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="Z40" s="24">
-        <v>7.9444444444444446</v>
-      </c>
-      <c r="AA40" s="28">
-        <v>8.6</v>
-      </c>
-      <c r="AB40" s="23">
-        <v>7</v>
-      </c>
-      <c r="AC40" s="24">
-        <v>7.7200000000000006</v>
-      </c>
-      <c r="AD40" s="28">
-        <v>8</v>
-      </c>
-      <c r="AE40" s="23" t="str">
-        <v>-</v>
-      </c>
       <c r="AF40" s="24">
-        <v>8</v>
+        <v>7.7249999999999996</v>
       </c>
       <c r="AG40" s="28" t="str">
         <v>-</v>
@@ -12800,16 +12800,16 @@
         <v>10</v>
       </c>
       <c r="B41" s="39">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C41" s="12" t="str">
-        <v>Arvid Lindblad</v>
+        <v>Sergio Perez</v>
       </c>
       <c r="D41" s="5" t="str">
-        <v>Racing Bulls</v>
+        <v>Cadillac</v>
       </c>
       <c r="E41" s="30">
-        <v>7.8321296296296294</v>
+        <v>7.6048148148148149</v>
       </c>
       <c r="F41" s="21" t="str">
         <v>-</v>
@@ -12863,34 +12863,34 @@
         <v>8.75</v>
       </c>
       <c r="W41" s="23">
-        <v>8.75</v>
+        <v>8</v>
       </c>
       <c r="X41" s="23">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="Y41" s="23" t="str">
-        <v>NR</v>
+        <v>-</v>
       </c>
       <c r="Z41" s="24">
-        <v>8.0888888888888886</v>
+        <v>7.9444444444444446</v>
       </c>
       <c r="AA41" s="28">
-        <v>5.75</v>
+        <v>8.6</v>
       </c>
       <c r="AB41" s="23">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AC41" s="24">
-        <v>7.2075000000000014</v>
+        <v>7.7200000000000006</v>
       </c>
       <c r="AD41" s="28">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="AE41" s="23" t="str">
-        <v>-</v>
+        <v>7.5</v>
+      </c>
+      <c r="AE41" s="23">
+        <v>7</v>
       </c>
       <c r="AF41" s="24">
-        <v>8.1999999999999993</v>
+        <v>7.1499999999999995</v>
       </c>
       <c r="AG41" s="28" t="str">
         <v>-</v>
@@ -13051,25 +13051,25 @@
         <v>11</v>
       </c>
       <c r="B42" s="40">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="C42" s="12" t="str">
-        <v>Franco Colapinto</v>
+        <v>Isack Hadjar</v>
       </c>
       <c r="D42" s="6" t="str">
-        <v>Alpine</v>
+        <v>Red Bull</v>
       </c>
       <c r="E42" s="30">
-        <v>7.722777777777778</v>
+        <v>7.5819444444444448</v>
       </c>
       <c r="F42" s="21" t="str">
         <v>-</v>
       </c>
       <c r="G42" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="H42" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="I42" s="28" t="str">
         <v>-</v>
@@ -13105,43 +13105,43 @@
         <v>-</v>
       </c>
       <c r="T42" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="U42" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="V42" s="28">
+        <v>6.95</v>
+      </c>
+      <c r="W42" s="23" t="str">
+        <v>NR</v>
+      </c>
+      <c r="X42" s="23">
+        <v>7.9</v>
+      </c>
+      <c r="Y42" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z42" s="24">
+        <v>7.4333333333333327</v>
+      </c>
+      <c r="AA42" s="28">
+        <v>8</v>
+      </c>
+      <c r="AB42" s="23">
+        <v>8.25</v>
+      </c>
+      <c r="AC42" s="24">
+        <v>8.1375000000000011</v>
+      </c>
+      <c r="AD42" s="28">
         <v>8.75</v>
       </c>
-      <c r="W42" s="23">
-        <v>9</v>
-      </c>
-      <c r="X42" s="23">
-        <v>8.75</v>
-      </c>
-      <c r="Y42" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="Z42" s="24">
-        <v>8.8333333333333321</v>
-      </c>
-      <c r="AA42" s="28">
+      <c r="AE42" s="23">
         <v>6.5</v>
       </c>
-      <c r="AB42" s="23">
-        <v>6.2</v>
-      </c>
-      <c r="AC42" s="24">
-        <v>6.3350000000000009</v>
-      </c>
-      <c r="AD42" s="28">
-        <v>8</v>
-      </c>
-      <c r="AE42" s="23" t="str">
-        <v>-</v>
-      </c>
       <c r="AF42" s="24">
-        <v>8</v>
+        <v>7.1749999999999998</v>
       </c>
       <c r="AG42" s="28" t="str">
         <v>-</v>
@@ -13302,16 +13302,16 @@
         <v>12</v>
       </c>
       <c r="B43" s="40">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="C43" s="12" t="str">
-        <v>George Russell</v>
+        <v>Pierre Gasly</v>
       </c>
       <c r="D43" s="6" t="str">
-        <v>Mercedes</v>
+        <v>Alpine</v>
       </c>
       <c r="E43" s="30">
-        <v>7.7055555555555557</v>
+        <v>7.4235185185185175</v>
       </c>
       <c r="F43" s="21" t="str">
         <v>-</v>
@@ -13356,43 +13356,43 @@
         <v>-</v>
       </c>
       <c r="T43" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="U43" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="V43" s="28">
-        <v>8.75</v>
+        <v>1.8</v>
       </c>
       <c r="W43" s="23">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="X43" s="23">
-        <v>8.75</v>
+        <v>6.5</v>
       </c>
       <c r="Y43" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z43" s="24">
-        <v>8.6666666666666661</v>
+        <v>4.9555555555555557</v>
       </c>
       <c r="AA43" s="28">
-        <v>6</v>
+        <v>8.9</v>
       </c>
       <c r="AB43" s="23">
-        <v>5</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AC43" s="24">
-        <v>5.45</v>
+        <v>9.0649999999999995</v>
       </c>
       <c r="AD43" s="28">
-        <v>9</v>
-      </c>
-      <c r="AE43" s="23" t="str">
-        <v>-</v>
+        <v>7.9</v>
+      </c>
+      <c r="AE43" s="23">
+        <v>8.4</v>
       </c>
       <c r="AF43" s="24">
-        <v>9</v>
+        <v>8.25</v>
       </c>
       <c r="AG43" s="28" t="str">
         <v>-</v>
@@ -13553,16 +13553,16 @@
         <v>13</v>
       </c>
       <c r="B44" s="41">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="C44" s="12" t="str">
-        <v>Fernando Alonso</v>
+        <v>George Russell</v>
       </c>
       <c r="D44" s="7" t="str">
-        <v>Aston Martin</v>
+        <v>Mercedes</v>
       </c>
       <c r="E44" s="30">
-        <v>7.5338888888888889</v>
+        <v>7.3822222222222225</v>
       </c>
       <c r="F44" s="21" t="str">
         <v>-</v>
@@ -13613,37 +13613,37 @@
         <v>-</v>
       </c>
       <c r="V44" s="28">
-        <v>7.5</v>
+        <v>8.75</v>
       </c>
       <c r="W44" s="23">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="X44" s="23">
-        <v>8.25</v>
+        <v>8.75</v>
       </c>
       <c r="Y44" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="Z44" s="24">
-        <v>7.666666666666667</v>
+        <v>8.1166666666666654</v>
       </c>
       <c r="AA44" s="28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB44" s="23">
-        <v>8.6999999999999993</v>
+        <v>5</v>
       </c>
       <c r="AC44" s="24">
-        <v>7.9350000000000005</v>
+        <v>5.45</v>
       </c>
       <c r="AD44" s="28">
-        <v>7</v>
-      </c>
-      <c r="AE44" s="23" t="str">
-        <v>-</v>
+        <v>9</v>
+      </c>
+      <c r="AE44" s="23">
+        <v>8.4</v>
       </c>
       <c r="AF44" s="24">
-        <v>7.0000000000000009</v>
+        <v>8.58</v>
       </c>
       <c r="AG44" s="28" t="str">
         <v>-</v>
@@ -13804,25 +13804,25 @@
         <v>14</v>
       </c>
       <c r="B45" s="41">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C45" s="12" t="str">
-        <v>Nico Hulkenberg</v>
+        <v>Fernando Alonso</v>
       </c>
       <c r="D45" s="7" t="str">
-        <v>Audi</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E45" s="30">
-        <v>7.3768518518518524</v>
+        <v>7.3505555555555562</v>
       </c>
       <c r="F45" s="21" t="str">
         <v>-</v>
       </c>
       <c r="G45" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="H45" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="I45" s="28" t="str">
         <v>-</v>
@@ -13867,34 +13867,34 @@
         <v>7.5</v>
       </c>
       <c r="W45" s="23">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="X45" s="23">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="Y45" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="Z45" s="24">
-        <v>6.8055555555555554</v>
+        <v>7.1166666666666671</v>
       </c>
       <c r="AA45" s="28">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AB45" s="23">
-        <v>5</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AC45" s="24">
-        <v>6.5750000000000002</v>
+        <v>7.9350000000000005</v>
       </c>
       <c r="AD45" s="28">
-        <v>8.75</v>
-      </c>
-      <c r="AE45" s="23" t="str">
-        <v>-</v>
+        <v>7</v>
+      </c>
+      <c r="AE45" s="23">
+        <v>7</v>
       </c>
       <c r="AF45" s="24">
-        <v>8.75</v>
+        <v>7</v>
       </c>
       <c r="AG45" s="28" t="str">
         <v>-</v>
@@ -14055,16 +14055,16 @@
         <v>15</v>
       </c>
       <c r="B46" s="42">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C46" s="12" t="str">
-        <v>Gabriel Bortoleto</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="D46" s="8" t="str">
-        <v>Audi</v>
+        <v>Ferrari</v>
       </c>
       <c r="E46" s="30">
-        <v>7.2805555555555559</v>
+        <v>7.2353703703703713</v>
       </c>
       <c r="F46" s="21" t="str">
         <v>-</v>
@@ -14115,37 +14115,37 @@
         <v>-</v>
       </c>
       <c r="V46" s="28">
+        <v>6.75</v>
+      </c>
+      <c r="W46" s="23">
+        <v>6.75</v>
+      </c>
+      <c r="X46" s="23">
         <v>7</v>
       </c>
-      <c r="W46" s="23">
-        <v>6.5</v>
-      </c>
-      <c r="X46" s="23">
-        <v>7.75</v>
-      </c>
       <c r="Y46" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z46" s="24">
-        <v>7.166666666666667</v>
+        <v>6.8611111111111116</v>
       </c>
       <c r="AA46" s="28">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="AB46" s="23">
         <v>7</v>
       </c>
       <c r="AC46" s="24">
-        <v>6.7750000000000004</v>
+        <v>7.36</v>
       </c>
       <c r="AD46" s="28">
-        <v>7.9</v>
-      </c>
-      <c r="AE46" s="23" t="str">
-        <v>-</v>
+        <v>5</v>
+      </c>
+      <c r="AE46" s="23">
+        <v>8.5500000000000007</v>
       </c>
       <c r="AF46" s="24">
-        <v>7.9</v>
+        <v>7.4850000000000003</v>
       </c>
       <c r="AG46" s="28" t="str">
         <v>-</v>
@@ -14306,25 +14306,25 @@
         <v>16</v>
       </c>
       <c r="B47" s="42">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C47" s="12" t="str">
-        <v>Pierre Gasly</v>
+        <v>Nico Hulkenberg</v>
       </c>
       <c r="D47" s="8" t="str">
-        <v>Alpine</v>
+        <v>Audi</v>
       </c>
       <c r="E47" s="30">
-        <v>7.2701851851851851</v>
+        <v>7.143518518518519</v>
       </c>
       <c r="F47" s="21" t="str">
         <v>-</v>
       </c>
       <c r="G47" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="H47" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="I47" s="28" t="str">
         <v>-</v>
@@ -14354,49 +14354,49 @@
         <v>-</v>
       </c>
       <c r="R47" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="S47" s="23" t="str">
         <v>-</v>
       </c>
       <c r="T47" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="U47" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="V47" s="28">
-        <v>1.8</v>
+        <v>7.5</v>
       </c>
       <c r="W47" s="23">
+        <v>4.75</v>
+      </c>
+      <c r="X47" s="23">
+        <v>8</v>
+      </c>
+      <c r="Y47" s="23" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z47" s="24">
+        <v>6.8055555555555554</v>
+      </c>
+      <c r="AA47" s="28">
+        <v>8.5</v>
+      </c>
+      <c r="AB47" s="23">
         <v>5</v>
       </c>
-      <c r="X47" s="23">
-        <v>6.5</v>
-      </c>
-      <c r="Y47" s="23" t="str">
-        <v>-</v>
-      </c>
-      <c r="Z47" s="24">
-        <v>4.9555555555555557</v>
-      </c>
-      <c r="AA47" s="28">
-        <v>8.9</v>
-      </c>
-      <c r="AB47" s="23">
-        <v>9</v>
-      </c>
       <c r="AC47" s="24">
-        <v>8.9550000000000001</v>
+        <v>6.5750000000000002</v>
       </c>
       <c r="AD47" s="28">
-        <v>7.9</v>
+        <v>8.75</v>
       </c>
       <c r="AE47" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="AF47" s="24">
-        <v>7.9</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="AG47" s="28" t="str">
         <v>-</v>
@@ -14557,16 +14557,16 @@
         <v>17</v>
       </c>
       <c r="B48" s="43">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="C48" s="12" t="str">
-        <v>Oliver Bearman</v>
+        <v>Gabriel Bortoleto</v>
       </c>
       <c r="D48" s="9" t="str">
-        <v>Haas</v>
+        <v>Audi</v>
       </c>
       <c r="E48" s="30">
-        <v>6.6370370370370368</v>
+        <v>6.7905555555555557</v>
       </c>
       <c r="F48" s="21" t="str">
         <v>-</v>
@@ -14587,10 +14587,10 @@
         <v>-</v>
       </c>
       <c r="L48" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="M48" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="N48" s="28" t="str">
         <v>-</v>
@@ -14617,37 +14617,37 @@
         <v>-</v>
       </c>
       <c r="V48" s="28">
+        <v>7</v>
+      </c>
+      <c r="W48" s="23">
         <v>6.5</v>
       </c>
-      <c r="W48" s="23">
-        <v>5</v>
-      </c>
       <c r="X48" s="23">
-        <v>6.75</v>
+        <v>7.75</v>
       </c>
       <c r="Y48" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z48" s="24">
-        <v>6.1111111111111107</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="AA48" s="28">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AB48" s="23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC48" s="24">
-        <v>6</v>
+        <v>6.7750000000000004</v>
       </c>
       <c r="AD48" s="28">
-        <v>7.8</v>
-      </c>
-      <c r="AE48" s="23" t="str">
-        <v>-</v>
+        <v>7.9</v>
+      </c>
+      <c r="AE48" s="23">
+        <v>5.8</v>
       </c>
       <c r="AF48" s="24">
-        <v>7.8</v>
+        <v>6.43</v>
       </c>
       <c r="AG48" s="28" t="str">
         <v>-</v>
@@ -14817,7 +14817,7 @@
         <v>Haas</v>
       </c>
       <c r="E49" s="30">
-        <v>6.4074074074074074</v>
+        <v>6.6507407407407406</v>
       </c>
       <c r="F49" s="21" t="str">
         <v>-</v>
@@ -14892,13 +14892,13 @@
         <v>7.5</v>
       </c>
       <c r="AD49" s="28">
-        <v>5.5</v>
-      </c>
-      <c r="AE49" s="23" t="str">
-        <v>-</v>
+        <v>5.6</v>
+      </c>
+      <c r="AE49" s="23">
+        <v>6.5</v>
       </c>
       <c r="AF49" s="24">
-        <v>5.5</v>
+        <v>6.2299999999999995</v>
       </c>
       <c r="AG49" s="28" t="str">
         <v>-</v>
@@ -15059,16 +15059,16 @@
         <v>19</v>
       </c>
       <c r="B50" s="44">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="C50" s="12" t="str">
-        <v>Charles Leclerc</v>
+        <v>Oliver Bearman</v>
       </c>
       <c r="D50" s="10" t="str">
-        <v>Ferrari</v>
+        <v>Haas</v>
       </c>
       <c r="E50" s="30">
-        <v>6.4070370370370382</v>
+        <v>6.383703703703703</v>
       </c>
       <c r="F50" s="21" t="str">
         <v>-</v>
@@ -15098,10 +15098,10 @@
         <v>-</v>
       </c>
       <c r="O50" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="P50" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="Q50" s="28" t="str">
         <v>-</v>
@@ -15119,37 +15119,37 @@
         <v>-</v>
       </c>
       <c r="V50" s="28">
+        <v>6.5</v>
+      </c>
+      <c r="W50" s="23">
+        <v>5</v>
+      </c>
+      <c r="X50" s="23">
         <v>6.75</v>
       </c>
-      <c r="W50" s="23">
-        <v>6.75</v>
-      </c>
-      <c r="X50" s="23">
-        <v>7</v>
-      </c>
       <c r="Y50" s="23" t="str">
         <v>-</v>
       </c>
       <c r="Z50" s="24">
-        <v>6.8611111111111116</v>
+        <v>6.1111111111111107</v>
       </c>
       <c r="AA50" s="28">
+        <v>6</v>
+      </c>
+      <c r="AB50" s="23" t="str">
+        <v>NR</v>
+      </c>
+      <c r="AC50" s="24">
+        <v>5.45</v>
+      </c>
+      <c r="AD50" s="28">
         <v>7.8</v>
       </c>
-      <c r="AB50" s="23">
-        <v>7</v>
-      </c>
-      <c r="AC50" s="24">
-        <v>7.36</v>
-      </c>
-      <c r="AD50" s="28">
-        <v>5</v>
-      </c>
-      <c r="AE50" s="23" t="str">
-        <v>-</v>
+      <c r="AE50" s="23">
+        <v>7.5</v>
       </c>
       <c r="AF50" s="24">
-        <v>5</v>
+        <v>7.59</v>
       </c>
       <c r="AG50" s="28" t="str">
         <v>-</v>
@@ -15319,7 +15319,7 @@
         <v>Williams</v>
       </c>
       <c r="E51" s="30">
-        <v>6.2061904761904758</v>
+        <v>6.2645238095238085</v>
       </c>
       <c r="F51" s="21" t="str">
         <v>-</v>
@@ -15340,10 +15340,10 @@
         <v>-</v>
       </c>
       <c r="L51" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="M51" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="N51" s="28" t="str">
         <v>-</v>
@@ -15396,11 +15396,11 @@
       <c r="AD51" s="28">
         <v>5.75</v>
       </c>
-      <c r="AE51" s="23" t="str">
-        <v>-</v>
+      <c r="AE51" s="23">
+        <v>6</v>
       </c>
       <c r="AF51" s="24">
-        <v>5.75</v>
+        <v>5.9249999999999989</v>
       </c>
       <c r="AG51" s="28" t="str">
         <v>-</v>
@@ -15570,16 +15570,16 @@
         <v>Cadillac</v>
       </c>
       <c r="E52" s="30">
-        <v>6.1722222222222216</v>
+        <v>5.9388888888888891</v>
       </c>
       <c r="F52" s="21" t="str">
         <v>-</v>
       </c>
       <c r="G52" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="H52" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="I52" s="28" t="str">
         <v>-</v>
@@ -15648,10 +15648,10 @@
         <v>7.5</v>
       </c>
       <c r="AE52" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="AF52" s="24">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AG52" s="28" t="str">
         <v>-</v>
@@ -15821,7 +15821,7 @@
         <v>Aston Martin</v>
       </c>
       <c r="E53" s="30">
-        <v>5.0175925925925924</v>
+        <v>4.784259259259259</v>
       </c>
       <c r="F53" s="21" t="str">
         <v>-</v>
@@ -15842,10 +15842,10 @@
         <v>-</v>
       </c>
       <c r="L53" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="M53" s="24" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="N53" s="28" t="str">
         <v>-</v>
@@ -15899,10 +15899,10 @@
         <v>7.5</v>
       </c>
       <c r="AE53" s="23" t="str">
-        <v>-</v>
+        <v>NR</v>
       </c>
       <c r="AF53" s="24">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="AG53" s="28" t="str">
         <v>-</v>
@@ -16084,28 +16084,67 @@
     </row>
   </sheetData>
   <mergeCells count="99">
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:M30"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="BW30:BY30"/>
-    <mergeCell ref="BZ30:CB30"/>
-    <mergeCell ref="Q30:U30"/>
-    <mergeCell ref="V30:Z30"/>
-    <mergeCell ref="AA30:AC30"/>
-    <mergeCell ref="AD30:AF30"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AJ30:AN30"/>
-    <mergeCell ref="AO30:AQ30"/>
-    <mergeCell ref="AR30:AT30"/>
-    <mergeCell ref="AU30:AY30"/>
-    <mergeCell ref="CC30:CE30"/>
-    <mergeCell ref="AZ30:BB30"/>
-    <mergeCell ref="BC30:BE30"/>
-    <mergeCell ref="BF30:BH30"/>
-    <mergeCell ref="BI30:BM30"/>
-    <mergeCell ref="BN30:BP30"/>
-    <mergeCell ref="BQ30:BS30"/>
-    <mergeCell ref="BT30:BV30"/>
+    <mergeCell ref="A1:E2"/>
+    <mergeCell ref="Q3:U3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="Q4:U4"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:M29"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="Q29:U29"/>
+    <mergeCell ref="V29:Z29"/>
+    <mergeCell ref="V4:Z4"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AJ3:AN3"/>
+    <mergeCell ref="AO3:AQ3"/>
+    <mergeCell ref="AR3:AT3"/>
+    <mergeCell ref="AA4:AC4"/>
+    <mergeCell ref="AD4:AF4"/>
+    <mergeCell ref="AG4:AI4"/>
+    <mergeCell ref="AJ4:AN4"/>
+    <mergeCell ref="AO4:AQ4"/>
+    <mergeCell ref="BW3:BY3"/>
+    <mergeCell ref="BZ3:CB3"/>
+    <mergeCell ref="CC3:CE3"/>
+    <mergeCell ref="I3:M3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="V3:Z3"/>
+    <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="BT3:BV3"/>
+    <mergeCell ref="AU3:AY3"/>
+    <mergeCell ref="AZ3:BB3"/>
+    <mergeCell ref="BC3:BE3"/>
+    <mergeCell ref="BF3:BH3"/>
+    <mergeCell ref="BI3:BM3"/>
+    <mergeCell ref="BN3:BP3"/>
+    <mergeCell ref="BQ3:BS3"/>
+    <mergeCell ref="CC4:CE4"/>
+    <mergeCell ref="AR4:AT4"/>
+    <mergeCell ref="AU4:AY4"/>
+    <mergeCell ref="AZ4:BB4"/>
+    <mergeCell ref="BC4:BE4"/>
+    <mergeCell ref="BF4:BH4"/>
+    <mergeCell ref="BI4:BM4"/>
+    <mergeCell ref="BN4:BP4"/>
+    <mergeCell ref="BQ4:BS4"/>
+    <mergeCell ref="BT4:BV4"/>
+    <mergeCell ref="BW4:BY4"/>
+    <mergeCell ref="BZ4:CB4"/>
+    <mergeCell ref="BQ29:BS29"/>
+    <mergeCell ref="BT29:BV29"/>
+    <mergeCell ref="AG29:AI29"/>
+    <mergeCell ref="AJ29:AN29"/>
+    <mergeCell ref="AO29:AQ29"/>
+    <mergeCell ref="AR29:AT29"/>
     <mergeCell ref="BW29:BY29"/>
     <mergeCell ref="BZ29:CB29"/>
     <mergeCell ref="CC29:CE29"/>
@@ -16122,67 +16161,28 @@
     <mergeCell ref="BN29:BP29"/>
     <mergeCell ref="AA29:AC29"/>
     <mergeCell ref="AD29:AF29"/>
-    <mergeCell ref="BQ29:BS29"/>
-    <mergeCell ref="BT29:BV29"/>
-    <mergeCell ref="AG29:AI29"/>
-    <mergeCell ref="AJ29:AN29"/>
-    <mergeCell ref="AO29:AQ29"/>
-    <mergeCell ref="AR29:AT29"/>
-    <mergeCell ref="CC4:CE4"/>
-    <mergeCell ref="AR4:AT4"/>
-    <mergeCell ref="AU4:AY4"/>
-    <mergeCell ref="AZ4:BB4"/>
-    <mergeCell ref="BC4:BE4"/>
-    <mergeCell ref="BF4:BH4"/>
-    <mergeCell ref="BI4:BM4"/>
-    <mergeCell ref="BN4:BP4"/>
-    <mergeCell ref="BQ4:BS4"/>
-    <mergeCell ref="BT4:BV4"/>
-    <mergeCell ref="BW4:BY4"/>
-    <mergeCell ref="BZ4:CB4"/>
-    <mergeCell ref="BW3:BY3"/>
-    <mergeCell ref="BZ3:CB3"/>
-    <mergeCell ref="CC3:CE3"/>
-    <mergeCell ref="I3:M3"/>
-    <mergeCell ref="N3:P3"/>
-    <mergeCell ref="V3:Z3"/>
-    <mergeCell ref="AA3:AC3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="BT3:BV3"/>
-    <mergeCell ref="AU3:AY3"/>
-    <mergeCell ref="AZ3:BB3"/>
-    <mergeCell ref="BC3:BE3"/>
-    <mergeCell ref="BF3:BH3"/>
-    <mergeCell ref="BI3:BM3"/>
-    <mergeCell ref="BN3:BP3"/>
-    <mergeCell ref="BQ3:BS3"/>
-    <mergeCell ref="V4:Z4"/>
-    <mergeCell ref="AG3:AI3"/>
-    <mergeCell ref="AJ3:AN3"/>
-    <mergeCell ref="AO3:AQ3"/>
-    <mergeCell ref="AR3:AT3"/>
-    <mergeCell ref="AA4:AC4"/>
-    <mergeCell ref="AD4:AF4"/>
-    <mergeCell ref="AG4:AI4"/>
-    <mergeCell ref="AJ4:AN4"/>
-    <mergeCell ref="AO4:AQ4"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:M29"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="Q29:U29"/>
-    <mergeCell ref="V29:Z29"/>
-    <mergeCell ref="A1:E2"/>
-    <mergeCell ref="Q3:U3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="Q4:U4"/>
+    <mergeCell ref="CC30:CE30"/>
+    <mergeCell ref="AZ30:BB30"/>
+    <mergeCell ref="BC30:BE30"/>
+    <mergeCell ref="BF30:BH30"/>
+    <mergeCell ref="BI30:BM30"/>
+    <mergeCell ref="BN30:BP30"/>
+    <mergeCell ref="BQ30:BS30"/>
+    <mergeCell ref="BT30:BV30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:M30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="BW30:BY30"/>
+    <mergeCell ref="BZ30:CB30"/>
+    <mergeCell ref="Q30:U30"/>
+    <mergeCell ref="V30:Z30"/>
+    <mergeCell ref="AA30:AC30"/>
+    <mergeCell ref="AD30:AF30"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AJ30:AN30"/>
+    <mergeCell ref="AO30:AQ30"/>
+    <mergeCell ref="AR30:AT30"/>
+    <mergeCell ref="AU30:AY30"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:B27 D6:D27 B32:B53 D32:D53">
     <cfRule type="expression" dxfId="104" priority="3">
@@ -16384,21 +16384,21 @@
       </c>
       <c r="B2" s="18" cm="1">
         <f t="array" ref="B2:E23">_xlfn._xlws.SORT(Ratings!B6:E27,4,-1)</f>
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C2" s="12" t="str">
-        <v>Max Verstappen</v>
+        <v>Lewis Hamilton</v>
       </c>
       <c r="D2" s="18" t="str">
-        <v>Red Bull</v>
+        <v>Ferrari</v>
       </c>
       <c r="E2" s="2">
-        <v>8.7962962962962958</v>
+        <v>8.76212962962963</v>
       </c>
       <c r="F2" s="31"/>
       <c r="G2" s="67">
         <f>K2-K3</f>
-        <v>-0.71203703703703702</v>
+        <v>-0.97537037037037155</v>
       </c>
       <c r="H2" s="18">
         <v>63</v>
@@ -16411,7 +16411,7 @@
       </c>
       <c r="K2" s="2">
         <f>Ratings!E6</f>
-        <v>7.7055555555555557</v>
+        <v>7.3822222222222225</v>
       </c>
       <c r="L2" s="31"/>
       <c r="M2" s="18">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="N2" s="29">
         <f>Simplified!G2</f>
-        <v>-0.71203703703703702</v>
+        <v>-0.97537037037037155</v>
       </c>
       <c r="O2" s="18">
         <v>12</v>
@@ -16430,15 +16430,15 @@
       </c>
       <c r="R2" s="32">
         <f>AVERAGE(K2:K3)</f>
-        <v>8.0615740740740733</v>
+        <v>7.8699074074074087</v>
       </c>
       <c r="S2" s="31"/>
       <c r="T2" s="33" t="str" cm="1">
         <f t="array" ref="T2:U12">_xlfn._xlws.SORT(Q2:R12,2,-1)</f>
-        <v>Red Bull</v>
+        <v>McLaren</v>
       </c>
       <c r="U2" s="33">
-        <v>8.4682870370370367</v>
+        <v>8.3281018518518515</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -16446,16 +16446,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="18">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C3" s="12" t="str">
-        <v>Lewis Hamilton</v>
+        <v>Lando Norris</v>
       </c>
       <c r="D3" s="18" t="str">
-        <v>Ferrari</v>
+        <v>McLaren</v>
       </c>
       <c r="E3" s="2">
-        <v>8.7454629629629625</v>
+        <v>8.7032407407407408</v>
       </c>
       <c r="F3" s="31"/>
       <c r="G3" s="67"/>
@@ -16470,7 +16470,7 @@
       </c>
       <c r="K3" s="2">
         <f>Ratings!E7</f>
-        <v>8.4175925925925927</v>
+        <v>8.357592592592594</v>
       </c>
       <c r="L3" s="31"/>
       <c r="M3" s="1">
@@ -16478,7 +16478,7 @@
       </c>
       <c r="N3" s="29">
         <f>Simplified!G4</f>
-        <v>0.56944444444444375</v>
+        <v>0.75027777777777693</v>
       </c>
       <c r="O3" s="1">
         <v>81</v>
@@ -16489,14 +16489,14 @@
       </c>
       <c r="R3" s="32">
         <f>AVERAGE(K4:K5)</f>
-        <v>8.2726851851851855</v>
+        <v>8.3281018518518515</v>
       </c>
       <c r="S3" s="31"/>
       <c r="T3" s="33" t="str">
-        <v>McLaren</v>
+        <v>Red Bull</v>
       </c>
       <c r="U3" s="33">
-        <v>8.2726851851851855</v>
+        <v>8.0697685185185186</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
@@ -16504,21 +16504,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" s="12" t="str">
-        <v>Lando Norris</v>
+        <v>Max Verstappen</v>
       </c>
       <c r="D4" s="1" t="str">
-        <v>McLaren</v>
+        <v>Red Bull</v>
       </c>
       <c r="E4" s="2">
-        <v>8.5574074074074069</v>
+        <v>8.5575925925925933</v>
       </c>
       <c r="F4" s="31"/>
       <c r="G4" s="67">
         <f>K4-K5</f>
-        <v>0.56944444444444375</v>
+        <v>0.75027777777777693</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="K4" s="2">
         <f>Ratings!E8</f>
-        <v>8.5574074074074069</v>
+        <v>8.7032407407407408</v>
       </c>
       <c r="L4" s="31"/>
       <c r="M4" s="3">
@@ -16539,7 +16539,7 @@
       </c>
       <c r="N4" s="29">
         <f>Simplified!G6</f>
-        <v>-2.3384259259259244</v>
+        <v>-1.5267592592592587</v>
       </c>
       <c r="O4" s="3">
         <v>44</v>
@@ -16550,14 +16550,14 @@
       </c>
       <c r="R4" s="32">
         <f>AVERAGE(K6:K7)</f>
-        <v>7.5762499999999999</v>
+        <v>7.9987500000000011</v>
       </c>
       <c r="S4" s="31"/>
       <c r="T4" s="33" t="str">
-        <v>Racing Bulls</v>
+        <v>Ferrari</v>
       </c>
       <c r="U4" s="33">
-        <v>8.138088624338625</v>
+        <v>7.9987500000000011</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.3">
@@ -16565,16 +16565,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C5" s="12" t="str">
-        <v>Liam Lawson</v>
+        <v>Kimi Antonelli</v>
       </c>
       <c r="D5" s="1" t="str">
-        <v>Racing Bulls</v>
+        <v>Mercedes</v>
       </c>
       <c r="E5" s="2">
-        <v>8.4440476190476197</v>
+        <v>8.357592592592594</v>
       </c>
       <c r="F5" s="31"/>
       <c r="G5" s="67"/>
@@ -16589,7 +16589,7 @@
       </c>
       <c r="K5" s="2">
         <f>Ratings!E9</f>
-        <v>7.9879629629629632</v>
+        <v>7.9529629629629639</v>
       </c>
       <c r="L5" s="31"/>
       <c r="M5" s="4">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="N5" s="29">
         <f>Simplified!G8</f>
-        <v>0.65601851851851833</v>
+        <v>0.97564814814814849</v>
       </c>
       <c r="O5" s="4">
         <v>6</v>
@@ -16608,14 +16608,14 @@
       </c>
       <c r="R5" s="32">
         <f>AVERAGE(K8:K9)</f>
-        <v>8.4682870370370367</v>
+        <v>8.0697685185185186</v>
       </c>
       <c r="S5" s="31"/>
       <c r="T5" s="33" t="str">
-        <v>Mercedes</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="U5" s="33">
-        <v>8.0615740740740733</v>
+        <v>7.9539219576719589</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.3">
@@ -16623,21 +16623,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C6" s="12" t="str">
-        <v>Kimi Antonelli</v>
+        <v>Liam Lawson</v>
       </c>
       <c r="D6" s="3" t="str">
-        <v>Mercedes</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E6" s="2">
-        <v>8.4175925925925927</v>
+        <v>8.2340476190476206</v>
       </c>
       <c r="F6" s="31"/>
       <c r="G6" s="67">
         <f>K6-K7</f>
-        <v>-2.3384259259259244</v>
+        <v>-1.5267592592592587</v>
       </c>
       <c r="H6" s="3">
         <v>16</v>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="K6" s="2">
         <f>Ratings!E10</f>
-        <v>6.4070370370370382</v>
+        <v>7.2353703703703713</v>
       </c>
       <c r="L6" s="31"/>
       <c r="M6" s="5">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="N6" s="29">
         <f>Simplified!G10</f>
-        <v>-0.45259259259259288</v>
+        <v>-0.25259259259259359</v>
       </c>
       <c r="O6" s="5">
         <v>43</v>
@@ -16669,14 +16669,14 @@
       </c>
       <c r="R6" s="32">
         <f>AVERAGE(K10:K11)</f>
-        <v>7.4964814814814815</v>
+        <v>7.5498148148148143</v>
       </c>
       <c r="S6" s="31"/>
       <c r="T6" s="33" t="str">
-        <v>Ferrari</v>
+        <v>Mercedes</v>
       </c>
       <c r="U6" s="33">
-        <v>7.5762499999999999</v>
+        <v>7.8699074074074087</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.3">
@@ -16684,16 +16684,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="C7" s="12" t="str">
-        <v>Isack Hadjar</v>
+        <v>Carlos Sainz</v>
       </c>
       <c r="D7" s="3" t="str">
-        <v>Red Bull</v>
+        <v>Williams</v>
       </c>
       <c r="E7" s="2">
-        <v>8.1402777777777775</v>
+        <v>7.9567592592592584</v>
       </c>
       <c r="F7" s="31"/>
       <c r="G7" s="67"/>
@@ -16708,7 +16708,7 @@
       </c>
       <c r="K7" s="2">
         <f>Ratings!E11</f>
-        <v>8.7454629629629625</v>
+        <v>8.76212962962963</v>
       </c>
       <c r="L7" s="31"/>
       <c r="M7" s="6">
@@ -16716,7 +16716,7 @@
       </c>
       <c r="N7" s="29">
         <f>Simplified!G12</f>
-        <v>0.61191798941799025</v>
+        <v>0.56025132275132439</v>
       </c>
       <c r="O7" s="6">
         <v>41</v>
@@ -16727,14 +16727,14 @@
       </c>
       <c r="R7" s="32">
         <f>AVERAGE(K12:K13)</f>
-        <v>8.138088624338625</v>
+        <v>7.9539219576719589</v>
       </c>
       <c r="S7" s="31"/>
       <c r="T7" s="33" t="str">
         <v>Alpine</v>
       </c>
       <c r="U7" s="33">
-        <v>7.4964814814814815</v>
+        <v>7.5498148148148143</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.3">
@@ -16742,21 +16742,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="4">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C8" s="12" t="str">
-        <v>Carlos Sainz</v>
+        <v>Oscar Piastri</v>
       </c>
       <c r="D8" s="4" t="str">
-        <v>Williams</v>
+        <v>McLaren</v>
       </c>
       <c r="E8" s="2">
-        <v>8.0967592592592599</v>
+        <v>7.9529629629629639</v>
       </c>
       <c r="F8" s="31"/>
       <c r="G8" s="67">
         <f>K8-K9</f>
-        <v>0.65601851851851833</v>
+        <v>0.97564814814814849</v>
       </c>
       <c r="H8" s="4">
         <v>3</v>
@@ -16769,7 +16769,7 @@
       </c>
       <c r="K8" s="2">
         <f>Ratings!E12</f>
-        <v>8.7962962962962958</v>
+        <v>8.5575925925925933</v>
       </c>
       <c r="L8" s="31"/>
       <c r="M8" s="7">
@@ -16777,7 +16777,7 @@
       </c>
       <c r="N8" s="29">
         <f>Simplified!G14</f>
-        <v>-0.22962962962962941</v>
+        <v>0.26703703703703763</v>
       </c>
       <c r="O8" s="7">
         <v>87</v>
@@ -16788,14 +16788,14 @@
       </c>
       <c r="R8" s="32">
         <f>AVERAGE(K14:K15)</f>
-        <v>6.5222222222222221</v>
+        <v>6.5172222222222214</v>
       </c>
       <c r="S8" s="31"/>
       <c r="T8" s="33" t="str">
-        <v>Audi</v>
+        <v>Williams</v>
       </c>
       <c r="U8" s="33">
-        <v>7.3287037037037042</v>
+        <v>7.110641534391533</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
@@ -16803,16 +16803,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="4">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="C9" s="12" t="str">
-        <v>Oscar Piastri</v>
+        <v>Franco Colapinto</v>
       </c>
       <c r="D9" s="4" t="str">
-        <v>McLaren</v>
+        <v>Alpine</v>
       </c>
       <c r="E9" s="2">
-        <v>7.9879629629629632</v>
+        <v>7.6761111111111111</v>
       </c>
       <c r="F9" s="31"/>
       <c r="G9" s="67"/>
@@ -16827,7 +16827,7 @@
       </c>
       <c r="K9" s="2">
         <f>Ratings!E13</f>
-        <v>8.1402777777777775</v>
+        <v>7.5819444444444448</v>
       </c>
       <c r="L9" s="31"/>
       <c r="M9" s="8">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="N9" s="29">
         <f>Simplified!G16</f>
-        <v>1.8905687830687841</v>
+        <v>1.6922354497354499</v>
       </c>
       <c r="O9" s="8">
         <v>23</v>
@@ -16846,14 +16846,14 @@
       </c>
       <c r="R9" s="32">
         <f>AVERAGE(K16:K17)</f>
-        <v>7.1514748677248683</v>
+        <v>7.110641534391533</v>
       </c>
       <c r="S9" s="31"/>
       <c r="T9" s="33" t="str">
-        <v>Williams</v>
+        <v>Audi</v>
       </c>
       <c r="U9" s="33">
-        <v>7.1514748677248683</v>
+        <v>6.9670370370370378</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.3">
@@ -16861,21 +16861,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="5">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C10" s="12" t="str">
-        <v>Sergio Perez</v>
+        <v>Arvid Lindblad</v>
       </c>
       <c r="D10" s="5" t="str">
-        <v>Cadillac</v>
+        <v>Racing Bulls</v>
       </c>
       <c r="E10" s="2">
-        <v>7.8881481481481481</v>
+        <v>7.6737962962962962</v>
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="67">
         <f>K10-K11</f>
-        <v>-0.45259259259259288</v>
+        <v>-0.25259259259259359</v>
       </c>
       <c r="H10" s="5">
         <v>10</v>
@@ -16888,7 +16888,7 @@
       </c>
       <c r="K10" s="2">
         <f>Ratings!E14</f>
-        <v>7.2701851851851851</v>
+        <v>7.4235185185185175</v>
       </c>
       <c r="L10" s="31"/>
       <c r="M10" s="9">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="N10" s="29">
         <f>Simplified!G18</f>
-        <v>9.6296296296296546E-2</v>
+        <v>0.35296296296296337</v>
       </c>
       <c r="O10" s="9">
         <v>5</v>
@@ -16907,14 +16907,14 @@
       </c>
       <c r="R10" s="32">
         <f>AVERAGE(K18:K19)</f>
-        <v>7.3287037037037042</v>
+        <v>6.9670370370370378</v>
       </c>
       <c r="S10" s="31"/>
       <c r="T10" s="33" t="str">
         <v>Cadillac</v>
       </c>
       <c r="U10" s="33">
-        <v>7.0301851851851849</v>
+        <v>6.771851851851852</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
@@ -16922,16 +16922,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="5">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="C11" s="12" t="str">
-        <v>Arvid Lindblad</v>
+        <v>Sergio Perez</v>
       </c>
       <c r="D11" s="5" t="str">
-        <v>Racing Bulls</v>
+        <v>Cadillac</v>
       </c>
       <c r="E11" s="2">
-        <v>7.8321296296296294</v>
+        <v>7.6048148148148149</v>
       </c>
       <c r="F11" s="31"/>
       <c r="G11" s="67"/>
@@ -16946,7 +16946,7 @@
       </c>
       <c r="K11" s="2">
         <f>Ratings!E15</f>
-        <v>7.722777777777778</v>
+        <v>7.6761111111111111</v>
       </c>
       <c r="L11" s="31"/>
       <c r="M11" s="10">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="N11" s="29">
         <f>Simplified!G20</f>
-        <v>1.7159259259259265</v>
+        <v>1.6659259259259258</v>
       </c>
       <c r="O11" s="10">
         <v>77</v>
@@ -16965,14 +16965,14 @@
       </c>
       <c r="R11" s="32">
         <f>AVERAGE(K20:K21)</f>
-        <v>7.0301851851851849</v>
+        <v>6.771851851851852</v>
       </c>
       <c r="S11" s="31"/>
       <c r="T11" s="33" t="str">
         <v>Haas</v>
       </c>
       <c r="U11" s="33">
-        <v>6.5222222222222221</v>
+        <v>6.5172222222222214</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
@@ -16980,21 +16980,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="6">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="C12" s="12" t="str">
-        <v>Franco Colapinto</v>
+        <v>Isack Hadjar</v>
       </c>
       <c r="D12" s="6" t="str">
-        <v>Alpine</v>
+        <v>Red Bull</v>
       </c>
       <c r="E12" s="2">
-        <v>7.722777777777778</v>
+        <v>7.5819444444444448</v>
       </c>
       <c r="F12" s="31"/>
       <c r="G12" s="67">
         <f>K12-K13</f>
-        <v>0.61191798941799025</v>
+        <v>0.56025132275132439</v>
       </c>
       <c r="H12" s="6">
         <v>30</v>
@@ -17007,7 +17007,7 @@
       </c>
       <c r="K12" s="2">
         <f>Ratings!E16</f>
-        <v>8.4440476190476197</v>
+        <v>8.2340476190476206</v>
       </c>
       <c r="L12" s="31"/>
       <c r="M12" s="11">
@@ -17015,7 +17015,7 @@
       </c>
       <c r="N12" s="29">
         <f>Simplified!G22</f>
-        <v>2.5162962962962965</v>
+        <v>2.5662962962962972</v>
       </c>
       <c r="O12" s="11">
         <v>18</v>
@@ -17026,14 +17026,14 @@
       </c>
       <c r="R12" s="32">
         <f>AVERAGE(K22:K23)</f>
-        <v>6.2757407407407406</v>
+        <v>6.0674074074074076</v>
       </c>
       <c r="S12" s="31"/>
       <c r="T12" s="33" t="str">
         <v>Aston Martin</v>
       </c>
       <c r="U12" s="33">
-        <v>6.2757407407407406</v>
+        <v>6.0674074074074076</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
@@ -17041,16 +17041,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="6">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="C13" s="12" t="str">
-        <v>George Russell</v>
+        <v>Pierre Gasly</v>
       </c>
       <c r="D13" s="6" t="str">
-        <v>Mercedes</v>
+        <v>Alpine</v>
       </c>
       <c r="E13" s="2">
-        <v>7.7055555555555557</v>
+        <v>7.4235185185185175</v>
       </c>
       <c r="F13" s="31"/>
       <c r="G13" s="67"/>
@@ -17065,7 +17065,7 @@
       </c>
       <c r="K13" s="2">
         <f>Ratings!E17</f>
-        <v>7.8321296296296294</v>
+        <v>7.6737962962962962</v>
       </c>
       <c r="L13" s="31"/>
       <c r="M13" s="31"/>
@@ -17083,21 +17083,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="7">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="C14" s="12" t="str">
-        <v>Fernando Alonso</v>
+        <v>George Russell</v>
       </c>
       <c r="D14" s="7" t="str">
-        <v>Aston Martin</v>
+        <v>Mercedes</v>
       </c>
       <c r="E14" s="2">
-        <v>7.5338888888888889</v>
+        <v>7.3822222222222225</v>
       </c>
       <c r="F14" s="31"/>
       <c r="G14" s="67">
         <f>K14-K15</f>
-        <v>-0.22962962962962941</v>
+        <v>0.26703703703703763</v>
       </c>
       <c r="H14" s="7">
         <v>31</v>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="K14" s="2">
         <f>Ratings!E18</f>
-        <v>6.4074074074074074</v>
+        <v>6.6507407407407406</v>
       </c>
       <c r="L14" s="31"/>
       <c r="M14" s="31"/>
@@ -17128,16 +17128,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="7">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C15" s="12" t="str">
-        <v>Nico Hulkenberg</v>
+        <v>Fernando Alonso</v>
       </c>
       <c r="D15" s="7" t="str">
-        <v>Audi</v>
+        <v>Aston Martin</v>
       </c>
       <c r="E15" s="2">
-        <v>7.3768518518518524</v>
+        <v>7.3505555555555562</v>
       </c>
       <c r="F15" s="31"/>
       <c r="G15" s="67"/>
@@ -17152,7 +17152,7 @@
       </c>
       <c r="K15" s="2">
         <f>Ratings!E19</f>
-        <v>6.6370370370370368</v>
+        <v>6.383703703703703</v>
       </c>
       <c r="L15" s="31"/>
       <c r="M15" s="31"/>
@@ -17170,21 +17170,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="8">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C16" s="12" t="str">
-        <v>Gabriel Bortoleto</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="D16" s="8" t="str">
-        <v>Audi</v>
+        <v>Ferrari</v>
       </c>
       <c r="E16" s="2">
-        <v>7.2805555555555559</v>
+        <v>7.2353703703703713</v>
       </c>
       <c r="F16" s="31"/>
       <c r="G16" s="67">
         <f>K16-K17</f>
-        <v>1.8905687830687841</v>
+        <v>1.6922354497354499</v>
       </c>
       <c r="H16" s="8">
         <v>55</v>
@@ -17197,7 +17197,7 @@
       </c>
       <c r="K16" s="2">
         <f>Ratings!E20</f>
-        <v>8.0967592592592599</v>
+        <v>7.9567592592592584</v>
       </c>
       <c r="L16" s="31"/>
       <c r="M16" s="31"/>
@@ -17215,16 +17215,16 @@
         <v>16</v>
       </c>
       <c r="B17" s="8">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C17" s="12" t="str">
-        <v>Pierre Gasly</v>
+        <v>Nico Hulkenberg</v>
       </c>
       <c r="D17" s="8" t="str">
-        <v>Alpine</v>
+        <v>Audi</v>
       </c>
       <c r="E17" s="2">
-        <v>7.2701851851851851</v>
+        <v>7.143518518518519</v>
       </c>
       <c r="F17" s="31"/>
       <c r="G17" s="67"/>
@@ -17239,7 +17239,7 @@
       </c>
       <c r="K17" s="2">
         <f>Ratings!E21</f>
-        <v>6.2061904761904758</v>
+        <v>6.2645238095238085</v>
       </c>
       <c r="L17" s="31"/>
       <c r="M17" s="31"/>
@@ -17257,21 +17257,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="9">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="C18" s="12" t="str">
-        <v>Oliver Bearman</v>
+        <v>Gabriel Bortoleto</v>
       </c>
       <c r="D18" s="9" t="str">
-        <v>Haas</v>
+        <v>Audi</v>
       </c>
       <c r="E18" s="2">
-        <v>6.6370370370370368</v>
+        <v>6.7905555555555557</v>
       </c>
       <c r="F18" s="31"/>
       <c r="G18" s="67">
         <f>K18-K19</f>
-        <v>9.6296296296296546E-2</v>
+        <v>0.35296296296296337</v>
       </c>
       <c r="H18" s="9">
         <v>27</v>
@@ -17284,7 +17284,7 @@
       </c>
       <c r="K18" s="2">
         <f>Ratings!E22</f>
-        <v>7.3768518518518524</v>
+        <v>7.143518518518519</v>
       </c>
       <c r="L18" s="31"/>
       <c r="M18" s="31"/>
@@ -17311,7 +17311,7 @@
         <v>Haas</v>
       </c>
       <c r="E19" s="2">
-        <v>6.4074074074074074</v>
+        <v>6.6507407407407406</v>
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="67"/>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="K19" s="2">
         <f>Ratings!E23</f>
-        <v>7.2805555555555559</v>
+        <v>6.7905555555555557</v>
       </c>
       <c r="L19" s="31"/>
       <c r="M19" s="31"/>
@@ -17344,21 +17344,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="10">
-        <v>16</v>
+        <v>87</v>
       </c>
       <c r="C20" s="12" t="str">
-        <v>Charles Leclerc</v>
+        <v>Oliver Bearman</v>
       </c>
       <c r="D20" s="10" t="str">
-        <v>Ferrari</v>
+        <v>Haas</v>
       </c>
       <c r="E20" s="2">
-        <v>6.4070370370370382</v>
+        <v>6.383703703703703</v>
       </c>
       <c r="F20" s="31"/>
       <c r="G20" s="67">
         <f>K20-K21</f>
-        <v>1.7159259259259265</v>
+        <v>1.6659259259259258</v>
       </c>
       <c r="H20" s="10">
         <v>11</v>
@@ -17371,7 +17371,7 @@
       </c>
       <c r="K20" s="2">
         <f>Ratings!E24</f>
-        <v>7.8881481481481481</v>
+        <v>7.6048148148148149</v>
       </c>
       <c r="L20" s="31"/>
       <c r="M20" s="31"/>
@@ -17398,7 +17398,7 @@
         <v>Williams</v>
       </c>
       <c r="E21" s="2">
-        <v>6.2061904761904758</v>
+        <v>6.2645238095238085</v>
       </c>
       <c r="F21" s="31"/>
       <c r="G21" s="67"/>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="K21" s="2">
         <f>Ratings!E25</f>
-        <v>6.1722222222222216</v>
+        <v>5.9388888888888891</v>
       </c>
       <c r="L21" s="31"/>
       <c r="M21" s="31"/>
@@ -17440,12 +17440,12 @@
         <v>Cadillac</v>
       </c>
       <c r="E22" s="2">
-        <v>6.1722222222222216</v>
+        <v>5.9388888888888891</v>
       </c>
       <c r="F22" s="31"/>
       <c r="G22" s="67">
         <f>K22-K23</f>
-        <v>2.5162962962962965</v>
+        <v>2.5662962962962972</v>
       </c>
       <c r="H22" s="11">
         <v>14</v>
@@ -17458,7 +17458,7 @@
       </c>
       <c r="K22" s="2">
         <f>Ratings!E26</f>
-        <v>7.5338888888888889</v>
+        <v>7.3505555555555562</v>
       </c>
       <c r="L22" s="31"/>
       <c r="M22" s="31"/>
@@ -17485,7 +17485,7 @@
         <v>Aston Martin</v>
       </c>
       <c r="E23" s="2">
-        <v>5.0175925925925924</v>
+        <v>4.784259259259259</v>
       </c>
       <c r="F23" s="31"/>
       <c r="G23" s="67"/>
@@ -17500,7 +17500,7 @@
       </c>
       <c r="K23" s="2">
         <f>Ratings!E27</f>
-        <v>5.0175925925925924</v>
+        <v>4.784259259259259</v>
       </c>
       <c r="L23" s="31"/>
       <c r="M23" s="31"/>
